--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ffffff"/>
+        <fgColor rgb="00ffe4b5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002f4f4f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffffff"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,12 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3958,11 +3964,11 @@
           <t>quality</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>SDGIO:00010029</t>
+          <t>Sustainable Development Goals Interface Ontology (SDGIO:00010029)</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -3977,7 +3983,7 @@
         </is>
       </c>
       <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="n"/>
+      <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="n"/>
       <c r="M63" s="3" t="n"/>
       <c r="N63" s="3" t="inlineStr">
@@ -3992,7 +3998,7 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q63" s="3" t="n"/>
@@ -6405,7 +6411,7 @@
         </is>
       </c>
       <c r="Q107" s="2" t="n"/>
-      <c r="R107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
       <c r="T107" s="2" t="n"/>
       <c r="U107" s="2" t="n"/>
@@ -8377,7 +8383,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
-      <c r="F143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="inlineStr">
@@ -8466,51 +8472,51 @@
       <c r="U144" s="2" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>BCIO:050976</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>number of people in a population</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="3" t="n"/>
-      <c r="L145" s="3" t="n"/>
-      <c r="M145" s="3" t="n"/>
-      <c r="N145" s="3" t="n"/>
-      <c r="O145" s="3" t="n"/>
-      <c r="P145" s="3" t="inlineStr">
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="5" t="n"/>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="n"/>
+      <c r="K145" s="5" t="n"/>
+      <c r="L145" s="5" t="n"/>
+      <c r="M145" s="5" t="n"/>
+      <c r="N145" s="5" t="n"/>
+      <c r="O145" s="5" t="n"/>
+      <c r="P145" s="5" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q145" s="3" t="n"/>
-      <c r="R145" s="3" t="n"/>
-      <c r="S145" s="3" t="n"/>
-      <c r="T145" s="3" t="n"/>
-      <c r="U145" s="3" t="n"/>
+      <c r="Q145" s="5" t="n"/>
+      <c r="R145" s="5" t="n"/>
+      <c r="S145" s="5" t="n"/>
+      <c r="T145" s="5" t="n"/>
+      <c r="U145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8922,7 +8928,7 @@
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>SDGIO:00010028</t>
+          <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
@@ -8951,7 +8957,7 @@
       </c>
       <c r="P153" s="3" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="Q153" s="3" t="n"/>
@@ -9279,52 +9285,52 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">BCIO:050975
 </t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>people with intervention source role</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
         <is>
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E160" s="3" t="n"/>
-      <c r="F160" s="3" t="n"/>
-      <c r="G160" s="3" t="n"/>
-      <c r="H160" s="3" t="n"/>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J160" s="3" t="n"/>
-      <c r="K160" s="3" t="n"/>
-      <c r="L160" s="3" t="n"/>
-      <c r="M160" s="3" t="n"/>
-      <c r="N160" s="3" t="n"/>
-      <c r="O160" s="3" t="n"/>
-      <c r="P160" s="3" t="inlineStr">
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="5" t="n"/>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="n"/>
+      <c r="K160" s="5" t="n"/>
+      <c r="L160" s="5" t="n"/>
+      <c r="M160" s="5" t="n"/>
+      <c r="N160" s="5" t="n"/>
+      <c r="O160" s="5" t="n"/>
+      <c r="P160" s="5" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q160" s="3" t="n"/>
-      <c r="R160" s="3" t="n"/>
-      <c r="S160" s="3" t="n"/>
-      <c r="T160" s="3" t="n"/>
-      <c r="U160" s="3" t="n"/>
+      <c r="Q160" s="5" t="n"/>
+      <c r="R160" s="5" t="n"/>
+      <c r="S160" s="5" t="n"/>
+      <c r="T160" s="5" t="n"/>
+      <c r="U160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10265,52 +10271,52 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>BCIO:050978</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>population statistic</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="inlineStr">
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="inlineStr">
         <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
-      <c r="G179" s="3" t="n"/>
-      <c r="H179" s="3" t="n"/>
-      <c r="I179" s="3" t="n"/>
-      <c r="J179" s="3" t="n"/>
-      <c r="K179" s="3" t="n"/>
-      <c r="L179" s="3" t="n"/>
-      <c r="M179" s="3" t="n"/>
-      <c r="N179" s="3" t="n"/>
-      <c r="O179" s="3" t="n"/>
-      <c r="P179" s="3" t="inlineStr">
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="5" t="n"/>
+      <c r="I179" s="5" t="n"/>
+      <c r="J179" s="5" t="n"/>
+      <c r="K179" s="5" t="n"/>
+      <c r="L179" s="5" t="n"/>
+      <c r="M179" s="5" t="n"/>
+      <c r="N179" s="5" t="n"/>
+      <c r="O179" s="5" t="n"/>
+      <c r="P179" s="5" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q179" s="3" t="n"/>
-      <c r="R179" s="3" t="n"/>
-      <c r="S179" s="3" t="n"/>
-      <c r="T179" s="3" t="n"/>
-      <c r="U179" s="3" t="n"/>
+      <c r="Q179" s="5" t="n"/>
+      <c r="R179" s="5" t="n"/>
+      <c r="S179" s="5" t="n"/>
+      <c r="T179" s="5" t="n"/>
+      <c r="U179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007fffd4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffe4b5"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,13 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3944,68 +3938,68 @@
       <c r="U62" s="2" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>BCIO:050999</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>A quality inhering in a person by virtue of that person bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Sustainable Development Goals Interface Ontology (SDGIO:00010029)</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>An employment process is a  planned process wherein an employee performs actions that are formally or informally specified by an employer in return for remuneration.
 This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="Q63" s="3" t="n"/>
-      <c r="R63" s="3" t="n"/>
-      <c r="S63" s="3" t="n"/>
-      <c r="T63" s="3" t="n"/>
-      <c r="U63" s="3" t="n"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="n"/>
+      <c r="S63" s="2" t="n"/>
+      <c r="T63" s="2" t="n"/>
+      <c r="U63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6916,67 +6910,67 @@
       <c r="U116" s="2" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>BCIO:015158</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>insured party role</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="4" t="inlineStr">
+      <c r="E117" s="3" t="n"/>
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>OMRSE:00000092</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="n"/>
-      <c r="K117" s="4" t="n"/>
-      <c r="L117" s="4" t="n"/>
-      <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
+      <c r="L117" s="3" t="n"/>
+      <c r="M117" s="3" t="n"/>
+      <c r="N117" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O117" s="4" t="inlineStr">
+      <c r="O117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P117" s="4" t="inlineStr">
+      <c r="P117" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="Q117" s="4" t="n"/>
-      <c r="R117" s="4" t="n"/>
-      <c r="S117" s="4" t="n"/>
-      <c r="T117" s="4" t="n"/>
-      <c r="U117" s="4" t="n"/>
+      <c r="Q117" s="3" t="n"/>
+      <c r="R117" s="3" t="n"/>
+      <c r="S117" s="3" t="n"/>
+      <c r="T117" s="3" t="n"/>
+      <c r="U117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8472,51 +8466,51 @@
       <c r="U144" s="2" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>BCIO:050976</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>number of people in a population</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n"/>
-      <c r="F145" s="5" t="n"/>
-      <c r="G145" s="5" t="n"/>
-      <c r="H145" s="5" t="n"/>
-      <c r="I145" s="5" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J145" s="5" t="n"/>
-      <c r="K145" s="5" t="n"/>
-      <c r="L145" s="5" t="n"/>
-      <c r="M145" s="5" t="n"/>
-      <c r="N145" s="5" t="n"/>
-      <c r="O145" s="5" t="n"/>
-      <c r="P145" s="5" t="inlineStr">
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="n"/>
+      <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q145" s="5" t="n"/>
-      <c r="R145" s="5" t="n"/>
-      <c r="S145" s="5" t="n"/>
-      <c r="T145" s="5" t="n"/>
-      <c r="U145" s="5" t="n"/>
+      <c r="Q145" s="4" t="n"/>
+      <c r="R145" s="4" t="n"/>
+      <c r="S145" s="4" t="n"/>
+      <c r="T145" s="4" t="n"/>
+      <c r="U145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8904,67 +8898,67 @@
       <c r="U152" s="2" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>BCIO:051000</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
         </is>
       </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J153" s="3" t="n"/>
-      <c r="K153" s="3" t="n"/>
-      <c r="L153" s="3" t="n"/>
-      <c r="M153" s="3" t="n"/>
-      <c r="N153" s="3" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n"/>
+      <c r="K153" s="2" t="n"/>
+      <c r="L153" s="2" t="n"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
         <is>
           <t>people</t>
         </is>
       </c>
-      <c r="O153" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P153" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="Q153" s="3" t="n"/>
-      <c r="R153" s="3" t="n"/>
-      <c r="S153" s="3" t="n"/>
-      <c r="T153" s="3" t="n"/>
-      <c r="U153" s="3" t="n"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr"/>
+      <c r="R153" s="2" t="n"/>
+      <c r="S153" s="2" t="n"/>
+      <c r="T153" s="2" t="n"/>
+      <c r="U153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9285,52 +9279,52 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">BCIO:050975
 </t>
         </is>
       </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>people with intervention source role</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="4" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E160" s="5" t="n"/>
-      <c r="F160" s="5" t="n"/>
-      <c r="G160" s="5" t="n"/>
-      <c r="H160" s="5" t="n"/>
-      <c r="I160" s="5" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J160" s="5" t="n"/>
-      <c r="K160" s="5" t="n"/>
-      <c r="L160" s="5" t="n"/>
-      <c r="M160" s="5" t="n"/>
-      <c r="N160" s="5" t="n"/>
-      <c r="O160" s="5" t="n"/>
-      <c r="P160" s="5" t="inlineStr">
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="n"/>
+      <c r="G160" s="4" t="n"/>
+      <c r="H160" s="4" t="n"/>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="n"/>
+      <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q160" s="5" t="n"/>
-      <c r="R160" s="5" t="n"/>
-      <c r="S160" s="5" t="n"/>
-      <c r="T160" s="5" t="n"/>
-      <c r="U160" s="5" t="n"/>
+      <c r="Q160" s="4" t="n"/>
+      <c r="R160" s="4" t="n"/>
+      <c r="S160" s="4" t="n"/>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10271,52 +10265,52 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>BCIO:050978</t>
         </is>
       </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t>population statistic</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
+      <c r="C179" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
         </is>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D179" s="4" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n"/>
-      <c r="F179" s="5" t="inlineStr">
+      <c r="E179" s="4" t="n"/>
+      <c r="F179" s="4" t="inlineStr">
         <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
-      <c r="G179" s="5" t="n"/>
-      <c r="H179" s="5" t="n"/>
-      <c r="I179" s="5" t="n"/>
-      <c r="J179" s="5" t="n"/>
-      <c r="K179" s="5" t="n"/>
-      <c r="L179" s="5" t="n"/>
-      <c r="M179" s="5" t="n"/>
-      <c r="N179" s="5" t="n"/>
-      <c r="O179" s="5" t="n"/>
-      <c r="P179" s="5" t="inlineStr">
+      <c r="G179" s="4" t="n"/>
+      <c r="H179" s="4" t="n"/>
+      <c r="I179" s="4" t="n"/>
+      <c r="J179" s="4" t="n"/>
+      <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
+      <c r="P179" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q179" s="5" t="n"/>
-      <c r="R179" s="5" t="n"/>
-      <c r="S179" s="5" t="n"/>
-      <c r="T179" s="5" t="n"/>
-      <c r="U179" s="5" t="n"/>
+      <c r="Q179" s="4" t="n"/>
+      <c r="R179" s="4" t="n"/>
+      <c r="S179" s="4" t="n"/>
+      <c r="T179" s="4" t="n"/>
+      <c r="U179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -462,77 +462,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Logical definition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-reference</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Synonyms</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Examples</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-reference</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informal definition</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sub-ontology</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'is attribute of'</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'aggregate of'</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>REL 'is about'</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'is attribute of'</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Curator note</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'aggregate of'</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Aggregate</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curation status</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>To be reviewed by</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Informal definition</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Logical definition</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -575,13 +575,13 @@
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="inlineStr">
@@ -594,13 +594,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
@@ -633,14 +633,14 @@
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="inlineStr">
@@ -653,13 +653,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
@@ -693,13 +693,13 @@
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="inlineStr">
@@ -712,13 +712,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="n"/>
@@ -752,13 +752,13 @@
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="inlineStr">
@@ -771,13 +771,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="n"/>
@@ -810,18 +810,18 @@
           <t>OMRSE_00002048</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is reserved for tertiary programmes (ISCED 6) that lead directly to the award of an advanced research qualification. The theoretical duration of these programmes is 3 years full-time in most countries (for a cumulative total of at least 7 years FTE at the tertiary level), although the actual enrolment time is typically longer. The programmes are devoted to advanced study and original research. For a programme to be classified at ISCED 6, it:• requires, for successful completion, the submission of a thesis or dissertation of publishable quality that is the product of original research and represents a significant contribution to knowledge</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="inlineStr">
@@ -834,13 +834,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="n"/>
       <c r="U6" s="2" t="n"/>
@@ -869,18 +869,18 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is a doctoral or equivalent level education.  Entry into doctoral (ISCED level 8) programmes or junior research positions normally requires the successful completion of specific ISCED level 7 programmes. Programmes at ISCED level 8, or doctoral or equivalent level, are designed primarily to lead to an advanced research qualification. Programmes at this ISCED level are devoted to advanced study and original research and are typically offered only by research-oriented tertiary educational institutions such as universities. Doctoral programmes exist in both academic and professional fields.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="inlineStr">
@@ -893,13 +893,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="2" t="n"/>
       <c r="U7" s="2" t="n"/>
@@ -928,18 +928,18 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A highest level of formal educational qualification achieved that is pre-primary education (ISCED 0), defined as the initial stage of organised instruction, designed primarily to introduce very young children to a school-type environment, that is, to provide a bridge between home and a school-based atmosphere. </t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="inlineStr">
@@ -952,13 +952,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n"/>
       <c r="U8" s="2" t="n"/>
@@ -991,18 +991,18 @@
           <t>OMRSE_00002036</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is lower secondary level of education (ISCED 2) which generally pursues the basic programmes of the primary level, although teaching is typically more subject-focused, often employing more specialised teachers who conduct classes in their field of specialisation. Lower secondary education may be either “terminal”(i.e. preparing students for direct entry into working life) and / or “preparatory” (i.e. preparing students for upper secondary education).This level can range from 2 to 6 years of schooling (the mode of OECD countries is 3 years).</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="inlineStr">
@@ -1015,13 +1015,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="n"/>
       <c r="U9" s="2" t="n"/>
@@ -1050,18 +1050,18 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is a master's or equivalent level education. Entry into master's (ISCED level 7) programmes preparing for a second or further degree normally requires the successful completion of an ISCED level 6 or 7 programme. Additionally, it may be required to take and succeed in entry examinations. Programmes at ISCED level 7, or Master’s or equivalent level, are often designed to provide participants with advanced academic and/or professional knowledge, skills and competencies, leading to a second degree or equivalent qualification. Programmes at this level may have a substantial research component but do not yet lead to the award of a doctoral qualification. Typically, programmes at this level are theoretically-based but may include practical components and are informed by state of the art research and/or best professional practice. They are traditionally offered by universities and other tertiary educational institutions.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="inlineStr">
@@ -1074,13 +1074,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n"/>
@@ -1113,18 +1113,18 @@
           <t xml:space="preserve">OMRSE_00002035  </t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is primary education (ISCED 1) which usually begins at age 5, 6, or 7 and generally lasts for 4 (e.g. Germany) to 6 years (the mode of the OECD countries being six years). Programmes at the primary level generally require no previous formal education, although it is becoming increasingly common for children to have attended a pre-primary programme before entering primary education</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="inlineStr">
@@ -1137,13 +1137,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n"/>
       <c r="U11" s="2" t="n"/>
@@ -1180,18 +1180,18 @@
           <t>OMRSE_00002040</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that corresponds to the final stage of secondary education in most OECD countries. Instruction is often more organised along subject-matter lines than at ISCED 2 level and teachers typically need to have a higher level, or more subject-specific, qualifications than at ISCED 2. The entrance age to this level is typically 15 or 16 years. There are substantial differences in the typical duration of ISCED 3 programmes both between and within countries, typically ranging from 2 to 5 years of schooling. ISCED 3 may either be “terminal” (i.e. preparing students for direct entry into working life) and/or “preparatory” (i.e. preparing students for tertiary education).</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="inlineStr">
@@ -1204,13 +1204,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="n"/>
       <c r="U12" s="2" t="n"/>
@@ -1240,13 +1240,13 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="inlineStr">
@@ -1259,13 +1259,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="n"/>
       <c r="U13" s="2" t="n"/>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="inlineStr">
@@ -1318,13 +1318,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="n"/>
@@ -1354,13 +1354,13 @@
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="inlineStr">
@@ -1373,13 +1373,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P15" s="2" t="n"/>
       <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n"/>
       <c r="U15" s="2" t="n"/>
@@ -1409,13 +1409,13 @@
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="inlineStr">
@@ -1428,13 +1428,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n"/>
       <c r="U16" s="2" t="n"/>
@@ -1464,13 +1464,13 @@
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="inlineStr">
@@ -1483,13 +1483,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
-      <c r="R17" s="2" t="n"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="inlineStr">
@@ -1542,13 +1542,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="n"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="n"/>
@@ -1578,13 +1578,13 @@
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="inlineStr">
@@ -1597,13 +1597,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
-      <c r="R19" s="2" t="n"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="n"/>
       <c r="U19" s="2" t="n"/>
@@ -1633,13 +1633,13 @@
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="inlineStr">
@@ -1652,13 +1652,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="n"/>
@@ -1688,13 +1688,13 @@
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="inlineStr">
@@ -1707,13 +1707,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="n"/>
@@ -1739,12 +1739,12 @@
           <t>person</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>The age at which a person is considered an adult will vary in different cultures and for different contexts.  For example, the age at which a person reaches physical maturity may not be the same age at which they are considered legally an adult in their country of residence.  For use in research contexts, the minimum age of an "adult" needs to be specified.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -1759,7 +1759,7 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -1790,13 +1790,13 @@
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="inlineStr">
@@ -1809,13 +1809,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="2" t="n"/>
       <c r="U23" s="2" t="n"/>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
@@ -1868,13 +1868,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="n"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="n"/>
       <c r="U24" s="2" t="n"/>
@@ -1904,13 +1904,13 @@
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="inlineStr">
@@ -1923,13 +1923,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
-      <c r="R25" s="2" t="n"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="n"/>
       <c r="U25" s="2" t="n"/>
@@ -1958,29 +1958,29 @@
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>"Exposed" encompasses both passive exposure to a behaviour change intervention e.g. nudges/environmental changes, and more active participation in a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
-      <c r="R26" s="2" t="n"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n"/>
       <c r="U26" s="2" t="n"/>
@@ -2010,24 +2010,24 @@
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
-      <c r="R27" s="2" t="n"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="2" t="n"/>
       <c r="U27" s="2" t="n"/>
@@ -2064,13 +2064,13 @@
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="n"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="n"/>
       <c r="U28" s="2" t="n"/>
@@ -2096,33 +2096,33 @@
           <t>person</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>actor</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>behaviour has to be specified
 s. also behaviour enacter, behaviour non-intender</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="2" t="n"/>
       <c r="U29" s="2" t="n"/>
@@ -2151,26 +2151,26 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>behaviour has to be specified
 s. also behaviour enacter, behaviour intender</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="n"/>
       <c r="U30" s="2" t="n"/>
@@ -2199,26 +2199,26 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>behaviour has to be specified
 s. also behaviour intender, behaviour non-intender</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
-      <c r="R31" s="2" t="n"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="n"/>
@@ -2250,24 +2250,24 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>The number of times a person performs a behaviour within a specific period.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>behaviour</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>The number of times a person performs a behaviour within a specific period.</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S32" s="2" t="n"/>
@@ -2299,13 +2299,13 @@
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="inlineStr">
@@ -2318,13 +2318,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
-      <c r="R33" s="2" t="n"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="n"/>
       <c r="U33" s="2" t="n"/>
@@ -2354,13 +2354,13 @@
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="inlineStr">
@@ -2373,13 +2373,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="n"/>
@@ -2409,13 +2409,13 @@
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="inlineStr">
@@ -2428,13 +2428,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="n"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n"/>
       <c r="U35" s="2" t="n"/>
@@ -2464,13 +2464,13 @@
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="inlineStr">
@@ -2483,13 +2483,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="n"/>
@@ -2519,13 +2519,13 @@
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="inlineStr">
@@ -2538,13 +2538,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n"/>
-      <c r="R37" s="2" t="n"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="n"/>
       <c r="U37" s="2" t="n"/>
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="inlineStr">
@@ -2597,13 +2597,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n"/>
-      <c r="R38" s="2" t="n"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n"/>
       <c r="U38" s="2" t="n"/>
@@ -2633,13 +2633,13 @@
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="inlineStr">
@@ -2652,13 +2652,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="n"/>
       <c r="U39" s="2" t="n"/>
@@ -2688,13 +2688,13 @@
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="inlineStr">
@@ -2707,13 +2707,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="n"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n"/>
       <c r="U40" s="2" t="n"/>
@@ -2743,13 +2743,13 @@
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="inlineStr">
@@ -2762,13 +2762,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
-      <c r="R41" s="2" t="n"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n"/>
       <c r="U41" s="2" t="n"/>
@@ -2798,13 +2798,13 @@
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
@@ -2817,13 +2817,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="n"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n"/>
       <c r="U42" s="2" t="n"/>
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="inlineStr">
@@ -2876,13 +2876,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="n"/>
       <c r="U43" s="2" t="n"/>
@@ -2908,12 +2908,12 @@
           <t>quality</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -2944,13 +2944,13 @@
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="n"/>
       <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="inlineStr">
@@ -2963,13 +2963,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="n"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="n"/>
       <c r="U45" s="2" t="n"/>
@@ -2998,18 +2998,18 @@
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage belonging to a specific caste</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="inlineStr">
@@ -3022,13 +3022,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="n"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
       <c r="U46" s="2" t="n"/>
@@ -3057,18 +3057,18 @@
       <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The age until which a person is considered a child will vary in different cultures and for different contexts.  For use in research contexts, the maximum age of a "child" needs to be specified.  </t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
       <c r="N47" s="2" t="inlineStr">
@@ -3081,13 +3081,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="n"/>
-      <c r="R47" s="2" t="n"/>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="n"/>
       <c r="U47" s="2" t="n"/>
@@ -3117,13 +3117,13 @@
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="inlineStr">
@@ -3136,13 +3136,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P48" s="2" t="n"/>
       <c r="Q48" s="2" t="n"/>
-      <c r="R48" s="2" t="n"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="n"/>
       <c r="U48" s="2" t="n"/>
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I49" s="2" t="n"/>
       <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="inlineStr">
@@ -3195,13 +3195,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P49" s="2" t="n"/>
       <c r="Q49" s="2" t="n"/>
-      <c r="R49" s="2" t="n"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="2" t="n"/>
       <c r="U49" s="2" t="n"/>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
       <c r="N50" s="2" t="inlineStr">
@@ -3254,13 +3254,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="n"/>
-      <c r="R50" s="2" t="n"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="n"/>
       <c r="U50" s="2" t="n"/>
@@ -3290,13 +3290,13 @@
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="n"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
       <c r="N51" s="2" t="inlineStr">
@@ -3309,13 +3309,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="n"/>
-      <c r="R51" s="2" t="n"/>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="2" t="n"/>
       <c r="U51" s="2" t="n"/>
@@ -3345,13 +3345,13 @@
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="inlineStr">
@@ -3364,13 +3364,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P52" s="2" t="n"/>
       <c r="Q52" s="2" t="n"/>
-      <c r="R52" s="2" t="n"/>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="n"/>
       <c r="U52" s="2" t="n"/>
@@ -3403,18 +3403,18 @@
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>The division of knowledge and practice into different disciplines or fields is complex and depends on historical, social and structural factors</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
       <c r="N53" s="2" t="inlineStr">
@@ -3427,13 +3427,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P53" s="2" t="n"/>
       <c r="Q53" s="2" t="n"/>
-      <c r="R53" s="2" t="n"/>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="2" t="n"/>
       <c r="U53" s="2" t="n"/>
@@ -3467,13 +3467,13 @@
       </c>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="inlineStr">
@@ -3486,13 +3486,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P54" s="2" t="n"/>
       <c r="Q54" s="2" t="n"/>
-      <c r="R54" s="2" t="n"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="n"/>
       <c r="U54" s="2" t="n"/>
@@ -3522,13 +3522,13 @@
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
       <c r="N55" s="2" t="inlineStr">
@@ -3541,13 +3541,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P55" s="2" t="n"/>
       <c r="Q55" s="2" t="n"/>
-      <c r="R55" s="2" t="n"/>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="2" t="n"/>
       <c r="U55" s="2" t="n"/>
@@ -3577,13 +3577,13 @@
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="n"/>
       <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
       <c r="N56" s="2" t="inlineStr">
@@ -3596,13 +3596,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P56" s="2" t="n"/>
       <c r="Q56" s="2" t="n"/>
-      <c r="R56" s="2" t="n"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="2" t="n"/>
       <c r="U56" s="2" t="n"/>
@@ -3635,21 +3635,21 @@
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>This definition is based on the work of Scholz et al (2025), as published here: https://osf.io/2364r/</t>
-        </is>
-      </c>
+      <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="n"/>
-      <c r="R57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>This definition is based on the work of Scholz et al (2025), as published here: https://osf.io/2364r/</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="2" t="n"/>
       <c r="U57" s="2" t="n"/>
@@ -3683,24 +3683,24 @@
         </is>
       </c>
       <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I58" s="2" t="n"/>
       <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="n"/>
-      <c r="R58" s="2" t="n"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="2" t="n"/>
       <c r="U58" s="2" t="n"/>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I59" s="2" t="n"/>
       <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="inlineStr">
@@ -3753,13 +3753,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="n"/>
-      <c r="R59" s="2" t="n"/>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="2" t="n"/>
       <c r="U59" s="2" t="n"/>
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I60" s="2" t="n"/>
       <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="inlineStr">
@@ -3812,13 +3812,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P60" s="2" t="n"/>
       <c r="Q60" s="2" t="n"/>
-      <c r="R60" s="2" t="n"/>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="2" t="n"/>
       <c r="U60" s="2" t="n"/>
@@ -3848,13 +3848,13 @@
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="inlineStr">
@@ -3867,13 +3867,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P61" s="2" t="n"/>
       <c r="Q61" s="2" t="n"/>
-      <c r="R61" s="2" t="n"/>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="2" t="n"/>
       <c r="U61" s="2" t="n"/>
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I62" s="2" t="n"/>
       <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="n"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="inlineStr">
@@ -3926,13 +3926,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P62" s="2" t="n"/>
       <c r="Q62" s="2" t="n"/>
-      <c r="R62" s="2" t="n"/>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="n"/>
       <c r="U62" s="2" t="n"/>
@@ -3958,26 +3958,26 @@
           <t>quality</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Sustainable Development Goals Interface Ontology (SDGIO:00010029)</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>An employment process is a  planned process wherein an employee performs actions that are formally or informally specified by an employer in return for remuneration.
 This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
       <c r="N63" s="2" t="inlineStr">
@@ -3990,13 +3990,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
+      <c r="Q63" s="2" t="n"/>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="2" t="n"/>
       <c r="U63" s="2" t="n"/>
@@ -4029,18 +4029,18 @@
           <t>EFO:0001799</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage who identify as belonging to a specific ethnic group</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="n"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="inlineStr">
@@ -4053,13 +4053,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P64" s="2" t="n"/>
       <c r="Q64" s="2" t="n"/>
-      <c r="R64" s="2" t="n"/>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="n"/>
       <c r="U64" s="2" t="n"/>
@@ -4089,13 +4089,13 @@
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I65" s="2" t="n"/>
       <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
       <c r="N65" s="2" t="inlineStr">
@@ -4108,13 +4108,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="n"/>
-      <c r="R65" s="2" t="n"/>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="n"/>
       <c r="T65" s="2" t="n"/>
       <c r="U65" s="2" t="n"/>
@@ -4144,24 +4144,24 @@
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I66" s="2" t="n"/>
       <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
       <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="n"/>
-      <c r="R66" s="2" t="n"/>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="2" t="n"/>
       <c r="U66" s="2" t="n"/>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I67" s="2" t="n"/>
       <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n"/>
       <c r="N67" s="2" t="inlineStr">
@@ -4214,13 +4214,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="n"/>
-      <c r="R67" s="2" t="n"/>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S67" s="2" t="n"/>
       <c r="T67" s="2" t="n"/>
       <c r="U67" s="2" t="n"/>
@@ -4250,13 +4250,13 @@
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I68" s="2" t="n"/>
       <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
       <c r="N68" s="2" t="inlineStr">
@@ -4269,13 +4269,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P68" s="2" t="n"/>
       <c r="Q68" s="2" t="n"/>
-      <c r="R68" s="2" t="n"/>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="2" t="n"/>
       <c r="U68" s="2" t="n"/>
@@ -4305,13 +4305,13 @@
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="n"/>
       <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="inlineStr">
@@ -4324,13 +4324,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="n"/>
-      <c r="R69" s="2" t="n"/>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S69" s="2" t="n"/>
       <c r="T69" s="2" t="n"/>
       <c r="U69" s="2" t="n"/>
@@ -4356,25 +4356,25 @@
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>GSSO:000089</t>
         </is>
       </c>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n"/>
       <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="inlineStr">
@@ -4387,13 +4387,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="n"/>
-      <c r="R70" s="2" t="n"/>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S70" s="2" t="n"/>
       <c r="T70" s="2" t="n"/>
       <c r="U70" s="2" t="n"/>
@@ -4423,13 +4423,13 @@
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="n"/>
       <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="n"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
       <c r="N71" s="2" t="inlineStr">
@@ -4442,13 +4442,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="n"/>
-      <c r="R71" s="2" t="n"/>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="n"/>
       <c r="T71" s="2" t="n"/>
       <c r="U71" s="2" t="n"/>
@@ -4478,13 +4478,13 @@
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I72" s="2" t="n"/>
       <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="inlineStr">
@@ -4497,13 +4497,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P72" s="2" t="n"/>
       <c r="Q72" s="2" t="n"/>
-      <c r="R72" s="2" t="n"/>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="n"/>
       <c r="U72" s="2" t="n"/>
@@ -4533,13 +4533,13 @@
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="n"/>
       <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="n"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="inlineStr">
@@ -4552,13 +4552,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="n"/>
-      <c r="R73" s="2" t="n"/>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S73" s="2" t="n"/>
       <c r="T73" s="2" t="n"/>
       <c r="U73" s="2" t="n"/>
@@ -4588,13 +4588,13 @@
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="n"/>
       <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="n"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="inlineStr">
@@ -4607,13 +4607,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P74" s="2" t="n"/>
       <c r="Q74" s="2" t="n"/>
-      <c r="R74" s="2" t="n"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="n"/>
       <c r="U74" s="2" t="n"/>
@@ -4643,13 +4643,13 @@
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I75" s="2" t="n"/>
       <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="n"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
       <c r="N75" s="2" t="inlineStr">
@@ -4662,13 +4662,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P75" s="2" t="n"/>
       <c r="Q75" s="2" t="n"/>
-      <c r="R75" s="2" t="n"/>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S75" s="2" t="n"/>
       <c r="T75" s="2" t="n"/>
       <c r="U75" s="2" t="n"/>
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I76" s="2" t="n"/>
       <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="n"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
       <c r="N76" s="2" t="inlineStr">
@@ -4721,13 +4721,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P76" s="2" t="n"/>
       <c r="Q76" s="2" t="n"/>
-      <c r="R76" s="2" t="n"/>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="2" t="n"/>
       <c r="U76" s="2" t="n"/>
@@ -4757,13 +4757,13 @@
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="n"/>
       <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="n"/>
       <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="n"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n"/>
       <c r="N77" s="2" t="inlineStr">
@@ -4776,13 +4776,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="n"/>
-      <c r="R77" s="2" t="n"/>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S77" s="2" t="n"/>
       <c r="T77" s="2" t="n"/>
       <c r="U77" s="2" t="n"/>
@@ -4812,13 +4812,13 @@
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="n"/>
       <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n"/>
       <c r="N78" s="2" t="inlineStr">
@@ -4831,13 +4831,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="n"/>
-      <c r="R78" s="2" t="n"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="2" t="n"/>
       <c r="U78" s="2" t="n"/>
@@ -4867,13 +4867,13 @@
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I79" s="2" t="n"/>
       <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="n"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="inlineStr">
@@ -4886,13 +4886,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="n"/>
-      <c r="R79" s="2" t="n"/>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S79" s="2" t="n"/>
       <c r="T79" s="2" t="n"/>
       <c r="U79" s="2" t="n"/>
@@ -4922,24 +4922,24 @@
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I80" s="2" t="n"/>
       <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="n"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P80" s="2" t="n"/>
       <c r="Q80" s="2" t="n"/>
-      <c r="R80" s="2" t="n"/>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="n"/>
       <c r="U80" s="2" t="n"/>
@@ -4969,13 +4969,13 @@
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I81" s="2" t="n"/>
       <c r="J81" s="2" t="n"/>
-      <c r="K81" s="2" t="n"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="inlineStr">
@@ -4988,13 +4988,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="n"/>
-      <c r="R81" s="2" t="n"/>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S81" s="2" t="n"/>
       <c r="T81" s="2" t="n"/>
       <c r="U81" s="2" t="n"/>
@@ -5024,13 +5024,13 @@
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I82" s="2" t="n"/>
       <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
       <c r="N82" s="2" t="inlineStr">
@@ -5043,13 +5043,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P82" s="2" t="n"/>
       <c r="Q82" s="2" t="n"/>
-      <c r="R82" s="2" t="n"/>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S82" s="2" t="n"/>
       <c r="T82" s="2" t="n"/>
       <c r="U82" s="2" t="n"/>
@@ -5079,13 +5079,13 @@
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="n"/>
       <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="inlineStr">
@@ -5098,13 +5098,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P83" s="2" t="n"/>
       <c r="Q83" s="2" t="n"/>
-      <c r="R83" s="2" t="n"/>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S83" s="2" t="n"/>
       <c r="T83" s="2" t="n"/>
       <c r="U83" s="2" t="n"/>
@@ -5134,13 +5134,13 @@
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="n"/>
       <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n"/>
       <c r="N84" s="2" t="inlineStr">
@@ -5153,13 +5153,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P84" s="2" t="n"/>
       <c r="Q84" s="2" t="n"/>
-      <c r="R84" s="2" t="n"/>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S84" s="2" t="n"/>
       <c r="T84" s="2" t="n"/>
       <c r="U84" s="2" t="n"/>
@@ -5189,13 +5189,13 @@
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I85" s="2" t="n"/>
       <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="n"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="2" t="n"/>
       <c r="N85" s="2" t="inlineStr">
@@ -5208,13 +5208,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="n"/>
-      <c r="R85" s="2" t="n"/>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S85" s="2" t="n"/>
       <c r="T85" s="2" t="n"/>
       <c r="U85" s="2" t="n"/>
@@ -5244,13 +5244,13 @@
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I86" s="2" t="n"/>
       <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="n"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="inlineStr">
@@ -5263,13 +5263,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="n"/>
-      <c r="R86" s="2" t="n"/>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="n"/>
       <c r="U86" s="2" t="n"/>
@@ -5303,13 +5303,13 @@
       </c>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I87" s="2" t="n"/>
       <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="n"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="2" t="n"/>
       <c r="N87" s="2" t="inlineStr">
@@ -5322,13 +5322,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="n"/>
-      <c r="R87" s="2" t="n"/>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S87" s="2" t="n"/>
       <c r="T87" s="2" t="n"/>
       <c r="U87" s="2" t="n"/>
@@ -5366,13 +5366,13 @@
         </is>
       </c>
       <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I88" s="2" t="n"/>
       <c r="J88" s="2" t="n"/>
-      <c r="K88" s="2" t="n"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="inlineStr">
@@ -5385,13 +5385,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P88" s="2" t="n"/>
       <c r="Q88" s="2" t="n"/>
-      <c r="R88" s="2" t="n"/>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S88" s="2" t="n"/>
       <c r="T88" s="2" t="n"/>
       <c r="U88" s="2" t="n"/>
@@ -5425,13 +5425,13 @@
         </is>
       </c>
       <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I89" s="2" t="n"/>
       <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="n"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="inlineStr">
@@ -5444,13 +5444,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P89" s="2" t="n"/>
       <c r="Q89" s="2" t="n"/>
-      <c r="R89" s="2" t="n"/>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S89" s="2" t="n"/>
       <c r="T89" s="2" t="n"/>
       <c r="U89" s="2" t="n"/>
@@ -5480,24 +5480,24 @@
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="n"/>
       <c r="J90" s="2" t="n"/>
-      <c r="K90" s="2" t="n"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L90" s="2" t="n"/>
       <c r="M90" s="2" t="n"/>
       <c r="N90" s="2" t="n"/>
       <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P90" s="2" t="n"/>
       <c r="Q90" s="2" t="n"/>
-      <c r="R90" s="2" t="n"/>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S90" s="2" t="n"/>
       <c r="T90" s="2" t="n"/>
       <c r="U90" s="2" t="n"/>
@@ -5527,13 +5527,13 @@
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="n"/>
       <c r="J91" s="2" t="n"/>
-      <c r="K91" s="2" t="n"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="inlineStr">
@@ -5546,13 +5546,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P91" s="2" t="n"/>
       <c r="Q91" s="2" t="n"/>
-      <c r="R91" s="2" t="n"/>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S91" s="2" t="n"/>
       <c r="T91" s="2" t="n"/>
       <c r="U91" s="2" t="n"/>
@@ -5585,18 +5585,18 @@
           <t xml:space="preserve">NCIT_C17953 </t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>The highest level of a packaged education process an individual has completed</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="n"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="inlineStr">
@@ -5609,13 +5609,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
-      <c r="R92" s="2" t="n"/>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S92" s="2" t="n"/>
       <c r="T92" s="2" t="n"/>
       <c r="U92" s="2" t="n"/>
@@ -5641,12 +5641,12 @@
           <t>process</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -5681,13 +5681,13 @@
       </c>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I94" s="2" t="n"/>
       <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="n"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="2" t="n"/>
       <c r="N94" s="2" t="inlineStr">
@@ -5700,13 +5700,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="n"/>
-      <c r="R94" s="2" t="n"/>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S94" s="2" t="n"/>
       <c r="T94" s="2" t="n"/>
       <c r="U94" s="2" t="n"/>
@@ -5740,13 +5740,13 @@
       </c>
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="n"/>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I95" s="2" t="n"/>
       <c r="J95" s="2" t="n"/>
-      <c r="K95" s="2" t="n"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n"/>
       <c r="N95" s="2" t="inlineStr">
@@ -5759,13 +5759,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="n"/>
-      <c r="R95" s="2" t="n"/>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S95" s="2" t="n"/>
       <c r="T95" s="2" t="n"/>
       <c r="U95" s="2" t="n"/>
@@ -5791,21 +5791,21 @@
           <t>person</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>person experiencing homelessness</t>
-        </is>
-      </c>
+      <c r="E96" s="2" t="n"/>
       <c r="F96" s="2" t="n"/>
       <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>person experiencing homelessness</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n"/>
       <c r="J96" s="2" t="n"/>
-      <c r="K96" s="2" t="n"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="2" t="n"/>
       <c r="N96" s="2" t="inlineStr">
@@ -5818,13 +5818,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="n"/>
-      <c r="R96" s="2" t="n"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S96" s="2" t="n"/>
       <c r="T96" s="2" t="n"/>
       <c r="U96" s="2" t="n"/>
@@ -5858,13 +5858,13 @@
         </is>
       </c>
       <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I97" s="2" t="n"/>
       <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="n"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="inlineStr">
@@ -5877,13 +5877,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P97" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n"/>
-      <c r="R97" s="2" t="n"/>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S97" s="2" t="n"/>
       <c r="T97" s="2" t="n"/>
       <c r="U97" s="2" t="n"/>
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I98" s="2" t="n"/>
       <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="2" t="n"/>
       <c r="N98" s="2" t="inlineStr">
@@ -5936,13 +5936,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="n"/>
-      <c r="R98" s="2" t="n"/>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S98" s="2" t="n"/>
       <c r="T98" s="2" t="n"/>
       <c r="U98" s="2" t="n"/>
@@ -5968,17 +5968,17 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>A household is a person of group of people that live in the same dwelling. A dwelling is a self-contained unit of accommodation where all of the rooms are behind a single door that only the household can use.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -6013,18 +6013,18 @@
         </is>
       </c>
       <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I100" s="2" t="n"/>
       <c r="J100" s="2" t="n"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
           <t>household</t>
         </is>
       </c>
-      <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
@@ -6036,13 +6036,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P100" s="2" t="n"/>
       <c r="Q100" s="2" t="n"/>
-      <c r="R100" s="2" t="n"/>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S100" s="2" t="n"/>
       <c r="T100" s="2" t="n"/>
       <c r="U100" s="2" t="n"/>
@@ -6076,13 +6076,13 @@
         </is>
       </c>
       <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I101" s="2" t="n"/>
       <c r="J101" s="2" t="n"/>
-      <c r="K101" s="2" t="n"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="inlineStr">
@@ -6095,13 +6095,13 @@
           <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P101" s="2" t="n"/>
       <c r="Q101" s="2" t="n"/>
-      <c r="R101" s="2" t="n"/>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S101" s="2" t="n"/>
       <c r="T101" s="2" t="n"/>
       <c r="U101" s="2" t="n"/>
@@ -6131,24 +6131,24 @@
       <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="n"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I102" s="2" t="n"/>
       <c r="J102" s="2" t="n"/>
-      <c r="K102" s="2" t="n"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="2" t="n"/>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="2" t="n"/>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P102" s="2" t="n"/>
       <c r="Q102" s="2" t="n"/>
-      <c r="R102" s="2" t="n"/>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S102" s="2" t="n"/>
       <c r="T102" s="2" t="n"/>
       <c r="U102" s="2" t="n"/>
@@ -6174,12 +6174,12 @@
           <t>cognitive representation</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -6210,13 +6210,13 @@
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I104" s="2" t="n"/>
       <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="n"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n"/>
       <c r="N104" s="2" t="inlineStr">
@@ -6229,13 +6229,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P104" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P104" s="2" t="n"/>
       <c r="Q104" s="2" t="n"/>
-      <c r="R104" s="2" t="n"/>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S104" s="2" t="n"/>
       <c r="T104" s="2" t="n"/>
       <c r="U104" s="2" t="n"/>
@@ -6265,13 +6265,13 @@
       <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I105" s="2" t="n"/>
       <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="n"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
       <c r="N105" s="2" t="inlineStr">
@@ -6285,13 +6285,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P105" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P105" s="2" t="n"/>
       <c r="Q105" s="2" t="n"/>
-      <c r="R105" s="2" t="n"/>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S105" s="2" t="n"/>
       <c r="T105" s="2" t="n"/>
       <c r="U105" s="2" t="n"/>
@@ -6320,18 +6320,18 @@
       <c r="E106" s="2" t="n"/>
       <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"Common law" relationship refers to a person who is living with another person as a couple but who is not in a legally recognised marriage or other civil union. </t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="n"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n"/>
       <c r="N106" s="2" t="inlineStr">
@@ -6344,13 +6344,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P106" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P106" s="2" t="n"/>
       <c r="Q106" s="2" t="n"/>
-      <c r="R106" s="2" t="n"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S106" s="2" t="n"/>
       <c r="T106" s="2" t="n"/>
       <c r="U106" s="2" t="n"/>
@@ -6380,13 +6380,13 @@
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I107" s="2" t="n"/>
       <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="n"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="inlineStr">
@@ -6399,13 +6399,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P107" s="2" t="n"/>
       <c r="Q107" s="2" t="n"/>
-      <c r="R107" s="2" t="n"/>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S107" s="2" t="n"/>
       <c r="T107" s="2" t="n"/>
       <c r="U107" s="2" t="n"/>
@@ -6435,13 +6435,13 @@
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I108" s="2" t="n"/>
       <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="n"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
       <c r="N108" s="2" t="inlineStr">
@@ -6454,13 +6454,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P108" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="n"/>
-      <c r="R108" s="2" t="n"/>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S108" s="2" t="n"/>
       <c r="T108" s="2" t="n"/>
       <c r="U108" s="2" t="n"/>
@@ -6490,13 +6490,13 @@
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I109" s="2" t="n"/>
       <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="n"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
       <c r="N109" s="2" t="inlineStr">
@@ -6509,13 +6509,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P109" s="2" t="n"/>
       <c r="Q109" s="2" t="n"/>
-      <c r="R109" s="2" t="n"/>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S109" s="2" t="n"/>
       <c r="T109" s="2" t="n"/>
       <c r="U109" s="2" t="n"/>
@@ -6545,13 +6545,13 @@
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I110" s="2" t="n"/>
       <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="n"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n"/>
       <c r="N110" s="2" t="inlineStr">
@@ -6564,13 +6564,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P110" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P110" s="2" t="n"/>
       <c r="Q110" s="2" t="n"/>
-      <c r="R110" s="2" t="n"/>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S110" s="2" t="n"/>
       <c r="T110" s="2" t="n"/>
       <c r="U110" s="2" t="n"/>
@@ -6600,13 +6600,13 @@
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I111" s="2" t="n"/>
       <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
       <c r="N111" s="2" t="inlineStr">
@@ -6619,13 +6619,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P111" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P111" s="2" t="n"/>
       <c r="Q111" s="2" t="n"/>
-      <c r="R111" s="2" t="n"/>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S111" s="2" t="n"/>
       <c r="T111" s="2" t="n"/>
       <c r="U111" s="2" t="n"/>
@@ -6659,13 +6659,13 @@
       </c>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I112" s="2" t="n"/>
       <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="n"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n"/>
       <c r="N112" s="2" t="inlineStr">
@@ -6678,13 +6678,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P112" s="2" t="n"/>
       <c r="Q112" s="2" t="n"/>
-      <c r="R112" s="2" t="n"/>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S112" s="2" t="n"/>
       <c r="T112" s="2" t="n"/>
       <c r="U112" s="2" t="n"/>
@@ -6712,15 +6712,19 @@
       </c>
       <c r="E113" s="2" t="n"/>
       <c r="F113" s="2" t="n"/>
-      <c r="G113" s="2" t="n"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>OMRSE_00002061</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I113" s="2" t="n"/>
       <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="n"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n"/>
       <c r="N113" s="2" t="inlineStr">
@@ -6733,13 +6737,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="n"/>
-      <c r="R113" s="2" t="n"/>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S113" s="2" t="n"/>
       <c r="T113" s="2" t="n"/>
       <c r="U113" s="2" t="n"/>
@@ -6769,13 +6773,13 @@
       <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I114" s="2" t="n"/>
       <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="n"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="inlineStr">
@@ -6788,13 +6792,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P114" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P114" s="2" t="n"/>
       <c r="Q114" s="2" t="n"/>
-      <c r="R114" s="2" t="n"/>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S114" s="2" t="n"/>
       <c r="T114" s="2" t="n"/>
       <c r="U114" s="2" t="n"/>
@@ -6824,13 +6828,13 @@
       <c r="F115" s="2" t="n"/>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I115" s="2" t="n"/>
       <c r="J115" s="2" t="n"/>
-      <c r="K115" s="2" t="n"/>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L115" s="2" t="n"/>
       <c r="M115" s="2" t="n"/>
       <c r="N115" s="2" t="inlineStr">
@@ -6843,13 +6847,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P115" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P115" s="2" t="n"/>
       <c r="Q115" s="2" t="n"/>
-      <c r="R115" s="2" t="n"/>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S115" s="2" t="n"/>
       <c r="T115" s="2" t="n"/>
       <c r="U115" s="2" t="n"/>
@@ -6879,13 +6883,13 @@
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I116" s="2" t="n"/>
       <c r="J116" s="2" t="n"/>
-      <c r="K116" s="2" t="n"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L116" s="2" t="n"/>
       <c r="M116" s="2" t="n"/>
       <c r="N116" s="2" t="inlineStr">
@@ -6898,13 +6902,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P116" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P116" s="2" t="n"/>
       <c r="Q116" s="2" t="n"/>
-      <c r="R116" s="2" t="n"/>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S116" s="2" t="n"/>
       <c r="T116" s="2" t="n"/>
       <c r="U116" s="2" t="n"/>
@@ -6937,18 +6941,18 @@
           <t>OMRSE:00000092</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J117" s="3" t="n"/>
-      <c r="K117" s="3" t="n"/>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L117" s="3" t="n"/>
       <c r="M117" s="3" t="n"/>
       <c r="N117" s="3" t="inlineStr">
@@ -6961,13 +6965,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P117" s="3" t="inlineStr">
+      <c r="P117" s="3" t="n"/>
+      <c r="Q117" s="3" t="n"/>
+      <c r="R117" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="Q117" s="3" t="n"/>
-      <c r="R117" s="3" t="n"/>
       <c r="S117" s="3" t="n"/>
       <c r="T117" s="3" t="n"/>
       <c r="U117" s="3" t="n"/>
@@ -6998,12 +7002,12 @@
           <t>OMRSE:00000092</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -7018,7 +7022,7 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
+      <c r="R118" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -7053,13 +7057,13 @@
         </is>
       </c>
       <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I119" s="2" t="n"/>
       <c r="J119" s="2" t="n"/>
-      <c r="K119" s="2" t="n"/>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n"/>
       <c r="N119" s="2" t="inlineStr">
@@ -7072,13 +7076,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P119" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P119" s="2" t="n"/>
       <c r="Q119" s="2" t="n"/>
-      <c r="R119" s="2" t="n"/>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S119" s="2" t="n"/>
       <c r="T119" s="2" t="n"/>
       <c r="U119" s="2" t="n"/>
@@ -7108,24 +7112,24 @@
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I120" s="2" t="n"/>
       <c r="J120" s="2" t="n"/>
-      <c r="K120" s="2" t="n"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
       <c r="N120" s="2" t="n"/>
       <c r="O120" s="2" t="n"/>
-      <c r="P120" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P120" s="2" t="n"/>
       <c r="Q120" s="2" t="n"/>
-      <c r="R120" s="2" t="n"/>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S120" s="2" t="n"/>
       <c r="T120" s="2" t="n"/>
       <c r="U120" s="2" t="n"/>
@@ -7155,24 +7159,24 @@
       <c r="F121" s="2" t="n"/>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I121" s="2" t="n"/>
       <c r="J121" s="2" t="n"/>
-      <c r="K121" s="2" t="n"/>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P121" s="2" t="n"/>
       <c r="Q121" s="2" t="n"/>
-      <c r="R121" s="2" t="n"/>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S121" s="2" t="n"/>
       <c r="T121" s="2" t="n"/>
       <c r="U121" s="2" t="n"/>
@@ -7206,13 +7210,13 @@
       </c>
       <c r="G122" s="2" t="n"/>
       <c r="H122" s="2" t="n"/>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I122" s="2" t="n"/>
       <c r="J122" s="2" t="n"/>
-      <c r="K122" s="2" t="n"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="2" t="n"/>
       <c r="N122" s="2" t="inlineStr">
@@ -7225,13 +7229,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P122" s="2" t="n"/>
       <c r="Q122" s="2" t="n"/>
-      <c r="R122" s="2" t="n"/>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S122" s="2" t="n"/>
       <c r="T122" s="2" t="n"/>
       <c r="U122" s="2" t="n"/>
@@ -7260,29 +7264,29 @@
       <c r="E123" s="2" t="n"/>
       <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="n"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>There are many usages of the term ‘leadership'. This class refers to one particular usage.</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="n"/>
-      <c r="K123" s="2" t="n"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n"/>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="2" t="n"/>
-      <c r="P123" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P123" s="2" t="n"/>
       <c r="Q123" s="2" t="n"/>
-      <c r="R123" s="2" t="n"/>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S123" s="2" t="n"/>
       <c r="T123" s="2" t="n"/>
       <c r="U123" s="2" t="n"/>
@@ -7308,7 +7312,7 @@
           <t>mental capability</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -7323,7 +7327,7 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="R124" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -7353,18 +7357,18 @@
       <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H125" s="2" t="n"/>
+      <c r="I125" s="2" t="n"/>
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>This is a fuzzy class. The minimum duration for a disability to be deemed long-term is subject to debate.  12 months seems reasonable, but others may wish to specify a different duration if required for their purposes.</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="n"/>
-      <c r="K125" s="2" t="n"/>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L125" s="2" t="n"/>
       <c r="M125" s="2" t="n"/>
       <c r="N125" s="2" t="inlineStr">
@@ -7377,13 +7381,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P125" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P125" s="2" t="n"/>
       <c r="Q125" s="2" t="n"/>
-      <c r="R125" s="2" t="n"/>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S125" s="2" t="n"/>
       <c r="T125" s="2" t="n"/>
       <c r="U125" s="2" t="n"/>
@@ -7414,24 +7418,24 @@
       <c r="F126" s="2" t="n"/>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I126" s="2" t="n"/>
       <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="n"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L126" s="2" t="n"/>
       <c r="M126" s="2" t="n"/>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P126" s="2" t="n"/>
       <c r="Q126" s="2" t="n"/>
-      <c r="R126" s="2" t="n"/>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S126" s="2" t="n"/>
       <c r="T126" s="2" t="n"/>
       <c r="U126" s="2" t="n"/>
@@ -7461,13 +7465,13 @@
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I127" s="2" t="n"/>
       <c r="J127" s="2" t="n"/>
-      <c r="K127" s="2" t="n"/>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
       <c r="N127" s="2" t="inlineStr">
@@ -7480,13 +7484,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P127" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P127" s="2" t="n"/>
       <c r="Q127" s="2" t="n"/>
-      <c r="R127" s="2" t="n"/>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S127" s="2" t="n"/>
       <c r="T127" s="2" t="n"/>
       <c r="U127" s="2" t="n"/>
@@ -7512,25 +7516,25 @@
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="E128" s="2" t="n"/>
       <c r="F128" s="2" t="n"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
           <t>GSSO:000090</t>
         </is>
       </c>
-      <c r="H128" s="2" t="n"/>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n"/>
       <c r="J128" s="2" t="n"/>
-      <c r="K128" s="2" t="n"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L128" s="2" t="n"/>
       <c r="M128" s="2" t="n"/>
       <c r="N128" s="2" t="inlineStr">
@@ -7543,13 +7547,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P128" s="2" t="n"/>
       <c r="Q128" s="2" t="n"/>
-      <c r="R128" s="2" t="n"/>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S128" s="2" t="n"/>
       <c r="T128" s="2" t="n"/>
       <c r="U128" s="2" t="n"/>
@@ -7579,13 +7583,13 @@
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I129" s="2" t="n"/>
       <c r="J129" s="2" t="n"/>
-      <c r="K129" s="2" t="n"/>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L129" s="2" t="n"/>
       <c r="M129" s="2" t="n"/>
       <c r="N129" s="2" t="inlineStr">
@@ -7598,13 +7602,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P129" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P129" s="2" t="n"/>
       <c r="Q129" s="2" t="n"/>
-      <c r="R129" s="2" t="n"/>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S129" s="2" t="n"/>
       <c r="T129" s="2" t="n"/>
       <c r="U129" s="2" t="n"/>
@@ -7637,18 +7641,18 @@
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>This entity reflects having been prescribed a medication.  Actual use of the medicine would be captured as a behaviour</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="n"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
       <c r="N130" s="2" t="inlineStr">
@@ -7661,13 +7665,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P130" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P130" s="2" t="n"/>
       <c r="Q130" s="2" t="n"/>
-      <c r="R130" s="2" t="n"/>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S130" s="2" t="n"/>
       <c r="T130" s="2" t="n"/>
       <c r="U130" s="2" t="n"/>
@@ -7696,18 +7700,18 @@
       <c r="E131" s="2" t="n"/>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A member of a multi-person household lives with at least one other person in the same dwelling. </t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="n"/>
-      <c r="K131" s="2" t="n"/>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n"/>
       <c r="N131" s="2" t="inlineStr">
@@ -7720,13 +7724,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P131" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P131" s="2" t="n"/>
       <c r="Q131" s="2" t="n"/>
-      <c r="R131" s="2" t="n"/>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S131" s="2" t="n"/>
       <c r="T131" s="2" t="n"/>
       <c r="U131" s="2" t="n"/>
@@ -7764,13 +7768,13 @@
         </is>
       </c>
       <c r="H132" s="2" t="n"/>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I132" s="2" t="n"/>
       <c r="J132" s="2" t="n"/>
-      <c r="K132" s="2" t="n"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L132" s="2" t="n"/>
       <c r="M132" s="2" t="n"/>
       <c r="N132" s="2" t="inlineStr">
@@ -7783,13 +7787,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P132" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P132" s="2" t="n"/>
       <c r="Q132" s="2" t="n"/>
-      <c r="R132" s="2" t="n"/>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S132" s="2" t="n"/>
       <c r="T132" s="2" t="n"/>
       <c r="U132" s="2" t="n"/>
@@ -7823,13 +7827,13 @@
       </c>
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="2" t="n"/>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I133" s="2" t="n"/>
       <c r="J133" s="2" t="n"/>
-      <c r="K133" s="2" t="n"/>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L133" s="2" t="n"/>
       <c r="M133" s="2" t="n"/>
       <c r="N133" s="2" t="inlineStr">
@@ -7842,13 +7846,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P133" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P133" s="2" t="n"/>
       <c r="Q133" s="2" t="n"/>
-      <c r="R133" s="2" t="n"/>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S133" s="2" t="n"/>
       <c r="T133" s="2" t="n"/>
       <c r="U133" s="2" t="n"/>
@@ -7882,13 +7886,13 @@
       </c>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I134" s="2" t="n"/>
       <c r="J134" s="2" t="n"/>
-      <c r="K134" s="2" t="n"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n"/>
       <c r="N134" s="2" t="inlineStr">
@@ -7901,13 +7905,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P134" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P134" s="2" t="n"/>
       <c r="Q134" s="2" t="n"/>
-      <c r="R134" s="2" t="n"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S134" s="2" t="n"/>
       <c r="T134" s="2" t="n"/>
       <c r="U134" s="2" t="n"/>
@@ -7940,18 +7944,18 @@
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>A member of a multi-generational household lives with other people that are from more than one generation. A generation is all the people of about the same age within a society or within a particular family</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="n"/>
-      <c r="K135" s="2" t="n"/>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n"/>
       <c r="N135" s="2" t="inlineStr">
@@ -7964,13 +7968,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P135" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P135" s="2" t="n"/>
       <c r="Q135" s="2" t="n"/>
-      <c r="R135" s="2" t="n"/>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S135" s="2" t="n"/>
       <c r="T135" s="2" t="n"/>
       <c r="U135" s="2" t="n"/>
@@ -8000,13 +8004,13 @@
       <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I136" s="2" t="n"/>
       <c r="J136" s="2" t="n"/>
-      <c r="K136" s="2" t="n"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n"/>
       <c r="N136" s="2" t="inlineStr">
@@ -8019,13 +8023,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P136" s="2" t="n"/>
       <c r="Q136" s="2" t="n"/>
-      <c r="R136" s="2" t="n"/>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S136" s="2" t="n"/>
       <c r="T136" s="2" t="n"/>
       <c r="U136" s="2" t="n"/>
@@ -8051,7 +8055,7 @@
           <t>personal capability</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -8066,7 +8070,7 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
+      <c r="R137" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -8097,13 +8101,13 @@
       <c r="F138" s="2" t="n"/>
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I138" s="2" t="n"/>
       <c r="J138" s="2" t="n"/>
-      <c r="K138" s="2" t="n"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
       <c r="N138" s="2" t="inlineStr">
@@ -8116,13 +8120,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P138" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P138" s="2" t="n"/>
       <c r="Q138" s="2" t="n"/>
-      <c r="R138" s="2" t="n"/>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S138" s="2" t="n"/>
       <c r="T138" s="2" t="n"/>
       <c r="U138" s="2" t="n"/>
@@ -8152,13 +8156,13 @@
       <c r="F139" s="2" t="n"/>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I139" s="2" t="n"/>
       <c r="J139" s="2" t="n"/>
-      <c r="K139" s="2" t="n"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="inlineStr">
@@ -8171,13 +8175,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P139" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P139" s="2" t="n"/>
       <c r="Q139" s="2" t="n"/>
-      <c r="R139" s="2" t="n"/>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S139" s="2" t="n"/>
       <c r="T139" s="2" t="n"/>
       <c r="U139" s="2" t="n"/>
@@ -8207,13 +8211,13 @@
       <c r="F140" s="2" t="n"/>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I140" s="2" t="n"/>
       <c r="J140" s="2" t="n"/>
-      <c r="K140" s="2" t="n"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="2" t="n"/>
       <c r="N140" s="2" t="inlineStr">
@@ -8226,13 +8230,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P140" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P140" s="2" t="n"/>
       <c r="Q140" s="2" t="n"/>
-      <c r="R140" s="2" t="n"/>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S140" s="2" t="n"/>
       <c r="T140" s="2" t="n"/>
       <c r="U140" s="2" t="n"/>
@@ -8266,13 +8270,13 @@
         </is>
       </c>
       <c r="H141" s="2" t="n"/>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I141" s="2" t="n"/>
       <c r="J141" s="2" t="n"/>
-      <c r="K141" s="2" t="n"/>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="2" t="n"/>
       <c r="N141" s="2" t="inlineStr">
@@ -8285,13 +8289,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P141" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P141" s="2" t="n"/>
       <c r="Q141" s="2" t="n"/>
-      <c r="R141" s="2" t="n"/>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S141" s="2" t="n"/>
       <c r="T141" s="2" t="n"/>
       <c r="U141" s="2" t="n"/>
@@ -8325,13 +8329,13 @@
         </is>
       </c>
       <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="n"/>
       <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L142" s="2" t="n"/>
       <c r="M142" s="2" t="n"/>
       <c r="N142" s="2" t="inlineStr">
@@ -8344,13 +8348,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P142" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P142" s="2" t="n"/>
       <c r="Q142" s="2" t="n"/>
-      <c r="R142" s="2" t="n"/>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S142" s="2" t="n"/>
       <c r="T142" s="2" t="n"/>
       <c r="U142" s="2" t="n"/>
@@ -8380,13 +8384,13 @@
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I143" s="2" t="n"/>
       <c r="J143" s="2" t="n"/>
-      <c r="K143" s="2" t="n"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L143" s="2" t="n"/>
       <c r="M143" s="2" t="n"/>
       <c r="N143" s="2" t="inlineStr">
@@ -8399,13 +8403,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P143" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P143" s="2" t="n"/>
       <c r="Q143" s="2" t="n"/>
-      <c r="R143" s="2" t="n"/>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S143" s="2" t="n"/>
       <c r="T143" s="2" t="n"/>
       <c r="U143" s="2" t="n"/>
@@ -8435,13 +8439,13 @@
       <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I144" s="2" t="n"/>
       <c r="J144" s="2" t="n"/>
-      <c r="K144" s="2" t="n"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L144" s="2" t="n"/>
       <c r="M144" s="2" t="n"/>
       <c r="N144" s="2" t="inlineStr">
@@ -8454,13 +8458,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P144" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P144" s="2" t="n"/>
       <c r="Q144" s="2" t="n"/>
-      <c r="R144" s="2" t="n"/>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S144" s="2" t="n"/>
       <c r="T144" s="2" t="n"/>
       <c r="U144" s="2" t="n"/>
@@ -8490,24 +8494,24 @@
       <c r="F145" s="4" t="n"/>
       <c r="G145" s="4" t="n"/>
       <c r="H145" s="4" t="n"/>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I145" s="4" t="n"/>
       <c r="J145" s="4" t="n"/>
-      <c r="K145" s="4" t="n"/>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
       <c r="O145" s="4" t="n"/>
-      <c r="P145" s="4" t="inlineStr">
+      <c r="P145" s="4" t="n"/>
+      <c r="Q145" s="4" t="n"/>
+      <c r="R145" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q145" s="4" t="n"/>
-      <c r="R145" s="4" t="n"/>
       <c r="S145" s="4" t="n"/>
       <c r="T145" s="4" t="n"/>
       <c r="U145" s="4" t="n"/>
@@ -8537,17 +8541,13 @@
       <c r="F146" s="2" t="n"/>
       <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>education process</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="2" t="n"/>
       <c r="N146" s="2" t="inlineStr">
@@ -8562,11 +8562,15 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>education process</t>
         </is>
       </c>
       <c r="Q146" s="2" t="n"/>
-      <c r="R146" s="2" t="n"/>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S146" s="2" t="n"/>
       <c r="T146" s="2" t="n"/>
       <c r="U146" s="2" t="n"/>
@@ -8596,13 +8600,13 @@
       <c r="F147" s="2" t="n"/>
       <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="n"/>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I147" s="2" t="n"/>
       <c r="J147" s="2" t="n"/>
-      <c r="K147" s="2" t="n"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L147" s="2" t="n"/>
       <c r="M147" s="2" t="n"/>
       <c r="N147" s="2" t="inlineStr">
@@ -8615,13 +8619,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P147" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P147" s="2" t="n"/>
       <c r="Q147" s="2" t="n"/>
-      <c r="R147" s="2" t="n"/>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S147" s="2" t="n"/>
       <c r="T147" s="2" t="n"/>
       <c r="U147" s="2" t="n"/>
@@ -8651,13 +8655,13 @@
       <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I148" s="2" t="n"/>
       <c r="J148" s="2" t="n"/>
-      <c r="K148" s="2" t="n"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="2" t="n"/>
       <c r="N148" s="2" t="inlineStr">
@@ -8670,13 +8674,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P148" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P148" s="2" t="n"/>
       <c r="Q148" s="2" t="n"/>
-      <c r="R148" s="2" t="n"/>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S148" s="2" t="n"/>
       <c r="T148" s="2" t="n"/>
       <c r="U148" s="2" t="n"/>
@@ -8710,13 +8714,13 @@
       </c>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I149" s="2" t="n"/>
       <c r="J149" s="2" t="n"/>
-      <c r="K149" s="2" t="n"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="2" t="n"/>
       <c r="N149" s="2" t="inlineStr">
@@ -8729,13 +8733,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P149" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P149" s="2" t="n"/>
       <c r="Q149" s="2" t="n"/>
-      <c r="R149" s="2" t="n"/>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S149" s="2" t="n"/>
       <c r="T149" s="2" t="n"/>
       <c r="U149" s="2" t="n"/>
@@ -8765,13 +8769,13 @@
       <c r="F150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I150" s="2" t="n"/>
       <c r="J150" s="2" t="n"/>
-      <c r="K150" s="2" t="n"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
       <c r="N150" s="2" t="inlineStr">
@@ -8784,13 +8788,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P150" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P150" s="2" t="n"/>
       <c r="Q150" s="2" t="n"/>
-      <c r="R150" s="2" t="n"/>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S150" s="2" t="n"/>
       <c r="T150" s="2" t="n"/>
       <c r="U150" s="2" t="n"/>
@@ -8820,24 +8824,24 @@
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I151" s="2" t="n"/>
       <c r="J151" s="2" t="n"/>
-      <c r="K151" s="2" t="n"/>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L151" s="2" t="n"/>
       <c r="M151" s="2" t="n"/>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="2" t="n"/>
-      <c r="P151" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P151" s="2" t="n"/>
       <c r="Q151" s="2" t="n"/>
-      <c r="R151" s="2" t="n"/>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S151" s="2" t="n"/>
       <c r="T151" s="2" t="n"/>
       <c r="U151" s="2" t="n"/>
@@ -8867,13 +8871,13 @@
       <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I152" s="2" t="n"/>
       <c r="J152" s="2" t="n"/>
-      <c r="K152" s="2" t="n"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L152" s="2" t="n"/>
       <c r="M152" s="2" t="n"/>
       <c r="N152" s="2" t="inlineStr">
@@ -8886,13 +8890,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P152" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P152" s="2" t="n"/>
       <c r="Q152" s="2" t="n"/>
-      <c r="R152" s="2" t="n"/>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S152" s="2" t="n"/>
       <c r="T152" s="2" t="n"/>
       <c r="U152" s="2" t="n"/>
@@ -8925,20 +8929,20 @@
           <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H153" s="2" t="n"/>
+      <c r="I153" s="2" t="n"/>
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n"/>
-      <c r="K153" s="2" t="n"/>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L153" s="2" t="n"/>
-      <c r="M153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="n"/>
       <c r="N153" s="2" t="inlineStr">
         <is>
           <t>people</t>
@@ -8949,13 +8953,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P153" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="Q153" s="2" t="inlineStr"/>
-      <c r="R153" s="2" t="n"/>
+      <c r="P153" s="2" t="n"/>
+      <c r="Q153" s="2" t="n"/>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S153" s="2" t="n"/>
       <c r="T153" s="2" t="n"/>
       <c r="U153" s="2" t="n"/>
@@ -8985,13 +8989,13 @@
       <c r="F154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I154" s="2" t="n"/>
       <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="n"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
       <c r="N154" s="2" t="inlineStr">
@@ -9005,13 +9009,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P154" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P154" s="2" t="n"/>
       <c r="Q154" s="2" t="n"/>
-      <c r="R154" s="2" t="n"/>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S154" s="2" t="n"/>
       <c r="T154" s="2" t="n"/>
       <c r="U154" s="2" t="n"/>
@@ -9045,13 +9049,13 @@
         </is>
       </c>
       <c r="H155" s="2" t="n"/>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I155" s="2" t="n"/>
       <c r="J155" s="2" t="n"/>
-      <c r="K155" s="2" t="n"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="inlineStr">
@@ -9064,13 +9068,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P155" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P155" s="2" t="n"/>
       <c r="Q155" s="2" t="n"/>
-      <c r="R155" s="2" t="n"/>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S155" s="2" t="n"/>
       <c r="T155" s="2" t="n"/>
       <c r="U155" s="2" t="n"/>
@@ -9099,18 +9103,18 @@
       <c r="E156" s="2" t="n"/>
       <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A person can hold a parental role in a child's life without being that child's biological or legal parent. </t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n"/>
-      <c r="K156" s="2" t="n"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
       <c r="N156" s="2" t="inlineStr">
@@ -9123,13 +9127,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P156" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P156" s="2" t="n"/>
       <c r="Q156" s="2" t="n"/>
-      <c r="R156" s="2" t="n"/>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S156" s="2" t="n"/>
       <c r="T156" s="2" t="n"/>
       <c r="U156" s="2" t="n"/>
@@ -9159,13 +9163,13 @@
       <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I157" s="2" t="n"/>
       <c r="J157" s="2" t="n"/>
-      <c r="K157" s="2" t="n"/>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n"/>
       <c r="N157" s="2" t="inlineStr">
@@ -9178,13 +9182,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P157" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P157" s="2" t="n"/>
       <c r="Q157" s="2" t="n"/>
-      <c r="R157" s="2" t="n"/>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S157" s="2" t="n"/>
       <c r="T157" s="2" t="n"/>
       <c r="U157" s="2" t="n"/>
@@ -9214,24 +9218,24 @@
       <c r="F158" s="2" t="n"/>
       <c r="G158" s="2" t="n"/>
       <c r="H158" s="2" t="n"/>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I158" s="2" t="n"/>
       <c r="J158" s="2" t="n"/>
-      <c r="K158" s="2" t="n"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L158" s="2" t="n"/>
       <c r="M158" s="2" t="n"/>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="2" t="n"/>
-      <c r="P158" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P158" s="2" t="n"/>
       <c r="Q158" s="2" t="n"/>
-      <c r="R158" s="2" t="n"/>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S158" s="2" t="n"/>
       <c r="T158" s="2" t="n"/>
       <c r="U158" s="2" t="n"/>
@@ -9257,7 +9261,7 @@
           <t>role</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -9272,7 +9276,7 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
+      <c r="R159" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -9304,24 +9308,24 @@
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I160" s="4" t="n"/>
       <c r="J160" s="4" t="n"/>
-      <c r="K160" s="4" t="n"/>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
       <c r="O160" s="4" t="n"/>
-      <c r="P160" s="4" t="inlineStr">
+      <c r="P160" s="4" t="n"/>
+      <c r="Q160" s="4" t="n"/>
+      <c r="R160" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q160" s="4" t="n"/>
-      <c r="R160" s="4" t="n"/>
       <c r="S160" s="4" t="n"/>
       <c r="T160" s="4" t="n"/>
       <c r="U160" s="4" t="n"/>
@@ -9347,12 +9351,12 @@
           <t>extended organism</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -9383,24 +9387,24 @@
       <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I162" s="2" t="n"/>
       <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="n"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="2" t="n"/>
-      <c r="P162" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P162" s="2" t="n"/>
       <c r="Q162" s="2" t="n"/>
-      <c r="R162" s="2" t="n"/>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S162" s="2" t="n"/>
       <c r="T162" s="2" t="n"/>
       <c r="U162" s="2" t="n"/>
@@ -9429,33 +9433,33 @@
       <c r="E163" s="2" t="n"/>
       <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H163" s="2" t="n"/>
+      <c r="I163" s="2" t="n"/>
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Attributes included under this header are age, immigration, social and economic conditions. </t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n"/>
       <c r="K163" s="2" t="inlineStr">
         <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
           <t>person</t>
         </is>
       </c>
-      <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="2" t="n"/>
-      <c r="P163" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P163" s="2" t="n"/>
       <c r="Q163" s="2" t="n"/>
-      <c r="R163" s="2" t="n"/>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S163" s="2" t="n"/>
       <c r="T163" s="2" t="n"/>
       <c r="U163" s="2" t="n"/>
@@ -9481,25 +9485,25 @@
           <t>bodily disposition</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>The ability of someone to perform some useful and/or beneficial activity.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
         <is>
           <t>The phrase 'ordinarily brings benefits to an organism or group of organism' is used to explain that capabilities normally provide a benefit. 
 For instance, having a musical ability is ordinarily an ability that is positive for a person (e.g., they receive positive feedback about their ability). However, in certain exceptional cases (e.g., a neighbour becoming annoyed with a person playing the piano and expressing this annoyance), the ability might not bring benefits.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>The ability of someone to perform some useful and/or beneficial activity.</t>
         </is>
       </c>
     </row>
@@ -9528,24 +9532,24 @@
       <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I165" s="2" t="n"/>
       <c r="J165" s="2" t="n"/>
-      <c r="K165" s="2" t="n"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n"/>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="2" t="n"/>
-      <c r="P165" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P165" s="2" t="n"/>
       <c r="Q165" s="2" t="n"/>
-      <c r="R165" s="2" t="n"/>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S165" s="2" t="n"/>
       <c r="T165" s="2" t="n"/>
       <c r="U165" s="2" t="n"/>
@@ -9575,13 +9579,13 @@
       <c r="F166" s="2" t="n"/>
       <c r="G166" s="2" t="n"/>
       <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I166" s="2" t="n"/>
       <c r="J166" s="2" t="n"/>
-      <c r="K166" s="2" t="n"/>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L166" s="2" t="n"/>
       <c r="M166" s="2" t="n"/>
       <c r="N166" s="2" t="inlineStr">
@@ -9594,13 +9598,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P166" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P166" s="2" t="n"/>
       <c r="Q166" s="2" t="n"/>
-      <c r="R166" s="2" t="n"/>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S166" s="2" t="n"/>
       <c r="T166" s="2" t="n"/>
       <c r="U166" s="2" t="n"/>
@@ -9630,13 +9634,13 @@
       <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I167" s="2" t="n"/>
       <c r="J167" s="2" t="n"/>
-      <c r="K167" s="2" t="n"/>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="2" t="n"/>
       <c r="N167" s="2" t="inlineStr">
@@ -9649,13 +9653,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P167" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P167" s="2" t="n"/>
       <c r="Q167" s="2" t="n"/>
-      <c r="R167" s="2" t="n"/>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S167" s="2" t="n"/>
       <c r="T167" s="2" t="n"/>
       <c r="U167" s="2" t="n"/>
@@ -9685,13 +9689,13 @@
       <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I168" s="2" t="n"/>
       <c r="J168" s="2" t="n"/>
-      <c r="K168" s="2" t="n"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="2" t="n"/>
       <c r="N168" s="2" t="inlineStr">
@@ -9704,13 +9708,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P168" s="2" t="n"/>
       <c r="Q168" s="2" t="n"/>
-      <c r="R168" s="2" t="n"/>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S168" s="2" t="n"/>
       <c r="T168" s="2" t="n"/>
       <c r="U168" s="2" t="n"/>
@@ -9740,13 +9744,13 @@
       <c r="F169" s="2" t="n"/>
       <c r="G169" s="2" t="n"/>
       <c r="H169" s="2" t="n"/>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I169" s="2" t="n"/>
       <c r="J169" s="2" t="n"/>
-      <c r="K169" s="2" t="n"/>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L169" s="2" t="n"/>
       <c r="M169" s="2" t="n"/>
       <c r="N169" s="2" t="inlineStr">
@@ -9759,13 +9763,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P169" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P169" s="2" t="n"/>
       <c r="Q169" s="2" t="n"/>
-      <c r="R169" s="2" t="n"/>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S169" s="2" t="n"/>
       <c r="T169" s="2" t="n"/>
       <c r="U169" s="2" t="n"/>
@@ -9794,18 +9798,18 @@
       <c r="E170" s="2" t="n"/>
       <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H170" s="2" t="n"/>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>This is a fuzzy class.  Users will need to specify exactly how similar an intervention needs to be to qualify as "the same" as the current intervention in their context.</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n"/>
-      <c r="K170" s="2" t="n"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L170" s="2" t="n"/>
       <c r="M170" s="2" t="n"/>
       <c r="N170" s="2" t="inlineStr">
@@ -9818,13 +9822,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P170" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P170" s="2" t="n"/>
       <c r="Q170" s="2" t="n"/>
-      <c r="R170" s="2" t="n"/>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S170" s="2" t="n"/>
       <c r="T170" s="2" t="n"/>
       <c r="U170" s="2" t="n"/>
@@ -9850,33 +9854,33 @@
           <t>process</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n"/>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>'process' and 'part of' some 'personal history'</t>
+        </is>
+      </c>
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I171" s="2" t="n"/>
       <c r="J171" s="2" t="n"/>
-      <c r="K171" s="2" t="n"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n"/>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="2" t="n"/>
-      <c r="P171" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P171" s="2" t="n"/>
       <c r="Q171" s="2" t="n"/>
-      <c r="R171" s="2" t="n"/>
-      <c r="S171" s="2" t="inlineStr">
-        <is>
-          <t>'process' and 'part of' some 'personal history'</t>
-        </is>
-      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="n"/>
       <c r="T171" s="2" t="n"/>
       <c r="U171" s="2" t="n"/>
     </row>
@@ -9905,13 +9909,13 @@
       <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I172" s="2" t="n"/>
       <c r="J172" s="2" t="n"/>
-      <c r="K172" s="2" t="n"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L172" s="2" t="n"/>
       <c r="M172" s="2" t="n"/>
       <c r="N172" s="2" t="inlineStr">
@@ -9924,13 +9928,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P172" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P172" s="2" t="n"/>
       <c r="Q172" s="2" t="n"/>
-      <c r="R172" s="2" t="n"/>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S172" s="2" t="n"/>
       <c r="T172" s="2" t="n"/>
       <c r="U172" s="2" t="n"/>
@@ -9964,13 +9968,13 @@
       </c>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I173" s="2" t="n"/>
       <c r="J173" s="2" t="n"/>
-      <c r="K173" s="2" t="n"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L173" s="2" t="n"/>
       <c r="M173" s="2" t="n"/>
       <c r="N173" s="2" t="inlineStr">
@@ -9983,13 +9987,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P173" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P173" s="2" t="n"/>
       <c r="Q173" s="2" t="n"/>
-      <c r="R173" s="2" t="n"/>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S173" s="2" t="n"/>
       <c r="T173" s="2" t="n"/>
       <c r="U173" s="2" t="n"/>
@@ -10018,31 +10022,31 @@
       <c r="E174" s="2" t="n"/>
       <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H174" s="2" t="n"/>
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n"/>
-      <c r="K174" s="2" t="n"/>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="2" t="n"/>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="2" t="n"/>
-      <c r="P174" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P174" s="2" t="n"/>
       <c r="Q174" s="2" t="n"/>
       <c r="R174" s="2" t="inlineStr">
         <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="S174" s="2" t="n"/>
@@ -10078,13 +10082,13 @@
       </c>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I175" s="2" t="n"/>
       <c r="J175" s="2" t="n"/>
-      <c r="K175" s="2" t="n"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="2" t="n"/>
       <c r="N175" s="2" t="inlineStr">
@@ -10097,13 +10101,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P175" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P175" s="2" t="n"/>
       <c r="Q175" s="2" t="n"/>
-      <c r="R175" s="2" t="n"/>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S175" s="2" t="n"/>
       <c r="T175" s="2" t="n"/>
       <c r="U175" s="2" t="n"/>
@@ -10129,21 +10133,21 @@
           <t>personal vulnerability</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>risk factor for harmful behaviour</t>
-        </is>
-      </c>
+      <c r="E176" s="2" t="n"/>
       <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
-      <c r="H176" s="2" t="n"/>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>risk factor for harmful behaviour</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n"/>
       <c r="J176" s="2" t="n"/>
-      <c r="K176" s="2" t="n"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="2" t="n"/>
       <c r="N176" s="2" t="inlineStr">
@@ -10156,13 +10160,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P176" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P176" s="2" t="n"/>
       <c r="Q176" s="2" t="n"/>
-      <c r="R176" s="2" t="n"/>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S176" s="2" t="n"/>
       <c r="T176" s="2" t="n"/>
       <c r="U176" s="2" t="n"/>
@@ -10192,13 +10196,13 @@
       <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I177" s="2" t="n"/>
       <c r="J177" s="2" t="n"/>
-      <c r="K177" s="2" t="n"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L177" s="2" t="n"/>
       <c r="M177" s="2" t="n"/>
       <c r="N177" s="2" t="inlineStr">
@@ -10211,13 +10215,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P177" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P177" s="2" t="n"/>
       <c r="Q177" s="2" t="n"/>
-      <c r="R177" s="2" t="n"/>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S177" s="2" t="n"/>
       <c r="T177" s="2" t="n"/>
       <c r="U177" s="2" t="n"/>
@@ -10243,7 +10247,7 @@
           <t>insured party role</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -10258,7 +10262,7 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P178" t="inlineStr">
+      <c r="R178" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -10301,13 +10305,13 @@
       <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="n"/>
-      <c r="P179" s="4" t="inlineStr">
+      <c r="P179" s="4" t="n"/>
+      <c r="Q179" s="4" t="n"/>
+      <c r="R179" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="Q179" s="4" t="n"/>
-      <c r="R179" s="4" t="n"/>
       <c r="S179" s="4" t="n"/>
       <c r="T179" s="4" t="n"/>
       <c r="U179" s="4" t="n"/>
@@ -10337,13 +10341,13 @@
       <c r="F180" s="2" t="n"/>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I180" s="2" t="n"/>
       <c r="J180" s="2" t="n"/>
-      <c r="K180" s="2" t="n"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="2" t="n"/>
       <c r="N180" s="2" t="inlineStr">
@@ -10356,13 +10360,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P180" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P180" s="2" t="n"/>
       <c r="Q180" s="2" t="n"/>
-      <c r="R180" s="2" t="n"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S180" s="2" t="n"/>
       <c r="T180" s="2" t="n"/>
       <c r="U180" s="2" t="n"/>
@@ -10392,13 +10396,13 @@
       <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="n"/>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I181" s="2" t="n"/>
       <c r="J181" s="2" t="n"/>
-      <c r="K181" s="2" t="n"/>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="2" t="n"/>
       <c r="N181" s="2" t="inlineStr">
@@ -10411,13 +10415,13 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P181" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P181" s="2" t="n"/>
       <c r="Q181" s="2" t="n"/>
-      <c r="R181" s="2" t="n"/>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S181" s="2" t="n"/>
       <c r="T181" s="2" t="n"/>
       <c r="U181" s="2" t="n"/>
@@ -10443,12 +10447,12 @@
           <t>specifically dependent continuant</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P182" t="inlineStr">
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -10483,17 +10487,13 @@
       </c>
       <c r="G183" s="2" t="n"/>
       <c r="H183" s="2" t="n"/>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
-      <c r="K183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
+      <c r="J183" s="2" t="n"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L183" s="2" t="n"/>
       <c r="M183" s="2" t="n"/>
       <c r="N183" s="2" t="inlineStr">
@@ -10508,11 +10508,15 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>valuable material resource owned</t>
         </is>
       </c>
       <c r="Q183" s="2" t="n"/>
-      <c r="R183" s="2" t="n"/>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S183" s="2" t="n"/>
       <c r="T183" s="2" t="n"/>
       <c r="U183" s="2" t="n"/>
@@ -10546,13 +10550,13 @@
         </is>
       </c>
       <c r="H184" s="2" t="n"/>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I184" s="2" t="n"/>
       <c r="J184" s="2" t="n"/>
-      <c r="K184" s="2" t="n"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L184" s="2" t="n"/>
       <c r="M184" s="2" t="n"/>
       <c r="N184" s="2" t="inlineStr">
@@ -10565,13 +10569,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P184" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P184" s="2" t="n"/>
       <c r="Q184" s="2" t="n"/>
-      <c r="R184" s="2" t="n"/>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S184" s="2" t="n"/>
       <c r="T184" s="2" t="n"/>
       <c r="U184" s="2" t="n"/>
@@ -10605,13 +10609,13 @@
         </is>
       </c>
       <c r="H185" s="2" t="n"/>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I185" s="2" t="n"/>
       <c r="J185" s="2" t="n"/>
-      <c r="K185" s="2" t="n"/>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L185" s="2" t="n"/>
       <c r="M185" s="2" t="n"/>
       <c r="N185" s="2" t="inlineStr">
@@ -10624,13 +10628,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P185" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P185" s="2" t="n"/>
       <c r="Q185" s="2" t="n"/>
-      <c r="R185" s="2" t="n"/>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S185" s="2" t="n"/>
       <c r="T185" s="2" t="n"/>
       <c r="U185" s="2" t="n"/>
@@ -10660,13 +10664,13 @@
       <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I186" s="2" t="n"/>
       <c r="J186" s="2" t="n"/>
-      <c r="K186" s="2" t="n"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L186" s="2" t="n"/>
       <c r="M186" s="2" t="n"/>
       <c r="N186" s="2" t="inlineStr">
@@ -10679,13 +10683,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P186" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P186" s="2" t="n"/>
       <c r="Q186" s="2" t="n"/>
-      <c r="R186" s="2" t="n"/>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S186" s="2" t="n"/>
       <c r="T186" s="2" t="n"/>
       <c r="U186" s="2" t="n"/>
@@ -10722,18 +10726,18 @@
           <t>NCIT_C103282</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H187" s="2" t="n"/>
+      <c r="I187" s="2" t="n"/>
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage belonging to a specified religious group</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="n"/>
-      <c r="K187" s="2" t="n"/>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L187" s="2" t="n"/>
       <c r="M187" s="2" t="n"/>
       <c r="N187" s="2" t="inlineStr">
@@ -10746,13 +10750,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P187" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P187" s="2" t="n"/>
       <c r="Q187" s="2" t="n"/>
-      <c r="R187" s="2" t="n"/>
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S187" s="2" t="n"/>
       <c r="T187" s="2" t="n"/>
       <c r="U187" s="2" t="n"/>
@@ -10782,13 +10786,13 @@
       <c r="F188" s="2" t="n"/>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I188" s="2" t="n"/>
       <c r="J188" s="2" t="n"/>
-      <c r="K188" s="2" t="n"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L188" s="2" t="n"/>
       <c r="M188" s="2" t="n"/>
       <c r="N188" s="2" t="inlineStr">
@@ -10801,13 +10805,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P188" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P188" s="2" t="n"/>
       <c r="Q188" s="2" t="n"/>
-      <c r="R188" s="2" t="n"/>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S188" s="2" t="n"/>
       <c r="T188" s="2" t="n"/>
       <c r="U188" s="2" t="n"/>
@@ -10841,13 +10845,13 @@
       </c>
       <c r="G189" s="2" t="n"/>
       <c r="H189" s="2" t="n"/>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I189" s="2" t="n"/>
       <c r="J189" s="2" t="n"/>
-      <c r="K189" s="2" t="n"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L189" s="2" t="n"/>
       <c r="M189" s="2" t="n"/>
       <c r="N189" s="2" t="inlineStr">
@@ -10860,13 +10864,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P189" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P189" s="2" t="n"/>
       <c r="Q189" s="2" t="n"/>
-      <c r="R189" s="2" t="n"/>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S189" s="2" t="n"/>
       <c r="T189" s="2" t="n"/>
       <c r="U189" s="2" t="n"/>
@@ -10896,13 +10900,13 @@
       <c r="F190" s="2" t="n"/>
       <c r="G190" s="2" t="n"/>
       <c r="H190" s="2" t="n"/>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I190" s="2" t="n"/>
       <c r="J190" s="2" t="n"/>
-      <c r="K190" s="2" t="n"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L190" s="2" t="n"/>
       <c r="M190" s="2" t="n"/>
       <c r="N190" s="2" t="inlineStr">
@@ -10915,13 +10919,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P190" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P190" s="2" t="n"/>
       <c r="Q190" s="2" t="n"/>
-      <c r="R190" s="2" t="n"/>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S190" s="2" t="n"/>
       <c r="T190" s="2" t="n"/>
       <c r="U190" s="2" t="n"/>
@@ -10955,13 +10959,13 @@
       </c>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I191" s="2" t="n"/>
       <c r="J191" s="2" t="n"/>
-      <c r="K191" s="2" t="n"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L191" s="2" t="n"/>
       <c r="M191" s="2" t="n"/>
       <c r="N191" s="2" t="inlineStr">
@@ -10974,13 +10978,13 @@
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P191" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P191" s="2" t="n"/>
       <c r="Q191" s="2" t="n"/>
-      <c r="R191" s="2" t="n"/>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S191" s="2" t="n"/>
       <c r="T191" s="2" t="n"/>
       <c r="U191" s="2" t="n"/>
@@ -11010,13 +11014,13 @@
       <c r="F192" s="2" t="n"/>
       <c r="G192" s="2" t="n"/>
       <c r="H192" s="2" t="n"/>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I192" s="2" t="n"/>
       <c r="J192" s="2" t="n"/>
-      <c r="K192" s="2" t="n"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L192" s="2" t="n"/>
       <c r="M192" s="2" t="n"/>
       <c r="N192" s="2" t="inlineStr">
@@ -11029,13 +11033,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P192" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P192" s="2" t="n"/>
       <c r="Q192" s="2" t="n"/>
-      <c r="R192" s="2" t="n"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S192" s="2" t="n"/>
       <c r="T192" s="2" t="n"/>
       <c r="U192" s="2" t="n"/>
@@ -11065,13 +11069,13 @@
       <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I193" s="2" t="n"/>
       <c r="J193" s="2" t="n"/>
-      <c r="K193" s="2" t="n"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L193" s="2" t="n"/>
       <c r="M193" s="2" t="n"/>
       <c r="N193" s="2" t="inlineStr">
@@ -11084,13 +11088,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P193" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P193" s="2" t="n"/>
       <c r="Q193" s="2" t="n"/>
-      <c r="R193" s="2" t="n"/>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S193" s="2" t="n"/>
       <c r="T193" s="2" t="n"/>
       <c r="U193" s="2" t="n"/>
@@ -11116,12 +11120,12 @@
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -11152,13 +11156,13 @@
       <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I195" s="2" t="n"/>
       <c r="J195" s="2" t="n"/>
-      <c r="K195" s="2" t="n"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L195" s="2" t="n"/>
       <c r="M195" s="2" t="n"/>
       <c r="N195" s="2" t="inlineStr">
@@ -11171,13 +11175,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P195" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P195" s="2" t="n"/>
       <c r="Q195" s="2" t="n"/>
-      <c r="R195" s="2" t="n"/>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S195" s="2" t="n"/>
       <c r="T195" s="2" t="n"/>
       <c r="U195" s="2" t="n"/>
@@ -11207,13 +11211,13 @@
       <c r="F196" s="2" t="n"/>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I196" s="2" t="n"/>
       <c r="J196" s="2" t="n"/>
-      <c r="K196" s="2" t="n"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="2" t="n"/>
       <c r="N196" s="2" t="inlineStr">
@@ -11226,13 +11230,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P196" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P196" s="2" t="n"/>
       <c r="Q196" s="2" t="n"/>
-      <c r="R196" s="2" t="n"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S196" s="2" t="n"/>
       <c r="T196" s="2" t="n"/>
       <c r="U196" s="2" t="n"/>
@@ -11265,18 +11269,18 @@
           <t xml:space="preserve">NCIT_C116000 </t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>employment status where the person is their own employer</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J197" s="2" t="n"/>
-      <c r="K197" s="2" t="n"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L197" s="2" t="n"/>
       <c r="M197" s="2" t="n"/>
       <c r="N197" s="2" t="inlineStr">
@@ -11289,13 +11293,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P197" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P197" s="2" t="n"/>
       <c r="Q197" s="2" t="n"/>
-      <c r="R197" s="2" t="n"/>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S197" s="2" t="n"/>
       <c r="T197" s="2" t="n"/>
       <c r="U197" s="2" t="n"/>
@@ -11321,12 +11325,12 @@
           <t>identity</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -11361,13 +11365,13 @@
         </is>
       </c>
       <c r="H199" s="2" t="n"/>
-      <c r="I199" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I199" s="2" t="n"/>
       <c r="J199" s="2" t="n"/>
-      <c r="K199" s="2" t="n"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L199" s="2" t="n"/>
       <c r="M199" s="2" t="n"/>
       <c r="N199" s="2" t="inlineStr">
@@ -11380,13 +11384,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P199" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P199" s="2" t="n"/>
       <c r="Q199" s="2" t="n"/>
-      <c r="R199" s="2" t="n"/>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S199" s="2" t="n"/>
       <c r="T199" s="2" t="n"/>
       <c r="U199" s="2" t="n"/>
@@ -11416,13 +11420,13 @@
       <c r="F200" s="2" t="n"/>
       <c r="G200" s="2" t="n"/>
       <c r="H200" s="2" t="n"/>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I200" s="2" t="n"/>
       <c r="J200" s="2" t="n"/>
-      <c r="K200" s="2" t="n"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L200" s="2" t="n"/>
       <c r="M200" s="2" t="n"/>
       <c r="N200" s="2" t="inlineStr">
@@ -11436,13 +11440,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P200" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P200" s="2" t="n"/>
       <c r="Q200" s="2" t="n"/>
-      <c r="R200" s="2" t="n"/>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S200" s="2" t="n"/>
       <c r="T200" s="2" t="n"/>
       <c r="U200" s="2" t="n"/>
@@ -11472,13 +11476,13 @@
       <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I201" s="2" t="n"/>
       <c r="J201" s="2" t="n"/>
-      <c r="K201" s="2" t="n"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L201" s="2" t="n"/>
       <c r="M201" s="2" t="n"/>
       <c r="N201" s="2" t="inlineStr">
@@ -11491,13 +11495,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P201" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P201" s="2" t="n"/>
       <c r="Q201" s="2" t="n"/>
-      <c r="R201" s="2" t="n"/>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S201" s="2" t="n"/>
       <c r="T201" s="2" t="n"/>
       <c r="U201" s="2" t="n"/>
@@ -11527,24 +11531,24 @@
       <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I202" s="2" t="n"/>
       <c r="J202" s="2" t="n"/>
-      <c r="K202" s="2" t="n"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="2" t="n"/>
       <c r="N202" s="2" t="n"/>
       <c r="O202" s="2" t="n"/>
-      <c r="P202" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P202" s="2" t="n"/>
       <c r="Q202" s="2" t="n"/>
-      <c r="R202" s="2" t="n"/>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S202" s="2" t="n"/>
       <c r="T202" s="2" t="n"/>
       <c r="U202" s="2" t="n"/>
@@ -11574,24 +11578,24 @@
       <c r="F203" s="2" t="n"/>
       <c r="G203" s="2" t="n"/>
       <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I203" s="2" t="n"/>
       <c r="J203" s="2" t="n"/>
-      <c r="K203" s="2" t="n"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L203" s="2" t="n"/>
       <c r="M203" s="2" t="n"/>
       <c r="N203" s="2" t="n"/>
       <c r="O203" s="2" t="n"/>
-      <c r="P203" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P203" s="2" t="n"/>
       <c r="Q203" s="2" t="n"/>
-      <c r="R203" s="2" t="n"/>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S203" s="2" t="n"/>
       <c r="T203" s="2" t="n"/>
       <c r="U203" s="2" t="n"/>
@@ -11620,29 +11624,29 @@
       <c r="E204" s="2" t="n"/>
       <c r="F204" s="2" t="n"/>
       <c r="G204" s="2" t="n"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>Population can be two or more people. the interaction may involve how other people treat members of the group.</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J204" s="2" t="n"/>
-      <c r="K204" s="2" t="n"/>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L204" s="2" t="n"/>
       <c r="M204" s="2" t="n"/>
       <c r="N204" s="2" t="n"/>
       <c r="O204" s="2" t="n"/>
-      <c r="P204" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P204" s="2" t="n"/>
       <c r="Q204" s="2" t="n"/>
-      <c r="R204" s="2" t="n"/>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S204" s="2" t="n"/>
       <c r="T204" s="2" t="n"/>
       <c r="U204" s="2" t="n"/>
@@ -11672,24 +11676,24 @@
       <c r="F205" s="2" t="n"/>
       <c r="G205" s="2" t="n"/>
       <c r="H205" s="2" t="n"/>
-      <c r="I205" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I205" s="2" t="n"/>
       <c r="J205" s="2" t="n"/>
-      <c r="K205" s="2" t="n"/>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L205" s="2" t="n"/>
       <c r="M205" s="2" t="n"/>
       <c r="N205" s="2" t="n"/>
       <c r="O205" s="2" t="n"/>
-      <c r="P205" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P205" s="2" t="n"/>
       <c r="Q205" s="2" t="n"/>
-      <c r="R205" s="2" t="n"/>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S205" s="2" t="n"/>
       <c r="T205" s="2" t="n"/>
       <c r="U205" s="2" t="n"/>
@@ -11718,29 +11722,29 @@
       <c r="E206" s="2" t="n"/>
       <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>This can include social history, current circumstances, age, gender identity, occupation, education level, socio-economic position (status or group), ethnicity, sexual orientation, disability</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J206" s="2" t="n"/>
-      <c r="K206" s="2" t="n"/>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L206" s="2" t="n"/>
       <c r="M206" s="2" t="n"/>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="2" t="n"/>
-      <c r="P206" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P206" s="2" t="n"/>
       <c r="Q206" s="2" t="n"/>
-      <c r="R206" s="2" t="n"/>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S206" s="2" t="n"/>
       <c r="T206" s="2" t="n"/>
       <c r="U206" s="2" t="n"/>
@@ -11766,12 +11770,12 @@
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -11806,17 +11810,13 @@
       </c>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J208" s="2" t="inlineStr">
-        <is>
-          <t>socioeconomic status</t>
-        </is>
-      </c>
-      <c r="K208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L208" s="2" t="n"/>
       <c r="M208" s="2" t="n"/>
       <c r="N208" s="2" t="inlineStr">
@@ -11831,11 +11831,15 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>socioeconomic status</t>
         </is>
       </c>
       <c r="Q208" s="2" t="n"/>
-      <c r="R208" s="2" t="n"/>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S208" s="2" t="n"/>
       <c r="T208" s="2" t="n"/>
       <c r="U208" s="2" t="n"/>
@@ -11865,17 +11869,13 @@
       <c r="F209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J209" s="2" t="inlineStr">
-        <is>
-          <t>socioeconomic status</t>
-        </is>
-      </c>
-      <c r="K209" s="2" t="n"/>
+      <c r="I209" s="2" t="n"/>
+      <c r="J209" s="2" t="n"/>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L209" s="2" t="n"/>
       <c r="M209" s="2" t="n"/>
       <c r="N209" s="2" t="inlineStr">
@@ -11890,11 +11890,15 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>socioeconomic status</t>
         </is>
       </c>
       <c r="Q209" s="2" t="n"/>
-      <c r="R209" s="2" t="n"/>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S209" s="2" t="n"/>
       <c r="T209" s="2" t="n"/>
       <c r="U209" s="2" t="n"/>
@@ -11928,13 +11932,13 @@
         </is>
       </c>
       <c r="H210" s="2" t="n"/>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I210" s="2" t="n"/>
       <c r="J210" s="2" t="n"/>
-      <c r="K210" s="2" t="n"/>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L210" s="2" t="n"/>
       <c r="M210" s="2" t="n"/>
       <c r="N210" s="2" t="inlineStr">
@@ -11947,13 +11951,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P210" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P210" s="2" t="n"/>
       <c r="Q210" s="2" t="n"/>
-      <c r="R210" s="2" t="n"/>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S210" s="2" t="n"/>
       <c r="T210" s="2" t="n"/>
       <c r="U210" s="2" t="n"/>
@@ -11987,13 +11991,13 @@
         </is>
       </c>
       <c r="H211" s="2" t="n"/>
-      <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I211" s="2" t="n"/>
       <c r="J211" s="2" t="n"/>
-      <c r="K211" s="2" t="n"/>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L211" s="2" t="n"/>
       <c r="M211" s="2" t="n"/>
       <c r="N211" s="2" t="inlineStr">
@@ -12006,13 +12010,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P211" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P211" s="2" t="n"/>
       <c r="Q211" s="2" t="n"/>
-      <c r="R211" s="2" t="n"/>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S211" s="2" t="n"/>
       <c r="T211" s="2" t="n"/>
       <c r="U211" s="2" t="n"/>
@@ -12042,13 +12046,13 @@
       <c r="F212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
-      <c r="I212" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I212" s="2" t="n"/>
       <c r="J212" s="2" t="n"/>
-      <c r="K212" s="2" t="n"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
       <c r="N212" s="2" t="inlineStr">
@@ -12061,13 +12065,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P212" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P212" s="2" t="n"/>
       <c r="Q212" s="2" t="n"/>
-      <c r="R212" s="2" t="n"/>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S212" s="2" t="n"/>
       <c r="T212" s="2" t="n"/>
       <c r="U212" s="2" t="n"/>
@@ -12097,13 +12101,13 @@
       <c r="F213" s="2" t="n"/>
       <c r="G213" s="2" t="n"/>
       <c r="H213" s="2" t="n"/>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I213" s="2" t="n"/>
       <c r="J213" s="2" t="n"/>
-      <c r="K213" s="2" t="n"/>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="2" t="n"/>
       <c r="N213" s="2" t="inlineStr">
@@ -12116,13 +12120,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P213" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P213" s="2" t="n"/>
       <c r="Q213" s="2" t="n"/>
-      <c r="R213" s="2" t="n"/>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S213" s="2" t="n"/>
       <c r="T213" s="2" t="n"/>
       <c r="U213" s="2" t="n"/>
@@ -12152,13 +12156,13 @@
       <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I214" s="2" t="n"/>
       <c r="J214" s="2" t="n"/>
-      <c r="K214" s="2" t="n"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L214" s="2" t="n"/>
       <c r="M214" s="2" t="n"/>
       <c r="N214" s="2" t="inlineStr">
@@ -12171,13 +12175,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P214" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P214" s="2" t="n"/>
       <c r="Q214" s="2" t="n"/>
-      <c r="R214" s="2" t="n"/>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S214" s="2" t="n"/>
       <c r="T214" s="2" t="n"/>
       <c r="U214" s="2" t="n"/>
@@ -12207,13 +12211,13 @@
       <c r="F215" s="2" t="n"/>
       <c r="G215" s="2" t="n"/>
       <c r="H215" s="2" t="n"/>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I215" s="2" t="n"/>
       <c r="J215" s="2" t="n"/>
-      <c r="K215" s="2" t="n"/>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L215" s="2" t="n"/>
       <c r="M215" s="2" t="n"/>
       <c r="N215" s="2" t="inlineStr">
@@ -12226,13 +12230,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P215" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P215" s="2" t="n"/>
       <c r="Q215" s="2" t="n"/>
-      <c r="R215" s="2" t="n"/>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S215" s="2" t="n"/>
       <c r="T215" s="2" t="n"/>
       <c r="U215" s="2" t="n"/>
@@ -12262,13 +12266,13 @@
       <c r="F216" s="2" t="n"/>
       <c r="G216" s="2" t="n"/>
       <c r="H216" s="2" t="n"/>
-      <c r="I216" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I216" s="2" t="n"/>
       <c r="J216" s="2" t="n"/>
-      <c r="K216" s="2" t="n"/>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L216" s="2" t="n"/>
       <c r="M216" s="2" t="n"/>
       <c r="N216" s="2" t="inlineStr">
@@ -12281,13 +12285,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P216" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P216" s="2" t="n"/>
       <c r="Q216" s="2" t="n"/>
-      <c r="R216" s="2" t="n"/>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S216" s="2" t="n"/>
       <c r="T216" s="2" t="n"/>
       <c r="U216" s="2" t="n"/>
@@ -12317,13 +12321,13 @@
       <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="n"/>
       <c r="H217" s="2" t="n"/>
-      <c r="I217" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I217" s="2" t="n"/>
       <c r="J217" s="2" t="n"/>
-      <c r="K217" s="2" t="n"/>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L217" s="2" t="n"/>
       <c r="M217" s="2" t="n"/>
       <c r="N217" s="2" t="inlineStr">
@@ -12336,13 +12340,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P217" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P217" s="2" t="n"/>
       <c r="Q217" s="2" t="n"/>
-      <c r="R217" s="2" t="n"/>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S217" s="2" t="n"/>
       <c r="T217" s="2" t="n"/>
       <c r="U217" s="2" t="n"/>
@@ -12372,13 +12376,13 @@
       <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
-      <c r="I218" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I218" s="2" t="n"/>
       <c r="J218" s="2" t="n"/>
-      <c r="K218" s="2" t="n"/>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L218" s="2" t="n"/>
       <c r="M218" s="2" t="n"/>
       <c r="N218" s="2" t="inlineStr">
@@ -12391,13 +12395,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P218" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P218" s="2" t="n"/>
       <c r="Q218" s="2" t="n"/>
-      <c r="R218" s="2" t="n"/>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S218" s="2" t="n"/>
       <c r="T218" s="2" t="n"/>
       <c r="U218" s="2" t="n"/>
@@ -12427,13 +12431,13 @@
       <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
-      <c r="I219" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I219" s="2" t="n"/>
       <c r="J219" s="2" t="n"/>
-      <c r="K219" s="2" t="n"/>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L219" s="2" t="n"/>
       <c r="M219" s="2" t="n"/>
       <c r="N219" s="2" t="inlineStr">
@@ -12446,13 +12450,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P219" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P219" s="2" t="n"/>
       <c r="Q219" s="2" t="n"/>
-      <c r="R219" s="2" t="n"/>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S219" s="2" t="n"/>
       <c r="T219" s="2" t="n"/>
       <c r="U219" s="2" t="n"/>
@@ -12482,13 +12486,13 @@
       <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
-      <c r="I220" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I220" s="2" t="n"/>
       <c r="J220" s="2" t="n"/>
-      <c r="K220" s="2" t="n"/>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L220" s="2" t="n"/>
       <c r="M220" s="2" t="n"/>
       <c r="N220" s="2" t="inlineStr">
@@ -12501,13 +12505,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P220" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P220" s="2" t="n"/>
       <c r="Q220" s="2" t="n"/>
-      <c r="R220" s="2" t="n"/>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S220" s="2" t="n"/>
       <c r="T220" s="2" t="n"/>
       <c r="U220" s="2" t="n"/>
@@ -12533,7 +12537,7 @@
           <t>person</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -12548,7 +12552,7 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr">
+      <c r="R221" t="inlineStr">
         <is>
           <t>External</t>
         </is>
@@ -12583,13 +12587,13 @@
         </is>
       </c>
       <c r="H222" s="2" t="n"/>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I222" s="2" t="n"/>
       <c r="J222" s="2" t="n"/>
-      <c r="K222" s="2" t="n"/>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L222" s="2" t="n"/>
       <c r="M222" s="2" t="n"/>
       <c r="N222" s="2" t="inlineStr">
@@ -12602,13 +12606,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P222" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P222" s="2" t="n"/>
       <c r="Q222" s="2" t="n"/>
-      <c r="R222" s="2" t="n"/>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S222" s="2" t="n"/>
       <c r="T222" s="2" t="n"/>
       <c r="U222" s="2" t="n"/>
@@ -12638,13 +12642,13 @@
       <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
-      <c r="I223" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I223" s="2" t="n"/>
       <c r="J223" s="2" t="n"/>
-      <c r="K223" s="2" t="n"/>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L223" s="2" t="n"/>
       <c r="M223" s="2" t="n"/>
       <c r="N223" s="2" t="inlineStr">
@@ -12657,13 +12661,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P223" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P223" s="2" t="n"/>
       <c r="Q223" s="2" t="n"/>
-      <c r="R223" s="2" t="n"/>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S223" s="2" t="n"/>
       <c r="T223" s="2" t="n"/>
       <c r="U223" s="2" t="n"/>
@@ -12693,13 +12697,13 @@
       <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
-      <c r="I224" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I224" s="2" t="n"/>
       <c r="J224" s="2" t="n"/>
-      <c r="K224" s="2" t="n"/>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L224" s="2" t="n"/>
       <c r="M224" s="2" t="n"/>
       <c r="N224" s="2" t="inlineStr">
@@ -12712,13 +12716,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P224" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P224" s="2" t="n"/>
       <c r="Q224" s="2" t="n"/>
-      <c r="R224" s="2" t="n"/>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S224" s="2" t="n"/>
       <c r="T224" s="2" t="n"/>
       <c r="U224" s="2" t="n"/>
@@ -12748,13 +12752,13 @@
       <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I225" s="2" t="n"/>
       <c r="J225" s="2" t="n"/>
-      <c r="K225" s="2" t="n"/>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L225" s="2" t="n"/>
       <c r="M225" s="2" t="n"/>
       <c r="N225" s="2" t="inlineStr">
@@ -12767,13 +12771,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P225" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P225" s="2" t="n"/>
       <c r="Q225" s="2" t="n"/>
-      <c r="R225" s="2" t="n"/>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S225" s="2" t="n"/>
       <c r="T225" s="2" t="n"/>
       <c r="U225" s="2" t="n"/>
@@ -12803,13 +12807,13 @@
       <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
-      <c r="I226" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I226" s="2" t="n"/>
       <c r="J226" s="2" t="n"/>
-      <c r="K226" s="2" t="n"/>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L226" s="2" t="n"/>
       <c r="M226" s="2" t="n"/>
       <c r="N226" s="2" t="inlineStr">
@@ -12822,13 +12826,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P226" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P226" s="2" t="n"/>
       <c r="Q226" s="2" t="n"/>
-      <c r="R226" s="2" t="n"/>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S226" s="2" t="n"/>
       <c r="T226" s="2" t="n"/>
       <c r="U226" s="2" t="n"/>
@@ -12858,13 +12862,13 @@
       <c r="F227" s="2" t="n"/>
       <c r="G227" s="2" t="n"/>
       <c r="H227" s="2" t="n"/>
-      <c r="I227" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I227" s="2" t="n"/>
       <c r="J227" s="2" t="n"/>
-      <c r="K227" s="2" t="n"/>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L227" s="2" t="n"/>
       <c r="M227" s="2" t="n"/>
       <c r="N227" s="2" t="inlineStr">
@@ -12877,13 +12881,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P227" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P227" s="2" t="n"/>
       <c r="Q227" s="2" t="n"/>
-      <c r="R227" s="2" t="n"/>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S227" s="2" t="n"/>
       <c r="T227" s="2" t="n"/>
       <c r="U227" s="2" t="n"/>
@@ -12917,13 +12921,13 @@
         </is>
       </c>
       <c r="H228" s="2" t="n"/>
-      <c r="I228" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I228" s="2" t="n"/>
       <c r="J228" s="2" t="n"/>
-      <c r="K228" s="2" t="n"/>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="inlineStr">
@@ -12936,13 +12940,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P228" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P228" s="2" t="n"/>
       <c r="Q228" s="2" t="n"/>
-      <c r="R228" s="2" t="n"/>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S228" s="2" t="n"/>
       <c r="T228" s="2" t="n"/>
       <c r="U228" s="2" t="n"/>
@@ -12972,13 +12976,13 @@
       <c r="F229" s="2" t="n"/>
       <c r="G229" s="2" t="n"/>
       <c r="H229" s="2" t="n"/>
-      <c r="I229" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I229" s="2" t="n"/>
       <c r="J229" s="2" t="n"/>
-      <c r="K229" s="2" t="n"/>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L229" s="2" t="n"/>
       <c r="M229" s="2" t="n"/>
       <c r="N229" s="2" t="inlineStr">
@@ -12991,13 +12995,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P229" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P229" s="2" t="n"/>
       <c r="Q229" s="2" t="n"/>
-      <c r="R229" s="2" t="n"/>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S229" s="2" t="n"/>
       <c r="T229" s="2" t="n"/>
       <c r="U229" s="2" t="n"/>
@@ -13035,24 +13039,24 @@
         </is>
       </c>
       <c r="H230" s="2" t="n"/>
-      <c r="I230" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I230" s="2" t="n"/>
       <c r="J230" s="2" t="n"/>
-      <c r="K230" s="2" t="n"/>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L230" s="2" t="n"/>
       <c r="M230" s="2" t="n"/>
       <c r="N230" s="2" t="n"/>
       <c r="O230" s="2" t="n"/>
-      <c r="P230" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P230" s="2" t="n"/>
       <c r="Q230" s="2" t="n"/>
-      <c r="R230" s="2" t="n"/>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S230" s="2" t="n"/>
       <c r="T230" s="2" t="n"/>
       <c r="U230" s="2" t="n"/>
@@ -13086,17 +13090,13 @@
       </c>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J231" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
-      <c r="K231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+      <c r="J231" s="2" t="n"/>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n"/>
       <c r="N231" s="2" t="inlineStr">
@@ -13111,11 +13111,15 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>valuable material resource owned</t>
         </is>
       </c>
       <c r="Q231" s="2" t="n"/>
-      <c r="R231" s="2" t="n"/>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S231" s="2" t="n"/>
       <c r="T231" s="2" t="n"/>
       <c r="U231" s="2" t="n"/>
@@ -13145,13 +13149,13 @@
       <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I232" s="2" t="n"/>
       <c r="J232" s="2" t="n"/>
-      <c r="K232" s="2" t="n"/>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L232" s="2" t="n"/>
       <c r="M232" s="2" t="n"/>
       <c r="N232" s="2" t="inlineStr">
@@ -13164,13 +13168,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P232" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P232" s="2" t="n"/>
       <c r="Q232" s="2" t="n"/>
-      <c r="R232" s="2" t="n"/>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S232" s="2" t="n"/>
       <c r="T232" s="2" t="n"/>
       <c r="U232" s="2" t="n"/>
@@ -13199,18 +13203,18 @@
       <c r="E233" s="2" t="n"/>
       <c r="F233" s="2" t="n"/>
       <c r="G233" s="2" t="n"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H233" s="2" t="n"/>
+      <c r="I233" s="2" t="n"/>
+      <c r="J233" s="2" t="inlineStr">
         <is>
           <t>may include unpaid internships</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="J233" s="2" t="n"/>
-      <c r="K233" s="2" t="n"/>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L233" s="2" t="n"/>
       <c r="M233" s="2" t="n"/>
       <c r="N233" s="2" t="inlineStr">
@@ -13223,13 +13227,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P233" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P233" s="2" t="n"/>
       <c r="Q233" s="2" t="n"/>
-      <c r="R233" s="2" t="n"/>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S233" s="2" t="n"/>
       <c r="T233" s="2" t="n"/>
       <c r="U233" s="2" t="n"/>
@@ -13259,13 +13263,13 @@
       <c r="F234" s="2" t="n"/>
       <c r="G234" s="2" t="n"/>
       <c r="H234" s="2" t="n"/>
-      <c r="I234" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I234" s="2" t="n"/>
       <c r="J234" s="2" t="n"/>
-      <c r="K234" s="2" t="n"/>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="L234" s="2" t="n"/>
       <c r="M234" s="2" t="n"/>
       <c r="N234" s="2" t="inlineStr">
@@ -13278,13 +13282,13 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P234" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="P234" s="2" t="n"/>
       <c r="Q234" s="2" t="n"/>
-      <c r="R234" s="2" t="n"/>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="S234" s="2" t="n"/>
       <c r="T234" s="2" t="n"/>
       <c r="U234" s="2" t="n"/>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -49,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ffffff"/>
+        <fgColor rgb="00ffe4b5"/>
       </patternFill>
     </fill>
   </fills>
@@ -3628,19 +3628,19 @@
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
       <c r="N57" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -3651,16 +3651,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr"/>
-      <c r="Q57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S57" s="4" t="inlineStr"/>
-      <c r="T57" s="4" t="inlineStr"/>
-      <c r="U57" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="n"/>
+      <c r="T57" s="4" t="n"/>
+      <c r="U57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5130,19 +5130,19 @@
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -5153,16 +5153,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P84" s="4" t="inlineStr"/>
-      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="n"/>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S84" s="4" t="inlineStr"/>
-      <c r="T84" s="4" t="inlineStr"/>
-      <c r="U84" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S84" s="4" t="n"/>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="inlineStr"/>
+      <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
@@ -5688,23 +5688,23 @@
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="inlineStr">
         <is>
           <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr"/>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -5715,16 +5715,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P94" s="4" t="inlineStr"/>
-      <c r="Q94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="n"/>
+      <c r="Q94" s="4" t="n"/>
       <c r="R94" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S94" s="4" t="inlineStr"/>
-      <c r="T94" s="4" t="inlineStr"/>
-      <c r="U94" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S94" s="4" t="n"/>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7048,19 +7048,19 @@
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
-      <c r="G119" s="4" t="inlineStr"/>
-      <c r="H119" s="4" t="inlineStr"/>
-      <c r="I119" s="4" t="inlineStr"/>
-      <c r="J119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L119" s="4" t="inlineStr"/>
-      <c r="M119" s="4" t="inlineStr"/>
+      <c r="L119" s="4" t="n"/>
+      <c r="M119" s="4" t="n"/>
       <c r="N119" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -7071,16 +7071,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P119" s="4" t="inlineStr"/>
-      <c r="Q119" s="4" t="inlineStr"/>
+      <c r="P119" s="4" t="n"/>
+      <c r="Q119" s="4" t="n"/>
       <c r="R119" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S119" s="4" t="inlineStr"/>
-      <c r="T119" s="4" t="inlineStr"/>
-      <c r="U119" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S119" s="4" t="n"/>
+      <c r="T119" s="4" t="n"/>
+      <c r="U119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="P133" s="3" t="n"/>
-      <c r="Q133" s="3" t="inlineStr"/>
+      <c r="Q133" s="3" t="n"/>
       <c r="R133" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7858,19 +7858,19 @@
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="4" t="inlineStr"/>
-      <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="4" t="inlineStr"/>
-      <c r="J134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="n"/>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="n"/>
+      <c r="J134" s="4" t="n"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="n"/>
+      <c r="M134" s="4" t="n"/>
       <c r="N134" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -7881,16 +7881,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P134" s="4" t="inlineStr"/>
-      <c r="Q134" s="4" t="inlineStr"/>
+      <c r="P134" s="4" t="n"/>
+      <c r="Q134" s="4" t="n"/>
       <c r="R134" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S134" s="4" t="inlineStr"/>
-      <c r="T134" s="4" t="inlineStr"/>
-      <c r="U134" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S134" s="4" t="n"/>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       <c r="Q150" s="4" t="n"/>
       <c r="R150" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S150" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       <c r="Q165" s="4" t="n"/>
       <c r="R165" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S165" s="4" t="n"/>
@@ -10588,7 +10588,7 @@
       <c r="Q184" s="4" t="n"/>
       <c r="R184" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S184" s="4" t="n"/>
@@ -11486,19 +11486,19 @@
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E201" s="4" t="inlineStr"/>
-      <c r="F201" s="4" t="inlineStr"/>
-      <c r="G201" s="4" t="inlineStr"/>
-      <c r="H201" s="4" t="inlineStr"/>
-      <c r="I201" s="4" t="inlineStr"/>
-      <c r="J201" s="4" t="inlineStr"/>
+      <c r="E201" s="4" t="n"/>
+      <c r="F201" s="4" t="n"/>
+      <c r="G201" s="4" t="n"/>
+      <c r="H201" s="4" t="n"/>
+      <c r="I201" s="4" t="n"/>
+      <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L201" s="4" t="inlineStr"/>
-      <c r="M201" s="4" t="inlineStr"/>
+      <c r="L201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -11509,16 +11509,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P201" s="4" t="inlineStr"/>
-      <c r="Q201" s="4" t="inlineStr"/>
+      <c r="P201" s="4" t="n"/>
+      <c r="Q201" s="4" t="n"/>
       <c r="R201" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S201" s="4" t="inlineStr"/>
-      <c r="T201" s="4" t="inlineStr"/>
-      <c r="U201" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S201" s="4" t="n"/>
+      <c r="T201" s="4" t="n"/>
+      <c r="U201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -13247,19 +13247,19 @@
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E234" s="4" t="inlineStr"/>
-      <c r="F234" s="4" t="inlineStr"/>
-      <c r="G234" s="4" t="inlineStr"/>
-      <c r="H234" s="4" t="inlineStr"/>
-      <c r="I234" s="4" t="inlineStr"/>
-      <c r="J234" s="4" t="inlineStr"/>
+      <c r="E234" s="4" t="n"/>
+      <c r="F234" s="4" t="n"/>
+      <c r="G234" s="4" t="n"/>
+      <c r="H234" s="4" t="n"/>
+      <c r="I234" s="4" t="n"/>
+      <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L234" s="4" t="inlineStr"/>
-      <c r="M234" s="4" t="inlineStr"/>
+      <c r="L234" s="4" t="n"/>
+      <c r="M234" s="4" t="n"/>
       <c r="N234" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -13270,16 +13270,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P234" s="4" t="inlineStr"/>
-      <c r="Q234" s="4" t="inlineStr"/>
+      <c r="P234" s="4" t="n"/>
+      <c r="Q234" s="4" t="n"/>
       <c r="R234" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S234" s="4" t="inlineStr"/>
-      <c r="T234" s="4" t="inlineStr"/>
-      <c r="U234" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S234" s="4" t="n"/>
+      <c r="T234" s="4" t="n"/>
+      <c r="U234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -13589,19 +13589,19 @@
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr"/>
-      <c r="F240" s="4" t="inlineStr"/>
-      <c r="G240" s="4" t="inlineStr"/>
-      <c r="H240" s="4" t="inlineStr"/>
-      <c r="I240" s="4" t="inlineStr"/>
-      <c r="J240" s="4" t="inlineStr"/>
+      <c r="E240" s="4" t="n"/>
+      <c r="F240" s="4" t="n"/>
+      <c r="G240" s="4" t="n"/>
+      <c r="H240" s="4" t="n"/>
+      <c r="I240" s="4" t="n"/>
+      <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="L240" s="4" t="inlineStr"/>
-      <c r="M240" s="4" t="inlineStr"/>
+      <c r="L240" s="4" t="n"/>
+      <c r="M240" s="4" t="n"/>
       <c r="N240" s="4" t="inlineStr">
         <is>
           <t>roles</t>
@@ -13612,16 +13612,16 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P240" s="4" t="inlineStr"/>
-      <c r="Q240" s="4" t="inlineStr"/>
+      <c r="P240" s="4" t="n"/>
+      <c r="Q240" s="4" t="n"/>
       <c r="R240" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S240" s="4" t="inlineStr"/>
-      <c r="T240" s="4" t="inlineStr"/>
-      <c r="U240" s="4" t="inlineStr"/>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S240" s="4" t="n"/>
+      <c r="T240" s="4" t="n"/>
+      <c r="U240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffe4b5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,12 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3608,59 +3602,59 @@
       <c r="U56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>BCIO:010092</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>doctoral student role</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O57" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S57" s="4" t="n"/>
-      <c r="T57" s="4" t="n"/>
-      <c r="U57" s="4" t="n"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="2" t="n"/>
+      <c r="U57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5110,59 +5104,59 @@
       <c r="U83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>BCIO:010090</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>graduate student role</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
-      <c r="J84" s="4" t="n"/>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="n"/>
-      <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O84" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n"/>
-      <c r="R84" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="n"/>
-      <c r="U84" s="4" t="n"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="n"/>
+      <c r="Q84" s="2" t="n"/>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="n"/>
+      <c r="T84" s="2" t="n"/>
+      <c r="U84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5668,63 +5662,63 @@
       <c r="U93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>BCIO:010088</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E94" s="4" t="n"/>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="n"/>
-      <c r="I94" s="4" t="n"/>
-      <c r="J94" s="4" t="n"/>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="n"/>
-      <c r="M94" s="4" t="n"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O94" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P94" s="4" t="n"/>
-      <c r="Q94" s="4" t="n"/>
-      <c r="R94" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S94" s="4" t="n"/>
-      <c r="T94" s="4" t="n"/>
-      <c r="U94" s="4" t="n"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n"/>
+      <c r="Q94" s="2" t="n"/>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="n"/>
+      <c r="T94" s="2" t="n"/>
+      <c r="U94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7028,59 +7022,59 @@
       <c r="U118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>BCIO:010085</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>informal education student role</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="4" t="n"/>
-      <c r="I119" s="4" t="n"/>
-      <c r="J119" s="4" t="n"/>
-      <c r="K119" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L119" s="4" t="n"/>
-      <c r="M119" s="4" t="n"/>
-      <c r="N119" s="4" t="inlineStr">
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="2" t="n"/>
+      <c r="N119" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O119" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P119" s="4" t="n"/>
-      <c r="Q119" s="4" t="n"/>
-      <c r="R119" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S119" s="4" t="n"/>
-      <c r="T119" s="4" t="n"/>
-      <c r="U119" s="4" t="n"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="n"/>
+      <c r="Q119" s="2" t="n"/>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="n"/>
+      <c r="T119" s="2" t="n"/>
+      <c r="U119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7838,59 +7832,59 @@
       <c r="U133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>BCIO:010091</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>masters student role</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
-      <c r="I134" s="4" t="n"/>
-      <c r="J134" s="4" t="n"/>
-      <c r="K134" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L134" s="4" t="n"/>
-      <c r="M134" s="4" t="n"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O134" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P134" s="4" t="n"/>
-      <c r="Q134" s="4" t="n"/>
-      <c r="R134" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S134" s="4" t="n"/>
-      <c r="T134" s="4" t="n"/>
-      <c r="U134" s="4" t="n"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="n"/>
+      <c r="Q134" s="2" t="n"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="n"/>
+      <c r="T134" s="2" t="n"/>
+      <c r="U134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8749,51 +8743,51 @@
       <c r="U149" s="2" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>BCIO:050976</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>number of people in a population</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="n"/>
-      <c r="I150" s="4" t="n"/>
-      <c r="J150" s="4" t="n"/>
-      <c r="K150" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L150" s="4" t="n"/>
-      <c r="M150" s="4" t="n"/>
-      <c r="N150" s="4" t="n"/>
-      <c r="O150" s="4" t="n"/>
-      <c r="P150" s="4" t="n"/>
-      <c r="Q150" s="4" t="n"/>
-      <c r="R150" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S150" s="4" t="n"/>
-      <c r="T150" s="4" t="n"/>
-      <c r="U150" s="4" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="2" t="n"/>
+      <c r="N150" s="2" t="n"/>
+      <c r="O150" s="2" t="n"/>
+      <c r="P150" s="2" t="n"/>
+      <c r="Q150" s="2" t="n"/>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="n"/>
+      <c r="T150" s="2" t="n"/>
+      <c r="U150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9562,52 +9556,52 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BCIO:050975
 </t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>people with intervention source role</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="4" t="n"/>
-      <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="n"/>
-      <c r="I165" s="4" t="n"/>
-      <c r="J165" s="4" t="n"/>
-      <c r="K165" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L165" s="4" t="n"/>
-      <c r="M165" s="4" t="n"/>
-      <c r="N165" s="4" t="n"/>
-      <c r="O165" s="4" t="n"/>
-      <c r="P165" s="4" t="n"/>
-      <c r="Q165" s="4" t="n"/>
-      <c r="R165" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S165" s="4" t="n"/>
-      <c r="T165" s="4" t="n"/>
-      <c r="U165" s="4" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="n"/>
+      <c r="I165" s="2" t="n"/>
+      <c r="J165" s="2" t="n"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n"/>
+      <c r="M165" s="2" t="n"/>
+      <c r="N165" s="2" t="n"/>
+      <c r="O165" s="2" t="n"/>
+      <c r="P165" s="2" t="n"/>
+      <c r="Q165" s="2" t="n"/>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="n"/>
+      <c r="T165" s="2" t="n"/>
+      <c r="U165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10548,52 +10542,52 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>BCIO:050978</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>population statistic</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E184" s="4" t="n"/>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n"/>
-      <c r="H184" s="4" t="n"/>
-      <c r="I184" s="4" t="n"/>
-      <c r="J184" s="4" t="n"/>
-      <c r="K184" s="4" t="n"/>
-      <c r="L184" s="4" t="n"/>
-      <c r="M184" s="4" t="n"/>
-      <c r="N184" s="4" t="n"/>
-      <c r="O184" s="4" t="n"/>
-      <c r="P184" s="4" t="n"/>
-      <c r="Q184" s="4" t="n"/>
-      <c r="R184" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S184" s="4" t="n"/>
-      <c r="T184" s="4" t="n"/>
-      <c r="U184" s="4" t="n"/>
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+      <c r="J184" s="2" t="n"/>
+      <c r="K184" s="2" t="n"/>
+      <c r="L184" s="2" t="n"/>
+      <c r="M184" s="2" t="n"/>
+      <c r="N184" s="2" t="n"/>
+      <c r="O184" s="2" t="n"/>
+      <c r="P184" s="2" t="n"/>
+      <c r="Q184" s="2" t="n"/>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="n"/>
+      <c r="T184" s="2" t="n"/>
+      <c r="U184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11466,59 +11460,59 @@
       <c r="U200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>BCIO:010086</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>school student role</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D201" s="4" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E201" s="4" t="n"/>
-      <c r="F201" s="4" t="n"/>
-      <c r="G201" s="4" t="n"/>
-      <c r="H201" s="4" t="n"/>
-      <c r="I201" s="4" t="n"/>
-      <c r="J201" s="4" t="n"/>
-      <c r="K201" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L201" s="4" t="n"/>
-      <c r="M201" s="4" t="n"/>
-      <c r="N201" s="4" t="inlineStr">
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="n"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="n"/>
+      <c r="M201" s="2" t="n"/>
+      <c r="N201" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O201" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P201" s="4" t="n"/>
-      <c r="Q201" s="4" t="n"/>
-      <c r="R201" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S201" s="4" t="n"/>
-      <c r="T201" s="4" t="n"/>
-      <c r="U201" s="4" t="n"/>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="n"/>
+      <c r="Q201" s="2" t="n"/>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="n"/>
+      <c r="T201" s="2" t="n"/>
+      <c r="U201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -13227,59 +13221,59 @@
       <c r="U233" s="3" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>BCIO:010089</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>undergraduate student role</t>
         </is>
       </c>
-      <c r="C234" s="4" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D234" s="4" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E234" s="4" t="n"/>
-      <c r="F234" s="4" t="n"/>
-      <c r="G234" s="4" t="n"/>
-      <c r="H234" s="4" t="n"/>
-      <c r="I234" s="4" t="n"/>
-      <c r="J234" s="4" t="n"/>
-      <c r="K234" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L234" s="4" t="n"/>
-      <c r="M234" s="4" t="n"/>
-      <c r="N234" s="4" t="inlineStr">
+      <c r="E234" s="2" t="n"/>
+      <c r="F234" s="2" t="n"/>
+      <c r="G234" s="2" t="n"/>
+      <c r="H234" s="2" t="n"/>
+      <c r="I234" s="2" t="n"/>
+      <c r="J234" s="2" t="n"/>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="n"/>
+      <c r="M234" s="2" t="n"/>
+      <c r="N234" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O234" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P234" s="4" t="n"/>
-      <c r="Q234" s="4" t="n"/>
-      <c r="R234" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S234" s="4" t="n"/>
-      <c r="T234" s="4" t="n"/>
-      <c r="U234" s="4" t="n"/>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="n"/>
+      <c r="Q234" s="2" t="n"/>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="n"/>
+      <c r="T234" s="2" t="n"/>
+      <c r="U234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -13569,59 +13563,59 @@
       <c r="U239" s="3" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="4" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>BCIO:010087</t>
         </is>
       </c>
-      <c r="B240" s="4" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>vocational training student or trainee role</t>
         </is>
       </c>
-      <c r="C240" s="4" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D240" s="4" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E240" s="4" t="n"/>
-      <c r="F240" s="4" t="n"/>
-      <c r="G240" s="4" t="n"/>
-      <c r="H240" s="4" t="n"/>
-      <c r="I240" s="4" t="n"/>
-      <c r="J240" s="4" t="n"/>
-      <c r="K240" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L240" s="4" t="n"/>
-      <c r="M240" s="4" t="n"/>
-      <c r="N240" s="4" t="inlineStr">
+      <c r="E240" s="2" t="n"/>
+      <c r="F240" s="2" t="n"/>
+      <c r="G240" s="2" t="n"/>
+      <c r="H240" s="2" t="n"/>
+      <c r="I240" s="2" t="n"/>
+      <c r="J240" s="2" t="n"/>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="n"/>
+      <c r="M240" s="2" t="n"/>
+      <c r="N240" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O240" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P240" s="4" t="n"/>
-      <c r="Q240" s="4" t="n"/>
-      <c r="R240" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S240" s="4" t="n"/>
-      <c r="T240" s="4" t="n"/>
-      <c r="U240" s="4" t="n"/>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="n"/>
+      <c r="Q240" s="2" t="n"/>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="n"/>
+      <c r="T240" s="2" t="n"/>
+      <c r="U240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="n"/>
+      <c r="U6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>A data item that is about the rate at which a population changes their behaviour.</t>
+          <t>A data item that is about the rate of individual human behaviour change.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2056,8 +2056,16 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="inlineStr">
@@ -3016,7 +3024,7 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P46" s="2" t="n"/>
+      <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3346,7 @@
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="inlineStr">
@@ -3359,7 +3367,7 @@
         </is>
       </c>
       <c r="P52" s="2" t="n"/>
-      <c r="Q52" s="2" t="n"/>
+      <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4181,7 +4189,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute that is the extent to which the person’s past behaviour has reached or exceeded a standard.</t>
+          <t>A data item that is the extent to which the person’s past behaviour has reached or exceeded a standard.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4201,9 +4209,17 @@
         </is>
       </c>
       <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="inlineStr">
@@ -6199,7 +6215,7 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P103" s="2" t="n"/>
+      <c r="P103" s="2" t="inlineStr"/>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="inlineStr">
         <is>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -451,17 +451,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Logical definition</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Examples</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -558,15 +558,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Comprehend the German language</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Comprehend the German language</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
@@ -617,15 +617,15 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>The exclusion criteria were an inability to read English</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>The exclusion criteria were an inability to read English</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
@@ -676,15 +676,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Able to speak Chinese.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Able to speak Chinese.</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
@@ -735,15 +735,15 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Fluency in written English.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Fluency in written English.</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
@@ -792,12 +792,12 @@
           <t>A highest level of formal education qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in a specialised discipline that culminated in the award of an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -855,12 +855,12 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process devoted to advanced study and original research that led to the award of a PhD or equivalent level qualification. </t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
@@ -914,12 +914,12 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process intended to introduce very young children to a school-type environment. </t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
@@ -973,12 +973,12 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in subject areas more specialised than basic reading, writing and mathematics, with the overall goal of laying the foundation for lifelong learning and human development on which education systems may systematically expand further educational opportunities.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process which has as a prerequisite an undergraduate degree and which is intended to result in the acquisition and development of advanced academic or professional skills and knowledge in a specialised discipline, that culminated in the award of a Master's or equivalent degree.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
@@ -1095,12 +1095,12 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition of fundamental skills in reading, writing and mathematics.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1160,15 +1160,15 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>graduated high school, International Baccaulaureate, A Levels</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>graduated high school, International Baccaulaureate, A Levels</t>
-        </is>
-      </c>
+      <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002040</t>
@@ -1225,12 +1225,12 @@
           <t>An adoptive sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>adoptive sibling</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
@@ -1280,12 +1280,12 @@
           <t xml:space="preserve">A child relation in a parent-child relationship established by a legal adoption process. </t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
           <t>An adoptive child who is female gender.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>adoptive child</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
@@ -1394,12 +1394,12 @@
           <t>An adoptive parent who is male gender.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>adoptive parent</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
@@ -1449,12 +1449,12 @@
           <t>An adoptive parent who is female gender.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>adoptive parent</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1504,12 +1504,12 @@
           <t>A parent in a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1563,12 +1563,12 @@
           <t>A sibling with whom the subject shares a parent through a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
@@ -1618,12 +1618,12 @@
           <t>An adoptive sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>adoptive sibling</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
@@ -1673,12 +1673,12 @@
           <t>An adoptive child who is male gender.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>adoptive child</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
           <t>A person who has reached maturity.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -1775,12 +1775,12 @@
           <t>A rent-free occupier who lives in the residential facility with the agreement of the residential facility owner.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>rent-free occupier</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
@@ -1830,12 +1830,12 @@
           <t xml:space="preserve">A sexual orientation of an individual who does not experience sexual attraction. </t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1889,12 +1889,12 @@
           <t>A family member who is the sister of one's parent.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
@@ -1944,12 +1944,12 @@
           <t>An intervention participant who is exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>intervention participant</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
@@ -1995,12 +1995,12 @@
           <t>An intervention population who are exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>intervention population</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
@@ -2042,12 +2042,12 @@
           <t>A data item that is about the rate of individual human behaviour change.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
@@ -2093,12 +2093,12 @@
           <t>A person who has formed an intention to enact a specified behaviour, and has enacted that behaviour.</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
@@ -2117,7 +2117,11 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="inlineStr">
@@ -2145,12 +2149,12 @@
           <t>A person who has formed an intention to enact a specified behaviour, but has not acted on this intention.</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
@@ -2165,7 +2169,11 @@
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="inlineStr">
@@ -2193,12 +2201,12 @@
           <t>A person who has not formed an intention to enact a specified behaviour.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">person </t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
@@ -2213,7 +2221,11 @@
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="inlineStr">
@@ -2241,12 +2253,12 @@
           <t xml:space="preserve">A data item that is about the number of times a behaviour occurs in a time period. </t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
@@ -2263,8 +2275,16 @@
       </c>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
@@ -2292,12 +2312,12 @@
           <t>A biological sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>biological sibling</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
@@ -2347,12 +2367,12 @@
           <t>A child relation who is genetically related to their parent.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
@@ -2402,12 +2422,12 @@
           <t>A biological child who is female gender.</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>biological child</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
@@ -2457,12 +2477,12 @@
           <t>A biological parent who provided the sperm.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>biological parent</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
@@ -2512,12 +2532,12 @@
           <t>A biological parent who provided an egg.</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>biological parent</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
@@ -2567,12 +2587,12 @@
           <t>A parent who provided one of the gametes that resulted in one's conception.</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2626,12 +2646,12 @@
           <t>A bodily quality based on reproductive function or organs.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>bodily quality</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
@@ -2681,12 +2701,12 @@
           <t>A sibling with whom the subject shares a biological parent.</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
@@ -2736,12 +2756,12 @@
           <t>A biological sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>biological sibling</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
@@ -2791,12 +2811,12 @@
           <t>A biological child who is male gender.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>biological child</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
@@ -2846,12 +2866,12 @@
           <t>A sexual orientation of an individual who experiences sexual attraction to members of more than one sex.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2905,7 +2925,7 @@
           <t>A quality that inheres in some extended organism.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
@@ -2937,12 +2957,12 @@
           <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
@@ -2992,12 +3012,12 @@
           <t>A personal attribute as belonging to a group within a stratified system of categorisation based on a status conferred at birth based on descent, in which individuals have limited or no mobility due to custom or law.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
@@ -3024,7 +3044,7 @@
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -3051,12 +3071,12 @@
           <t xml:space="preserve">A person who has not yet reached maturity. </t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
@@ -3110,12 +3130,12 @@
           <t>A family member who is a person's first generation offspring.</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
@@ -3165,12 +3185,12 @@
           <t>A gender identity that matches the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3224,12 +3244,12 @@
           <t xml:space="preserve">A geographic location that is the country in which a person was born. </t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>geographic location</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3283,12 +3303,12 @@
           <t>A family member who is a child relation of one's aunt or uncle.</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n"/>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
@@ -3338,15 +3358,15 @@
           <t>A personal attribute in which the person has impaired physical or mental functioning that has a notable effect on their ability to do typical daily activities.</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="inlineStr">
@@ -3367,7 +3387,7 @@
         </is>
       </c>
       <c r="P52" s="2" t="n"/>
-      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="n"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3395,15 +3415,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>psychology, counselling, public health</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>expertise discipline</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>psychology, counselling, public health</t>
-        </is>
-      </c>
+      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
@@ -3458,15 +3478,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>expertise discipline</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
-        </is>
-      </c>
+      <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
@@ -3515,12 +3535,12 @@
           <t>A relationship status where the individual was previously in a legally formalised relationship and this relationship has now ended or dissolved.</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
@@ -3570,12 +3590,12 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
@@ -3625,12 +3645,12 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n"/>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
@@ -3680,12 +3700,12 @@
           <t>A &lt;social group&gt; of two people who interact and influence each other.</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>social group</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
@@ -3727,12 +3747,12 @@
           <t>A planned process wherein knowledge and skills is imparted.</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>planned process</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3778,12 +3798,12 @@
           <t>An employment status realised by an individual being engaged in an activity or service for wages or salary.</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3837,12 +3857,12 @@
           <t>An employment status realised by an individual working a standard number of hours defined as full-time by their employer.</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3896,12 +3916,12 @@
           <t>An employment status realised by an individual working for recurring periods in which different groups of workers do the same jobs in relay.</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
@@ -3951,12 +3971,12 @@
           <t>An employment status realised by an individual whose working hours involving less than the standard or customary working time.</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4010,12 +4030,12 @@
           <t>A quality inhering in a person by virtue of that person bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4074,12 +4094,12 @@
           <t>A self-identity as belonging to a social group or groups whose members have a common cultural or ancestral heritage.</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4137,12 +4157,12 @@
           <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
@@ -4192,12 +4212,12 @@
           <t>A data item that is the extent to which the person’s past behaviour has reached or exceeded a standard.</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
@@ -4209,7 +4229,7 @@
         </is>
       </c>
       <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="n"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>value</t>
@@ -4247,12 +4267,12 @@
           <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4306,12 +4326,12 @@
           <t>A parent who is male gender.</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n"/>
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
@@ -4361,12 +4381,12 @@
           <t>A biological sex associated with the ability to produce female gametes.</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>biological sex</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
@@ -4416,12 +4436,12 @@
           <t>A gender identity as being female.</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4479,12 +4499,12 @@
           <t>A foster sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>foster sibling</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
@@ -4534,12 +4554,12 @@
           <t xml:space="preserve">A child relation in a parent-child relationship created by a foster care arrangement. </t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n"/>
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
@@ -4589,12 +4609,12 @@
           <t>A foster child who is female gender.</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>foster child</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
@@ -4644,12 +4664,12 @@
           <t>A foster parent who is male gender.</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>foster parent</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n"/>
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
@@ -4699,12 +4719,12 @@
           <t>A foster parent who is female gender.</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>foster parent</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
@@ -4754,12 +4774,12 @@
           <t>A parent who cares for a child who has been placed with them in a foster care arrangement.</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4813,12 +4833,12 @@
           <t>A sibling who shares a parent through a parent-child relationship created by a foster care agreement.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
@@ -4868,12 +4888,12 @@
           <t>A foster sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>foster sibling</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
@@ -4923,12 +4943,12 @@
           <t>A foster child who is male gender.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>foster child</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
@@ -4978,12 +4998,12 @@
           <t>A behavioural frequency about the number of times a person has enacted a behaviour per unit of time.</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>behavioural frequency</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
@@ -4996,8 +5016,16 @@
       </c>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
-      <c r="N81" s="2" t="n"/>
-      <c r="O81" s="2" t="n"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="inlineStr">
@@ -5025,12 +5053,12 @@
           <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
@@ -5080,12 +5108,12 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="n"/>
@@ -5135,12 +5163,12 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
@@ -5190,12 +5218,12 @@
           <t>A grandparent who is male gender.</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>grandparent</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
@@ -5245,12 +5273,12 @@
           <t>A grandparent who is female gender.</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>grandparent</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n"/>
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
@@ -5300,12 +5328,12 @@
           <t>A family member who is the parent of one's parent.</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
@@ -5355,12 +5383,12 @@
           <t xml:space="preserve">A personal history part that includes previously performing a behaviour. </t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
@@ -5412,15 +5440,15 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>policy holder role</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
-        </is>
-      </c>
+      <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
@@ -5471,15 +5499,15 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>Having chicken pox, asthma, a heart attack</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Having chicken pox, asthma, a heart attack</t>
-        </is>
-      </c>
+      <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>NCIT_C16669</t>
@@ -5532,12 +5560,12 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of a different sex.</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5591,12 +5619,12 @@
           <t>A frequency of past behaviour that is above a threshold.</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>frequency of past behaviour</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n"/>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
@@ -5610,7 +5638,11 @@
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="n"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
       <c r="R92" s="2" t="inlineStr">
@@ -5638,12 +5670,12 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. For example, completing a university bachelor's or master's course of study, medical school or other professional school. </t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
@@ -5695,15 +5727,15 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
+      <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
@@ -5752,12 +5784,12 @@
           <t>A personal attribute related to the highest level of education achieved.</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5815,7 +5847,7 @@
           <t>A process that is the sum of the totality of processes taking place in the spatiotemporal region occupied by a material entity or site, including processes on the surface of the entity or within the cavities to which it serves as host.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>process</t>
         </is>
@@ -5849,15 +5881,15 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>history of exposure to asbestos due to one's job</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>history of exposure to asbestos due to one's job</t>
-        </is>
-      </c>
+      <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
@@ -5908,15 +5940,15 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>history of physical abuse by a parent</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>history of physical abuse by a parent</t>
-        </is>
-      </c>
+      <c r="F98" s="2" t="n"/>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
@@ -5965,12 +5997,12 @@
           <t>A person who does not own a residential facility and does not have an agreement with a residential facility owner that would enable them to live in a residential facility.</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n"/>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="inlineStr">
@@ -6024,12 +6056,12 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process and who manages their home as their main daily activity.</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n"/>
       <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6083,12 +6115,12 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of the same sex.</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n"/>
       <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6142,7 +6174,7 @@
           <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of its residence function.</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
@@ -6179,12 +6211,12 @@
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n"/>
       <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6215,7 +6247,7 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
@@ -6242,12 +6274,12 @@
           <t>A personal attribute that is a time quality inhering in a person by virtue of how long since the person was born.</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n"/>
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6301,12 +6333,12 @@
           <t>An object aggregate that consists of two or more people.</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E105" s="2" t="n"/>
       <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
@@ -6348,7 +6380,7 @@
           <t>A cognitive representation of themselves by a person or group.</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>cognitive representation</t>
         </is>
@@ -6380,12 +6412,12 @@
           <t>A person who has previously been a resident of a country and is now resident in another country.</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
@@ -6435,12 +6467,12 @@
           <t xml:space="preserve">A relationship status where the individual is in a legally formalised marriage or civil partnership. </t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n"/>
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
@@ -6491,12 +6523,12 @@
           <t>A relationship status where the individual has had the same partner for a significant length of time but is not in a legal union.</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n"/>
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
@@ -6550,12 +6582,12 @@
           <t>An employment status realised by an individual working for a company or other organisation without a pre-determined end date, with security of employment and known working conditions.</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n"/>
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
@@ -6605,12 +6637,12 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position that is of a known, fixed duration with security of employment for that duration and certain working conditions.</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n"/>
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
@@ -6660,12 +6692,12 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position with uncertain duration or hours with unknown or low security of working conditions or pay.</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n"/>
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
@@ -6715,12 +6747,12 @@
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>individual income</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n"/>
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
@@ -6770,12 +6802,12 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process due to possessing enough wealth to not need financial support from another person or require income from employment.</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n"/>
       <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
@@ -6827,15 +6859,15 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
           <t>bodily process</t>
         </is>
       </c>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
-        </is>
-      </c>
+      <c r="F115" s="2" t="n"/>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
@@ -6884,12 +6916,12 @@
           <t>A personal attribute reflecting a benefit the person receives  derived from their capital or labour, usually measured in money.</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -6943,12 +6975,12 @@
           <t>A social role that involves influencing other people to adopt new ideas or behaviours.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>social role</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
@@ -6998,12 +7030,12 @@
           <t>A student or trainee role realised by  currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="3" t="n"/>
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
       <c r="H118" s="3" t="n"/>
@@ -7053,12 +7085,12 @@
           <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n"/>
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
@@ -7108,12 +7140,12 @@
           <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>patient role</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n"/>
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
@@ -7163,12 +7195,12 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="3" t="n"/>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -7226,7 +7258,7 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -7278,12 +7310,12 @@
           <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E123" s="2" t="n"/>
       <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -7337,12 +7369,12 @@
           <t>A person who is exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n"/>
       <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
@@ -7384,12 +7416,12 @@
           <t>A human population who are exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
@@ -7433,15 +7465,15 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
-        </is>
-      </c>
+      <c r="F126" s="2" t="n"/>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
@@ -7490,12 +7522,12 @@
           <t>A social role in which the holder is given or creates authority to exert influence on other members of a social group.</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>social role</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
@@ -7513,7 +7545,11 @@
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
       <c r="N127" s="2" t="n"/>
-      <c r="O127" s="2" t="n"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="P127" s="2" t="n"/>
       <c r="Q127" s="2" t="n"/>
       <c r="R127" s="2" t="inlineStr">
@@ -7541,7 +7577,7 @@
           <t>A mental capability that is realised in processes of communication involving language or in expressions of language.</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>mental capability</t>
         </is>
@@ -7583,12 +7619,12 @@
           <t>Disabled for at least 12 months.</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n"/>
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
@@ -7643,12 +7679,12 @@
           <t>A frequency of past behaviour that is below a threshold.</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>frequency of past behaviour</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n"/>
       <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
@@ -7662,7 +7698,11 @@
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
       <c r="N130" s="2" t="n"/>
-      <c r="O130" s="2" t="n"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="P130" s="2" t="n"/>
       <c r="Q130" s="2" t="n"/>
       <c r="R130" s="2" t="inlineStr">
@@ -7690,12 +7730,12 @@
           <t>A biological sex associated with the ability to produce male gametes.</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>biological sex</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n"/>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
@@ -7745,12 +7785,12 @@
           <t>A gender identity as being male.</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n"/>
       <c r="F132" s="2" t="n"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -7808,12 +7848,12 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D133" s="3" t="n"/>
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="n"/>
@@ -7863,12 +7903,12 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n"/>
       <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
@@ -7920,15 +7960,15 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
+          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
           <t>health status attribute</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
-        </is>
-      </c>
+      <c r="F135" s="2" t="n"/>
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
@@ -7981,12 +8021,12 @@
           <t>A person living in  a household with at least one other person.</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n"/>
       <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
@@ -8042,15 +8082,15 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
+          <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
           <t>member of a multi-person household</t>
         </is>
       </c>
-      <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
-        </is>
-      </c>
+      <c r="F137" s="2" t="n"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
@@ -8105,15 +8145,15 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
+          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
           <t>member of a multi-person household</t>
         </is>
       </c>
-      <c r="E138" s="2" t="n"/>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
-        </is>
-      </c>
+      <c r="F138" s="2" t="n"/>
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
@@ -8164,15 +8204,15 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
           <t>member of a multi-person household</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n"/>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
-        </is>
-      </c>
+      <c r="F139" s="2" t="n"/>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
@@ -8223,15 +8263,15 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
+          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
           <t>member of a multi-person household</t>
         </is>
       </c>
-      <c r="E140" s="2" t="n"/>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
-        </is>
-      </c>
+      <c r="F140" s="2" t="n"/>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
@@ -8284,12 +8324,12 @@
           <t>A person living alone in a household.</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n"/>
       <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
@@ -8339,7 +8379,7 @@
           <t>A personal capability that includes mental processes in its realisation.</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>personal capability</t>
         </is>
@@ -8381,12 +8421,12 @@
           <t>A parent who is female gender.</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n"/>
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
@@ -8436,12 +8476,12 @@
           <t xml:space="preserve">A family member who is a child relation of one's sibling and is male gender. </t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n"/>
       <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
@@ -8491,12 +8531,12 @@
           <t>A family member who is a child relation of one's sibling and is female gender.</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n"/>
       <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
@@ -8546,12 +8586,12 @@
           <t>A self-identity as not having a particular gender.</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n"/>
       <c r="F146" s="2" t="n"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -8605,12 +8645,12 @@
           <t>A gender identity as having a gender that is not well-described by the binary categories of male or female.</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n"/>
       <c r="F147" s="2" t="n"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -8664,12 +8704,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not having a paid job and not currently seeking to begin participating in an employment process.</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n"/>
       <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
@@ -8719,12 +8759,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being unable to work due to illness or disability.</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n"/>
       <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
@@ -8774,12 +8814,12 @@
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E150" s="2" t="n"/>
       <c r="F150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
@@ -8821,12 +8861,12 @@
           <t>The number of years a person spent engaged in an education process.</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E151" s="2" t="n"/>
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
@@ -8880,12 +8920,12 @@
           <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>personal role</t>
         </is>
       </c>
-      <c r="E152" s="2" t="n"/>
       <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
@@ -8935,12 +8975,12 @@
           <t>A person who lives in a residential facility they do not own  with the agreement of the residential facility owner, by virtue of the occupier bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E153" s="2" t="n"/>
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
@@ -8992,15 +9032,15 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
+          <t>Scout leader, club chairperson</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n"/>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>Scout leader, club chairperson</t>
-        </is>
-      </c>
+      <c r="F154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
@@ -9049,12 +9089,12 @@
           <t>A sexual orientation of an individual who is sure of their sexual orientation and reports it as other than asexual, bisexual, heterosexual, homosexual, queer or questioning.</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n"/>
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
@@ -9104,12 +9144,12 @@
           <t>A social group that is part of a person’s social environmental system and with which the person does not identify.</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>social group</t>
         </is>
       </c>
-      <c r="E156" s="2" t="n"/>
       <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
@@ -9151,12 +9191,12 @@
           <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>patient role</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n"/>
       <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
@@ -9206,12 +9246,12 @@
           <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n"/>
       <c r="F158" s="2" t="n"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -9269,12 +9309,12 @@
           <t>A person who lives in a residential facility of which they are the residential facility owner</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n"/>
       <c r="F159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
@@ -9325,12 +9365,12 @@
           <t xml:space="preserve">A family member who is a key caretaker or immediate progenitor of a child. </t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n"/>
       <c r="F160" s="2" t="n"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -9384,12 +9424,12 @@
           <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>interpersonal role</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n"/>
       <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
@@ -9443,12 +9483,12 @@
           <t>A personal history part that includes a behaviour.</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E162" s="2" t="n"/>
       <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
@@ -9498,12 +9538,12 @@
           <t>A past behaviour that is the target of an intervention.</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
-      <c r="E163" s="2" t="n"/>
       <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
@@ -9517,7 +9557,11 @@
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="2" t="n"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="P163" s="2" t="n"/>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="inlineStr">
@@ -9545,7 +9589,7 @@
           <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -9588,12 +9632,12 @@
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n"/>
       <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
@@ -9635,7 +9679,7 @@
           <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>extended organism</t>
         </is>
@@ -9667,12 +9711,12 @@
           <t>A &lt;person&gt; who is part of a social environmental system.</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n"/>
       <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
@@ -9714,12 +9758,12 @@
           <t>A specifically dependent continuant that inheres in a person.</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
       </c>
-      <c r="E168" s="2" t="n"/>
       <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
@@ -9769,7 +9813,7 @@
           <t>A bodily disposition whose realization ordinarily brings benefits to an organism or group of organisms, where "ordinarily" means within a typical range or context.</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>bodily disposition</t>
         </is>
@@ -9812,12 +9856,12 @@
           <t>A history that is of a person.</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>history</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n"/>
       <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
@@ -9859,12 +9903,12 @@
           <t xml:space="preserve">A personal history part that includes a change from a less desired behaviour pattern to a more desired behaviour pattern followed by a temporary reversion to the previous behaviour pattern. </t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n"/>
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
@@ -9914,12 +9958,12 @@
           <t xml:space="preserve">A personal history part that includes experience of events that influence behaviour. </t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n"/>
       <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
@@ -9969,12 +10013,12 @@
           <t>A personal history part of exposure to an intervention targeting the same outcome as the current intervention.</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n"/>
       <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
@@ -10024,12 +10068,12 @@
           <t>A personal history part  that includes exposure to a prior intervention targeting the same outcome behaviour as the current intervention.</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E174" s="2" t="n"/>
       <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
@@ -10079,12 +10123,12 @@
           <t>A personal history part that includes exposure to the same intervention as the current intervention.</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E175" s="2" t="n"/>
       <c r="F175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
@@ -10138,17 +10182,17 @@
           <t>A process that is part of a personal history.</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>'process' and 'part of' some 'personal history'</t>
         </is>
       </c>
-      <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
@@ -10189,12 +10233,12 @@
           <t xml:space="preserve">A personal history part  that includes exposure to one or more interventions. </t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n"/>
       <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
@@ -10246,15 +10290,15 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
+          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E178" s="2" t="n"/>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
-        </is>
-      </c>
+      <c r="F178" s="2" t="n"/>
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
@@ -10303,12 +10347,12 @@
           <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n"/>
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
@@ -10360,15 +10404,15 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
+          <t>susceptibility to addiction, vulnerability to depression</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
           <t>disposition</t>
         </is>
       </c>
-      <c r="E180" s="2" t="n"/>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>susceptibility to addiction, vulnerability to depression</t>
-        </is>
-      </c>
+      <c r="F180" s="2" t="n"/>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
@@ -10417,12 +10461,12 @@
           <t>A personal vulnerability towards performing a behaviour that causes net harm.</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>personal vulnerability</t>
         </is>
       </c>
-      <c r="E181" s="2" t="n"/>
       <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="inlineStr">
@@ -10476,12 +10520,12 @@
           <t>A geographic location in which a person resides.</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>geographic location</t>
         </is>
       </c>
-      <c r="E182" s="2" t="n"/>
       <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
@@ -10531,7 +10575,7 @@
           <t>An insured party role that inheres in a person who participates in the creation of the insurance contract and is eligible to receive benefits as specified by the insurance contract.</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>insured party role</t>
         </is>
@@ -10575,16 +10619,16 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="n"/>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n"/>
       <c r="G184" s="2" t="n"/>
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
@@ -10621,12 +10665,12 @@
           <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E185" s="2" t="n"/>
       <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
@@ -10676,12 +10720,12 @@
           <t>A &lt;disposition&gt; that decreases the likelihood of engaging with harmful behaviour.</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>disposition</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n"/>
       <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
@@ -10731,7 +10775,7 @@
           <t>A specifically dependent continuant that, in contrast to roles and dispositions, does not require any further process in order to be realized.</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
@@ -10765,15 +10809,15 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
+          <t>12 acres, a flock of 20 goats</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E188" s="2" t="n"/>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>12 acres, a flock of 20 goats</t>
-        </is>
-      </c>
+      <c r="F188" s="2" t="n"/>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
@@ -10826,12 +10870,12 @@
           <t>A sexual orientation that is not exclusively homosexual or heterosexual, or of a person who does not identify with heterosexual, homosexual or bisexual labels.</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n"/>
       <c r="F189" s="2" t="n"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -10885,12 +10929,12 @@
           <t xml:space="preserve">A self-identity as being in the process of exploring one's sexual orientation. </t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n"/>
       <c r="F190" s="2" t="n"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -10944,12 +10988,12 @@
           <t>A personal attribute that is whether an individual is connected or associated with another through romantic attraction or marriage.</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E191" s="2" t="n"/>
       <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
@@ -11001,15 +11045,15 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E192" s="2" t="n"/>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
-        </is>
-      </c>
+      <c r="F192" s="2" t="n"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
           <t>NCIT_C103282</t>
@@ -11066,12 +11110,12 @@
           <t>A person who lives in a residential facility they do not own without paying an agreed sum of money to the residential facility owner.</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E193" s="2" t="n"/>
       <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
@@ -11123,15 +11167,15 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
+          <t>squatters</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
           <t>rent-free occupier</t>
         </is>
       </c>
-      <c r="E194" s="2" t="n"/>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>squatters</t>
-        </is>
-      </c>
+      <c r="F194" s="2" t="n"/>
       <c r="G194" s="2" t="n"/>
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
@@ -11180,12 +11224,12 @@
           <t>A person who lives in a residential facility they do not own in return for paying an agreed sum of money to the residential facility owner</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n"/>
       <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
@@ -11237,15 +11281,15 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
+          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
           <t>renter</t>
         </is>
       </c>
-      <c r="E196" s="2" t="n"/>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
-        </is>
-      </c>
+      <c r="F196" s="2" t="n"/>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
@@ -11294,12 +11338,12 @@
           <t>An owner of a residential facility.</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="E197" s="2" t="n"/>
       <c r="F197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
@@ -11349,12 +11393,12 @@
           <t>A personal attribute inhering in a person who previously bore a role realised in an employment process but has withdrawn from that employment process, having concluded their working or professional career.</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n"/>
       <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
@@ -11404,7 +11448,7 @@
           <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
@@ -11436,12 +11480,12 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E200" s="3" t="n"/>
       <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="n"/>
@@ -11491,12 +11535,12 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n"/>
       <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
@@ -11546,12 +11590,12 @@
           <t>A person who has at least one parent who is an immigrant.</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E202" s="2" t="n"/>
       <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
@@ -11601,12 +11645,12 @@
           <t>An employment status realised by a person earning income directly from customers, clients, or other organisations rather than as a specified salary or wages from an employer.</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E203" s="2" t="n"/>
       <c r="F203" s="2" t="n"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -11664,7 +11708,7 @@
           <t>An identity that a person has about themselves.</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>identity</t>
         </is>
@@ -11696,12 +11740,12 @@
           <t xml:space="preserve">A personal attribute that is the pattern of a person's emotional, romantic and/or sexual attractions. </t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E205" s="2" t="n"/>
       <c r="F205" s="2" t="n"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -11755,12 +11799,12 @@
           <t>A family member with whom the subject shares a parent.</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n"/>
       <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
@@ -11811,12 +11855,12 @@
           <t>A relationship status where the individual is not in a relationship with another person.</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n"/>
       <c r="F207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
@@ -11866,12 +11910,12 @@
           <t>A personal attribute that holds within a given situation.</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E208" s="2" t="n"/>
       <c r="F208" s="2" t="n"/>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
@@ -11913,12 +11957,12 @@
           <t>A social grouping that identifies as such and sometimes acts collectively.</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>social grouping</t>
         </is>
       </c>
-      <c r="E209" s="2" t="n"/>
       <c r="F209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
@@ -11960,12 +12004,12 @@
           <t>A human population who share some common attribute that involves some form of social interaction.</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E210" s="2" t="n"/>
       <c r="F210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
@@ -12011,12 +12055,12 @@
           <t>A personal role that is realised in human social processes.</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>personal role</t>
         </is>
       </c>
-      <c r="E211" s="2" t="n"/>
       <c r="F211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
@@ -12058,12 +12102,12 @@
           <t>A &lt;personal attribute&gt; that, together with other attributes, characterises a person’s position in society.</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E212" s="2" t="n"/>
       <c r="F212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
@@ -12109,7 +12153,7 @@
           <t xml:space="preserve">A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.  </t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
@@ -12143,15 +12187,15 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
+          <t>Semi-routine and routine occupations, blue collar occupations</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E214" s="2" t="n"/>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>Semi-routine and routine occupations, blue collar occupations</t>
-        </is>
-      </c>
+      <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="2" t="n"/>
@@ -12204,12 +12248,12 @@
           <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic status, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D215" s="2" t="n"/>
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E215" s="2" t="n"/>
       <c r="F215" s="2" t="n"/>
       <c r="G215" s="2" t="n"/>
       <c r="H215" s="2" t="n"/>
@@ -12263,12 +12307,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being a homemaker whose work includes caring for children.</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D216" s="2" t="n"/>
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E216" s="2" t="n"/>
       <c r="F216" s="2" t="n"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -12322,12 +12366,12 @@
           <t>A parent in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D217" s="2" t="n"/>
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E217" s="2" t="n"/>
       <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -12381,12 +12425,12 @@
           <t>A sibling who is the child of one's step-parent.</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D218" s="2" t="n"/>
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E218" s="2" t="n"/>
       <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
@@ -12436,12 +12480,12 @@
           <t>A step-sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>step-sibling</t>
         </is>
       </c>
-      <c r="E219" s="2" t="n"/>
       <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
@@ -12491,12 +12535,12 @@
           <t>A child relation in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E220" s="2" t="n"/>
       <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
@@ -12546,12 +12590,12 @@
           <t>A stepchild who is female gender.</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>stepchild</t>
         </is>
       </c>
-      <c r="E221" s="2" t="n"/>
       <c r="F221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
@@ -12601,12 +12645,12 @@
           <t>A step-parent who is male gender.</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>step-parent</t>
         </is>
       </c>
-      <c r="E222" s="2" t="n"/>
       <c r="F222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
@@ -12656,12 +12700,12 @@
           <t>A step-parent who is female gender.</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>step-parent</t>
         </is>
       </c>
-      <c r="E223" s="2" t="n"/>
       <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
@@ -12711,12 +12755,12 @@
           <t>A step-sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>step-sibling</t>
         </is>
       </c>
-      <c r="E224" s="2" t="n"/>
       <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
@@ -12766,12 +12810,12 @@
           <t>A stepchild who is male gender.</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>stepchild</t>
         </is>
       </c>
-      <c r="E225" s="2" t="n"/>
       <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
@@ -12821,12 +12865,12 @@
           <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E226" s="2" t="n"/>
       <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
@@ -12876,7 +12920,7 @@
           <t>A person between 13 and 19 years of age.</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -12918,12 +12962,12 @@
           <t>A gender identity that differs from the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E228" s="2" t="n"/>
       <c r="F228" s="2" t="n"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
@@ -12977,12 +13021,12 @@
           <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E229" s="2" t="n"/>
       <c r="F229" s="2" t="n"/>
       <c r="G229" s="2" t="n"/>
       <c r="H229" s="2" t="n"/>
@@ -13032,12 +13076,12 @@
           <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>situational personal attribute</t>
         </is>
       </c>
-      <c r="E230" s="2" t="n"/>
       <c r="F230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="H230" s="2" t="n"/>
@@ -13087,12 +13131,12 @@
           <t>A family member who is the brother of one's parent.</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E231" s="2" t="n"/>
       <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
@@ -13142,12 +13186,12 @@
           <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>situational personal attribute</t>
         </is>
       </c>
-      <c r="E232" s="2" t="n"/>
       <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
@@ -13197,12 +13241,12 @@
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D233" s="3" t="inlineStr">
+      <c r="D233" s="3" t="n"/>
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E233" s="3" t="n"/>
       <c r="F233" s="3" t="n"/>
       <c r="G233" s="3" t="n"/>
       <c r="H233" s="3" t="n"/>
@@ -13252,12 +13296,12 @@
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D234" s="2" t="n"/>
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E234" s="2" t="n"/>
       <c r="F234" s="2" t="n"/>
       <c r="G234" s="2" t="n"/>
       <c r="H234" s="2" t="n"/>
@@ -13307,12 +13351,12 @@
           <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E235" s="2" t="n"/>
       <c r="F235" s="2" t="n"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
@@ -13366,12 +13410,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E236" s="2" t="n"/>
       <c r="F236" s="2" t="n"/>
       <c r="G236" s="2" t="n"/>
       <c r="H236" s="2" t="n"/>
@@ -13423,15 +13467,15 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
+          <t>farmland, jewellery, livestock</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E237" s="2" t="n"/>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>farmland, jewellery, livestock</t>
-        </is>
-      </c>
+      <c r="F237" s="2" t="n"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
           <t>SDGIO:00010048</t>
@@ -13478,15 +13522,15 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
+          <t>$400, 3000 euros</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E238" s="2" t="n"/>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>$400, 3000 euros</t>
-        </is>
-      </c>
+      <c r="F238" s="2" t="n"/>
       <c r="G238" s="2" t="n"/>
       <c r="H238" s="2" t="n"/>
       <c r="I238" s="2" t="n"/>
@@ -13539,12 +13583,12 @@
           <t>A student or trainee role realised by currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D239" s="3" t="inlineStr">
+      <c r="D239" s="3" t="n"/>
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E239" s="3" t="n"/>
       <c r="F239" s="3" t="n"/>
       <c r="G239" s="3" t="n"/>
       <c r="H239" s="3" t="n"/>
@@ -13594,12 +13638,12 @@
           <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D240" s="2" t="n"/>
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E240" s="2" t="n"/>
       <c r="F240" s="2" t="n"/>
       <c r="G240" s="2" t="n"/>
       <c r="H240" s="2" t="n"/>
@@ -13649,12 +13693,12 @@
           <t>A personal attribute inhering in a person by virtue of that person working or assisting at a workplace without receiving remuneration.</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E241" s="2" t="n"/>
       <c r="F241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="n"/>
@@ -13708,12 +13752,12 @@
           <t xml:space="preserve">A relationship status where the individual is no longer in a legally formalised marriage or civil partnership due to the death of their spouse or partner. </t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E242" s="2" t="n"/>
       <c r="F242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -9501,16 +9501,8 @@
       </c>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
-      <c r="N162" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O162" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr"/>
       <c r="P162" s="2" t="n"/>
       <c r="Q162" s="2" t="n"/>
       <c r="R162" s="2" t="inlineStr">
@@ -9557,11 +9549,7 @@
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O163" s="2" t="inlineStr"/>
       <c r="P163" s="2" t="n"/>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -451,19 +451,19 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Logical definition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Examples</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Logical definition</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cross-reference</t>
@@ -506,17 +506,17 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Curator note</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'is about'</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Aggregate</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'is about'</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curator note</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -558,15 +558,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Comprehend the German language</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
@@ -583,13 +583,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -617,15 +617,15 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>The exclusion criteria were an inability to read English</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
@@ -642,13 +642,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -676,15 +676,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Able to speak Chinese.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
@@ -701,13 +701,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -735,15 +735,15 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Fluency in written English.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
@@ -760,13 +760,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -792,12 +792,12 @@
           <t>A highest level of formal education qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in a specialised discipline that culminated in the award of an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -855,12 +855,12 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process devoted to advanced study and original research that led to the award of a PhD or equivalent level qualification. </t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
@@ -882,13 +882,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -914,12 +914,12 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process intended to introduce very young children to a school-type environment. </t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
@@ -941,13 +941,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -973,12 +973,12 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in subject areas more specialised than basic reading, writing and mathematics, with the overall goal of laying the foundation for lifelong learning and human development on which education systems may systematically expand further educational opportunities.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1004,13 +1004,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1036,12 +1036,12 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process which has as a prerequisite an undergraduate degree and which is intended to result in the acquisition and development of advanced academic or professional skills and knowledge in a specialised discipline, that culminated in the award of a Master's or equivalent degree.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
@@ -1063,13 +1063,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1095,12 +1095,12 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition of fundamental skills in reading, writing and mathematics.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1126,13 +1126,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1160,15 +1160,15 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>graduated high school, International Baccaulaureate, A Levels</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002040</t>
@@ -1193,13 +1193,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1225,12 +1225,12 @@
           <t>An adoptive sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>adoptive sibling</t>
         </is>
       </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
@@ -1248,13 +1248,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1280,12 +1280,12 @@
           <t xml:space="preserve">A child relation in a parent-child relationship established by a legal adoption process. </t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1339,12 +1339,12 @@
           <t>An adoptive child who is female gender.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>adoptive child</t>
         </is>
       </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
@@ -1362,13 +1362,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1394,12 +1394,12 @@
           <t>An adoptive parent who is male gender.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>adoptive parent</t>
         </is>
       </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
@@ -1417,13 +1417,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1449,12 +1449,12 @@
           <t>An adoptive parent who is female gender.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>adoptive parent</t>
         </is>
       </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1472,13 +1472,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1504,12 +1504,12 @@
           <t>A parent in a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1563,12 +1563,12 @@
           <t>A sibling with whom the subject shares a parent through a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
@@ -1586,13 +1586,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1618,12 +1618,12 @@
           <t>An adoptive sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>adoptive sibling</t>
         </is>
       </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
@@ -1641,13 +1641,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1673,12 +1673,12 @@
           <t>An adoptive child who is male gender.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>adoptive child</t>
         </is>
       </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
@@ -1696,13 +1696,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1728,7 +1728,7 @@
           <t>A person who has reached maturity.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -1748,7 +1748,7 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
@@ -1775,12 +1775,12 @@
           <t>A rent-free occupier who lives in the residential facility with the agreement of the residential facility owner.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>rent-free occupier</t>
         </is>
       </c>
+      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
@@ -1798,13 +1798,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1830,12 +1830,12 @@
           <t xml:space="preserve">A sexual orientation of an individual who does not experience sexual attraction. </t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
+      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1850,20 +1850,20 @@
           <t>population</t>
         </is>
       </c>
-      <c r="L24" s="2" t="n"/>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>attributes</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1889,12 +1889,12 @@
           <t>A family member who is the sister of one's parent.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
@@ -1912,13 +1912,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
-      <c r="Q25" s="2" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1944,12 +1944,12 @@
           <t>An intervention participant who is exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>intervention participant</t>
         </is>
       </c>
+      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
@@ -1995,12 +1995,12 @@
           <t>An intervention population who are exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>intervention population</t>
         </is>
       </c>
+      <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
@@ -2042,12 +2042,12 @@
           <t>A data item that is about the rate of individual human behaviour change.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
+      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
@@ -2061,13 +2061,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2093,12 +2093,12 @@
           <t>A person who has formed an intention to enact a specified behaviour, and has enacted that behaviour.</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
@@ -2117,13 +2117,13 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2149,12 +2149,12 @@
           <t>A person who has formed an intention to enact a specified behaviour, but has not acted on this intention.</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
@@ -2169,13 +2169,13 @@
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2201,12 +2201,12 @@
           <t>A person who has not formed an intention to enact a specified behaviour.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">person </t>
         </is>
       </c>
+      <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
@@ -2221,13 +2221,13 @@
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
-      <c r="Q31" s="2" t="n"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2253,12 +2253,12 @@
           <t xml:space="preserve">A data item that is about the number of times a behaviour occurs in a time period. </t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
@@ -2280,13 +2280,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2312,12 +2312,12 @@
           <t>A biological sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>biological sibling</t>
         </is>
       </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
@@ -2335,13 +2335,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
-      <c r="Q33" s="2" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2367,12 +2367,12 @@
           <t>A child relation who is genetically related to their parent.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
@@ -2390,13 +2390,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2422,12 +2422,12 @@
           <t>A biological child who is female gender.</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>biological child</t>
         </is>
       </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
@@ -2445,13 +2445,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2477,12 +2477,12 @@
           <t>A biological parent who provided the sperm.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>biological parent</t>
         </is>
       </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
@@ -2500,13 +2500,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2532,12 +2532,12 @@
           <t>A biological parent who provided an egg.</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>biological parent</t>
         </is>
       </c>
+      <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
@@ -2555,13 +2555,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
-      <c r="Q37" s="2" t="n"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2587,12 +2587,12 @@
           <t>A parent who provided one of the gametes that resulted in one's conception.</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
+      <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2614,13 +2614,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2646,12 +2646,12 @@
           <t>A bodily quality based on reproductive function or organs.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>bodily quality</t>
         </is>
       </c>
+      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
@@ -2669,13 +2669,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="n"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2701,12 +2701,12 @@
           <t>A sibling with whom the subject shares a biological parent.</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
+      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
@@ -2724,13 +2724,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="n"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2756,12 +2756,12 @@
           <t>A biological sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>biological sibling</t>
         </is>
       </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
@@ -2779,13 +2779,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="n"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2811,12 +2811,12 @@
           <t>A biological child who is male gender.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>biological child</t>
         </is>
       </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
@@ -2834,13 +2834,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n"/>
-      <c r="Q42" s="2" t="n"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2866,12 +2866,12 @@
           <t>A sexual orientation of an individual who experiences sexual attraction to members of more than one sex.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
+      <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2925,7 +2925,7 @@
           <t>A quality that inheres in some extended organism.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
@@ -2957,12 +2957,12 @@
           <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
+      <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
@@ -2980,13 +2980,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3012,12 +3012,12 @@
           <t>A personal attribute as belonging to a group within a stratified system of categorisation based on a status conferred at birth based on descent, in which individuals have limited or no mobility due to custom or law.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
@@ -3039,13 +3039,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="n"/>
-      <c r="Q46" s="2" t="n"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3071,12 +3071,12 @@
           <t xml:space="preserve">A person who has not yet reached maturity. </t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
@@ -3098,13 +3098,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="n"/>
-      <c r="Q47" s="2" t="n"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3130,12 +3130,12 @@
           <t>A family member who is a person's first generation offspring.</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
@@ -3153,13 +3153,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="n"/>
-      <c r="Q48" s="2" t="n"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3185,12 +3185,12 @@
           <t>A gender identity that matches the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
+      <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3212,13 +3212,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="n"/>
-      <c r="Q49" s="2" t="n"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3244,12 +3244,12 @@
           <t xml:space="preserve">A geographic location that is the country in which a person was born. </t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>geographic location</t>
         </is>
       </c>
+      <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="n"/>
-      <c r="Q50" s="2" t="n"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3303,12 +3303,12 @@
           <t>A family member who is a child relation of one's aunt or uncle.</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E51" s="2" t="n"/>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
@@ -3326,13 +3326,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="n"/>
-      <c r="Q51" s="2" t="n"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3358,12 +3358,12 @@
           <t>A personal attribute in which the person has impaired physical or mental functioning that has a notable effect on their ability to do typical daily activities.</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
@@ -3381,13 +3381,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="n"/>
-      <c r="Q52" s="2" t="n"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3415,15 +3415,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>psychology, counselling, public health</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
@@ -3444,13 +3444,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="n"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3478,15 +3478,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
@@ -3503,13 +3503,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="n"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3535,12 +3535,12 @@
           <t>A relationship status where the individual was previously in a legally formalised relationship and this relationship has now ended or dissolved.</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
+      <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
@@ -3558,13 +3558,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="n"/>
-      <c r="Q55" s="2" t="n"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3590,12 +3590,12 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
+      <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
@@ -3613,13 +3613,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O56" s="3" t="n"/>
       <c r="P56" s="3" t="n"/>
-      <c r="Q56" s="3" t="n"/>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -3645,12 +3645,12 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
+      <c r="E57" s="2" t="n"/>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
@@ -3668,13 +3668,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="n"/>
-      <c r="Q57" s="2" t="n"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3700,12 +3700,12 @@
           <t>A &lt;social group&gt; of two people who interact and influence each other.</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>social group</t>
         </is>
       </c>
+      <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
@@ -3715,13 +3715,13 @@
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="n"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>This definition is based on the work of Scholz et al (2025), as published here: https://osf.io/2364r/</t>
+        </is>
+      </c>
       <c r="P58" s="2" t="n"/>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>This definition is based on the work of Scholz et al (2025), as published here: https://osf.io/2364r/</t>
-        </is>
-      </c>
+      <c r="Q58" s="2" t="n"/>
       <c r="R58" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3747,12 +3747,12 @@
           <t>A planned process wherein knowledge and skills is imparted.</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>planned process</t>
         </is>
       </c>
+      <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3798,12 +3798,12 @@
           <t>An employment status realised by an individual being engaged in an activity or service for wages or salary.</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3825,13 +3825,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="n"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3857,12 +3857,12 @@
           <t>An employment status realised by an individual working a standard number of hours defined as full-time by their employer.</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3884,13 +3884,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="n"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3916,12 +3916,12 @@
           <t>An employment status realised by an individual working for recurring periods in which different groups of workers do the same jobs in relay.</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
@@ -3939,13 +3939,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="n"/>
-      <c r="Q62" s="2" t="n"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3971,12 +3971,12 @@
           <t>An employment status realised by an individual whose working hours involving less than the standard or customary working time.</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -3998,13 +3998,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="n"/>
-      <c r="Q63" s="2" t="n"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4030,12 +4030,12 @@
           <t>A quality inhering in a person by virtue of that person bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
+      <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4062,13 +4062,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="n"/>
-      <c r="Q64" s="2" t="n"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4094,12 +4094,12 @@
           <t>A self-identity as belonging to a social group or groups whose members have a common cultural or ancestral heritage.</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
+      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4125,13 +4125,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="n"/>
-      <c r="Q65" s="2" t="n"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4157,12 +4157,12 @@
           <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
       </c>
+      <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
@@ -4180,13 +4180,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="n"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4212,12 +4212,12 @@
           <t>A data item that is the extent to which the person’s past behaviour has reached or exceeded a standard.</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
@@ -4235,13 +4235,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P67" s="2" t="n"/>
-      <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4267,12 +4267,12 @@
           <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4294,13 +4294,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="n"/>
-      <c r="Q68" s="2" t="n"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4326,12 +4326,12 @@
           <t>A parent who is male gender.</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
+      <c r="E69" s="2" t="n"/>
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
@@ -4349,13 +4349,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="n"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4381,12 +4381,12 @@
           <t>A biological sex associated with the ability to produce female gametes.</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>biological sex</t>
         </is>
       </c>
+      <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
@@ -4404,13 +4404,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="n"/>
-      <c r="Q70" s="2" t="n"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4436,12 +4436,12 @@
           <t>A gender identity as being female.</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
+      <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4467,13 +4467,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="n"/>
-      <c r="Q71" s="2" t="n"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4499,12 +4499,12 @@
           <t>A foster sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>foster sibling</t>
         </is>
       </c>
+      <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
@@ -4522,13 +4522,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O72" s="2" t="n"/>
       <c r="P72" s="2" t="n"/>
-      <c r="Q72" s="2" t="n"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4554,12 +4554,12 @@
           <t xml:space="preserve">A child relation in a parent-child relationship created by a foster care arrangement. </t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
+      <c r="E73" s="2" t="n"/>
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
@@ -4577,13 +4577,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="n"/>
-      <c r="Q73" s="2" t="n"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4609,12 +4609,12 @@
           <t>A foster child who is female gender.</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>foster child</t>
         </is>
       </c>
+      <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
@@ -4632,13 +4632,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="n"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4664,12 +4664,12 @@
           <t>A foster parent who is male gender.</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>foster parent</t>
         </is>
       </c>
+      <c r="E75" s="2" t="n"/>
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
@@ -4687,13 +4687,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="n"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4719,12 +4719,12 @@
           <t>A foster parent who is female gender.</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>foster parent</t>
         </is>
       </c>
+      <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
@@ -4742,13 +4742,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="n"/>
-      <c r="Q76" s="2" t="n"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4774,12 +4774,12 @@
           <t>A parent who cares for a child who has been placed with them in a foster care arrangement.</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
+      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4801,13 +4801,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="n"/>
-      <c r="Q77" s="2" t="n"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4833,12 +4833,12 @@
           <t>A sibling who shares a parent through a parent-child relationship created by a foster care agreement.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
+      <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
@@ -4856,13 +4856,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="n"/>
-      <c r="Q78" s="2" t="n"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4888,12 +4888,12 @@
           <t>A foster sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>foster sibling</t>
         </is>
       </c>
+      <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
@@ -4911,13 +4911,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O79" s="2" t="n"/>
       <c r="P79" s="2" t="n"/>
-      <c r="Q79" s="2" t="n"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4943,12 +4943,12 @@
           <t>A foster child who is male gender.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>foster child</t>
         </is>
       </c>
+      <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
@@ -4966,13 +4966,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O80" s="2" t="n"/>
       <c r="P80" s="2" t="n"/>
-      <c r="Q80" s="2" t="n"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4998,12 +4998,12 @@
           <t>A behavioural frequency about the number of times a person has enacted a behaviour per unit of time.</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>behavioural frequency</t>
         </is>
       </c>
+      <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
@@ -5021,13 +5021,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="n"/>
+      <c r="P81" s="2" t="n"/>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P81" s="2" t="n"/>
-      <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5053,12 +5053,12 @@
           <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
+      <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
@@ -5076,13 +5076,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O82" s="2" t="n"/>
       <c r="P82" s="2" t="n"/>
-      <c r="Q82" s="2" t="n"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5108,12 +5108,12 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
+      <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="n"/>
@@ -5131,13 +5131,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O83" s="3" t="n"/>
       <c r="P83" s="3" t="n"/>
-      <c r="Q83" s="3" t="n"/>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -5163,12 +5163,12 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
+      <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
@@ -5186,13 +5186,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O84" s="2" t="n"/>
       <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="n"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5218,12 +5218,12 @@
           <t>A grandparent who is male gender.</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>grandparent</t>
         </is>
       </c>
+      <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
@@ -5241,13 +5241,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O85" s="2" t="n"/>
       <c r="P85" s="2" t="n"/>
-      <c r="Q85" s="2" t="n"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5273,12 +5273,12 @@
           <t>A grandparent who is female gender.</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>grandparent</t>
         </is>
       </c>
+      <c r="E86" s="2" t="n"/>
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
@@ -5296,13 +5296,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O86" s="2" t="n"/>
       <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="n"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5328,12 +5328,12 @@
           <t>A family member who is the parent of one's parent.</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
@@ -5351,13 +5351,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O87" s="2" t="n"/>
       <c r="P87" s="2" t="n"/>
-      <c r="Q87" s="2" t="n"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5383,12 +5383,12 @@
           <t xml:space="preserve">A personal history part that includes previously performing a behaviour. </t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
@@ -5406,13 +5406,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O88" s="2" t="n"/>
       <c r="P88" s="2" t="n"/>
-      <c r="Q88" s="2" t="n"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5440,15 +5440,15 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>policy holder role</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>policy holder role</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
@@ -5465,13 +5465,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O89" s="2" t="n"/>
       <c r="P89" s="2" t="n"/>
-      <c r="Q89" s="2" t="n"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5499,15 +5499,15 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>Having chicken pox, asthma, a heart attack</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>NCIT_C16669</t>
@@ -5528,13 +5528,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="2" t="n"/>
+      <c r="Q90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P90" s="2" t="n"/>
-      <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5560,12 +5560,12 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of a different sex.</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
+      <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O91" s="2" t="n"/>
       <c r="P91" s="2" t="n"/>
-      <c r="Q91" s="2" t="n"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5619,12 +5619,12 @@
           <t>A frequency of past behaviour that is above a threshold.</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>frequency of past behaviour</t>
         </is>
       </c>
+      <c r="E92" s="2" t="n"/>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
@@ -5638,13 +5638,13 @@
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O92" s="2" t="n"/>
       <c r="P92" s="2" t="n"/>
-      <c r="Q92" s="2" t="n"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5670,12 +5670,12 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. For example, completing a university bachelor's or master's course of study, medical school or other professional school. </t>
         </is>
       </c>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
+      <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
@@ -5693,13 +5693,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O93" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O93" s="3" t="n"/>
       <c r="P93" s="3" t="n"/>
-      <c r="Q93" s="3" t="n"/>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -5727,15 +5727,15 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
@@ -5752,13 +5752,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O94" s="2" t="n"/>
       <c r="P94" s="2" t="n"/>
-      <c r="Q94" s="2" t="n"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5784,12 +5784,12 @@
           <t>A personal attribute related to the highest level of education achieved.</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5815,13 +5815,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O95" s="2" t="n"/>
       <c r="P95" s="2" t="n"/>
-      <c r="Q95" s="2" t="n"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5847,7 +5847,7 @@
           <t>A process that is the sum of the totality of processes taking place in the spatiotemporal region occupied by a material entity or site, including processes on the surface of the entity or within the cavities to which it serves as host.</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>process</t>
         </is>
@@ -5881,15 +5881,15 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>personal history part</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>history of exposure to asbestos due to one's job</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
@@ -5906,13 +5906,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O97" s="2" t="n"/>
       <c r="P97" s="2" t="n"/>
-      <c r="Q97" s="2" t="n"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5940,15 +5940,15 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>personal history part</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>history of physical abuse by a parent</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="n"/>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
@@ -5965,13 +5965,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O98" s="2" t="n"/>
       <c r="P98" s="2" t="n"/>
-      <c r="Q98" s="2" t="n"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5997,12 +5997,12 @@
           <t>A person who does not own a residential facility and does not have an agreement with a residential facility owner that would enable them to live in a residential facility.</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E99" s="2" t="n"/>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="inlineStr">
@@ -6024,13 +6024,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O99" s="2" t="n"/>
+      <c r="P99" s="2" t="n"/>
+      <c r="Q99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P99" s="2" t="n"/>
-      <c r="Q99" s="2" t="n"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6056,12 +6056,12 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process and who manages their home as their main daily activity.</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E100" s="2" t="n"/>
       <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6083,13 +6083,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O100" s="2" t="n"/>
       <c r="P100" s="2" t="n"/>
-      <c r="Q100" s="2" t="n"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6115,12 +6115,12 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of the same sex.</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
+      <c r="E101" s="2" t="n"/>
       <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6142,13 +6142,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O101" s="2" t="n"/>
       <c r="P101" s="2" t="n"/>
-      <c r="Q101" s="2" t="n"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6174,7 +6174,7 @@
           <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of its residence function.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
@@ -6211,12 +6211,12 @@
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
+      <c r="E103" s="2" t="n"/>
       <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6242,13 +6242,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
+      <c r="Q103" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P103" s="2" t="n"/>
-      <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6274,12 +6274,12 @@
           <t>A personal attribute that is a time quality inhering in a person by virtue of how long since the person was born.</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E104" s="2" t="n"/>
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6301,13 +6301,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O104" s="2" t="inlineStr">
+      <c r="O104" s="2" t="n"/>
+      <c r="P104" s="2" t="n"/>
+      <c r="Q104" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
-      <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6333,12 +6333,12 @@
           <t>An object aggregate that consists of two or more people.</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
+      <c r="E105" s="2" t="n"/>
       <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
@@ -6380,7 +6380,7 @@
           <t>A cognitive representation of themselves by a person or group.</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>cognitive representation</t>
         </is>
@@ -6412,12 +6412,12 @@
           <t>A person who has previously been a resident of a country and is now resident in another country.</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
@@ -6435,13 +6435,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O107" s="2" t="n"/>
       <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="n"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6467,12 +6467,12 @@
           <t xml:space="preserve">A relationship status where the individual is in a legally formalised marriage or civil partnership. </t>
         </is>
       </c>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
+      <c r="E108" s="2" t="n"/>
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
@@ -6491,13 +6491,13 @@
 </t>
         </is>
       </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O108" s="2" t="n"/>
       <c r="P108" s="2" t="n"/>
-      <c r="Q108" s="2" t="n"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6523,12 +6523,12 @@
           <t>A relationship status where the individual has had the same partner for a significant length of time but is not in a legal union.</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
+      <c r="E109" s="2" t="n"/>
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
@@ -6550,13 +6550,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O109" s="2" t="n"/>
       <c r="P109" s="2" t="n"/>
-      <c r="Q109" s="2" t="n"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6582,12 +6582,12 @@
           <t>An employment status realised by an individual working for a company or other organisation without a pre-determined end date, with security of employment and known working conditions.</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E110" s="2" t="n"/>
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
@@ -6605,13 +6605,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O110" s="2" t="n"/>
       <c r="P110" s="2" t="n"/>
-      <c r="Q110" s="2" t="n"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6637,12 +6637,12 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position that is of a known, fixed duration with security of employment for that duration and certain working conditions.</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E111" s="2" t="n"/>
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
@@ -6660,13 +6660,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O111" s="2" t="n"/>
       <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="n"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6692,12 +6692,12 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position with uncertain duration or hours with unknown or low security of working conditions or pay.</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E112" s="2" t="n"/>
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
@@ -6715,13 +6715,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O112" s="2" t="n"/>
       <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="2" t="n"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6747,12 +6747,12 @@
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>individual income</t>
         </is>
       </c>
+      <c r="E113" s="2" t="n"/>
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
@@ -6770,13 +6770,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O113" s="2" t="n"/>
       <c r="P113" s="2" t="n"/>
-      <c r="Q113" s="2" t="n"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6802,12 +6802,12 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process due to possessing enough wealth to not need financial support from another person or require income from employment.</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E114" s="2" t="n"/>
       <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
@@ -6825,13 +6825,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O114" s="2" t="n"/>
       <c r="P114" s="2" t="n"/>
-      <c r="Q114" s="2" t="n"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6859,15 +6859,15 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>walks for 15 mins/day, never eats meat, attends school daily</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n"/>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
@@ -6884,13 +6884,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="O115" s="2" t="n"/>
+      <c r="P115" s="2" t="n"/>
+      <c r="Q115" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P115" s="2" t="n"/>
-      <c r="Q115" s="2" t="n"/>
       <c r="R115" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6916,12 +6916,12 @@
           <t>A personal attribute reflecting a benefit the person receives  derived from their capital or labour, usually measured in money.</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -6943,13 +6943,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O116" s="2" t="n"/>
+      <c r="P116" s="2" t="n"/>
+      <c r="Q116" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P116" s="2" t="n"/>
-      <c r="Q116" s="2" t="n"/>
       <c r="R116" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6975,12 +6975,12 @@
           <t>A social role that involves influencing other people to adopt new ideas or behaviours.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>social role</t>
         </is>
       </c>
+      <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
@@ -6998,13 +6998,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O117" s="2" t="n"/>
       <c r="P117" s="2" t="n"/>
-      <c r="Q117" s="2" t="n"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7030,12 +7030,12 @@
           <t>A student or trainee role realised by  currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
+      <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
       <c r="H118" s="3" t="n"/>
@@ -7053,13 +7053,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O118" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O118" s="3" t="n"/>
       <c r="P118" s="3" t="n"/>
-      <c r="Q118" s="3" t="n"/>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R118" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7085,12 +7085,12 @@
           <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
+      <c r="E119" s="2" t="n"/>
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
@@ -7108,13 +7108,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O119" s="2" t="n"/>
       <c r="P119" s="2" t="n"/>
-      <c r="Q119" s="2" t="n"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7140,12 +7140,12 @@
           <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>patient role</t>
         </is>
       </c>
+      <c r="E120" s="2" t="n"/>
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
@@ -7163,13 +7163,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O120" s="2" t="n"/>
       <c r="P120" s="2" t="n"/>
-      <c r="Q120" s="2" t="n"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7195,12 +7195,12 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D121" s="3" t="n"/>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
+      <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -7226,13 +7226,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O121" s="3" t="inlineStr">
+      <c r="O121" s="3" t="n"/>
+      <c r="P121" s="3" t="n"/>
+      <c r="Q121" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P121" s="3" t="n"/>
-      <c r="Q121" s="3" t="n"/>
       <c r="R121" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7258,7 +7258,7 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -7283,7 +7283,7 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="Q122" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
@@ -7310,12 +7310,12 @@
           <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n"/>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
+      <c r="E123" s="2" t="n"/>
       <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -7337,13 +7337,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O123" s="2" t="n"/>
       <c r="P123" s="2" t="n"/>
-      <c r="Q123" s="2" t="n"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7369,12 +7369,12 @@
           <t>A person who is exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E124" s="2" t="n"/>
       <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
@@ -7416,12 +7416,12 @@
           <t>A human population who are exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
+      <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
@@ -7465,15 +7465,15 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="n"/>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
@@ -7490,13 +7490,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O126" s="2" t="n"/>
+      <c r="P126" s="2" t="n"/>
+      <c r="Q126" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="2" t="n"/>
       <c r="R126" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7522,12 +7522,12 @@
           <t>A social role in which the holder is given or creates authority to exert influence on other members of a social group.</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>social role</t>
         </is>
       </c>
+      <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
@@ -7545,13 +7545,13 @@
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
       <c r="N127" s="2" t="n"/>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O127" s="2" t="n"/>
       <c r="P127" s="2" t="n"/>
-      <c r="Q127" s="2" t="n"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7577,7 +7577,7 @@
           <t>A mental capability that is realised in processes of communication involving language or in expressions of language.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>mental capability</t>
         </is>
@@ -7592,7 +7592,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="Q128" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
@@ -7619,12 +7619,12 @@
           <t>Disabled for at least 12 months.</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
+      <c r="E129" s="2" t="n"/>
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
@@ -7646,13 +7646,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O129" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O129" s="2" t="n"/>
       <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="n"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7679,12 +7679,12 @@
           <t>A frequency of past behaviour that is below a threshold.</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>frequency of past behaviour</t>
         </is>
       </c>
+      <c r="E130" s="2" t="n"/>
       <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
@@ -7698,13 +7698,13 @@
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
       <c r="N130" s="2" t="n"/>
-      <c r="O130" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O130" s="2" t="n"/>
       <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="n"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7730,12 +7730,12 @@
           <t>A biological sex associated with the ability to produce male gametes.</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n"/>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>biological sex</t>
         </is>
       </c>
+      <c r="E131" s="2" t="n"/>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
@@ -7753,13 +7753,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O131" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O131" s="2" t="n"/>
       <c r="P131" s="2" t="n"/>
-      <c r="Q131" s="2" t="n"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7785,12 +7785,12 @@
           <t>A gender identity as being male.</t>
         </is>
       </c>
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
+      <c r="E132" s="2" t="n"/>
       <c r="F132" s="2" t="n"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -7816,13 +7816,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O132" s="2" t="n"/>
       <c r="P132" s="2" t="n"/>
-      <c r="Q132" s="2" t="n"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7848,12 +7848,12 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
+      <c r="E133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="n"/>
@@ -7871,13 +7871,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O133" s="3" t="n"/>
       <c r="P133" s="3" t="n"/>
-      <c r="Q133" s="3" t="n"/>
+      <c r="Q133" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R133" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7903,12 +7903,12 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n"/>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
+      <c r="E134" s="2" t="n"/>
       <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
@@ -7926,13 +7926,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O134" s="2" t="n"/>
       <c r="P134" s="2" t="n"/>
-      <c r="Q134" s="2" t="n"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7960,15 +7960,15 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
+          <t>health status attribute</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>health status attribute</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="n"/>
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
@@ -7989,13 +7989,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O135" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O135" s="2" t="n"/>
       <c r="P135" s="2" t="n"/>
-      <c r="Q135" s="2" t="n"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8021,12 +8021,12 @@
           <t>A person living in  a household with at least one other person.</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n"/>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E136" s="2" t="n"/>
       <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
@@ -8048,13 +8048,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O136" s="2" t="n"/>
       <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="n"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8082,15 +8082,15 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="n"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
@@ -8111,13 +8111,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O137" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O137" s="2" t="n"/>
       <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="2" t="n"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8145,15 +8145,15 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
           <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="n"/>
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
@@ -8170,13 +8170,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O138" s="2" t="n"/>
       <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="n"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8204,15 +8204,15 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="n"/>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
@@ -8229,13 +8229,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O139" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O139" s="2" t="n"/>
       <c r="P139" s="2" t="n"/>
-      <c r="Q139" s="2" t="n"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8263,15 +8263,15 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="n"/>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
@@ -8292,13 +8292,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O140" s="2" t="n"/>
       <c r="P140" s="2" t="n"/>
-      <c r="Q140" s="2" t="n"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R140" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8324,12 +8324,12 @@
           <t>A person living alone in a household.</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E141" s="2" t="n"/>
       <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
@@ -8347,13 +8347,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O141" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O141" s="2" t="n"/>
       <c r="P141" s="2" t="n"/>
-      <c r="Q141" s="2" t="n"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R141" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8379,7 +8379,7 @@
           <t>A personal capability that includes mental processes in its realisation.</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>personal capability</t>
         </is>
@@ -8394,7 +8394,7 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr">
+      <c r="Q142" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
@@ -8421,12 +8421,12 @@
           <t>A parent who is female gender.</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
+      <c r="E143" s="2" t="n"/>
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
@@ -8444,13 +8444,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O143" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O143" s="2" t="n"/>
       <c r="P143" s="2" t="n"/>
-      <c r="Q143" s="2" t="n"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8476,12 +8476,12 @@
           <t xml:space="preserve">A family member who is a child relation of one's sibling and is male gender. </t>
         </is>
       </c>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E144" s="2" t="n"/>
       <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
@@ -8499,13 +8499,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O144" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O144" s="2" t="n"/>
       <c r="P144" s="2" t="n"/>
-      <c r="Q144" s="2" t="n"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8531,12 +8531,12 @@
           <t>A family member who is a child relation of one's sibling and is female gender.</t>
         </is>
       </c>
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E145" s="2" t="n"/>
       <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
@@ -8554,13 +8554,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O145" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O145" s="2" t="n"/>
       <c r="P145" s="2" t="n"/>
-      <c r="Q145" s="2" t="n"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8586,12 +8586,12 @@
           <t>A self-identity as not having a particular gender.</t>
         </is>
       </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
+      <c r="E146" s="2" t="n"/>
       <c r="F146" s="2" t="n"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -8613,13 +8613,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O146" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O146" s="2" t="n"/>
       <c r="P146" s="2" t="n"/>
-      <c r="Q146" s="2" t="n"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R146" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8645,12 +8645,12 @@
           <t>A gender identity as having a gender that is not well-described by the binary categories of male or female.</t>
         </is>
       </c>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
+      <c r="E147" s="2" t="n"/>
       <c r="F147" s="2" t="n"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -8672,13 +8672,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O147" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O147" s="2" t="n"/>
       <c r="P147" s="2" t="n"/>
-      <c r="Q147" s="2" t="n"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R147" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8704,12 +8704,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not having a paid job and not currently seeking to begin participating in an employment process.</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E148" s="2" t="n"/>
       <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
@@ -8727,13 +8727,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O148" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O148" s="2" t="n"/>
       <c r="P148" s="2" t="n"/>
-      <c r="Q148" s="2" t="n"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8759,12 +8759,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being unable to work due to illness or disability.</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E149" s="2" t="n"/>
       <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
@@ -8782,13 +8782,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O149" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O149" s="2" t="n"/>
       <c r="P149" s="2" t="n"/>
-      <c r="Q149" s="2" t="n"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R149" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8814,12 +8814,12 @@
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
+      <c r="E150" s="2" t="n"/>
       <c r="F150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
@@ -8861,12 +8861,12 @@
           <t>The number of years a person spent engaged in an education process.</t>
         </is>
       </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
+      <c r="E151" s="2" t="n"/>
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
@@ -8884,17 +8884,17 @@
           <t>number</t>
         </is>
       </c>
-      <c r="O151" s="2" t="inlineStr">
+      <c r="O151" s="2" t="n"/>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>education process</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
-      <c r="P151" s="2" t="inlineStr">
-        <is>
-          <t>education process</t>
-        </is>
-      </c>
-      <c r="Q151" s="2" t="n"/>
       <c r="R151" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8920,12 +8920,12 @@
           <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>personal role</t>
         </is>
       </c>
+      <c r="E152" s="2" t="n"/>
       <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
@@ -8943,13 +8943,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O152" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O152" s="2" t="n"/>
       <c r="P152" s="2" t="n"/>
-      <c r="Q152" s="2" t="n"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8975,12 +8975,12 @@
           <t>A person who lives in a residential facility they do not own  with the agreement of the residential facility owner, by virtue of the occupier bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E153" s="2" t="n"/>
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
@@ -8998,13 +8998,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O153" s="2" t="inlineStr">
+      <c r="O153" s="2" t="n"/>
+      <c r="P153" s="2" t="n"/>
+      <c r="Q153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P153" s="2" t="n"/>
-      <c r="Q153" s="2" t="n"/>
       <c r="R153" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9032,15 +9032,15 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
           <t>Scout leader, club chairperson</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
@@ -9057,13 +9057,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O154" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O154" s="2" t="n"/>
       <c r="P154" s="2" t="n"/>
-      <c r="Q154" s="2" t="n"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R154" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9089,12 +9089,12 @@
           <t>A sexual orientation of an individual who is sure of their sexual orientation and reports it as other than asexual, bisexual, heterosexual, homosexual, queer or questioning.</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
+      <c r="E155" s="2" t="n"/>
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
@@ -9112,13 +9112,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O155" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O155" s="2" t="n"/>
       <c r="P155" s="2" t="n"/>
-      <c r="Q155" s="2" t="n"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R155" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9144,12 +9144,12 @@
           <t>A social group that is part of a person’s social environmental system and with which the person does not identify.</t>
         </is>
       </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>social group</t>
         </is>
       </c>
+      <c r="E156" s="2" t="n"/>
       <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
@@ -9191,12 +9191,12 @@
           <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>patient role</t>
         </is>
       </c>
+      <c r="E157" s="2" t="n"/>
       <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
@@ -9214,13 +9214,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O157" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O157" s="2" t="n"/>
       <c r="P157" s="2" t="n"/>
-      <c r="Q157" s="2" t="n"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9246,12 +9246,12 @@
           <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
         </is>
       </c>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="E158" s="2" t="n"/>
       <c r="F158" s="2" t="n"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -9277,13 +9277,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O158" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O158" s="2" t="n"/>
       <c r="P158" s="2" t="n"/>
-      <c r="Q158" s="2" t="n"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R158" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9309,12 +9309,12 @@
           <t>A person who lives in a residential facility of which they are the residential facility owner</t>
         </is>
       </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E159" s="2" t="n"/>
       <c r="F159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
@@ -9333,13 +9333,13 @@
 </t>
         </is>
       </c>
-      <c r="O159" s="2" t="inlineStr">
+      <c r="O159" s="2" t="n"/>
+      <c r="P159" s="2" t="n"/>
+      <c r="Q159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P159" s="2" t="n"/>
-      <c r="Q159" s="2" t="n"/>
       <c r="R159" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9365,12 +9365,12 @@
           <t xml:space="preserve">A family member who is a key caretaker or immediate progenitor of a child. </t>
         </is>
       </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E160" s="2" t="n"/>
       <c r="F160" s="2" t="n"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -9392,13 +9392,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O160" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O160" s="2" t="n"/>
       <c r="P160" s="2" t="n"/>
-      <c r="Q160" s="2" t="n"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9424,12 +9424,12 @@
           <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
         </is>
       </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>interpersonal role</t>
         </is>
       </c>
+      <c r="E161" s="2" t="n"/>
       <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
@@ -9451,13 +9451,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O161" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O161" s="2" t="n"/>
       <c r="P161" s="2" t="n"/>
-      <c r="Q161" s="2" t="n"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R161" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9483,12 +9483,12 @@
           <t>A personal history part that includes a behaviour.</t>
         </is>
       </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E162" s="2" t="n"/>
       <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
@@ -9501,8 +9501,8 @@
       </c>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
-      <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="n"/>
+      <c r="O162" s="2" t="n"/>
       <c r="P162" s="2" t="n"/>
       <c r="Q162" s="2" t="n"/>
       <c r="R162" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
           <t>A past behaviour that is the target of an intervention.</t>
         </is>
       </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
+      <c r="E163" s="2" t="n"/>
       <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
@@ -9549,7 +9549,7 @@
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="n"/>
       <c r="P163" s="2" t="n"/>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
           <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -9592,7 +9592,7 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
+      <c r="Q164" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
@@ -9620,12 +9620,12 @@
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
+      <c r="E165" s="2" t="n"/>
       <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
@@ -9667,7 +9667,7 @@
           <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>extended organism</t>
         </is>
@@ -9699,12 +9699,12 @@
           <t>A &lt;person&gt; who is part of a social environmental system.</t>
         </is>
       </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E167" s="2" t="n"/>
       <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
@@ -9746,12 +9746,12 @@
           <t>A specifically dependent continuant that inheres in a person.</t>
         </is>
       </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
       </c>
+      <c r="E168" s="2" t="n"/>
       <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
@@ -9801,7 +9801,7 @@
           <t>A bodily disposition whose realization ordinarily brings benefits to an organism or group of organisms, where "ordinarily" means within a typical range or context.</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>bodily disposition</t>
         </is>
@@ -9844,12 +9844,12 @@
           <t>A history that is of a person.</t>
         </is>
       </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>history</t>
         </is>
       </c>
+      <c r="E170" s="2" t="n"/>
       <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
@@ -9891,12 +9891,12 @@
           <t xml:space="preserve">A personal history part that includes a change from a less desired behaviour pattern to a more desired behaviour pattern followed by a temporary reversion to the previous behaviour pattern. </t>
         </is>
       </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E171" s="2" t="n"/>
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
@@ -9914,13 +9914,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O171" s="2" t="n"/>
+      <c r="P171" s="2" t="n"/>
+      <c r="Q171" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P171" s="2" t="n"/>
-      <c r="Q171" s="2" t="n"/>
       <c r="R171" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9946,12 +9946,12 @@
           <t xml:space="preserve">A personal history part that includes experience of events that influence behaviour. </t>
         </is>
       </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E172" s="2" t="n"/>
       <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
@@ -9969,13 +9969,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O172" s="2" t="inlineStr">
+      <c r="O172" s="2" t="n"/>
+      <c r="P172" s="2" t="n"/>
+      <c r="Q172" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P172" s="2" t="n"/>
-      <c r="Q172" s="2" t="n"/>
       <c r="R172" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10001,12 +10001,12 @@
           <t>A personal history part of exposure to an intervention targeting the same outcome as the current intervention.</t>
         </is>
       </c>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E173" s="2" t="n"/>
       <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
@@ -10024,13 +10024,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O173" s="2" t="n"/>
+      <c r="P173" s="2" t="n"/>
+      <c r="Q173" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P173" s="2" t="n"/>
-      <c r="Q173" s="2" t="n"/>
       <c r="R173" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10056,12 +10056,12 @@
           <t>A personal history part  that includes exposure to a prior intervention targeting the same outcome behaviour as the current intervention.</t>
         </is>
       </c>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E174" s="2" t="n"/>
       <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
@@ -10079,13 +10079,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O174" s="2" t="inlineStr">
+      <c r="O174" s="2" t="n"/>
+      <c r="P174" s="2" t="n"/>
+      <c r="Q174" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P174" s="2" t="n"/>
-      <c r="Q174" s="2" t="n"/>
       <c r="R174" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10111,12 +10111,12 @@
           <t>A personal history part that includes exposure to the same intervention as the current intervention.</t>
         </is>
       </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E175" s="2" t="n"/>
       <c r="F175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
@@ -10138,13 +10138,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O175" s="2" t="n"/>
+      <c r="P175" s="2" t="n"/>
+      <c r="Q175" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P175" s="2" t="n"/>
-      <c r="Q175" s="2" t="n"/>
       <c r="R175" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10170,17 +10170,17 @@
           <t>A process that is part of a personal history.</t>
         </is>
       </c>
-      <c r="D176" s="2" t="n"/>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
           <t>'process' and 'part of' some 'personal history'</t>
         </is>
       </c>
+      <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
@@ -10221,12 +10221,12 @@
           <t xml:space="preserve">A personal history part  that includes exposure to one or more interventions. </t>
         </is>
       </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
+      <c r="E177" s="2" t="n"/>
       <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
@@ -10244,13 +10244,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O177" s="2" t="inlineStr">
+      <c r="O177" s="2" t="n"/>
+      <c r="P177" s="2" t="n"/>
+      <c r="Q177" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P177" s="2" t="n"/>
-      <c r="Q177" s="2" t="n"/>
       <c r="R177" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10278,15 +10278,15 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
           <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="n"/>
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
@@ -10303,13 +10303,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O178" s="2" t="inlineStr">
+      <c r="O178" s="2" t="n"/>
+      <c r="P178" s="2" t="n"/>
+      <c r="Q178" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P178" s="2" t="n"/>
-      <c r="Q178" s="2" t="n"/>
       <c r="R178" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10335,12 +10335,12 @@
           <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
+      <c r="E179" s="2" t="n"/>
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
@@ -10392,15 +10392,15 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
           <t>susceptibility to addiction, vulnerability to depression</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="n"/>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
@@ -10417,13 +10417,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O180" s="2" t="inlineStr">
+      <c r="O180" s="2" t="n"/>
+      <c r="P180" s="2" t="n"/>
+      <c r="Q180" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P180" s="2" t="n"/>
-      <c r="Q180" s="2" t="n"/>
       <c r="R180" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10449,12 +10449,12 @@
           <t>A personal vulnerability towards performing a behaviour that causes net harm.</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>personal vulnerability</t>
         </is>
       </c>
+      <c r="E181" s="2" t="n"/>
       <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="inlineStr">
@@ -10476,13 +10476,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O181" s="2" t="inlineStr">
+      <c r="O181" s="2" t="n"/>
+      <c r="P181" s="2" t="n"/>
+      <c r="Q181" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P181" s="2" t="n"/>
-      <c r="Q181" s="2" t="n"/>
       <c r="R181" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10508,12 +10508,12 @@
           <t>A geographic location in which a person resides.</t>
         </is>
       </c>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>geographic location</t>
         </is>
       </c>
+      <c r="E182" s="2" t="n"/>
       <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
@@ -10531,13 +10531,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O182" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O182" s="2" t="n"/>
       <c r="P182" s="2" t="n"/>
-      <c r="Q182" s="2" t="n"/>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R182" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10563,7 +10563,7 @@
           <t>An insured party role that inheres in a person who participates in the creation of the insurance contract and is eligible to receive benefits as specified by the insurance contract.</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>insured party role</t>
         </is>
@@ -10578,7 +10578,7 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr">
+      <c r="Q183" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
@@ -10607,16 +10607,16 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="n"/>
       <c r="G184" s="2" t="n"/>
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
@@ -10653,12 +10653,12 @@
           <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
+      <c r="E185" s="2" t="n"/>
       <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
@@ -10676,13 +10676,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O185" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O185" s="2" t="n"/>
       <c r="P185" s="2" t="n"/>
-      <c r="Q185" s="2" t="n"/>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R185" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10708,12 +10708,12 @@
           <t>A &lt;disposition&gt; that decreases the likelihood of engaging with harmful behaviour.</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>disposition</t>
         </is>
       </c>
+      <c r="E186" s="2" t="n"/>
       <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
@@ -10731,13 +10731,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O186" s="2" t="inlineStr">
+      <c r="O186" s="2" t="n"/>
+      <c r="P186" s="2" t="n"/>
+      <c r="Q186" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="P186" s="2" t="n"/>
-      <c r="Q186" s="2" t="n"/>
       <c r="R186" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10763,7 +10763,7 @@
           <t>A specifically dependent continuant that, in contrast to roles and dispositions, does not require any further process in order to be realized.</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
@@ -10797,15 +10797,15 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
           <t>12 acres, a flock of 20 goats</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="n"/>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
@@ -10822,17 +10822,17 @@
           <t>number</t>
         </is>
       </c>
-      <c r="O188" s="2" t="inlineStr">
+      <c r="O188" s="2" t="n"/>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>valuable material resource owned</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
-      <c r="P188" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
-      <c r="Q188" s="2" t="n"/>
       <c r="R188" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10858,12 +10858,12 @@
           <t>A sexual orientation that is not exclusively homosexual or heterosexual, or of a person who does not identify with heterosexual, homosexual or bisexual labels.</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
+      <c r="E189" s="2" t="n"/>
       <c r="F189" s="2" t="n"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -10885,13 +10885,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O189" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O189" s="2" t="n"/>
       <c r="P189" s="2" t="n"/>
-      <c r="Q189" s="2" t="n"/>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R189" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10917,12 +10917,12 @@
           <t xml:space="preserve">A self-identity as being in the process of exploring one's sexual orientation. </t>
         </is>
       </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
+      <c r="E190" s="2" t="n"/>
       <c r="F190" s="2" t="n"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -10944,13 +10944,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O190" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O190" s="2" t="n"/>
       <c r="P190" s="2" t="n"/>
-      <c r="Q190" s="2" t="n"/>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R190" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10976,12 +10976,12 @@
           <t>A personal attribute that is whether an individual is connected or associated with another through romantic attraction or marriage.</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E191" s="2" t="n"/>
       <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
@@ -10999,13 +10999,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O191" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O191" s="2" t="n"/>
       <c r="P191" s="2" t="n"/>
-      <c r="Q191" s="2" t="n"/>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R191" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11033,15 +11033,15 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="n"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
           <t>NCIT_C103282</t>
@@ -11066,13 +11066,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O192" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O192" s="2" t="n"/>
       <c r="P192" s="2" t="n"/>
-      <c r="Q192" s="2" t="n"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R192" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11098,12 +11098,12 @@
           <t>A person who lives in a residential facility they do not own without paying an agreed sum of money to the residential facility owner.</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E193" s="2" t="n"/>
       <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
@@ -11121,13 +11121,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O193" s="2" t="inlineStr">
+      <c r="O193" s="2" t="n"/>
+      <c r="P193" s="2" t="n"/>
+      <c r="Q193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P193" s="2" t="n"/>
-      <c r="Q193" s="2" t="n"/>
       <c r="R193" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11155,15 +11155,15 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
+          <t>rent-free occupier</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
           <t>squatters</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>rent-free occupier</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="n"/>
       <c r="G194" s="2" t="n"/>
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
@@ -11180,13 +11180,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O194" s="2" t="inlineStr">
+      <c r="O194" s="2" t="n"/>
+      <c r="P194" s="2" t="n"/>
+      <c r="Q194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P194" s="2" t="n"/>
-      <c r="Q194" s="2" t="n"/>
       <c r="R194" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11212,12 +11212,12 @@
           <t>A person who lives in a residential facility they do not own in return for paying an agreed sum of money to the residential facility owner</t>
         </is>
       </c>
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E195" s="2" t="n"/>
       <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
@@ -11235,13 +11235,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O195" s="2" t="inlineStr">
+      <c r="O195" s="2" t="n"/>
+      <c r="P195" s="2" t="n"/>
+      <c r="Q195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P195" s="2" t="n"/>
-      <c r="Q195" s="2" t="n"/>
       <c r="R195" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11269,15 +11269,15 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
+          <t>renter</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
           <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>renter</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="n"/>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
@@ -11294,13 +11294,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O196" s="2" t="inlineStr">
+      <c r="O196" s="2" t="n"/>
+      <c r="P196" s="2" t="n"/>
+      <c r="Q196" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
-      <c r="P196" s="2" t="n"/>
-      <c r="Q196" s="2" t="n"/>
       <c r="R196" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11326,12 +11326,12 @@
           <t>An owner of a residential facility.</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n"/>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
+      <c r="E197" s="2" t="n"/>
       <c r="F197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
@@ -11349,13 +11349,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O197" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O197" s="2" t="n"/>
       <c r="P197" s="2" t="n"/>
-      <c r="Q197" s="2" t="n"/>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R197" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11381,12 +11381,12 @@
           <t>A personal attribute inhering in a person who previously bore a role realised in an employment process but has withdrawn from that employment process, having concluded their working or professional career.</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E198" s="2" t="n"/>
       <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
@@ -11404,13 +11404,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O198" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O198" s="2" t="n"/>
       <c r="P198" s="2" t="n"/>
-      <c r="Q198" s="2" t="n"/>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R198" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11436,7 +11436,7 @@
           <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
@@ -11468,12 +11468,12 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
+      <c r="E200" s="3" t="n"/>
       <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="n"/>
@@ -11491,13 +11491,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O200" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O200" s="3" t="n"/>
       <c r="P200" s="3" t="n"/>
-      <c r="Q200" s="3" t="n"/>
+      <c r="Q200" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R200" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -11523,12 +11523,12 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
+      <c r="E201" s="2" t="n"/>
       <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
@@ -11546,13 +11546,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O201" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O201" s="2" t="n"/>
       <c r="P201" s="2" t="n"/>
-      <c r="Q201" s="2" t="n"/>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R201" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11578,12 +11578,12 @@
           <t>A person who has at least one parent who is an immigrant.</t>
         </is>
       </c>
-      <c r="D202" s="2" t="n"/>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
+      <c r="E202" s="2" t="n"/>
       <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
@@ -11601,13 +11601,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O202" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O202" s="2" t="n"/>
       <c r="P202" s="2" t="n"/>
-      <c r="Q202" s="2" t="n"/>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R202" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11633,12 +11633,12 @@
           <t>An employment status realised by a person earning income directly from customers, clients, or other organisations rather than as a specified salary or wages from an employer.</t>
         </is>
       </c>
-      <c r="D203" s="2" t="n"/>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
+      <c r="E203" s="2" t="n"/>
       <c r="F203" s="2" t="n"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -11664,13 +11664,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O203" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O203" s="2" t="n"/>
       <c r="P203" s="2" t="n"/>
-      <c r="Q203" s="2" t="n"/>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R203" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11696,7 +11696,7 @@
           <t>An identity that a person has about themselves.</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>identity</t>
         </is>
@@ -11728,12 +11728,12 @@
           <t xml:space="preserve">A personal attribute that is the pattern of a person's emotional, romantic and/or sexual attractions. </t>
         </is>
       </c>
-      <c r="D205" s="2" t="n"/>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E205" s="2" t="n"/>
       <c r="F205" s="2" t="n"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -11755,13 +11755,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O205" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O205" s="2" t="n"/>
       <c r="P205" s="2" t="n"/>
-      <c r="Q205" s="2" t="n"/>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R205" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11787,12 +11787,12 @@
           <t>A family member with whom the subject shares a parent.</t>
         </is>
       </c>
-      <c r="D206" s="2" t="n"/>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
+      <c r="E206" s="2" t="n"/>
       <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
@@ -11811,13 +11811,13 @@
 roles</t>
         </is>
       </c>
-      <c r="O206" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O206" s="2" t="n"/>
       <c r="P206" s="2" t="n"/>
-      <c r="Q206" s="2" t="n"/>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R206" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11843,12 +11843,12 @@
           <t>A relationship status where the individual is not in a relationship with another person.</t>
         </is>
       </c>
-      <c r="D207" s="2" t="n"/>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
+      <c r="E207" s="2" t="n"/>
       <c r="F207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
@@ -11866,13 +11866,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O207" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O207" s="2" t="n"/>
       <c r="P207" s="2" t="n"/>
-      <c r="Q207" s="2" t="n"/>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R207" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11898,12 +11898,12 @@
           <t>A personal attribute that holds within a given situation.</t>
         </is>
       </c>
-      <c r="D208" s="2" t="n"/>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E208" s="2" t="n"/>
       <c r="F208" s="2" t="n"/>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
@@ -11945,12 +11945,12 @@
           <t>A social grouping that identifies as such and sometimes acts collectively.</t>
         </is>
       </c>
-      <c r="D209" s="2" t="n"/>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>social grouping</t>
         </is>
       </c>
+      <c r="E209" s="2" t="n"/>
       <c r="F209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
@@ -11992,12 +11992,12 @@
           <t>A human population who share some common attribute that involves some form of social interaction.</t>
         </is>
       </c>
-      <c r="D210" s="2" t="n"/>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
+      <c r="E210" s="2" t="n"/>
       <c r="F210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
@@ -12043,12 +12043,12 @@
           <t>A personal role that is realised in human social processes.</t>
         </is>
       </c>
-      <c r="D211" s="2" t="n"/>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>personal role</t>
         </is>
       </c>
+      <c r="E211" s="2" t="n"/>
       <c r="F211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
@@ -12090,12 +12090,12 @@
           <t>A &lt;personal attribute&gt; that, together with other attributes, characterises a person’s position in society.</t>
         </is>
       </c>
-      <c r="D212" s="2" t="n"/>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E212" s="2" t="n"/>
       <c r="F212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
@@ -12141,7 +12141,7 @@
           <t xml:space="preserve">A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.  </t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
@@ -12175,15 +12175,15 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
           <t>Semi-routine and routine occupations, blue collar occupations</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="2" t="n"/>
@@ -12200,17 +12200,17 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O214" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O214" s="2" t="n"/>
       <c r="P214" s="2" t="inlineStr">
         <is>
           <t>socioeconomic status</t>
         </is>
       </c>
-      <c r="Q214" s="2" t="n"/>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R214" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12236,12 +12236,12 @@
           <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic status, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
         </is>
       </c>
-      <c r="D215" s="2" t="n"/>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
+      <c r="E215" s="2" t="n"/>
       <c r="F215" s="2" t="n"/>
       <c r="G215" s="2" t="n"/>
       <c r="H215" s="2" t="n"/>
@@ -12259,17 +12259,17 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O215" s="2" t="inlineStr">
+      <c r="O215" s="2" t="n"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>socioeconomic status</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
-      <c r="P215" s="2" t="inlineStr">
-        <is>
-          <t>socioeconomic status</t>
-        </is>
-      </c>
-      <c r="Q215" s="2" t="n"/>
       <c r="R215" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12295,12 +12295,12 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being a homemaker whose work includes caring for children.</t>
         </is>
       </c>
-      <c r="D216" s="2" t="n"/>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E216" s="2" t="n"/>
       <c r="F216" s="2" t="n"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -12322,13 +12322,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O216" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O216" s="2" t="n"/>
       <c r="P216" s="2" t="n"/>
-      <c r="Q216" s="2" t="n"/>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R216" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12354,12 +12354,12 @@
           <t>A parent in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D217" s="2" t="n"/>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
+      <c r="E217" s="2" t="n"/>
       <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -12381,13 +12381,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O217" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O217" s="2" t="n"/>
       <c r="P217" s="2" t="n"/>
-      <c r="Q217" s="2" t="n"/>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R217" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12413,12 +12413,12 @@
           <t>A sibling who is the child of one's step-parent.</t>
         </is>
       </c>
-      <c r="D218" s="2" t="n"/>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
+      <c r="E218" s="2" t="n"/>
       <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
@@ -12436,13 +12436,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O218" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O218" s="2" t="n"/>
       <c r="P218" s="2" t="n"/>
-      <c r="Q218" s="2" t="n"/>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R218" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12468,12 +12468,12 @@
           <t>A step-sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D219" s="2" t="n"/>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>step-sibling</t>
         </is>
       </c>
+      <c r="E219" s="2" t="n"/>
       <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
@@ -12491,13 +12491,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O219" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O219" s="2" t="n"/>
       <c r="P219" s="2" t="n"/>
-      <c r="Q219" s="2" t="n"/>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R219" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12523,12 +12523,12 @@
           <t>A child relation in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D220" s="2" t="n"/>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
+      <c r="E220" s="2" t="n"/>
       <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
@@ -12546,13 +12546,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O220" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O220" s="2" t="n"/>
       <c r="P220" s="2" t="n"/>
-      <c r="Q220" s="2" t="n"/>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R220" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12578,12 +12578,12 @@
           <t>A stepchild who is female gender.</t>
         </is>
       </c>
-      <c r="D221" s="2" t="n"/>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>stepchild</t>
         </is>
       </c>
+      <c r="E221" s="2" t="n"/>
       <c r="F221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
@@ -12601,13 +12601,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O221" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O221" s="2" t="n"/>
       <c r="P221" s="2" t="n"/>
-      <c r="Q221" s="2" t="n"/>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R221" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12633,12 +12633,12 @@
           <t>A step-parent who is male gender.</t>
         </is>
       </c>
-      <c r="D222" s="2" t="n"/>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>step-parent</t>
         </is>
       </c>
+      <c r="E222" s="2" t="n"/>
       <c r="F222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
@@ -12656,13 +12656,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O222" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O222" s="2" t="n"/>
       <c r="P222" s="2" t="n"/>
-      <c r="Q222" s="2" t="n"/>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R222" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12688,12 +12688,12 @@
           <t>A step-parent who is female gender.</t>
         </is>
       </c>
-      <c r="D223" s="2" t="n"/>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>step-parent</t>
         </is>
       </c>
+      <c r="E223" s="2" t="n"/>
       <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
@@ -12711,13 +12711,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O223" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O223" s="2" t="n"/>
       <c r="P223" s="2" t="n"/>
-      <c r="Q223" s="2" t="n"/>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R223" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12743,12 +12743,12 @@
           <t>A step-sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D224" s="2" t="n"/>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>step-sibling</t>
         </is>
       </c>
+      <c r="E224" s="2" t="n"/>
       <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
@@ -12766,13 +12766,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O224" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O224" s="2" t="n"/>
       <c r="P224" s="2" t="n"/>
-      <c r="Q224" s="2" t="n"/>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R224" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12798,12 +12798,12 @@
           <t>A stepchild who is male gender.</t>
         </is>
       </c>
-      <c r="D225" s="2" t="n"/>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>stepchild</t>
         </is>
       </c>
+      <c r="E225" s="2" t="n"/>
       <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
@@ -12821,13 +12821,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O225" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O225" s="2" t="n"/>
       <c r="P225" s="2" t="n"/>
-      <c r="Q225" s="2" t="n"/>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R225" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12853,12 +12853,12 @@
           <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
-      <c r="D226" s="2" t="n"/>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
+      <c r="E226" s="2" t="n"/>
       <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
@@ -12876,13 +12876,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O226" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O226" s="2" t="n"/>
       <c r="P226" s="2" t="n"/>
-      <c r="Q226" s="2" t="n"/>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R226" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12908,7 +12908,7 @@
           <t>A person between 13 and 19 years of age.</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -12923,7 +12923,7 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr">
+      <c r="Q227" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
@@ -12937,31 +12937,27 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015103</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>transgender</t>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>A gender identity that differs from the person's assigned sex at birth.</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="n"/>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n"/>
       <c r="F228" s="2" t="n"/>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:000096</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="n"/>
       <c r="H228" s="2" t="n"/>
       <c r="I228" s="2" t="n"/>
       <c r="J228" s="2" t="n"/>
@@ -12974,16 +12970,16 @@
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
-        </is>
-      </c>
-      <c r="O228" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="n"/>
       <c r="P228" s="2" t="n"/>
-      <c r="Q228" s="2" t="n"/>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R228" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12996,27 +12992,31 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015149</t>
+          <t>BCIO:015103</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>twin</t>
+          <t>transgender</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="n"/>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>sibling</t>
-        </is>
-      </c>
+          <t>A gender identity that differs from the person's assigned sex at birth.</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n"/>
       <c r="F229" s="2" t="n"/>
-      <c r="G229" s="2" t="n"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:000096</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="n"/>
       <c r="I229" s="2" t="n"/>
       <c r="J229" s="2" t="n"/>
@@ -13029,16 +13029,16 @@
       <c r="M229" s="2" t="n"/>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>people</t>
-        </is>
-      </c>
-      <c r="O229" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>attributes</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="n"/>
       <c r="P229" s="2" t="n"/>
-      <c r="Q229" s="2" t="n"/>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R229" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13051,25 +13051,25 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050492</t>
+          <t>BCIO:015149</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>unawareness of a behaviour</t>
+          <t>twin</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="n"/>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>situational personal attribute</t>
-        </is>
-      </c>
+          <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n"/>
       <c r="F230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="H230" s="2" t="n"/>
@@ -13084,16 +13084,16 @@
       <c r="M230" s="2" t="n"/>
       <c r="N230" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O230" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="n"/>
       <c r="P230" s="2" t="n"/>
-      <c r="Q230" s="2" t="n"/>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R230" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13106,25 +13106,25 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015154</t>
+          <t>BCIO:050492</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>uncle</t>
+          <t>unawareness of a behaviour</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>A family member who is the brother of one's parent.</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="n"/>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+          <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>situational personal attribute</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n"/>
       <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
@@ -13139,16 +13139,16 @@
       <c r="M231" s="2" t="n"/>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t>people</t>
-        </is>
-      </c>
-      <c r="O231" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="n"/>
       <c r="P231" s="2" t="n"/>
-      <c r="Q231" s="2" t="n"/>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13161,25 +13161,25 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050493</t>
+          <t>BCIO:015154</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>undecidedness about enacting a behaviour</t>
+          <t>uncle</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="n"/>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>situational personal attribute</t>
-        </is>
-      </c>
+          <t>A family member who is the brother of one's parent.</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n"/>
       <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
@@ -13194,16 +13194,16 @@
       <c r="M232" s="2" t="n"/>
       <c r="N232" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O232" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="n"/>
       <c r="P232" s="2" t="n"/>
-      <c r="Q232" s="2" t="n"/>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R232" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13214,143 +13214,139 @@
       <c r="U232" s="2" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050493</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>undecidedness about enacting a behaviour</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>situational personal attribute</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n"/>
+      <c r="F233" s="2" t="n"/>
+      <c r="G233" s="2" t="n"/>
+      <c r="H233" s="2" t="n"/>
+      <c r="I233" s="2" t="n"/>
+      <c r="J233" s="2" t="n"/>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="n"/>
+      <c r="M233" s="2" t="n"/>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="n"/>
+      <c r="P233" s="2" t="n"/>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="n"/>
+      <c r="T233" s="2" t="n"/>
+      <c r="U233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
         <is>
           <t>BCIO:015088</t>
         </is>
       </c>
-      <c r="B233" s="3" t="inlineStr">
+      <c r="B234" s="3" t="inlineStr">
         <is>
           <t>undergraduate student role</t>
         </is>
       </c>
-      <c r="C233" s="3" t="inlineStr">
+      <c r="C234" s="3" t="inlineStr">
         <is>
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D233" s="3" t="n"/>
-      <c r="E233" s="3" t="inlineStr">
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="F233" s="3" t="n"/>
-      <c r="G233" s="3" t="n"/>
-      <c r="H233" s="3" t="n"/>
-      <c r="I233" s="3" t="n"/>
-      <c r="J233" s="3" t="n"/>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="n"/>
-      <c r="M233" s="3" t="n"/>
-      <c r="N233" s="3" t="inlineStr">
+      <c r="E234" s="3" t="n"/>
+      <c r="F234" s="3" t="n"/>
+      <c r="G234" s="3" t="n"/>
+      <c r="H234" s="3" t="n"/>
+      <c r="I234" s="3" t="n"/>
+      <c r="J234" s="3" t="n"/>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="n"/>
+      <c r="M234" s="3" t="n"/>
+      <c r="N234" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O233" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P233" s="3" t="n"/>
-      <c r="Q233" s="3" t="n"/>
-      <c r="R233" s="3" t="inlineStr">
+      <c r="O234" s="3" t="n"/>
+      <c r="P234" s="3" t="n"/>
+      <c r="Q234" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R234" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="S233" s="3" t="n"/>
-      <c r="T233" s="3" t="n"/>
-      <c r="U233" s="3" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010089</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="n"/>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="n"/>
-      <c r="G234" s="2" t="n"/>
-      <c r="H234" s="2" t="n"/>
-      <c r="I234" s="2" t="n"/>
-      <c r="J234" s="2" t="n"/>
-      <c r="K234" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L234" s="2" t="n"/>
-      <c r="M234" s="2" t="n"/>
-      <c r="N234" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O234" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P234" s="2" t="n"/>
-      <c r="Q234" s="2" t="n"/>
-      <c r="R234" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S234" s="2" t="n"/>
-      <c r="T234" s="2" t="n"/>
-      <c r="U234" s="2" t="n"/>
+      <c r="S234" s="3" t="n"/>
+      <c r="T234" s="3" t="n"/>
+      <c r="U234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050977</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="n"/>
-      <c r="E235" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n"/>
       <c r="F235" s="2" t="n"/>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SDGIO_00010026 </t>
-        </is>
-      </c>
+      <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
       <c r="I235" s="2" t="n"/>
       <c r="J235" s="2" t="n"/>
@@ -13363,16 +13359,16 @@
       <c r="M235" s="2" t="n"/>
       <c r="N235" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
-        </is>
-      </c>
-      <c r="O235" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="n"/>
       <c r="P235" s="2" t="n"/>
-      <c r="Q235" s="2" t="n"/>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R235" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13385,27 +13381,31 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015064</t>
+          <t>BCIO:050977</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>unpaid carer for an adult status</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="n"/>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+          <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n"/>
       <c r="F236" s="2" t="n"/>
-      <c r="G236" s="2" t="n"/>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDGIO_00010026 </t>
+        </is>
+      </c>
       <c r="H236" s="2" t="n"/>
       <c r="I236" s="2" t="n"/>
       <c r="J236" s="2" t="n"/>
@@ -13418,16 +13418,16 @@
       <c r="M236" s="2" t="n"/>
       <c r="N236" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
-        </is>
-      </c>
-      <c r="O236" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+          <t>attributes</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="n"/>
       <c r="P236" s="2" t="n"/>
-      <c r="Q236" s="2" t="n"/>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R236" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13440,35 +13440,27 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015039</t>
+          <t>BCIO:015064</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>valuable material resource owned</t>
+          <t>unpaid carer for an adult status</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>An object aggregate under the control of some person or organisation which confers an economic benefit to that person or organisation in an economic system.</t>
+          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>farmland, jewellery, livestock</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n"/>
       <c r="F237" s="2" t="n"/>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>SDGIO:00010048</t>
-        </is>
-      </c>
+      <c r="G237" s="2" t="n"/>
       <c r="H237" s="2" t="n"/>
       <c r="I237" s="2" t="n"/>
       <c r="J237" s="2" t="n"/>
@@ -13479,10 +13471,18 @@
       </c>
       <c r="L237" s="2" t="n"/>
       <c r="M237" s="2" t="n"/>
-      <c r="N237" s="2" t="n"/>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>past behaviour</t>
+        </is>
+      </c>
       <c r="O237" s="2" t="n"/>
       <c r="P237" s="2" t="n"/>
-      <c r="Q237" s="2" t="n"/>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R237" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13495,31 +13495,35 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015041</t>
+          <t>BCIO:015039</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>value of valuable material resource owned</t>
+          <t>valuable material resource owned</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>A data item about the monetary value of a valuable material resource possessed by a person.</t>
+          <t>An object aggregate under the control of some person or organisation which confers an economic benefit to that person or organisation in an economic system.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>$400, 3000 euros</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="n"/>
-      <c r="G238" s="2" t="n"/>
+          <t>object aggregate</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>farmland, jewellery, livestock</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>SDGIO:00010048</t>
+        </is>
+      </c>
       <c r="H238" s="2" t="n"/>
       <c r="I238" s="2" t="n"/>
       <c r="J238" s="2" t="n"/>
@@ -13530,21 +13534,9 @@
       </c>
       <c r="L238" s="2" t="n"/>
       <c r="M238" s="2" t="n"/>
-      <c r="N238" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O238" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
-      <c r="P238" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
+      <c r="N238" s="2" t="n"/>
+      <c r="O238" s="2" t="n"/>
+      <c r="P238" s="2" t="n"/>
       <c r="Q238" s="2" t="n"/>
       <c r="R238" s="2" t="inlineStr">
         <is>
@@ -13556,114 +13548,122 @@
       <c r="U238" s="2" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015041</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>value of valuable material resource owned</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>A data item about the monetary value of a valuable material resource possessed by a person.</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>$400, 3000 euros</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="n"/>
+      <c r="H239" s="2" t="n"/>
+      <c r="I239" s="2" t="n"/>
+      <c r="J239" s="2" t="n"/>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="n"/>
+      <c r="M239" s="2" t="n"/>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="n"/>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>valuable material resource owned</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="n"/>
+      <c r="T239" s="2" t="n"/>
+      <c r="U239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
         <is>
           <t>BCIO:015086</t>
         </is>
       </c>
-      <c r="B239" s="3" t="inlineStr">
+      <c r="B240" s="3" t="inlineStr">
         <is>
           <t>vocational training student or trainee role</t>
         </is>
       </c>
-      <c r="C239" s="3" t="inlineStr">
+      <c r="C240" s="3" t="inlineStr">
         <is>
           <t>A student or trainee role realised by currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D239" s="3" t="n"/>
-      <c r="E239" s="3" t="inlineStr">
+      <c r="D240" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="F239" s="3" t="n"/>
-      <c r="G239" s="3" t="n"/>
-      <c r="H239" s="3" t="n"/>
-      <c r="I239" s="3" t="n"/>
-      <c r="J239" s="3" t="n"/>
-      <c r="K239" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L239" s="3" t="n"/>
-      <c r="M239" s="3" t="n"/>
-      <c r="N239" s="3" t="inlineStr">
+      <c r="E240" s="3" t="n"/>
+      <c r="F240" s="3" t="n"/>
+      <c r="G240" s="3" t="n"/>
+      <c r="H240" s="3" t="n"/>
+      <c r="I240" s="3" t="n"/>
+      <c r="J240" s="3" t="n"/>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="n"/>
+      <c r="M240" s="3" t="n"/>
+      <c r="N240" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O239" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P239" s="3" t="n"/>
-      <c r="Q239" s="3" t="n"/>
-      <c r="R239" s="3" t="inlineStr">
+      <c r="O240" s="3" t="n"/>
+      <c r="P240" s="3" t="n"/>
+      <c r="Q240" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R240" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="S239" s="3" t="n"/>
-      <c r="T239" s="3" t="n"/>
-      <c r="U239" s="3" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010087</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="n"/>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="n"/>
-      <c r="G240" s="2" t="n"/>
-      <c r="H240" s="2" t="n"/>
-      <c r="I240" s="2" t="n"/>
-      <c r="J240" s="2" t="n"/>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L240" s="2" t="n"/>
-      <c r="M240" s="2" t="n"/>
-      <c r="N240" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O240" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="P240" s="2" t="n"/>
-      <c r="Q240" s="2" t="n"/>
-      <c r="R240" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S240" s="2" t="n"/>
-      <c r="T240" s="2" t="n"/>
-      <c r="U240" s="2" t="n"/>
+      <c r="S240" s="3" t="n"/>
+      <c r="T240" s="3" t="n"/>
+      <c r="U240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -13681,12 +13681,12 @@
           <t>A personal attribute inhering in a person by virtue of that person working or assisting at a workplace without receiving remuneration.</t>
         </is>
       </c>
-      <c r="D241" s="2" t="n"/>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
+      <c r="E241" s="2" t="n"/>
       <c r="F241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="n"/>
@@ -13708,13 +13708,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O241" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O241" s="2" t="n"/>
       <c r="P241" s="2" t="n"/>
-      <c r="Q241" s="2" t="n"/>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R241" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13740,12 +13740,12 @@
           <t xml:space="preserve">A relationship status where the individual is no longer in a legally formalised marriage or civil partnership due to the death of their spouse or partner. </t>
         </is>
       </c>
-      <c r="D242" s="2" t="n"/>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
+      <c r="E242" s="2" t="n"/>
       <c r="F242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>
@@ -13763,13 +13763,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O242" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="O242" s="2" t="n"/>
       <c r="P242" s="2" t="n"/>
-      <c r="Q242" s="2" t="n"/>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R242" s="2" t="inlineStr">
         <is>
           <t>Published</t>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -1850,7 +1850,7 @@
           <t>population</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -12151,6 +12151,16 @@
           <t>population</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
           <t>External</t>
@@ -12158,67 +12168,67 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+      <c r="A214" s="3" t="inlineStr">
         <is>
           <t>BCIO:015068</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B214" s="3" t="inlineStr">
         <is>
           <t>socioeconomic status category</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C214" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A  data item about a category assigned to a person based on an assessment of a score calculated from various measures of their income, education, occupation, family size or household. </t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E214" s="2" t="n"/>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="E214" s="3" t="n"/>
+      <c r="F214" s="3" t="inlineStr">
         <is>
           <t>Semi-routine and routine occupations, blue collar occupations</t>
         </is>
       </c>
-      <c r="G214" s="2" t="n"/>
-      <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="n"/>
-      <c r="J214" s="2" t="n"/>
-      <c r="K214" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L214" s="2" t="n"/>
-      <c r="M214" s="2" t="n"/>
-      <c r="N214" s="2" t="inlineStr">
+      <c r="G214" s="3" t="n"/>
+      <c r="H214" s="3" t="n"/>
+      <c r="I214" s="3" t="n"/>
+      <c r="J214" s="3" t="n"/>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="n"/>
+      <c r="M214" s="3" t="n"/>
+      <c r="N214" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O214" s="2" t="n"/>
-      <c r="P214" s="2" t="inlineStr">
+      <c r="O214" s="3" t="n"/>
+      <c r="P214" s="3" t="inlineStr">
         <is>
           <t>socioeconomic status</t>
         </is>
       </c>
-      <c r="Q214" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R214" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S214" s="2" t="n"/>
-      <c r="T214" s="2" t="n"/>
-      <c r="U214" s="2" t="n"/>
+      <c r="Q214" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R214" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S214" s="3" t="n"/>
+      <c r="T214" s="3" t="n"/>
+      <c r="U214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -9504,7 +9504,11 @@
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="2" t="n"/>
       <c r="P162" s="2" t="n"/>
-      <c r="Q162" s="2" t="n"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9551,7 +9555,11 @@
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="2" t="n"/>
       <c r="P163" s="2" t="n"/>
-      <c r="Q163" s="2" t="n"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="R163" s="2" t="inlineStr">
         <is>
           <t>Published</t>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffffff"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12134,168 +12140,185 @@
       <c r="U212" s="2" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>BCIO:051022</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>socioeconomic position</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>A personal attribute reflecting a person's economic and social position in relation to others</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="4" t="n"/>
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>OPMI:0000121</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="H213" s="4" t="n"/>
+      <c r="I213" s="4" t="n"/>
+      <c r="J213" s="4" t="n"/>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="O213" s="4" t="n"/>
+      <c r="P213" s="4" t="n"/>
+      <c r="Q213" s="4" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R213" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="S213" s="4" t="n"/>
+      <c r="T213" s="4" t="n"/>
+      <c r="U213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015069</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>socioeconomic position score</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic position, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="n"/>
+      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="n"/>
+      <c r="M214" s="2" t="n"/>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="inlineStr">
         <is>
           <t>socioeconomic status</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.  </t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>attribute</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="3" t="inlineStr">
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="n"/>
+      <c r="T214" s="2" t="n"/>
+      <c r="U214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
         <is>
           <t>BCIO:015068</t>
         </is>
       </c>
-      <c r="B214" s="3" t="inlineStr">
+      <c r="B215" s="3" t="inlineStr">
         <is>
           <t>socioeconomic status category</t>
         </is>
       </c>
-      <c r="C214" s="3" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A  data item about a category assigned to a person based on an assessment of a score calculated from various measures of their income, education, occupation, family size or household. </t>
         </is>
       </c>
-      <c r="D214" s="3" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E214" s="3" t="n"/>
-      <c r="F214" s="3" t="inlineStr">
+      <c r="E215" s="3" t="n"/>
+      <c r="F215" s="3" t="inlineStr">
         <is>
           <t>Semi-routine and routine occupations, blue collar occupations</t>
         </is>
       </c>
-      <c r="G214" s="3" t="n"/>
-      <c r="H214" s="3" t="n"/>
-      <c r="I214" s="3" t="n"/>
-      <c r="J214" s="3" t="n"/>
-      <c r="K214" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L214" s="3" t="n"/>
-      <c r="M214" s="3" t="n"/>
-      <c r="N214" s="3" t="inlineStr">
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="3" t="n"/>
+      <c r="I215" s="3" t="n"/>
+      <c r="J215" s="3" t="n"/>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="n"/>
+      <c r="M215" s="3" t="n"/>
+      <c r="N215" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O214" s="3" t="n"/>
-      <c r="P214" s="3" t="inlineStr">
+      <c r="O215" s="3" t="n"/>
+      <c r="P215" s="3" t="inlineStr">
         <is>
           <t>socioeconomic status</t>
         </is>
       </c>
-      <c r="Q214" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R214" s="3" t="inlineStr">
+      <c r="Q215" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R215" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="S214" s="3" t="n"/>
-      <c r="T214" s="3" t="n"/>
-      <c r="U214" s="3" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015069</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>socioeconomic status score</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic status, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="n"/>
-      <c r="F215" s="2" t="n"/>
-      <c r="G215" s="2" t="n"/>
-      <c r="H215" s="2" t="n"/>
-      <c r="I215" s="2" t="n"/>
-      <c r="J215" s="2" t="n"/>
-      <c r="K215" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L215" s="2" t="n"/>
-      <c r="M215" s="2" t="n"/>
-      <c r="N215" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O215" s="2" t="n"/>
-      <c r="P215" s="2" t="inlineStr">
-        <is>
-          <t>socioeconomic status</t>
-        </is>
-      </c>
-      <c r="Q215" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
-      <c r="R215" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S215" s="2" t="n"/>
-      <c r="T215" s="2" t="n"/>
-      <c r="U215" s="2" t="n"/>
+      <c r="S215" s="3" t="n"/>
+      <c r="T215" s="3" t="n"/>
+      <c r="U215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -49,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ffffff"/>
+        <fgColor rgb="00ffe4b5"/>
       </patternFill>
     </fill>
   </fills>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="R213" s="4" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="S213" s="4" t="n"/>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffe4b5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,12 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12140,63 +12134,63 @@
       <c r="U212" s="2" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>BCIO:051022</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>socioeconomic position</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>A personal attribute reflecting a person's economic and social position in relation to others</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E213" s="4" t="n"/>
-      <c r="F213" s="4" t="n"/>
-      <c r="G213" s="4" t="inlineStr">
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="n"/>
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>OPMI:0000121</t>
         </is>
       </c>
-      <c r="H213" s="4" t="n"/>
-      <c r="I213" s="4" t="n"/>
-      <c r="J213" s="4" t="n"/>
-      <c r="K213" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L213" s="4" t="n"/>
-      <c r="M213" s="4" t="n"/>
-      <c r="N213" s="4" t="inlineStr">
+      <c r="H213" s="2" t="n"/>
+      <c r="I213" s="2" t="n"/>
+      <c r="J213" s="2" t="n"/>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="n"/>
+      <c r="M213" s="2" t="n"/>
+      <c r="N213" s="2" t="inlineStr">
         <is>
           <t>attribute</t>
         </is>
       </c>
-      <c r="O213" s="4" t="n"/>
-      <c r="P213" s="4" t="n"/>
-      <c r="Q213" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R213" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S213" s="4" t="n"/>
-      <c r="T213" s="4" t="n"/>
-      <c r="U213" s="4" t="n"/>
+      <c r="O213" s="2" t="n"/>
+      <c r="P213" s="2" t="n"/>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="n"/>
+      <c r="T213" s="2" t="n"/>
+      <c r="U213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -451,32 +451,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Informal definition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Logical definition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Logical definition</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-reference</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Examples</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-reference</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Informal definition</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -556,20 +556,20 @@
           <t>A linguistic capability that is realised by following and understanding speech in the intervention language.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Comprehend the German language</t>
+          <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Comprehend the German language</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -615,20 +615,20 @@
           <t>A linguistic capability that is realised by reading and understanding text in the intervention language.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The exclusion criteria were an inability to read English</t>
+          <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>The exclusion criteria were an inability to read English</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -674,20 +674,20 @@
           <t xml:space="preserve">A linguistic capability that is realised by producing speech  in the intervention language. </t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Able to speak Chinese.</t>
+          <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Able to speak Chinese.</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -733,20 +733,20 @@
           <t>A linguistic capability that is realised by generating written text in the intervention language.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Fluency in written English.</t>
+          <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Fluency in written English.</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -792,13 +792,13 @@
           <t>A highest level of formal education qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in a specialised discipline that culminated in the award of an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002048</t>
@@ -855,13 +855,13 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process devoted to advanced study and original research that led to the award of a PhD or equivalent level qualification. </t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -914,13 +914,13 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process intended to introduce very young children to a school-type environment. </t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
@@ -973,13 +973,13 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in subject areas more specialised than basic reading, writing and mathematics, with the overall goal of laying the foundation for lifelong learning and human development on which education systems may systematically expand further educational opportunities.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002036</t>
@@ -1036,13 +1036,13 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process which has as a prerequisite an undergraduate degree and which is intended to result in the acquisition and development of advanced academic or professional skills and knowledge in a specialised discipline, that culminated in the award of a Master's or equivalent degree.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
@@ -1095,13 +1095,13 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition of fundamental skills in reading, writing and mathematics.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>highest level of formal educational qualification achieved</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OMRSE_00002035  </t>
@@ -1158,24 +1158,24 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge that prepare participants for tertiary education or employment.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>OMRSE_00002040</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>graduated high school, International Baccaulaureate, A Levels</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>OMRSE_00002040</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that corresponds to the final stage of secondary education in most OECD countries. Instruction is often more organised along subject-matter lines than at ISCED 2 level and teachers typically need to have a higher level, or more subject-specific, qualifications than at ISCED 2. The entrance age to this level is typically 15 or 16 years. There are substantial differences in the typical duration of ISCED 3 programmes both between and within countries, typically ranging from 2 to 5 years of schooling. ISCED 3 may either be “terminal” (i.e. preparing students for direct entry into working life) and/or “preparatory” (i.e. preparing students for tertiary education).</t>
@@ -1225,13 +1225,13 @@
           <t>An adoptive sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>adoptive sibling</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
@@ -1280,13 +1280,13 @@
           <t xml:space="preserve">A child relation in a parent-child relationship established by a legal adoption process. </t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166130</t>
@@ -1339,13 +1339,13 @@
           <t>An adoptive child who is female gender.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>adoptive child</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
@@ -1394,13 +1394,13 @@
           <t>An adoptive parent who is male gender.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>adoptive parent</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
@@ -1449,13 +1449,13 @@
           <t>An adoptive parent who is female gender.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>adoptive parent</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
@@ -1504,13 +1504,13 @@
           <t>A parent in a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166129</t>
@@ -1563,13 +1563,13 @@
           <t>A sibling with whom the subject shares a parent through a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
@@ -1618,13 +1618,13 @@
           <t>An adoptive sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>adoptive sibling</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
@@ -1673,13 +1673,13 @@
           <t>An adoptive child who is male gender.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>adoptive child</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
           <t>A person who has reached maturity.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -1775,13 +1775,13 @@
           <t>A rent-free occupier who lives in the residential facility with the agreement of the residential facility owner.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>rent-free occupier</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
@@ -1830,13 +1830,13 @@
           <t xml:space="preserve">A sexual orientation of an individual who does not experience sexual attraction. </t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>NCIT_C155696</t>
@@ -1889,13 +1889,13 @@
           <t>A family member who is the sister of one's parent.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
@@ -1944,13 +1944,13 @@
           <t>An intervention participant who is exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>intervention participant</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
@@ -1995,13 +1995,13 @@
           <t>An intervention population who are exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>intervention population</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
@@ -2042,13 +2042,13 @@
           <t>A data item that is about the rate of individual human behaviour change.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
@@ -2093,13 +2093,13 @@
           <t>A person who has formed an intention to enact a specified behaviour, and has enacted that behaviour.</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
           <t>A person who has formed an intention to enact a specified behaviour, but has not acted on this intention.</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
@@ -2201,13 +2201,13 @@
           <t>A person who has not formed an intention to enact a specified behaviour.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">person </t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
@@ -2255,18 +2255,18 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>The number of times a person performs a behaviour within a specific period.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>The number of times a person performs a behaviour within a specific period.</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2312,13 +2312,13 @@
           <t>A biological sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>biological sibling</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
@@ -2367,13 +2367,13 @@
           <t>A child relation who is genetically related to their parent.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
@@ -2422,13 +2422,13 @@
           <t>A biological child who is female gender.</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>biological child</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
@@ -2477,13 +2477,13 @@
           <t>A biological parent who provided the sperm.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>biological parent</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
@@ -2532,13 +2532,13 @@
           <t>A biological parent who provided an egg.</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>biological parent</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
@@ -2587,13 +2587,13 @@
           <t>A parent who provided one of the gametes that resulted in one's conception.</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166114, GSSO:001986</t>
@@ -2646,13 +2646,13 @@
           <t>A bodily quality based on reproductive function or organs.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>bodily quality</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -2701,13 +2701,13 @@
           <t>A sibling with whom the subject shares a biological parent.</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
@@ -2756,13 +2756,13 @@
           <t>A biological sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>biological sibling</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -2811,13 +2811,13 @@
           <t>A biological child who is male gender.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>biological child</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -2866,13 +2866,13 @@
           <t>A sexual orientation of an individual who experiences sexual attraction to members of more than one sex.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84364</t>
@@ -2925,7 +2925,7 @@
           <t>A quality that inheres in some extended organism.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
@@ -2957,13 +2957,13 @@
           <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
@@ -3012,13 +3012,13 @@
           <t>A personal attribute as belonging to a group within a stratified system of categorisation based on a status conferred at birth based on descent, in which individuals have limited or no mobility due to custom or law.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
@@ -3071,13 +3071,13 @@
           <t xml:space="preserve">A person who has not yet reached maturity. </t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
@@ -3130,13 +3130,13 @@
           <t>A family member who is a person's first generation offspring.</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
@@ -3185,13 +3185,13 @@
           <t>A gender identity that matches the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>GSSO:004240</t>
@@ -3244,13 +3244,13 @@
           <t xml:space="preserve">A geographic location that is the country in which a person was born. </t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>geographic location</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>GENEPIO_0001094</t>
@@ -3303,13 +3303,13 @@
           <t>A family member who is a child relation of one's aunt or uncle.</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
@@ -3358,13 +3358,13 @@
           <t>A personal attribute in which the person has impaired physical or mental functioning that has a notable effect on their ability to do typical daily activities.</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
@@ -3413,20 +3413,20 @@
           <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>psychology, counselling, public health</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>psychology, counselling, public health</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>The division of knowledge and practice into different disciplines or fields is complex and depends on historical, social and structural factors</t>
@@ -3476,20 +3476,20 @@
           <t>An expertise discipline of the highest level of formal educational qualification a person has achieved.</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3535,13 +3535,13 @@
           <t>A relationship status where the individual was previously in a legally formalised relationship and this relationship has now ended or dissolved.</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
@@ -3590,13 +3590,13 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
@@ -3645,13 +3645,13 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
@@ -3700,13 +3700,13 @@
           <t>A &lt;social group&gt; of two people who interact and influence each other.</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>social group</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
@@ -3747,13 +3747,13 @@
           <t>A planned process wherein knowledge and skills is imparted.</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>planned process</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>education process in the Sustainable Development Goals Interface Ontology (SDGIO:00010001)</t>
@@ -3798,13 +3798,13 @@
           <t>An employment status realised by an individual being engaged in an activity or service for wages or salary.</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>NCIT_C25172</t>
@@ -3857,13 +3857,13 @@
           <t>An employment status realised by an individual working a standard number of hours defined as full-time by their employer.</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>OPMI:0000123</t>
@@ -3916,13 +3916,13 @@
           <t>An employment status realised by an individual working for recurring periods in which different groups of workers do the same jobs in relay.</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
@@ -3971,13 +3971,13 @@
           <t>An employment status realised by an individual whose working hours involving less than the standard or customary working time.</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>NCIT_C75562</t>
@@ -4030,13 +4030,13 @@
           <t>A quality inhering in a person by virtue of that person bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Sustainable Development Goals Interface Ontology (SDGIO:00010029)</t>
@@ -4094,13 +4094,13 @@
           <t>A self-identity as belonging to a social group or groups whose members have a common cultural or ancestral heritage.</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>EFO:0001799</t>
@@ -4157,13 +4157,13 @@
           <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
@@ -4212,13 +4212,13 @@
           <t>A data item that is the extent to which the person’s past behaviour has reached or exceeded a standard.</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
@@ -4267,13 +4267,13 @@
           <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>NCIT:C41256</t>
@@ -4326,13 +4326,13 @@
           <t>A parent who is male gender.</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
@@ -4381,13 +4381,13 @@
           <t>A biological sex associated with the ability to produce female gametes.</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>biological sex</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
@@ -4436,13 +4436,13 @@
           <t>A gender identity as being female.</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>GSSO:000089</t>
@@ -4499,13 +4499,13 @@
           <t>A foster sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>foster sibling</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
@@ -4554,13 +4554,13 @@
           <t xml:space="preserve">A child relation in a parent-child relationship created by a foster care arrangement. </t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
@@ -4609,13 +4609,13 @@
           <t>A foster child who is female gender.</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>foster child</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
@@ -4664,13 +4664,13 @@
           <t>A foster parent who is male gender.</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>foster parent</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
@@ -4719,13 +4719,13 @@
           <t>A foster parent who is female gender.</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>foster parent</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
@@ -4774,13 +4774,13 @@
           <t>A parent who cares for a child who has been placed with them in a foster care arrangement.</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>GSSO:001987</t>
@@ -4833,13 +4833,13 @@
           <t>A sibling who shares a parent through a parent-child relationship created by a foster care agreement.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
@@ -4888,13 +4888,13 @@
           <t>A foster sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>foster sibling</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
@@ -4943,13 +4943,13 @@
           <t>A foster child who is male gender.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>foster child</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
@@ -4998,13 +4998,13 @@
           <t>A behavioural frequency about the number of times a person has enacted a behaviour per unit of time.</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>behavioural frequency</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
@@ -5053,13 +5053,13 @@
           <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
@@ -5108,13 +5108,13 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
@@ -5163,13 +5163,13 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
@@ -5218,13 +5218,13 @@
           <t>A grandparent who is male gender.</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>grandparent</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
@@ -5273,13 +5273,13 @@
           <t>A grandparent who is female gender.</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>grandparent</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
@@ -5328,13 +5328,13 @@
           <t>A family member who is the parent of one's parent.</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
@@ -5383,13 +5383,13 @@
           <t xml:space="preserve">A personal history part that includes previously performing a behaviour. </t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
@@ -5438,20 +5438,20 @@
           <t>A policy holder role that inheres in a person who participates in the creation of an insurance contract designed to cover some or all of the cost of treating the insured person's illnesses or injuries as well as possibly providing preventive health care.</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>policy holder role</t>
-        </is>
-      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
+          <t>policy holder role</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5497,24 +5497,24 @@
           <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C16669</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
           <t>Having chicken pox, asthma, a heart attack</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C16669</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -5560,13 +5560,13 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of a different sex.</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84362</t>
@@ -5619,13 +5619,13 @@
           <t>A frequency of past behaviour that is above a threshold.</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>frequency of past behaviour</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
@@ -5670,13 +5670,13 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. For example, completing a university bachelor's or master's course of study, medical school or other professional school. </t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
@@ -5725,20 +5725,20 @@
           <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="n"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
           <t>A personal attribute related to the highest level of education achieved.</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NCIT_C17953 </t>
@@ -5847,7 +5847,7 @@
           <t>A process that is the sum of the totality of processes taking place in the spatiotemporal region occupied by a material entity or site, including processes on the surface of the entity or within the cavities to which it serves as host.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>process</t>
         </is>
@@ -5879,20 +5879,20 @@
           <t>A personal history part that includes exposure to a potentially harmful agent as a result of one's occupation.</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="n"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>history of exposure to asbestos due to one's job</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>history of exposure to asbestos due to one's job</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -5938,20 +5938,20 @@
           <t>A personal history part that includes experience of physical, sexual, or psychological maltreatment during the first 18 years of life.</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>history of physical abuse by a parent</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>history of physical abuse by a parent</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="n"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5997,13 +5997,13 @@
           <t>A person who does not own a residential facility and does not have an agreement with a residential facility owner that would enable them to live in a residential facility.</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -6056,13 +6056,13 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process and who manages their home as their main daily activity.</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>NCIT_C75560</t>
@@ -6115,13 +6115,13 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of the same sex.</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84363</t>
@@ -6174,7 +6174,7 @@
           <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of its residence function.</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
@@ -6211,13 +6211,13 @@
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EFO_0009695 </t>
@@ -6274,13 +6274,13 @@
           <t>A personal attribute that is a time quality inhering in a person by virtue of how long since the person was born.</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>PATO:0000011</t>
@@ -6333,13 +6333,13 @@
           <t>An object aggregate that consists of two or more people.</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E105" s="2" t="n"/>
-      <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
@@ -6380,7 +6380,7 @@
           <t>A cognitive representation of themselves by a person or group.</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>cognitive representation</t>
         </is>
@@ -6412,13 +6412,13 @@
           <t>A person who has previously been a resident of a country and is now resident in another country.</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
@@ -6467,13 +6467,13 @@
           <t xml:space="preserve">A relationship status where the individual is in a legally formalised marriage or civil partnership. </t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
@@ -6523,13 +6523,13 @@
           <t>A relationship status where the individual has had the same partner for a significant length of time but is not in a legal union.</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
@@ -6582,13 +6582,13 @@
           <t>An employment status realised by an individual working for a company or other organisation without a pre-determined end date, with security of employment and known working conditions.</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
@@ -6637,13 +6637,13 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position that is of a known, fixed duration with security of employment for that duration and certain working conditions.</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
@@ -6692,13 +6692,13 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position with uncertain duration or hours with unknown or low security of working conditions or pay.</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
@@ -6747,13 +6747,13 @@
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>individual income</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n"/>
-      <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
@@ -6802,13 +6802,13 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process due to possessing enough wealth to not need financial support from another person or require income from employment.</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
@@ -6857,20 +6857,20 @@
           <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
+          <t>bodily process</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
+        </is>
+      </c>
       <c r="J115" s="2" t="n"/>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -6916,13 +6916,13 @@
           <t>A personal attribute reflecting a benefit the person receives  derived from their capital or labour, usually measured in money.</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002061</t>
@@ -6975,13 +6975,13 @@
           <t>A social role that involves influencing other people to adopt new ideas or behaviours.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>social role</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
@@ -7030,13 +7030,13 @@
           <t>A student or trainee role realised by  currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="3" t="n"/>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="n"/>
@@ -7085,13 +7085,13 @@
           <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
@@ -7140,13 +7140,13 @@
           <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>patient role</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
@@ -7195,13 +7195,13 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="3" t="n"/>
+      <c r="E121" s="3" t="n"/>
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
           <t>OMRSE:00000092</t>
@@ -7258,7 +7258,7 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -7310,13 +7310,13 @@
           <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E123" s="2" t="n"/>
-      <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>NCIT_C92454</t>
@@ -7369,13 +7369,13 @@
           <t>A person who is exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
@@ -7416,13 +7416,13 @@
           <t>A human population who are exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n"/>
-      <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
@@ -7463,20 +7463,20 @@
           <t>A linguistic capability that is realised by using a language accurately and appropriately in more than one setting.</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linguistic capability </t>
-        </is>
-      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
+          <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
+        </is>
+      </c>
       <c r="J126" s="2" t="n"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -7522,13 +7522,13 @@
           <t>A social role in which the holder is given or creates authority to exert influence on other members of a social group.</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>social role</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n"/>
-      <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
@@ -7577,7 +7577,7 @@
           <t>A mental capability that is realised in processes of communication involving language or in expressions of language.</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>mental capability</t>
         </is>
@@ -7619,13 +7619,13 @@
           <t>Disabled for at least 12 months.</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
@@ -7679,13 +7679,13 @@
           <t>A frequency of past behaviour that is below a threshold.</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>frequency of past behaviour</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
@@ -7730,13 +7730,13 @@
           <t>A biological sex associated with the ability to produce male gametes.</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>biological sex</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
@@ -7785,13 +7785,13 @@
           <t>A gender identity as being male.</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="n"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>GSSO:000090</t>
@@ -7848,13 +7848,13 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D133" s="3" t="n"/>
+      <c r="E133" s="3" t="n"/>
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n"/>
@@ -7903,13 +7903,13 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n"/>
-      <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
@@ -7958,20 +7958,20 @@
           <t>A health status attribute that is having been prescribed the use of one or more drugs to improve, maintain or protect one's health.</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>health status attribute</t>
-        </is>
-      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" s="2" t="n"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
+          <t>health status attribute</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
-      <c r="I135" s="2" t="n"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
+        </is>
+      </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
           <t>This entity reflects having been prescribed a medication.  Actual use of the medicine would be captured as a behaviour</t>
@@ -8021,13 +8021,13 @@
           <t>A person living in  a household with at least one other person.</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n"/>
-      <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
@@ -8080,24 +8080,24 @@
           <t>A member of a multi-person household where all of the household members are related.</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="n"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
           <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="n"/>
-      <c r="I137" s="2" t="n"/>
       <c r="J137" s="2" t="n"/>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -8143,20 +8143,20 @@
           <t>A member of a multi-person household where none of the household members are related.</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="n"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
+          <t>member of a multi-person household</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
-      <c r="I138" s="2" t="n"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="n"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -8202,20 +8202,20 @@
           <t>A member of a multi-person household where some household members are related.</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" s="2" t="n"/>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
+          <t>member of a multi-person household</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
-      <c r="I139" s="2" t="n"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="n"/>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -8261,20 +8261,20 @@
           <t>A member of a multi-person household where some household members belong to different generations.</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="n"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
+          <t>member of a multi-person household</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="n"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
+        </is>
+      </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
           <t>A member of a multi-generational household lives with other people that are from more than one generation. A generation is all the people of about the same age within a society or within a particular family</t>
@@ -8324,13 +8324,13 @@
           <t>A person living alone in a household.</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n"/>
-      <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
@@ -8379,7 +8379,7 @@
           <t>A personal capability that includes mental processes in its realisation.</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>personal capability</t>
         </is>
@@ -8421,13 +8421,13 @@
           <t>A parent who is female gender.</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n"/>
-      <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
@@ -8476,13 +8476,13 @@
           <t xml:space="preserve">A family member who is a child relation of one's sibling and is male gender. </t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n"/>
-      <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
@@ -8531,13 +8531,13 @@
           <t>A family member who is a child relation of one's sibling and is female gender.</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
@@ -8586,13 +8586,13 @@
           <t>A self-identity as not having a particular gender.</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="n"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>GSSO:002331</t>
@@ -8645,13 +8645,13 @@
           <t>A gender identity as having a gender that is not well-described by the binary categories of male or female.</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n"/>
-      <c r="F147" s="2" t="n"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>GSSO:002328</t>
@@ -8704,13 +8704,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not having a paid job and not currently seeking to begin participating in an employment process.</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="n"/>
@@ -8759,13 +8759,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being unable to work due to illness or disability.</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="n"/>
@@ -8814,13 +8814,13 @@
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E150" s="2" t="n"/>
-      <c r="F150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
@@ -8861,13 +8861,13 @@
           <t>The number of years a person spent engaged in an education process.</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E151" s="2" t="n"/>
-      <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
@@ -8920,13 +8920,13 @@
           <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>personal role</t>
         </is>
       </c>
-      <c r="E152" s="2" t="n"/>
-      <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="n"/>
@@ -8975,13 +8975,13 @@
           <t>A person who lives in a residential facility they do not own  with the agreement of the residential facility owner, by virtue of the occupier bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E153" s="2" t="n"/>
-      <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
@@ -9030,20 +9030,20 @@
           <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" s="2" t="n"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Scout leader, club chairperson</t>
+          <t>role</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="n"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Scout leader, club chairperson</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="n"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -9089,13 +9089,13 @@
           <t>A sexual orientation of an individual who is sure of their sexual orientation and reports it as other than asexual, bisexual, heterosexual, homosexual, queer or questioning.</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n"/>
-      <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
@@ -9144,13 +9144,13 @@
           <t>A social group that is part of a person’s social environmental system and with which the person does not identify.</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>social group</t>
         </is>
       </c>
-      <c r="E156" s="2" t="n"/>
-      <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
@@ -9191,13 +9191,13 @@
           <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>patient role</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n"/>
-      <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
@@ -9246,13 +9246,13 @@
           <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n"/>
-      <c r="F158" s="2" t="n"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
           <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
@@ -9309,13 +9309,13 @@
           <t>A person who lives in a residential facility of which they are the residential facility owner</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n"/>
-      <c r="F159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
@@ -9365,13 +9365,13 @@
           <t xml:space="preserve">A family member who is a key caretaker or immediate progenitor of a child. </t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n"/>
-      <c r="F160" s="2" t="n"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>GSSO:001953</t>
@@ -9424,13 +9424,13 @@
           <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>interpersonal role</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n"/>
-      <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
@@ -9483,13 +9483,13 @@
           <t>A personal history part that includes a behaviour.</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E162" s="2" t="n"/>
-      <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
@@ -9534,13 +9534,13 @@
           <t>A past behaviour that is the target of an intervention.</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
-      <c r="E163" s="2" t="n"/>
-      <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
@@ -9585,7 +9585,7 @@
           <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -9628,13 +9628,13 @@
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
           <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>extended organism</t>
         </is>
@@ -9707,13 +9707,13 @@
           <t>A &lt;person&gt; who is part of a social environmental system.</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n"/>
-      <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
@@ -9754,13 +9754,13 @@
           <t>A specifically dependent continuant that inheres in a person.</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
       </c>
-      <c r="E168" s="2" t="n"/>
-      <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
@@ -9811,12 +9811,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t>The ability of someone to perform some useful and/or beneficial activity.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
           <t>bodily disposition</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>The ability of someone to perform some useful and/or beneficial activity.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9852,13 +9852,13 @@
           <t>A history that is of a person.</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>history</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n"/>
-      <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
@@ -9899,13 +9899,13 @@
           <t xml:space="preserve">A personal history part that includes a change from a less desired behaviour pattern to a more desired behaviour pattern followed by a temporary reversion to the previous behaviour pattern. </t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n"/>
-      <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
@@ -9954,13 +9954,13 @@
           <t xml:space="preserve">A personal history part that includes experience of events that influence behaviour. </t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
@@ -10009,13 +10009,13 @@
           <t>A personal history part of exposure to an intervention targeting the same outcome as the current intervention.</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n"/>
-      <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="n"/>
@@ -10064,13 +10064,13 @@
           <t>A personal history part  that includes exposure to a prior intervention targeting the same outcome behaviour as the current intervention.</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E174" s="2" t="n"/>
-      <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
@@ -10119,13 +10119,13 @@
           <t>A personal history part that includes exposure to the same intervention as the current intervention.</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E175" s="2" t="n"/>
-      <c r="F175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
@@ -10178,17 +10178,17 @@
           <t>A process that is part of a personal history.</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>'process' and 'part of' some 'personal history'</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>'process' and 'part of' some 'personal history'</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
@@ -10229,13 +10229,13 @@
           <t xml:space="preserve">A personal history part  that includes exposure to one or more interventions. </t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n"/>
-      <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
@@ -10284,20 +10284,20 @@
           <t>An attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="n"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
-      <c r="I178" s="2" t="n"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="n"/>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -10345,18 +10345,18 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n"/>
-      <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
-        </is>
-      </c>
+      <c r="I179" s="2" t="n"/>
       <c r="J179" s="2" t="inlineStr">
         <is>
           <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
@@ -10398,20 +10398,20 @@
           <t>A disposition to undergo undesirable change in response to exposure to another entity.</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
+      <c r="D180" s="2" t="n"/>
       <c r="E180" s="2" t="n"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>susceptibility to addiction, vulnerability to depression</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="n"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>susceptibility to addiction, vulnerability to depression</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="n"/>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -10457,13 +10457,13 @@
           <t>A personal vulnerability towards performing a behaviour that causes net harm.</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>personal vulnerability</t>
         </is>
       </c>
-      <c r="E181" s="2" t="n"/>
-      <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -10516,13 +10516,13 @@
           <t>A geographic location in which a person resides.</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>geographic location</t>
         </is>
       </c>
-      <c r="E182" s="2" t="n"/>
-      <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
           <t>An insured party role that inheres in a person who participates in the creation of the insurance contract and is eligible to receive benefits as specified by the insurance contract.</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>insured party role</t>
         </is>
@@ -10613,21 +10613,21 @@
           <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="n"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="n"/>
-      <c r="H184" s="2" t="n"/>
-      <c r="I184" s="2" t="n"/>
       <c r="J184" s="2" t="n"/>
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="n"/>
@@ -10661,13 +10661,13 @@
           <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E185" s="2" t="n"/>
-      <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="n"/>
@@ -10716,13 +10716,13 @@
           <t>A &lt;disposition&gt; that decreases the likelihood of engaging with harmful behaviour.</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>disposition</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n"/>
-      <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="n"/>
@@ -10771,7 +10771,7 @@
           <t>A specifically dependent continuant that, in contrast to roles and dispositions, does not require any further process in order to be realized.</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
@@ -10803,20 +10803,20 @@
           <t>A data item about the number of units of a valuable material resource possessed by a person.</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="D188" s="2" t="n"/>
       <c r="E188" s="2" t="n"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>12 acres, a flock of 20 goats</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
-      <c r="I188" s="2" t="n"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>12 acres, a flock of 20 goats</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="n"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -10866,13 +10866,13 @@
           <t>A sexual orientation that is not exclusively homosexual or heterosexual, or of a person who does not identify with heterosexual, homosexual or bisexual labels.</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>sexual orientation</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n"/>
-      <c r="F189" s="2" t="n"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
           <t>NCIT_C155691</t>
@@ -10925,13 +10925,13 @@
           <t xml:space="preserve">A self-identity as being in the process of exploring one's sexual orientation. </t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>self-identity</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n"/>
-      <c r="F190" s="2" t="n"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
           <t>NCIT_C155692</t>
@@ -10984,13 +10984,13 @@
           <t>A personal attribute that is whether an individual is connected or associated with another through romantic attraction or marriage.</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E191" s="2" t="n"/>
-      <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="n"/>
@@ -11039,24 +11039,24 @@
           <t xml:space="preserve">A personal attribute that is belonging to a group that is characterised by the practice of a common religion by the group members. </t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="D192" s="2" t="n"/>
       <c r="E192" s="2" t="n"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C103282</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C103282</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="n"/>
-      <c r="I192" s="2" t="n"/>
       <c r="J192" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage belonging to a specified religious group</t>
@@ -11106,13 +11106,13 @@
           <t>A person who lives in a residential facility they do not own without paying an agreed sum of money to the residential facility owner.</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E193" s="2" t="n"/>
-      <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="n"/>
@@ -11161,20 +11161,20 @@
           <t>A rent-free occupier who lives in the residential facility without the agreement of the residential facility owner.</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>rent-free occupier</t>
-        </is>
-      </c>
+      <c r="D194" s="2" t="n"/>
       <c r="E194" s="2" t="n"/>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>squatters</t>
+          <t>rent-free occupier</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
       <c r="H194" s="2" t="n"/>
-      <c r="I194" s="2" t="n"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>squatters</t>
+        </is>
+      </c>
       <c r="J194" s="2" t="n"/>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -11220,13 +11220,13 @@
           <t>A person who lives in a residential facility they do not own in return for paying an agreed sum of money to the residential facility owner</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n"/>
-      <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="n"/>
@@ -11275,20 +11275,20 @@
           <t>A renter who lives in a residential facility where the residential facility owner decides who can live in the residential facility based on their perceived social or economic needs.</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>renter</t>
-        </is>
-      </c>
+      <c r="D196" s="2" t="n"/>
       <c r="E196" s="2" t="n"/>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
+          <t>renter</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
-      <c r="I196" s="2" t="n"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
+        </is>
+      </c>
       <c r="J196" s="2" t="n"/>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -11334,13 +11334,13 @@
           <t>An owner of a residential facility.</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="E197" s="2" t="n"/>
-      <c r="F197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="n"/>
@@ -11389,13 +11389,13 @@
           <t>A personal attribute inhering in a person who previously bore a role realised in an employment process but has withdrawn from that employment process, having concluded their working or professional career.</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n"/>
-      <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
@@ -11444,7 +11444,7 @@
           <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
@@ -11476,13 +11476,13 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
@@ -11531,13 +11531,13 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n"/>
-      <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="n"/>
@@ -11586,13 +11586,13 @@
           <t>A person who has at least one parent who is an immigrant.</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="n"/>
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="E202" s="2" t="n"/>
-      <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
       <c r="I202" s="2" t="n"/>
@@ -11641,13 +11641,13 @@
           <t>An employment status realised by a person earning income directly from customers, clients, or other organisations rather than as a specified salary or wages from an employer.</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="n"/>
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E203" s="2" t="n"/>
-      <c r="F203" s="2" t="n"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NCIT_C116000 </t>
@@ -11704,7 +11704,7 @@
           <t>An identity that a person has about themselves.</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>identity</t>
         </is>
@@ -11736,13 +11736,13 @@
           <t xml:space="preserve">A personal attribute that is the pattern of a person's emotional, romantic and/or sexual attractions. </t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="n"/>
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E205" s="2" t="n"/>
-      <c r="F205" s="2" t="n"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84361</t>
@@ -11795,13 +11795,13 @@
           <t>A family member with whom the subject shares a parent.</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="n"/>
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n"/>
-      <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
       <c r="I206" s="2" t="n"/>
@@ -11851,13 +11851,13 @@
           <t>A relationship status where the individual is not in a relationship with another person.</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="n"/>
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n"/>
-      <c r="F207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="n"/>
@@ -11906,13 +11906,13 @@
           <t>A personal attribute that holds within a given situation.</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="n"/>
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E208" s="2" t="n"/>
-      <c r="F208" s="2" t="n"/>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="2" t="n"/>
@@ -11953,13 +11953,13 @@
           <t>A social grouping that identifies as such and sometimes acts collectively.</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n"/>
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>social grouping</t>
         </is>
       </c>
-      <c r="E209" s="2" t="n"/>
-      <c r="F209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="2" t="n"/>
@@ -12000,13 +12000,13 @@
           <t>A human population who share some common attribute that involves some form of social interaction.</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n"/>
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>human population</t>
         </is>
       </c>
-      <c r="E210" s="2" t="n"/>
-      <c r="F210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="2" t="n"/>
@@ -12051,13 +12051,13 @@
           <t>A personal role that is realised in human social processes.</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="n"/>
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>personal role</t>
         </is>
       </c>
-      <c r="E211" s="2" t="n"/>
-      <c r="F211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="2" t="n"/>
@@ -12098,13 +12098,13 @@
           <t>A &lt;personal attribute&gt; that, together with other attributes, characterises a person’s position in society.</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="n"/>
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E212" s="2" t="n"/>
-      <c r="F212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="2" t="n"/>
@@ -12149,13 +12149,13 @@
           <t>A personal attribute reflecting a person's economic and social position in relation to others</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E213" s="2" t="n"/>
-      <c r="F213" s="2" t="n"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
           <t>OPMI:0000121</t>
@@ -12173,7 +12173,7 @@
       <c r="M213" s="2" t="n"/>
       <c r="N213" s="2" t="inlineStr">
         <is>
-          <t>attribute</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O213" s="2" t="n"/>
@@ -12208,13 +12208,13 @@
           <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic position, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="E214" s="2" t="n"/>
-      <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="2" t="n"/>
@@ -12267,20 +12267,20 @@
           <t xml:space="preserve">A  data item about a category assigned to a person based on an assessment of a score calculated from various measures of their income, education, occupation, family size or household. </t>
         </is>
       </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="D215" s="3" t="n"/>
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Semi-routine and routine occupations, blue collar occupations</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G215" s="3" t="n"/>
       <c r="H215" s="3" t="n"/>
-      <c r="I215" s="3" t="n"/>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>Semi-routine and routine occupations, blue collar occupations</t>
+        </is>
+      </c>
       <c r="J215" s="3" t="n"/>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -12330,13 +12330,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being a homemaker whose work includes caring for children.</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D216" s="2" t="n"/>
+      <c r="E216" s="2" t="n"/>
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E216" s="2" t="n"/>
-      <c r="F216" s="2" t="n"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
           <t>NCIT_C148253</t>
@@ -12389,13 +12389,13 @@
           <t>A parent in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D217" s="2" t="n"/>
+      <c r="E217" s="2" t="n"/>
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="E217" s="2" t="n"/>
-      <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166116</t>
@@ -12448,13 +12448,13 @@
           <t>A sibling who is the child of one's step-parent.</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D218" s="2" t="n"/>
+      <c r="E218" s="2" t="n"/>
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E218" s="2" t="n"/>
-      <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
       <c r="I218" s="2" t="n"/>
@@ -12503,13 +12503,13 @@
           <t>A step-sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="n"/>
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>step-sibling</t>
         </is>
       </c>
-      <c r="E219" s="2" t="n"/>
-      <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
       <c r="I219" s="2" t="n"/>
@@ -12558,13 +12558,13 @@
           <t>A child relation in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="n"/>
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>child relation</t>
         </is>
       </c>
-      <c r="E220" s="2" t="n"/>
-      <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
       <c r="I220" s="2" t="n"/>
@@ -12613,13 +12613,13 @@
           <t>A stepchild who is female gender.</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="n"/>
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>stepchild</t>
         </is>
       </c>
-      <c r="E221" s="2" t="n"/>
-      <c r="F221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
       <c r="I221" s="2" t="n"/>
@@ -12668,13 +12668,13 @@
           <t>A step-parent who is male gender.</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="n"/>
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>step-parent</t>
         </is>
       </c>
-      <c r="E222" s="2" t="n"/>
-      <c r="F222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
       <c r="I222" s="2" t="n"/>
@@ -12723,13 +12723,13 @@
           <t>A step-parent who is female gender.</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="n"/>
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>step-parent</t>
         </is>
       </c>
-      <c r="E223" s="2" t="n"/>
-      <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
       <c r="I223" s="2" t="n"/>
@@ -12778,13 +12778,13 @@
           <t>A step-sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="n"/>
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>step-sibling</t>
         </is>
       </c>
-      <c r="E224" s="2" t="n"/>
-      <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
       <c r="I224" s="2" t="n"/>
@@ -12833,13 +12833,13 @@
           <t>A stepchild who is male gender.</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="n"/>
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>stepchild</t>
         </is>
       </c>
-      <c r="E225" s="2" t="n"/>
-      <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
       <c r="I225" s="2" t="n"/>
@@ -12888,13 +12888,13 @@
           <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="n"/>
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E226" s="2" t="n"/>
-      <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
       <c r="I226" s="2" t="n"/>
@@ -12943,7 +12943,7 @@
           <t>A person between 13 and 19 years of age.</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -12985,13 +12985,13 @@
           <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="n"/>
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E228" s="2" t="n"/>
-      <c r="F228" s="2" t="n"/>
       <c r="G228" s="2" t="n"/>
       <c r="H228" s="2" t="n"/>
       <c r="I228" s="2" t="n"/>
@@ -13040,13 +13040,13 @@
           <t>A gender identity that differs from the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="n"/>
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>gender identity</t>
         </is>
       </c>
-      <c r="E229" s="2" t="n"/>
-      <c r="F229" s="2" t="n"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
           <t>GSSO:000096</t>
@@ -13099,13 +13099,13 @@
           <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n"/>
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>sibling</t>
         </is>
       </c>
-      <c r="E230" s="2" t="n"/>
-      <c r="F230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="H230" s="2" t="n"/>
       <c r="I230" s="2" t="n"/>
@@ -13154,13 +13154,13 @@
           <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="n"/>
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>situational personal attribute</t>
         </is>
       </c>
-      <c r="E231" s="2" t="n"/>
-      <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
       <c r="I231" s="2" t="n"/>
@@ -13209,13 +13209,13 @@
           <t>A family member who is the brother of one's parent.</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="n"/>
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>family member</t>
         </is>
       </c>
-      <c r="E232" s="2" t="n"/>
-      <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
       <c r="I232" s="2" t="n"/>
@@ -13264,13 +13264,13 @@
           <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D233" s="2" t="n"/>
+      <c r="E233" s="2" t="n"/>
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>situational personal attribute</t>
         </is>
       </c>
-      <c r="E233" s="2" t="n"/>
-      <c r="F233" s="2" t="n"/>
       <c r="G233" s="2" t="n"/>
       <c r="H233" s="2" t="n"/>
       <c r="I233" s="2" t="n"/>
@@ -13319,13 +13319,13 @@
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D234" s="3" t="inlineStr">
+      <c r="D234" s="3" t="n"/>
+      <c r="E234" s="3" t="n"/>
+      <c r="F234" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E234" s="3" t="n"/>
-      <c r="F234" s="3" t="n"/>
       <c r="G234" s="3" t="n"/>
       <c r="H234" s="3" t="n"/>
       <c r="I234" s="3" t="n"/>
@@ -13374,13 +13374,13 @@
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="n"/>
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E235" s="2" t="n"/>
-      <c r="F235" s="2" t="n"/>
       <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
       <c r="I235" s="2" t="n"/>
@@ -13429,13 +13429,13 @@
           <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n"/>
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>employment status</t>
         </is>
       </c>
-      <c r="E236" s="2" t="n"/>
-      <c r="F236" s="2" t="n"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SDGIO_00010026 </t>
@@ -13488,13 +13488,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D237" s="2" t="n"/>
+      <c r="E237" s="2" t="n"/>
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E237" s="2" t="n"/>
-      <c r="F237" s="2" t="n"/>
       <c r="G237" s="2" t="n"/>
       <c r="H237" s="2" t="n"/>
       <c r="I237" s="2" t="n"/>
@@ -13543,24 +13543,24 @@
           <t>An object aggregate under the control of some person or organisation which confers an economic benefit to that person or organisation in an economic system.</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
+      <c r="D238" s="2" t="n"/>
       <c r="E238" s="2" t="n"/>
       <c r="F238" s="2" t="inlineStr">
         <is>
+          <t>object aggregate</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>SDGIO:00010048</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="n"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
           <t>farmland, jewellery, livestock</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>SDGIO:00010048</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="n"/>
-      <c r="I238" s="2" t="n"/>
       <c r="J238" s="2" t="n"/>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -13598,20 +13598,20 @@
           <t>A data item about the monetary value of a valuable material resource possessed by a person.</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="D239" s="2" t="n"/>
       <c r="E239" s="2" t="n"/>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>$400, 3000 euros</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
       <c r="H239" s="2" t="n"/>
-      <c r="I239" s="2" t="n"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>$400, 3000 euros</t>
+        </is>
+      </c>
       <c r="J239" s="2" t="n"/>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -13661,13 +13661,13 @@
           <t>A student or trainee role realised by currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D240" s="3" t="inlineStr">
+      <c r="D240" s="3" t="n"/>
+      <c r="E240" s="3" t="n"/>
+      <c r="F240" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E240" s="3" t="n"/>
-      <c r="F240" s="3" t="n"/>
       <c r="G240" s="3" t="n"/>
       <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
@@ -13716,13 +13716,13 @@
           <t>A personal attribute inhering in a person by virtue of that person working or assisting at a workplace without receiving remuneration.</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="n"/>
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E241" s="2" t="n"/>
-      <c r="F241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="n"/>
       <c r="I241" s="2" t="n"/>
@@ -13775,13 +13775,13 @@
           <t xml:space="preserve">A relationship status where the individual is no longer in a legally formalised marriage or civil partnership due to the death of their spouse or partner. </t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n"/>
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>relationship status</t>
         </is>
       </c>
-      <c r="E242" s="2" t="n"/>
-      <c r="F242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>
       <c r="I242" s="2" t="n"/>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -6196,67 +6196,67 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>BCIO:015027</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>household income</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EFO_0009695 </t>
         </is>
       </c>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
         <is>
           <t>household</t>
         </is>
       </c>
-      <c r="M103" s="2" t="n"/>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="M103" s="3" t="n"/>
+      <c r="N103" s="3" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="O103" s="2" t="n"/>
-      <c r="P103" s="2" t="n"/>
-      <c r="Q103" s="2" t="inlineStr">
+      <c r="O103" s="3" t="n"/>
+      <c r="P103" s="3" t="n"/>
+      <c r="Q103" s="3" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="R103" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S103" s="2" t="n"/>
-      <c r="T103" s="2" t="n"/>
-      <c r="U103" s="2" t="n"/>
+      <c r="R103" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S103" s="3" t="n"/>
+      <c r="T103" s="3" t="n"/>
+      <c r="U103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6732,59 +6732,59 @@
       <c r="U112" s="2" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>BCIO:015037</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>income-related welfare benefit</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="D113" s="3" t="n"/>
+      <c r="E113" s="3" t="n"/>
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>individual income</t>
         </is>
       </c>
-      <c r="G113" s="2" t="n"/>
-      <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="n"/>
-      <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n"/>
-      <c r="M113" s="2" t="n"/>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="G113" s="3" t="n"/>
+      <c r="H113" s="3" t="n"/>
+      <c r="I113" s="3" t="n"/>
+      <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="n"/>
+      <c r="M113" s="3" t="n"/>
+      <c r="N113" s="3" t="inlineStr">
         <is>
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O113" s="2" t="n"/>
-      <c r="P113" s="2" t="n"/>
-      <c r="Q113" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R113" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S113" s="2" t="n"/>
-      <c r="T113" s="2" t="n"/>
-      <c r="U113" s="2" t="n"/>
+      <c r="O113" s="3" t="n"/>
+      <c r="P113" s="3" t="n"/>
+      <c r="Q113" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R113" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S113" s="3" t="n"/>
+      <c r="T113" s="3" t="n"/>
+      <c r="U113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -451,32 +451,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Logical definition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-reference</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Logical definition</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-reference</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Examples</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -556,20 +556,20 @@
           <t>A linguistic capability that is realised by following and understanding speech in the intervention language.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linguistic capability </t>
+          <t>Comprehend the German language</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Comprehend the German language</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -615,20 +615,20 @@
           <t>A linguistic capability that is realised by reading and understanding text in the intervention language.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linguistic capability </t>
+          <t>The exclusion criteria were an inability to read English</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>The exclusion criteria were an inability to read English</t>
-        </is>
-      </c>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -674,20 +674,20 @@
           <t xml:space="preserve">A linguistic capability that is realised by producing speech  in the intervention language. </t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linguistic capability </t>
+          <t>Able to speak Chinese.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Able to speak Chinese.</t>
-        </is>
-      </c>
+      <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -733,20 +733,20 @@
           <t>A linguistic capability that is realised by generating written text in the intervention language.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linguistic capability </t>
+          <t>Fluency in written English.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Fluency in written English.</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -792,13 +792,13 @@
           <t>A highest level of formal education qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in a specialised discipline that culminated in the award of an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002048</t>
@@ -855,13 +855,13 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process devoted to advanced study and original research that led to the award of a PhD or equivalent level qualification. </t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -914,13 +914,13 @@
           <t xml:space="preserve">A highest level of formal educational qualification achieved after participating in an education process intended to introduce very young children to a school-type environment. </t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
@@ -973,13 +973,13 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge in subject areas more specialised than basic reading, writing and mathematics, with the overall goal of laying the foundation for lifelong learning and human development on which education systems may systematically expand further educational opportunities.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002036</t>
@@ -1036,13 +1036,13 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process which has as a prerequisite an undergraduate degree and which is intended to result in the acquisition and development of advanced academic or professional skills and knowledge in a specialised discipline, that culminated in the award of a Master's or equivalent degree.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
@@ -1095,13 +1095,13 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition of fundamental skills in reading, writing and mathematics.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>highest level of formal educational qualification achieved</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OMRSE_00002035  </t>
@@ -1158,11 +1158,15 @@
           <t>A highest level of formal educational qualification achieved after participating in an education process intended to result in the acquisition and development of skills and knowledge that prepare participants for tertiary education or employment.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>highest level of formal educational qualification achieved</t>
+          <t>graduated high school, International Baccaulaureate, A Levels</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1171,11 +1175,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>graduated high school, International Baccaulaureate, A Levels</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that corresponds to the final stage of secondary education in most OECD countries. Instruction is often more organised along subject-matter lines than at ISCED 2 level and teachers typically need to have a higher level, or more subject-specific, qualifications than at ISCED 2. The entrance age to this level is typically 15 or 16 years. There are substantial differences in the typical duration of ISCED 3 programmes both between and within countries, typically ranging from 2 to 5 years of schooling. ISCED 3 may either be “terminal” (i.e. preparing students for direct entry into working life) and/or “preparatory” (i.e. preparing students for tertiary education).</t>
@@ -1225,13 +1225,13 @@
           <t>An adoptive sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>adoptive sibling</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>adoptive sibling</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
@@ -1280,13 +1280,13 @@
           <t xml:space="preserve">A child relation in a parent-child relationship established by a legal adoption process. </t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>child relation</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>child relation</t>
-        </is>
-      </c>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166130</t>
@@ -1339,13 +1339,13 @@
           <t>An adoptive child who is female gender.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>adoptive child</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>adoptive child</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
@@ -1394,13 +1394,13 @@
           <t>An adoptive parent who is male gender.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>adoptive parent</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>adoptive parent</t>
-        </is>
-      </c>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
@@ -1449,13 +1449,13 @@
           <t>An adoptive parent who is female gender.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>adoptive parent</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>adoptive parent</t>
-        </is>
-      </c>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
@@ -1504,13 +1504,13 @@
           <t>A parent in a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166129</t>
@@ -1563,13 +1563,13 @@
           <t>A sibling with whom the subject shares a parent through a parent-child relationship established by a legal adoption process.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>sibling</t>
-        </is>
-      </c>
+      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
@@ -1618,13 +1618,13 @@
           <t>An adoptive sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>adoptive sibling</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>adoptive sibling</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
@@ -1673,13 +1673,13 @@
           <t>An adoptive child who is male gender.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>adoptive child</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>adoptive child</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
           <t>A person who has reached maturity.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -1775,13 +1775,13 @@
           <t>A rent-free occupier who lives in the residential facility with the agreement of the residential facility owner.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>rent-free occupier</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>rent-free occupier</t>
-        </is>
-      </c>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
@@ -1830,13 +1830,13 @@
           <t xml:space="preserve">A sexual orientation of an individual who does not experience sexual attraction. </t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>sexual orientation</t>
-        </is>
-      </c>
+      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>NCIT_C155696</t>
@@ -1889,13 +1889,13 @@
           <t>A family member who is the sister of one's parent.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
@@ -1944,13 +1944,13 @@
           <t>An intervention participant who is exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>intervention participant</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>intervention participant</t>
-        </is>
-      </c>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
@@ -1995,13 +1995,13 @@
           <t>An intervention population who are exposed to a behaviour change intervention.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>intervention population</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>intervention population</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
@@ -2042,13 +2042,13 @@
           <t>A data item that is about the rate of individual human behaviour change.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
@@ -2093,13 +2093,13 @@
           <t>A person who has formed an intention to enact a specified behaviour, and has enacted that behaviour.</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
           <t>A person who has formed an intention to enact a specified behaviour, but has not acted on this intention.</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
@@ -2201,13 +2201,13 @@
           <t>A person who has not formed an intention to enact a specified behaviour.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">person </t>
+        </is>
+      </c>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">person </t>
-        </is>
-      </c>
+      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
@@ -2255,18 +2255,18 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>The number of times a person performs a behaviour within a specific period.</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>The number of times a person performs a behaviour within a specific period.</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2312,13 +2312,13 @@
           <t>A biological sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>biological sibling</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>biological sibling</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
@@ -2367,13 +2367,13 @@
           <t>A child relation who is genetically related to their parent.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>child relation</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>child relation</t>
-        </is>
-      </c>
+      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
@@ -2422,13 +2422,13 @@
           <t>A biological child who is female gender.</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>biological child</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>biological child</t>
-        </is>
-      </c>
+      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
@@ -2477,13 +2477,13 @@
           <t>A biological parent who provided the sperm.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>biological parent</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>biological parent</t>
-        </is>
-      </c>
+      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
@@ -2532,13 +2532,13 @@
           <t>A biological parent who provided an egg.</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>biological parent</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>biological parent</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
@@ -2587,13 +2587,13 @@
           <t>A parent who provided one of the gametes that resulted in one's conception.</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
+      <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166114, GSSO:001986</t>
@@ -2646,13 +2646,13 @@
           <t>A bodily quality based on reproductive function or organs.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>bodily quality</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>bodily quality</t>
-        </is>
-      </c>
+      <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -2701,13 +2701,13 @@
           <t>A sibling with whom the subject shares a biological parent.</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>sibling</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
@@ -2756,13 +2756,13 @@
           <t>A biological sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>biological sibling</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>biological sibling</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -2811,13 +2811,13 @@
           <t>A biological child who is male gender.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>biological child</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>biological child</t>
-        </is>
-      </c>
+      <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -2866,13 +2866,13 @@
           <t>A sexual orientation of an individual who experiences sexual attraction to members of more than one sex.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>sexual orientation</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84364</t>
@@ -2925,7 +2925,7 @@
           <t>A quality that inheres in some extended organism.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
@@ -2957,13 +2957,13 @@
           <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
@@ -3012,13 +3012,13 @@
           <t>A personal attribute as belonging to a group within a stratified system of categorisation based on a status conferred at birth based on descent, in which individuals have limited or no mobility due to custom or law.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
@@ -3071,13 +3071,13 @@
           <t xml:space="preserve">A person who has not yet reached maturity. </t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
@@ -3130,13 +3130,13 @@
           <t>A family member who is a person's first generation offspring.</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
@@ -3185,13 +3185,13 @@
           <t>A gender identity that matches the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>GSSO:004240</t>
@@ -3244,13 +3244,13 @@
           <t xml:space="preserve">A geographic location that is the country in which a person was born. </t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>geographic location</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>geographic location</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>GENEPIO_0001094</t>
@@ -3303,13 +3303,13 @@
           <t>A family member who is a child relation of one's aunt or uncle.</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
@@ -3358,13 +3358,13 @@
           <t>A personal attribute in which the person has impaired physical or mental functioning that has a notable effect on their ability to do typical daily activities.</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
@@ -3413,20 +3413,20 @@
           <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t>psychology, counselling, public health</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>psychology, counselling, public health</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>The division of knowledge and practice into different disciplines or fields is complex and depends on historical, social and structural factors</t>
@@ -3476,20 +3476,20 @@
           <t>An expertise discipline of the highest level of formal educational qualification a person has achieved.</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3535,13 +3535,13 @@
           <t>A relationship status where the individual was previously in a legally formalised relationship and this relationship has now ended or dissolved.</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>relationship status</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
+      <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
@@ -3590,13 +3590,13 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
@@ -3645,13 +3645,13 @@
           <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
@@ -3700,13 +3700,13 @@
           <t>A &lt;social group&gt; of two people who interact and influence each other.</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>social group</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>social group</t>
-        </is>
-      </c>
+      <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
@@ -3747,13 +3747,13 @@
           <t>A planned process wherein knowledge and skills is imparted.</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
+      <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>education process in the Sustainable Development Goals Interface Ontology (SDGIO:00010001)</t>
@@ -3798,13 +3798,13 @@
           <t>An employment status realised by an individual being engaged in an activity or service for wages or salary.</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>NCIT_C25172</t>
@@ -3857,13 +3857,13 @@
           <t>An employment status realised by an individual working a standard number of hours defined as full-time by their employer.</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>OPMI:0000123</t>
@@ -3916,13 +3916,13 @@
           <t>An employment status realised by an individual working for recurring periods in which different groups of workers do the same jobs in relay.</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
@@ -3971,13 +3971,13 @@
           <t>An employment status realised by an individual whose working hours involving less than the standard or customary working time.</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>NCIT_C75562</t>
@@ -4027,16 +4027,16 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>A quality inhering in a person by virtue of that person bearing a role realised in an employment process.</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n"/>
+          <t>A personal attribute relating the bearer to an employment process.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
+      <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Sustainable Development Goals Interface Ontology (SDGIO:00010029)</t>
@@ -4094,13 +4094,13 @@
           <t>A self-identity as belonging to a social group or groups whose members have a common cultural or ancestral heritage.</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>EFO:0001799</t>
@@ -4157,13 +4157,13 @@
           <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
@@ -4212,13 +4212,13 @@
           <t>A data item that is the extent to which the person’s past behaviour has reached or exceeded a standard.</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
@@ -4267,13 +4267,13 @@
           <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>NCIT:C41256</t>
@@ -4326,13 +4326,13 @@
           <t>A parent who is male gender.</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
+      <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
@@ -4381,13 +4381,13 @@
           <t>A biological sex associated with the ability to produce female gametes.</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>biological sex</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>biological sex</t>
-        </is>
-      </c>
+      <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
@@ -4436,13 +4436,13 @@
           <t>A gender identity as being female.</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>GSSO:000089</t>
@@ -4499,13 +4499,13 @@
           <t>A foster sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>foster sibling</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>foster sibling</t>
-        </is>
-      </c>
+      <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
@@ -4554,13 +4554,13 @@
           <t xml:space="preserve">A child relation in a parent-child relationship created by a foster care arrangement. </t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>child relation</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>child relation</t>
-        </is>
-      </c>
+      <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
@@ -4609,13 +4609,13 @@
           <t>A foster child who is female gender.</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>foster child</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>foster child</t>
-        </is>
-      </c>
+      <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
@@ -4664,13 +4664,13 @@
           <t>A foster parent who is male gender.</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>foster parent</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>foster parent</t>
-        </is>
-      </c>
+      <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
@@ -4719,13 +4719,13 @@
           <t>A foster parent who is female gender.</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>foster parent</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>foster parent</t>
-        </is>
-      </c>
+      <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
@@ -4774,13 +4774,13 @@
           <t>A parent who cares for a child who has been placed with them in a foster care arrangement.</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
+      <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>GSSO:001987</t>
@@ -4833,13 +4833,13 @@
           <t>A sibling who shares a parent through a parent-child relationship created by a foster care agreement.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>sibling</t>
-        </is>
-      </c>
+      <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
@@ -4888,13 +4888,13 @@
           <t>A foster sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>foster sibling</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>foster sibling</t>
-        </is>
-      </c>
+      <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
@@ -4943,13 +4943,13 @@
           <t>A foster child who is male gender.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>foster child</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>foster child</t>
-        </is>
-      </c>
+      <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
@@ -4998,13 +4998,13 @@
           <t>A behavioural frequency about the number of times a person has enacted a behaviour per unit of time.</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>behavioural frequency</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="n"/>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>behavioural frequency</t>
-        </is>
-      </c>
+      <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
@@ -5053,13 +5053,13 @@
           <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
@@ -5108,13 +5108,13 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
@@ -5163,13 +5163,13 @@
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
@@ -5218,13 +5218,13 @@
           <t>A grandparent who is male gender.</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>grandparent</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>grandparent</t>
-        </is>
-      </c>
+      <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
@@ -5273,13 +5273,13 @@
           <t>A grandparent who is female gender.</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>grandparent</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>grandparent</t>
-        </is>
-      </c>
+      <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
@@ -5328,13 +5328,13 @@
           <t>A family member who is the parent of one's parent.</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
@@ -5383,13 +5383,13 @@
           <t xml:space="preserve">A personal history part that includes previously performing a behaviour. </t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
@@ -5438,20 +5438,20 @@
           <t>A policy holder role that inheres in a person who participates in the creation of an insurance contract designed to cover some or all of the cost of treating the insured person's illnesses or injuries as well as possibly providing preventive health care.</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>policy holder role</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>policy holder role</t>
+          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
-        </is>
-      </c>
+      <c r="I89" s="2" t="n"/>
       <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5497,11 +5497,15 @@
           <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>Having chicken pox, asthma, a heart attack</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5510,11 +5514,7 @@
         </is>
       </c>
       <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>Having chicken pox, asthma, a heart attack</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="n"/>
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -5560,13 +5560,13 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of a different sex.</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
       <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>sexual orientation</t>
-        </is>
-      </c>
+      <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84362</t>
@@ -5619,13 +5619,13 @@
           <t>A frequency of past behaviour that is above a threshold.</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>frequency of past behaviour</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>frequency of past behaviour</t>
-        </is>
-      </c>
+      <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
@@ -5670,13 +5670,13 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. For example, completing a university bachelor's or master's course of study, medical school or other professional school. </t>
         </is>
       </c>
-      <c r="D93" s="3" t="n"/>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
@@ -5725,20 +5725,20 @@
           <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
+      <c r="I94" s="2" t="n"/>
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
           <t>A personal attribute related to the highest level of education achieved.</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NCIT_C17953 </t>
@@ -5847,7 +5847,7 @@
           <t>A process that is the sum of the totality of processes taking place in the spatiotemporal region occupied by a material entity or site, including processes on the surface of the entity or within the cavities to which it serves as host.</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>process</t>
         </is>
@@ -5879,20 +5879,20 @@
           <t>A personal history part that includes exposure to a potentially harmful agent as a result of one's occupation.</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="n"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>history of exposure to asbestos due to one's job</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>history of exposure to asbestos due to one's job</t>
-        </is>
-      </c>
+      <c r="I97" s="2" t="n"/>
       <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -5938,20 +5938,20 @@
           <t>A personal history part that includes experience of physical, sexual, or psychological maltreatment during the first 18 years of life.</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="n"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>history of physical abuse by a parent</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>history of physical abuse by a parent</t>
-        </is>
-      </c>
+      <c r="I98" s="2" t="n"/>
       <c r="J98" s="2" t="n"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5997,13 +5997,13 @@
           <t>A person who does not own a residential facility and does not have an agreement with a residential facility owner that would enable them to live in a residential facility.</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -6056,13 +6056,13 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process and who manages their home as their main daily activity.</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>NCIT_C75560</t>
@@ -6115,13 +6115,13 @@
           <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of the same sex.</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
       <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>sexual orientation</t>
-        </is>
-      </c>
+      <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84363</t>
@@ -6174,7 +6174,7 @@
           <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of its residence function.</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
@@ -6211,13 +6211,13 @@
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="3" t="n"/>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>object aggregate</t>
+        </is>
+      </c>
       <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
+      <c r="F103" s="3" t="n"/>
       <c r="G103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EFO_0009695 </t>
@@ -6274,13 +6274,13 @@
           <t>A personal attribute that is a time quality inhering in a person by virtue of how long since the person was born.</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>PATO:0000011</t>
@@ -6333,13 +6333,13 @@
           <t>An object aggregate that consists of two or more people.</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>object aggregate</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="n"/>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
+      <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
@@ -6380,7 +6380,7 @@
           <t>A cognitive representation of themselves by a person or group.</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>cognitive representation</t>
         </is>
@@ -6412,13 +6412,13 @@
           <t>A person who has previously been a resident of a country and is now resident in another country.</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
@@ -6467,13 +6467,13 @@
           <t xml:space="preserve">A relationship status where the individual is in a legally formalised marriage or civil partnership. </t>
         </is>
       </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>relationship status</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
+      <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
@@ -6523,13 +6523,13 @@
           <t>A relationship status where the individual has had the same partner for a significant length of time but is not in a legal union.</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>relationship status</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
+      <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
@@ -6582,13 +6582,13 @@
           <t>An employment status realised by an individual working for a company or other organisation without a pre-determined end date, with security of employment and known working conditions.</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
@@ -6637,13 +6637,13 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position that is of a known, fixed duration with security of employment for that duration and certain working conditions.</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
@@ -6692,13 +6692,13 @@
           <t>An employment status realised by an individual working for a company or other organisation in a position with uncertain duration or hours with unknown or low security of working conditions or pay.</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
@@ -6747,13 +6747,13 @@
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="3" t="n"/>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>individual income</t>
+        </is>
+      </c>
       <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>individual income</t>
-        </is>
-      </c>
+      <c r="F113" s="3" t="n"/>
       <c r="G113" s="3" t="n"/>
       <c r="H113" s="3" t="n"/>
       <c r="I113" s="3" t="n"/>
@@ -6802,13 +6802,13 @@
           <t>A personal attribute inhering in a person who does not bear a role realised in an employment process due to possessing enough wealth to not need financial support from another person or require income from employment.</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
@@ -6857,20 +6857,20 @@
           <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>bodily process</t>
+          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
-        </is>
-      </c>
+      <c r="I115" s="2" t="n"/>
       <c r="J115" s="2" t="n"/>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -6916,13 +6916,13 @@
           <t>A personal attribute reflecting a benefit the person receives  derived from their capital or labour, usually measured in money.</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>OMRSE_00002061</t>
@@ -6975,13 +6975,13 @@
           <t>A social role that involves influencing other people to adopt new ideas or behaviours.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>social role</t>
+        </is>
+      </c>
       <c r="E117" s="2" t="n"/>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>social role</t>
-        </is>
-      </c>
+      <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
@@ -7030,13 +7030,13 @@
           <t>A student or trainee role realised by  currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D118" s="3" t="n"/>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="n"/>
@@ -7085,13 +7085,13 @@
           <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
@@ -7140,13 +7140,13 @@
           <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>patient role</t>
+        </is>
+      </c>
       <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>patient role</t>
-        </is>
-      </c>
+      <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
@@ -7195,13 +7195,13 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="D121" s="3" t="n"/>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
           <t>OMRSE:00000092</t>
@@ -7258,7 +7258,7 @@
           <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -7310,13 +7310,13 @@
           <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="E123" s="2" t="n"/>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>NCIT_C92454</t>
@@ -7369,13 +7369,13 @@
           <t>A person who is exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
@@ -7416,13 +7416,13 @@
           <t>A human population who are exposed to an intervention.</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>human population</t>
+        </is>
+      </c>
       <c r="E125" s="2" t="n"/>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>human population</t>
-        </is>
-      </c>
+      <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
@@ -7463,20 +7463,20 @@
           <t>A linguistic capability that is realised by using a language accurately and appropriately in more than one setting.</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguistic capability </t>
+        </is>
+      </c>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linguistic capability </t>
+          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
-        </is>
-      </c>
+      <c r="I126" s="2" t="n"/>
       <c r="J126" s="2" t="n"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -7522,13 +7522,13 @@
           <t>A social role in which the holder is given or creates authority to exert influence on other members of a social group.</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>social role</t>
+        </is>
+      </c>
       <c r="E127" s="2" t="n"/>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>social role</t>
-        </is>
-      </c>
+      <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
@@ -7577,7 +7577,7 @@
           <t>A mental capability that is realised in processes of communication involving language or in expressions of language.</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>mental capability</t>
         </is>
@@ -7619,13 +7619,13 @@
           <t>Disabled for at least 12 months.</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
+      <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
@@ -7679,13 +7679,13 @@
           <t>A frequency of past behaviour that is below a threshold.</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>frequency of past behaviour</t>
+        </is>
+      </c>
       <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>frequency of past behaviour</t>
-        </is>
-      </c>
+      <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
@@ -7730,13 +7730,13 @@
           <t>A biological sex associated with the ability to produce male gametes.</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>biological sex</t>
+        </is>
+      </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>biological sex</t>
-        </is>
-      </c>
+      <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
@@ -7785,13 +7785,13 @@
           <t>A gender identity as being male.</t>
         </is>
       </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="F132" s="2" t="n"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>GSSO:000090</t>
@@ -7848,13 +7848,13 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D133" s="3" t="n"/>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n"/>
@@ -7903,13 +7903,13 @@
           <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E134" s="2" t="n"/>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
@@ -7958,20 +7958,20 @@
           <t>A health status attribute that is having been prescribed the use of one or more drugs to improve, maintain or protect one's health.</t>
         </is>
       </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>health status attribute</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="n"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>health status attribute</t>
+          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
-        </is>
-      </c>
+      <c r="I135" s="2" t="n"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
           <t>This entity reflects having been prescribed a medication.  Actual use of the medicine would be captured as a behaviour</t>
@@ -8021,13 +8021,13 @@
           <t>A person living in  a household with at least one other person.</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="n"/>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
@@ -8080,11 +8080,15 @@
           <t>A member of a multi-person household where all of the household members are related.</t>
         </is>
       </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
       <c r="E137" s="2" t="n"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -8093,11 +8097,7 @@
         </is>
       </c>
       <c r="H137" s="2" t="n"/>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
-        </is>
-      </c>
+      <c r="I137" s="2" t="n"/>
       <c r="J137" s="2" t="n"/>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -8143,20 +8143,20 @@
           <t>A member of a multi-person household where none of the household members are related.</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
       <c r="E138" s="2" t="n"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
-        </is>
-      </c>
+      <c r="I138" s="2" t="n"/>
       <c r="J138" s="2" t="n"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -8202,20 +8202,20 @@
           <t>A member of a multi-person household where some household members are related.</t>
         </is>
       </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
       <c r="E139" s="2" t="n"/>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
-        </is>
-      </c>
+      <c r="I139" s="2" t="n"/>
       <c r="J139" s="2" t="n"/>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -8261,20 +8261,20 @@
           <t>A member of a multi-person household where some household members belong to different generations.</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
       <c r="E140" s="2" t="n"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
-        </is>
-      </c>
+      <c r="I140" s="2" t="n"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
           <t>A member of a multi-generational household lives with other people that are from more than one generation. A generation is all the people of about the same age within a society or within a particular family</t>
@@ -8324,13 +8324,13 @@
           <t>A person living alone in a household.</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E141" s="2" t="n"/>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
@@ -8379,7 +8379,7 @@
           <t>A personal capability that includes mental processes in its realisation.</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>personal capability</t>
         </is>
@@ -8421,13 +8421,13 @@
           <t>A parent who is female gender.</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
       <c r="E143" s="2" t="n"/>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
+      <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
@@ -8476,13 +8476,13 @@
           <t xml:space="preserve">A family member who is a child relation of one's sibling and is male gender. </t>
         </is>
       </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="n"/>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
@@ -8531,13 +8531,13 @@
           <t>A family member who is a child relation of one's sibling and is female gender.</t>
         </is>
       </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
@@ -8586,13 +8586,13 @@
           <t>A self-identity as not having a particular gender.</t>
         </is>
       </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
       <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="F146" s="2" t="n"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>GSSO:002331</t>
@@ -8645,13 +8645,13 @@
           <t>A gender identity as having a gender that is not well-described by the binary categories of male or female.</t>
         </is>
       </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="E147" s="2" t="n"/>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="F147" s="2" t="n"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>GSSO:002328</t>
@@ -8704,13 +8704,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not having a paid job and not currently seeking to begin participating in an employment process.</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="n"/>
@@ -8759,13 +8759,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being unable to work due to illness or disability.</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="n"/>
@@ -8814,13 +8814,13 @@
           <t>A data item about the number of people in a population.</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E150" s="2" t="n"/>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
@@ -8861,13 +8861,13 @@
           <t>The number of years a person spent engaged in an education process.</t>
         </is>
       </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E151" s="2" t="n"/>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
@@ -8920,13 +8920,13 @@
           <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
-      <c r="D152" s="2" t="n"/>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
       <c r="E152" s="2" t="n"/>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>personal role</t>
-        </is>
-      </c>
+      <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="n"/>
@@ -8975,13 +8975,13 @@
           <t>A person who lives in a residential facility they do not own  with the agreement of the residential facility owner, by virtue of the occupier bearing a role realised in an employment process.</t>
         </is>
       </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E153" s="2" t="n"/>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
@@ -9030,20 +9030,20 @@
           <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
         </is>
       </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="E154" s="2" t="n"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>Scout leader, club chairperson</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Scout leader, club chairperson</t>
-        </is>
-      </c>
+      <c r="I154" s="2" t="n"/>
       <c r="J154" s="2" t="n"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -9089,13 +9089,13 @@
           <t>A sexual orientation of an individual who is sure of their sexual orientation and reports it as other than asexual, bisexual, heterosexual, homosexual, queer or questioning.</t>
         </is>
       </c>
-      <c r="D155" s="2" t="n"/>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
       <c r="E155" s="2" t="n"/>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>sexual orientation</t>
-        </is>
-      </c>
+      <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
@@ -9144,13 +9144,13 @@
           <t>A social group that is part of a person’s social environmental system and with which the person does not identify.</t>
         </is>
       </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>social group</t>
+        </is>
+      </c>
       <c r="E156" s="2" t="n"/>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>social group</t>
-        </is>
-      </c>
+      <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
@@ -9191,13 +9191,13 @@
           <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>patient role</t>
+        </is>
+      </c>
       <c r="E157" s="2" t="n"/>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>patient role</t>
-        </is>
-      </c>
+      <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
@@ -9246,13 +9246,13 @@
           <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
         </is>
       </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="E158" s="2" t="n"/>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="F158" s="2" t="n"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
           <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
@@ -9309,13 +9309,13 @@
           <t>A person who lives in a residential facility of which they are the residential facility owner</t>
         </is>
       </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E159" s="2" t="n"/>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
@@ -9365,13 +9365,13 @@
           <t xml:space="preserve">A family member who is a key caretaker or immediate progenitor of a child. </t>
         </is>
       </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E160" s="2" t="n"/>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F160" s="2" t="n"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>GSSO:001953</t>
@@ -9424,13 +9424,13 @@
           <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
         </is>
       </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>interpersonal role</t>
+        </is>
+      </c>
       <c r="E161" s="2" t="n"/>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>interpersonal role</t>
-        </is>
-      </c>
+      <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
@@ -9483,13 +9483,13 @@
           <t>A personal history part that includes a behaviour.</t>
         </is>
       </c>
-      <c r="D162" s="2" t="n"/>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E162" s="2" t="n"/>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
@@ -9534,13 +9534,13 @@
           <t>A past behaviour that is the target of an intervention.</t>
         </is>
       </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">past behaviour </t>
+        </is>
+      </c>
       <c r="E163" s="2" t="n"/>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">past behaviour </t>
-        </is>
-      </c>
+      <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
@@ -9585,7 +9585,7 @@
           <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -9628,13 +9628,13 @@
           <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
         </is>
       </c>
-      <c r="D165" s="2" t="n"/>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>human population</t>
+        </is>
+      </c>
       <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>human population</t>
-        </is>
-      </c>
+      <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
           <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>extended organism</t>
         </is>
@@ -9707,13 +9707,13 @@
           <t>A &lt;person&gt; who is part of a social environmental system.</t>
         </is>
       </c>
-      <c r="D167" s="2" t="n"/>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E167" s="2" t="n"/>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
@@ -9754,13 +9754,13 @@
           <t>A specifically dependent continuant that inheres in a person.</t>
         </is>
       </c>
-      <c r="D168" s="2" t="n"/>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
       <c r="E168" s="2" t="n"/>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
@@ -9811,12 +9811,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t>bodily disposition</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
           <t>The ability of someone to perform some useful and/or beneficial activity.</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>bodily disposition</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9852,13 +9852,13 @@
           <t>A history that is of a person.</t>
         </is>
       </c>
-      <c r="D170" s="2" t="n"/>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
       <c r="E170" s="2" t="n"/>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>history</t>
-        </is>
-      </c>
+      <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
@@ -9899,13 +9899,13 @@
           <t xml:space="preserve">A personal history part that includes a change from a less desired behaviour pattern to a more desired behaviour pattern followed by a temporary reversion to the previous behaviour pattern. </t>
         </is>
       </c>
-      <c r="D171" s="2" t="n"/>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E171" s="2" t="n"/>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
@@ -9954,13 +9954,13 @@
           <t xml:space="preserve">A personal history part that includes experience of events that influence behaviour. </t>
         </is>
       </c>
-      <c r="D172" s="2" t="n"/>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
@@ -10009,13 +10009,13 @@
           <t>A personal history part of exposure to an intervention targeting the same outcome as the current intervention.</t>
         </is>
       </c>
-      <c r="D173" s="2" t="n"/>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E173" s="2" t="n"/>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="n"/>
@@ -10064,13 +10064,13 @@
           <t>A personal history part  that includes exposure to a prior intervention targeting the same outcome behaviour as the current intervention.</t>
         </is>
       </c>
-      <c r="D174" s="2" t="n"/>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E174" s="2" t="n"/>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
@@ -10119,13 +10119,13 @@
           <t>A personal history part that includes exposure to the same intervention as the current intervention.</t>
         </is>
       </c>
-      <c r="D175" s="2" t="n"/>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E175" s="2" t="n"/>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
@@ -10178,17 +10178,17 @@
           <t>A process that is part of a personal history.</t>
         </is>
       </c>
-      <c r="D176" s="2" t="n"/>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
           <t>'process' and 'part of' some 'personal history'</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
@@ -10229,13 +10229,13 @@
           <t xml:space="preserve">A personal history part  that includes exposure to one or more interventions. </t>
         </is>
       </c>
-      <c r="D177" s="2" t="n"/>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
       <c r="E177" s="2" t="n"/>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
+      <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
@@ -10284,20 +10284,20 @@
           <t>An attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
         </is>
       </c>
-      <c r="D178" s="2" t="n"/>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E178" s="2" t="n"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
-        </is>
-      </c>
+      <c r="I178" s="2" t="n"/>
       <c r="J178" s="2" t="n"/>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -10345,18 +10345,18 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+          <t>role</t>
         </is>
       </c>
       <c r="E179" s="2" t="n"/>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="n"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
           <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
@@ -10398,20 +10398,20 @@
           <t>A disposition to undergo undesirable change in response to exposure to another entity.</t>
         </is>
       </c>
-      <c r="D180" s="2" t="n"/>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
       <c r="E180" s="2" t="n"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>susceptibility to addiction, vulnerability to depression</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>susceptibility to addiction, vulnerability to depression</t>
-        </is>
-      </c>
+      <c r="I180" s="2" t="n"/>
       <c r="J180" s="2" t="n"/>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -10457,13 +10457,13 @@
           <t>A personal vulnerability towards performing a behaviour that causes net harm.</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n"/>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>personal vulnerability</t>
+        </is>
+      </c>
       <c r="E181" s="2" t="n"/>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>personal vulnerability</t>
-        </is>
-      </c>
+      <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -10516,13 +10516,13 @@
           <t>A geographic location in which a person resides.</t>
         </is>
       </c>
-      <c r="D182" s="2" t="n"/>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>geographic location</t>
+        </is>
+      </c>
       <c r="E182" s="2" t="n"/>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>geographic location</t>
-        </is>
-      </c>
+      <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
           <t>An insured party role that inheres in a person who participates in the creation of the insurance contract and is eligible to receive benefits as specified by the insurance contract.</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>insured party role</t>
         </is>
@@ -10613,21 +10613,21 @@
           <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
         </is>
       </c>
-      <c r="D184" s="2" t="n"/>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E184" s="2" t="n"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>Percentage of highly educated individuals in a population. 
+Mean age in a population.</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
       <c r="H184" s="2" t="n"/>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>Percentage of highly educated individuals in a population. 
-Mean age in a population.</t>
-        </is>
-      </c>
+      <c r="I184" s="2" t="n"/>
       <c r="J184" s="2" t="n"/>
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="n"/>
@@ -10661,13 +10661,13 @@
           <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n"/>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E185" s="2" t="n"/>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="n"/>
@@ -10716,13 +10716,13 @@
           <t>A &lt;disposition&gt; that decreases the likelihood of engaging with harmful behaviour.</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n"/>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
       <c r="E186" s="2" t="n"/>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
+      <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="n"/>
@@ -10771,7 +10771,7 @@
           <t>A specifically dependent continuant that, in contrast to roles and dispositions, does not require any further process in order to be realized.</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>specifically dependent continuant</t>
         </is>
@@ -10803,20 +10803,20 @@
           <t>A data item about the number of units of a valuable material resource possessed by a person.</t>
         </is>
       </c>
-      <c r="D188" s="2" t="n"/>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E188" s="2" t="n"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>12 acres, a flock of 20 goats</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>12 acres, a flock of 20 goats</t>
-        </is>
-      </c>
+      <c r="I188" s="2" t="n"/>
       <c r="J188" s="2" t="n"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -10866,13 +10866,13 @@
           <t>A sexual orientation that is not exclusively homosexual or heterosexual, or of a person who does not identify with heterosexual, homosexual or bisexual labels.</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n"/>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
       <c r="E189" s="2" t="n"/>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t>sexual orientation</t>
-        </is>
-      </c>
+      <c r="F189" s="2" t="n"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
           <t>NCIT_C155691</t>
@@ -10925,13 +10925,13 @@
           <t xml:space="preserve">A self-identity as being in the process of exploring one's sexual orientation. </t>
         </is>
       </c>
-      <c r="D190" s="2" t="n"/>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
       <c r="E190" s="2" t="n"/>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="F190" s="2" t="n"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
           <t>NCIT_C155692</t>
@@ -10984,13 +10984,13 @@
           <t>A personal attribute that is whether an individual is connected or associated with another through romantic attraction or marriage.</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n"/>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E191" s="2" t="n"/>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="n"/>
@@ -11039,11 +11039,15 @@
           <t xml:space="preserve">A personal attribute that is belonging to a group that is characterised by the practice of a common religion by the group members. </t>
         </is>
       </c>
-      <c r="D192" s="2" t="n"/>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E192" s="2" t="n"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -11052,11 +11056,7 @@
         </is>
       </c>
       <c r="H192" s="2" t="n"/>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
-        </is>
-      </c>
+      <c r="I192" s="2" t="n"/>
       <c r="J192" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage belonging to a specified religious group</t>
@@ -11106,13 +11106,13 @@
           <t>A person who lives in a residential facility they do not own without paying an agreed sum of money to the residential facility owner.</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n"/>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E193" s="2" t="n"/>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="n"/>
@@ -11161,20 +11161,20 @@
           <t>A rent-free occupier who lives in the residential facility without the agreement of the residential facility owner.</t>
         </is>
       </c>
-      <c r="D194" s="2" t="n"/>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>rent-free occupier</t>
+        </is>
+      </c>
       <c r="E194" s="2" t="n"/>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>rent-free occupier</t>
+          <t>squatters</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
       <c r="H194" s="2" t="n"/>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>squatters</t>
-        </is>
-      </c>
+      <c r="I194" s="2" t="n"/>
       <c r="J194" s="2" t="n"/>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -11220,13 +11220,13 @@
           <t>A person who lives in a residential facility they do not own in return for paying an agreed sum of money to the residential facility owner</t>
         </is>
       </c>
-      <c r="D195" s="2" t="n"/>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E195" s="2" t="n"/>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="n"/>
@@ -11275,20 +11275,20 @@
           <t>A renter who lives in a residential facility where the residential facility owner decides who can live in the residential facility based on their perceived social or economic needs.</t>
         </is>
       </c>
-      <c r="D196" s="2" t="n"/>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>renter</t>
+        </is>
+      </c>
       <c r="E196" s="2" t="n"/>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>renter</t>
+          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
-        </is>
-      </c>
+      <c r="I196" s="2" t="n"/>
       <c r="J196" s="2" t="n"/>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -11334,13 +11334,13 @@
           <t>An owner of a residential facility.</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n"/>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
       <c r="E197" s="2" t="n"/>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="F197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="n"/>
@@ -11389,13 +11389,13 @@
           <t>A personal attribute inhering in a person who previously bore a role realised in an employment process but has withdrawn from that employment process, having concluded their working or professional career.</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n"/>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E198" s="2" t="n"/>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
@@ -11444,7 +11444,7 @@
           <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
@@ -11476,13 +11476,13 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D200" s="3" t="n"/>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
@@ -11531,13 +11531,13 @@
           <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D201" s="2" t="n"/>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E201" s="2" t="n"/>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="n"/>
@@ -11586,13 +11586,13 @@
           <t>A person who has at least one parent who is an immigrant.</t>
         </is>
       </c>
-      <c r="D202" s="2" t="n"/>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="E202" s="2" t="n"/>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
       <c r="I202" s="2" t="n"/>
@@ -11641,13 +11641,13 @@
           <t>An employment status realised by a person earning income directly from customers, clients, or other organisations rather than as a specified salary or wages from an employer.</t>
         </is>
       </c>
-      <c r="D203" s="2" t="n"/>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E203" s="2" t="n"/>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F203" s="2" t="n"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NCIT_C116000 </t>
@@ -11704,7 +11704,7 @@
           <t>An identity that a person has about themselves.</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>identity</t>
         </is>
@@ -11736,13 +11736,13 @@
           <t xml:space="preserve">A personal attribute that is the pattern of a person's emotional, romantic and/or sexual attractions. </t>
         </is>
       </c>
-      <c r="D205" s="2" t="n"/>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E205" s="2" t="n"/>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F205" s="2" t="n"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
           <t>NCIT_C84361</t>
@@ -11795,13 +11795,13 @@
           <t>A family member with whom the subject shares a parent.</t>
         </is>
       </c>
-      <c r="D206" s="2" t="n"/>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E206" s="2" t="n"/>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
       <c r="I206" s="2" t="n"/>
@@ -11851,13 +11851,13 @@
           <t>A relationship status where the individual is not in a relationship with another person.</t>
         </is>
       </c>
-      <c r="D207" s="2" t="n"/>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>relationship status</t>
+        </is>
+      </c>
       <c r="E207" s="2" t="n"/>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
+      <c r="F207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="n"/>
@@ -11906,13 +11906,13 @@
           <t>A personal attribute that holds within a given situation.</t>
         </is>
       </c>
-      <c r="D208" s="2" t="n"/>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E208" s="2" t="n"/>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F208" s="2" t="n"/>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="2" t="n"/>
@@ -11953,13 +11953,13 @@
           <t>A social grouping that identifies as such and sometimes acts collectively.</t>
         </is>
       </c>
-      <c r="D209" s="2" t="n"/>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>social grouping</t>
+        </is>
+      </c>
       <c r="E209" s="2" t="n"/>
-      <c r="F209" s="2" t="inlineStr">
-        <is>
-          <t>social grouping</t>
-        </is>
-      </c>
+      <c r="F209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="2" t="n"/>
@@ -12000,13 +12000,13 @@
           <t>A human population who share some common attribute that involves some form of social interaction.</t>
         </is>
       </c>
-      <c r="D210" s="2" t="n"/>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>human population</t>
+        </is>
+      </c>
       <c r="E210" s="2" t="n"/>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>human population</t>
-        </is>
-      </c>
+      <c r="F210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="2" t="n"/>
@@ -12051,13 +12051,13 @@
           <t>A personal role that is realised in human social processes.</t>
         </is>
       </c>
-      <c r="D211" s="2" t="n"/>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
       <c r="E211" s="2" t="n"/>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>personal role</t>
-        </is>
-      </c>
+      <c r="F211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="2" t="n"/>
@@ -12098,13 +12098,13 @@
           <t>A &lt;personal attribute&gt; that, together with other attributes, characterises a person’s position in society.</t>
         </is>
       </c>
-      <c r="D212" s="2" t="n"/>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E212" s="2" t="n"/>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="2" t="n"/>
@@ -12149,13 +12149,13 @@
           <t>A personal attribute reflecting a person's economic and social position in relation to others</t>
         </is>
       </c>
-      <c r="D213" s="2" t="n"/>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E213" s="2" t="n"/>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F213" s="2" t="n"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
           <t>OPMI:0000121</t>
@@ -12208,13 +12208,13 @@
           <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic position, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
         </is>
       </c>
-      <c r="D214" s="2" t="n"/>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E214" s="2" t="n"/>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="2" t="n"/>
@@ -12267,20 +12267,20 @@
           <t xml:space="preserve">A  data item about a category assigned to a person based on an assessment of a score calculated from various measures of their income, education, occupation, family size or household. </t>
         </is>
       </c>
-      <c r="D215" s="3" t="n"/>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>Semi-routine and routine occupations, blue collar occupations</t>
         </is>
       </c>
       <c r="G215" s="3" t="n"/>
       <c r="H215" s="3" t="n"/>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>Semi-routine and routine occupations, blue collar occupations</t>
-        </is>
-      </c>
+      <c r="I215" s="3" t="n"/>
       <c r="J215" s="3" t="n"/>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -12330,13 +12330,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being a homemaker whose work includes caring for children.</t>
         </is>
       </c>
-      <c r="D216" s="2" t="n"/>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E216" s="2" t="n"/>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F216" s="2" t="n"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
           <t>NCIT_C148253</t>
@@ -12389,13 +12389,13 @@
           <t>A parent in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D217" s="2" t="n"/>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
       <c r="E217" s="2" t="n"/>
-      <c r="F217" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
+      <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
           <t>NCIT:C166116</t>
@@ -12448,13 +12448,13 @@
           <t>A sibling who is the child of one's step-parent.</t>
         </is>
       </c>
-      <c r="D218" s="2" t="n"/>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
       <c r="E218" s="2" t="n"/>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>sibling</t>
-        </is>
-      </c>
+      <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
       <c r="I218" s="2" t="n"/>
@@ -12503,13 +12503,13 @@
           <t>A step-sibling who is male gender.</t>
         </is>
       </c>
-      <c r="D219" s="2" t="n"/>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>step-sibling</t>
+        </is>
+      </c>
       <c r="E219" s="2" t="n"/>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>step-sibling</t>
-        </is>
-      </c>
+      <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
       <c r="I219" s="2" t="n"/>
@@ -12558,13 +12558,13 @@
           <t>A child relation in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
-      <c r="D220" s="2" t="n"/>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>child relation</t>
+        </is>
+      </c>
       <c r="E220" s="2" t="n"/>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>child relation</t>
-        </is>
-      </c>
+      <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
       <c r="I220" s="2" t="n"/>
@@ -12613,13 +12613,13 @@
           <t>A stepchild who is female gender.</t>
         </is>
       </c>
-      <c r="D221" s="2" t="n"/>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>stepchild</t>
+        </is>
+      </c>
       <c r="E221" s="2" t="n"/>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>stepchild</t>
-        </is>
-      </c>
+      <c r="F221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
       <c r="I221" s="2" t="n"/>
@@ -12668,13 +12668,13 @@
           <t>A step-parent who is male gender.</t>
         </is>
       </c>
-      <c r="D222" s="2" t="n"/>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>step-parent</t>
+        </is>
+      </c>
       <c r="E222" s="2" t="n"/>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>step-parent</t>
-        </is>
-      </c>
+      <c r="F222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
       <c r="I222" s="2" t="n"/>
@@ -12723,13 +12723,13 @@
           <t>A step-parent who is female gender.</t>
         </is>
       </c>
-      <c r="D223" s="2" t="n"/>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>step-parent</t>
+        </is>
+      </c>
       <c r="E223" s="2" t="n"/>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>step-parent</t>
-        </is>
-      </c>
+      <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
       <c r="I223" s="2" t="n"/>
@@ -12778,13 +12778,13 @@
           <t>A step-sibling who is female gender.</t>
         </is>
       </c>
-      <c r="D224" s="2" t="n"/>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>step-sibling</t>
+        </is>
+      </c>
       <c r="E224" s="2" t="n"/>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>step-sibling</t>
-        </is>
-      </c>
+      <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
       <c r="I224" s="2" t="n"/>
@@ -12833,13 +12833,13 @@
           <t>A stepchild who is male gender.</t>
         </is>
       </c>
-      <c r="D225" s="2" t="n"/>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>stepchild</t>
+        </is>
+      </c>
       <c r="E225" s="2" t="n"/>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>stepchild</t>
-        </is>
-      </c>
+      <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
       <c r="I225" s="2" t="n"/>
@@ -12888,13 +12888,13 @@
           <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
-      <c r="D226" s="2" t="n"/>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="E226" s="2" t="n"/>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
       <c r="I226" s="2" t="n"/>
@@ -12943,7 +12943,7 @@
           <t>A person between 13 and 19 years of age.</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>person</t>
         </is>
@@ -12985,13 +12985,13 @@
           <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D228" s="2" t="n"/>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E228" s="2" t="n"/>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F228" s="2" t="n"/>
       <c r="G228" s="2" t="n"/>
       <c r="H228" s="2" t="n"/>
       <c r="I228" s="2" t="n"/>
@@ -13040,13 +13040,13 @@
           <t>A gender identity that differs from the person's assigned sex at birth.</t>
         </is>
       </c>
-      <c r="D229" s="2" t="n"/>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="E229" s="2" t="n"/>
-      <c r="F229" s="2" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="F229" s="2" t="n"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
           <t>GSSO:000096</t>
@@ -13099,13 +13099,13 @@
           <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
         </is>
       </c>
-      <c r="D230" s="2" t="n"/>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
       <c r="E230" s="2" t="n"/>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>sibling</t>
-        </is>
-      </c>
+      <c r="F230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="H230" s="2" t="n"/>
       <c r="I230" s="2" t="n"/>
@@ -13154,13 +13154,13 @@
           <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
         </is>
       </c>
-      <c r="D231" s="2" t="n"/>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>situational personal attribute</t>
+        </is>
+      </c>
       <c r="E231" s="2" t="n"/>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>situational personal attribute</t>
-        </is>
-      </c>
+      <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
       <c r="I231" s="2" t="n"/>
@@ -13209,13 +13209,13 @@
           <t>A family member who is the brother of one's parent.</t>
         </is>
       </c>
-      <c r="D232" s="2" t="n"/>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="E232" s="2" t="n"/>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
       <c r="I232" s="2" t="n"/>
@@ -13264,13 +13264,13 @@
           <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
         </is>
       </c>
-      <c r="D233" s="2" t="n"/>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>situational personal attribute</t>
+        </is>
+      </c>
       <c r="E233" s="2" t="n"/>
-      <c r="F233" s="2" t="inlineStr">
-        <is>
-          <t>situational personal attribute</t>
-        </is>
-      </c>
+      <c r="F233" s="2" t="n"/>
       <c r="G233" s="2" t="n"/>
       <c r="H233" s="2" t="n"/>
       <c r="I233" s="2" t="n"/>
@@ -13319,13 +13319,13 @@
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D234" s="3" t="n"/>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E234" s="3" t="n"/>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F234" s="3" t="n"/>
       <c r="G234" s="3" t="n"/>
       <c r="H234" s="3" t="n"/>
       <c r="I234" s="3" t="n"/>
@@ -13374,13 +13374,13 @@
           <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D235" s="2" t="n"/>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="E235" s="2" t="n"/>
-      <c r="F235" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="F235" s="2" t="n"/>
       <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
       <c r="I235" s="2" t="n"/>
@@ -13429,13 +13429,13 @@
           <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
         </is>
       </c>
-      <c r="D236" s="2" t="n"/>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
       <c r="E236" s="2" t="n"/>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
+      <c r="F236" s="2" t="n"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SDGIO_00010026 </t>
@@ -13488,13 +13488,13 @@
           <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
-      <c r="D237" s="2" t="n"/>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E237" s="2" t="n"/>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F237" s="2" t="n"/>
       <c r="G237" s="2" t="n"/>
       <c r="H237" s="2" t="n"/>
       <c r="I237" s="2" t="n"/>
@@ -13543,11 +13543,15 @@
           <t>An object aggregate under the control of some person or organisation which confers an economic benefit to that person or organisation in an economic system.</t>
         </is>
       </c>
-      <c r="D238" s="2" t="n"/>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>object aggregate</t>
+        </is>
+      </c>
       <c r="E238" s="2" t="n"/>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>object aggregate</t>
+          <t>farmland, jewellery, livestock</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -13556,11 +13560,7 @@
         </is>
       </c>
       <c r="H238" s="2" t="n"/>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>farmland, jewellery, livestock</t>
-        </is>
-      </c>
+      <c r="I238" s="2" t="n"/>
       <c r="J238" s="2" t="n"/>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -13598,20 +13598,20 @@
           <t>A data item about the monetary value of a valuable material resource possessed by a person.</t>
         </is>
       </c>
-      <c r="D239" s="2" t="n"/>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="E239" s="2" t="n"/>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>$400, 3000 euros</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
       <c r="H239" s="2" t="n"/>
-      <c r="I239" s="2" t="inlineStr">
-        <is>
-          <t>$400, 3000 euros</t>
-        </is>
-      </c>
+      <c r="I239" s="2" t="n"/>
       <c r="J239" s="2" t="n"/>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -13661,13 +13661,13 @@
           <t>A student or trainee role realised by currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D240" s="3" t="n"/>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="E240" s="3" t="n"/>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F240" s="3" t="n"/>
       <c r="G240" s="3" t="n"/>
       <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
@@ -13716,13 +13716,13 @@
           <t>A personal attribute inhering in a person by virtue of that person working or assisting at a workplace without receiving remuneration.</t>
         </is>
       </c>
-      <c r="D241" s="2" t="n"/>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
       <c r="E241" s="2" t="n"/>
-      <c r="F241" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
+      <c r="F241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="n"/>
       <c r="I241" s="2" t="n"/>
@@ -13775,13 +13775,13 @@
           <t xml:space="preserve">A relationship status where the individual is no longer in a legally formalised marriage or civil partnership due to the death of their spouse or partner. </t>
         </is>
       </c>
-      <c r="D242" s="2" t="n"/>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>relationship status</t>
+        </is>
+      </c>
       <c r="E242" s="2" t="n"/>
-      <c r="F242" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
+      <c r="F242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>
       <c r="I242" s="2" t="n"/>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -461,17 +461,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-reference</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Examples</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-reference</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Comprehend the German language</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>The exclusion criteria were an inability to read English</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="inlineStr">
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Able to speak Chinese.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="inlineStr">
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Fluency in written English.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="inlineStr">
@@ -1164,17 +1164,17 @@
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>OMRSE_00002040</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>graduated high school, International Baccaulaureate, A Levels</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>OMRSE_00002040</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>actor</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>psychology, counselling, public health</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -3482,13 +3482,13 @@
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="inlineStr">
@@ -4442,17 +4442,17 @@
         </is>
       </c>
       <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>GSSO:000089</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>woman</t>
-        </is>
-      </c>
+      <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
       <c r="J71" s="2" t="n"/>
       <c r="K71" s="2" t="inlineStr">
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
         </is>
       </c>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
       <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="inlineStr">
@@ -5503,17 +5503,17 @@
         </is>
       </c>
       <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C16669</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Having chicken pox, asthma, a heart attack</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C16669</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="inlineStr">
@@ -5731,13 +5731,13 @@
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="inlineStr">
@@ -5885,13 +5885,13 @@
         </is>
       </c>
       <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>history of exposure to asbestos due to one's job</t>
         </is>
       </c>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
       <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="inlineStr">
@@ -5944,13 +5944,13 @@
         </is>
       </c>
       <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>history of physical abuse by a parent</t>
         </is>
       </c>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
       <c r="J98" s="2" t="n"/>
       <c r="K98" s="2" t="inlineStr">
@@ -6003,13 +6003,13 @@
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>person experiencing homelessness</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>person experiencing homelessness</t>
-        </is>
-      </c>
+      <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
       <c r="J99" s="2" t="n"/>
       <c r="K99" s="2" t="inlineStr">
@@ -6863,13 +6863,13 @@
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>walks for 15 mins/day, never eats meat, attends school daily</t>
         </is>
       </c>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
       <c r="J115" s="2" t="n"/>
       <c r="K115" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7469,13 +7469,13 @@
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
         </is>
       </c>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
       <c r="J126" s="2" t="n"/>
       <c r="K126" s="2" t="inlineStr">
@@ -7791,17 +7791,17 @@
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>GSSO:000090</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
+      <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="n"/>
       <c r="J132" s="2" t="n"/>
       <c r="K132" s="2" t="inlineStr">
@@ -7964,13 +7964,13 @@
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
         </is>
       </c>
-      <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -8086,17 +8086,17 @@
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="n"/>
       <c r="J137" s="2" t="n"/>
       <c r="K137" s="2" t="inlineStr">
@@ -8149,13 +8149,13 @@
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="n"/>
-      <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
       <c r="J138" s="2" t="n"/>
       <c r="K138" s="2" t="inlineStr">
@@ -8208,13 +8208,13 @@
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
         </is>
       </c>
-      <c r="G139" s="2" t="n"/>
-      <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2" t="n"/>
       <c r="K139" s="2" t="inlineStr">
@@ -8267,13 +8267,13 @@
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="n"/>
-      <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="E154" s="2" t="n"/>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="n"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Scout leader, club chairperson</t>
         </is>
       </c>
-      <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
       <c r="J154" s="2" t="n"/>
       <c r="K154" s="2" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>An attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
+          <t>A personal attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -10290,13 +10290,13 @@
         </is>
       </c>
       <c r="E178" s="2" t="n"/>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="n"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
         </is>
       </c>
-      <c r="G178" s="2" t="n"/>
-      <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
       <c r="J178" s="2" t="n"/>
       <c r="K178" s="2" t="inlineStr">
@@ -10404,13 +10404,13 @@
         </is>
       </c>
       <c r="E180" s="2" t="n"/>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>susceptibility to addiction, vulnerability to depression</t>
         </is>
       </c>
-      <c r="G180" s="2" t="n"/>
-      <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
       <c r="J180" s="2" t="n"/>
       <c r="K180" s="2" t="inlineStr">
@@ -10463,13 +10463,13 @@
         </is>
       </c>
       <c r="E181" s="2" t="n"/>
-      <c r="F181" s="2" t="n"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>risk factor for harmful behaviour</t>
+        </is>
+      </c>
       <c r="G181" s="2" t="n"/>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>risk factor for harmful behaviour</t>
-        </is>
-      </c>
+      <c r="H181" s="2" t="n"/>
       <c r="I181" s="2" t="n"/>
       <c r="J181" s="2" t="n"/>
       <c r="K181" s="2" t="inlineStr">
@@ -10619,14 +10619,14 @@
         </is>
       </c>
       <c r="E184" s="2" t="n"/>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Percentage of highly educated individuals in a population. 
 Mean age in a population.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="n"/>
-      <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
       <c r="J184" s="2" t="n"/>
       <c r="K184" s="2" t="n"/>
@@ -10809,13 +10809,13 @@
         </is>
       </c>
       <c r="E188" s="2" t="n"/>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="2" t="n"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>12 acres, a flock of 20 goats</t>
         </is>
       </c>
-      <c r="G188" s="2" t="n"/>
-      <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
       <c r="J188" s="2" t="n"/>
       <c r="K188" s="2" t="inlineStr">
@@ -11045,17 +11045,17 @@
         </is>
       </c>
       <c r="E192" s="2" t="n"/>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="2" t="n"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C103282</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C103282</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="n"/>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -11167,13 +11167,13 @@
         </is>
       </c>
       <c r="E194" s="2" t="n"/>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="2" t="n"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>squatters</t>
         </is>
       </c>
-      <c r="G194" s="2" t="n"/>
-      <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
       <c r="J194" s="2" t="n"/>
       <c r="K194" s="2" t="inlineStr">
@@ -11281,13 +11281,13 @@
         </is>
       </c>
       <c r="E196" s="2" t="n"/>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F196" s="2" t="n"/>
+      <c r="G196" s="2" t="n"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
         </is>
       </c>
-      <c r="G196" s="2" t="n"/>
-      <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
       <c r="J196" s="2" t="n"/>
       <c r="K196" s="2" t="inlineStr">
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="E215" s="3" t="n"/>
-      <c r="F215" s="3" t="inlineStr">
+      <c r="F215" s="3" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="3" t="inlineStr">
         <is>
           <t>Semi-routine and routine occupations, blue collar occupations</t>
         </is>
       </c>
-      <c r="G215" s="3" t="n"/>
-      <c r="H215" s="3" t="n"/>
       <c r="I215" s="3" t="n"/>
       <c r="J215" s="3" t="n"/>
       <c r="K215" s="3" t="inlineStr">
@@ -13549,17 +13549,17 @@
         </is>
       </c>
       <c r="E238" s="2" t="n"/>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F238" s="2" t="n"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>SDGIO:00010048</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>farmland, jewellery, livestock</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>SDGIO:00010048</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="n"/>
       <c r="I238" s="2" t="n"/>
       <c r="J238" s="2" t="n"/>
       <c r="K238" s="2" t="inlineStr">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="E239" s="2" t="n"/>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F239" s="2" t="n"/>
+      <c r="G239" s="2" t="n"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>$400, 3000 euros</t>
         </is>
       </c>
-      <c r="G239" s="2" t="n"/>
-      <c r="H239" s="2" t="n"/>
       <c r="I239" s="2" t="n"/>
       <c r="J239" s="2" t="n"/>
       <c r="K239" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffffff"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6196,67 +6202,67 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>BCIO:015027</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>household income</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EFO_0009695 </t>
         </is>
       </c>
-      <c r="H103" s="3" t="n"/>
-      <c r="I103" s="3" t="n"/>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
         <is>
           <t>household</t>
         </is>
       </c>
-      <c r="M103" s="3" t="n"/>
-      <c r="N103" s="3" t="inlineStr">
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="O103" s="3" t="n"/>
-      <c r="P103" s="3" t="n"/>
-      <c r="Q103" s="3" t="inlineStr">
+      <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
+      <c r="Q103" s="4" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="R103" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S103" s="3" t="n"/>
-      <c r="T103" s="3" t="n"/>
-      <c r="U103" s="3" t="n"/>
+      <c r="R103" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="S103" s="4" t="n"/>
+      <c r="T103" s="4" t="n"/>
+      <c r="U103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffffff"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,12 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6202,67 +6196,67 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>BCIO:015027</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>household income</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E103" s="4" t="n"/>
-      <c r="F103" s="4" t="n"/>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EFO_0009695 </t>
         </is>
       </c>
-      <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
-      <c r="J103" s="4" t="n"/>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>household</t>
         </is>
       </c>
-      <c r="M103" s="4" t="n"/>
-      <c r="N103" s="4" t="inlineStr">
+      <c r="M103" s="2" t="n"/>
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="O103" s="4" t="n"/>
-      <c r="P103" s="4" t="n"/>
-      <c r="Q103" s="4" t="inlineStr">
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
+      <c r="Q103" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="R103" s="4" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="S103" s="4" t="n"/>
-      <c r="T103" s="4" t="n"/>
-      <c r="U103" s="4" t="n"/>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="n"/>
+      <c r="T103" s="2" t="n"/>
+      <c r="U103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffe4b5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6732,59 +6738,59 @@
       <c r="U112" s="2" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>BCIO:015037</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>income-related welfare benefit</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>individual income</t>
         </is>
       </c>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="n"/>
-      <c r="M113" s="3" t="n"/>
-      <c r="N113" s="3" t="inlineStr">
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O113" s="3" t="n"/>
-      <c r="P113" s="3" t="n"/>
-      <c r="Q113" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R113" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S113" s="3" t="n"/>
-      <c r="T113" s="3" t="n"/>
-      <c r="U113" s="3" t="n"/>
+      <c r="O113" s="4" t="n"/>
+      <c r="P113" s="4" t="n"/>
+      <c r="Q113" s="4" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R113" s="4" t="inlineStr">
+        <is>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="S113" s="4" t="n"/>
+      <c r="T113" s="4" t="n"/>
+      <c r="U113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffe4b5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,12 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6738,59 +6732,59 @@
       <c r="U112" s="2" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>BCIO:015037</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>income-related welfare benefit</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>individual income</t>
         </is>
       </c>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="n"/>
-      <c r="M113" s="4" t="n"/>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O113" s="4" t="n"/>
-      <c r="P113" s="4" t="n"/>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="R113" s="4" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="S113" s="4" t="n"/>
-      <c r="T113" s="4" t="n"/>
-      <c r="U113" s="4" t="n"/>
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="n"/>
+      <c r="T113" s="2" t="n"/>
+      <c r="U113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -456,67 +456,67 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Informal definition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Logical definition</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-reference</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Synonyms</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-reference</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Examples</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Informal definition</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'is attribute of'</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'aggregate of'</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sub-ontology</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'is attribute of'</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'aggregate of'</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'is about'</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Curator note</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'is about'</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Aggregate</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -569,13 +569,13 @@
           <t>Comprehend the German language</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="inlineStr">
@@ -583,13 +583,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -628,13 +628,13 @@
           <t>The exclusion criteria were an inability to read English</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="inlineStr">
@@ -642,13 +642,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -687,13 +687,13 @@
           <t>Able to speak Chinese.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="inlineStr">
@@ -701,13 +701,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -746,13 +746,13 @@
           <t>Fluency in written English.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="inlineStr">
@@ -760,13 +760,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -805,15 +805,15 @@
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is reserved for tertiary programmes (ISCED 6) that lead directly to the award of an advanced research qualification. The theoretical duration of these programmes is 3 years full-time in most countries (for a cumulative total of at least 7 years FTE at the tertiary level), although the actual enrolment time is typically longer. The programmes are devoted to advanced study and original research. For a programme to be classified at ISCED 6, it:• requires, for successful completion, the submission of a thesis or dissertation of publishable quality that is the product of original research and represents a significant contribution to knowledge</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -823,13 +823,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -864,15 +864,15 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is a doctoral or equivalent level education.  Entry into doctoral (ISCED level 8) programmes or junior research positions normally requires the successful completion of specific ISCED level 7 programmes. Programmes at ISCED level 8, or doctoral or equivalent level, are designed primarily to lead to an advanced research qualification. Programmes at this ISCED level are devoted to advanced study and original research and are typically offered only by research-oriented tertiary educational institutions such as universities. Doctoral programmes exist in both academic and professional fields.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L7" s="2" t="n"/>
@@ -882,13 +882,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -923,15 +923,15 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A highest level of formal educational qualification achieved that is pre-primary education (ISCED 0), defined as the initial stage of organised instruction, designed primarily to introduce very young children to a school-type environment, that is, to provide a bridge between home and a school-based atmosphere. </t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -941,13 +941,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -986,15 +986,15 @@
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is lower secondary level of education (ISCED 2) which generally pursues the basic programmes of the primary level, although teaching is typically more subject-focused, often employing more specialised teachers who conduct classes in their field of specialisation. Lower secondary education may be either “terminal”(i.e. preparing students for direct entry into working life) and / or “preparatory” (i.e. preparing students for upper secondary education).This level can range from 2 to 6 years of schooling (the mode of OECD countries is 3 years).</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L9" s="2" t="n"/>
@@ -1004,13 +1004,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1045,15 +1045,15 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is a master's or equivalent level education. Entry into master's (ISCED level 7) programmes preparing for a second or further degree normally requires the successful completion of an ISCED level 6 or 7 programme. Additionally, it may be required to take and succeed in entry examinations. Programmes at ISCED level 7, or Master’s or equivalent level, are often designed to provide participants with advanced academic and/or professional knowledge, skills and competencies, leading to a second degree or equivalent qualification. Programmes at this level may have a substantial research component but do not yet lead to the award of a doctoral qualification. Typically, programmes at this level are theoretically-based but may include practical components and are informed by state of the art research and/or best professional practice. They are traditionally offered by universities and other tertiary educational institutions.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -1063,13 +1063,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1108,15 +1108,15 @@
         </is>
       </c>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that is primary education (ISCED 1) which usually begins at age 5, 6, or 7 and generally lasts for 4 (e.g. Germany) to 6 years (the mode of the OECD countries being six years). Programmes at the primary level generally require no previous formal education, although it is becoming increasingly common for children to have attended a pre-primary programme before entering primary education</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L11" s="2" t="n"/>
@@ -1126,13 +1126,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1175,15 +1175,15 @@
           <t>graduated high school, International Baccaulaureate, A Levels</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>A highest level of formal educational qualification achieved that corresponds to the final stage of secondary education in most OECD countries. Instruction is often more organised along subject-matter lines than at ISCED 2 level and teachers typically need to have a higher level, or more subject-specific, qualifications than at ISCED 2. The entrance age to this level is typically 15 or 16 years. There are substantial differences in the typical duration of ISCED 3 programmes both between and within countries, typically ranging from 2 to 5 years of schooling. ISCED 3 may either be “terminal” (i.e. preparing students for direct entry into working life) and/or “preparatory” (i.e. preparing students for tertiary education).</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -1193,13 +1193,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1234,13 +1234,13 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="inlineStr">
@@ -1248,13 +1248,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="inlineStr">
@@ -1307,13 +1307,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q14" s="2" t="n"/>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1348,13 +1348,13 @@
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="inlineStr">
@@ -1362,13 +1362,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q15" s="2" t="n"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1403,13 +1403,13 @@
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="inlineStr">
@@ -1417,13 +1417,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q16" s="2" t="n"/>
       <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1458,13 +1458,13 @@
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="inlineStr">
@@ -1472,13 +1472,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="inlineStr">
@@ -1531,13 +1531,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1572,13 +1572,13 @@
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="inlineStr">
@@ -1586,13 +1586,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1627,13 +1627,13 @@
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="inlineStr">
@@ -1641,13 +1641,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O20" s="2" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1682,13 +1682,13 @@
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="inlineStr">
@@ -1696,13 +1696,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1733,24 +1733,24 @@
           <t>person</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>The age at which a person is considered an adult will vary in different cultures and for different contexts.  For example, the age at which a person reaches physical maturity may not be the same age at which they are considered legally an adult in their country of residence.  For use in research contexts, the minimum age of an "adult" needs to be specified.</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>people</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1784,13 +1784,13 @@
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="inlineStr">
@@ -1798,13 +1798,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
@@ -1857,13 +1857,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1898,13 +1898,13 @@
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="inlineStr">
@@ -1912,13 +1912,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O25" s="2" t="n"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="n"/>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -1954,20 +1954,20 @@
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>"Exposed" encompasses both passive exposure to a behaviour change intervention e.g. nudges/environmental changes, and more active participation in a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="inlineStr">
@@ -2006,15 +2006,15 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="inlineStr">
@@ -2051,7 +2051,11 @@
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
@@ -2063,11 +2067,7 @@
       </c>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>actor</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>behaviour has to be specified
 s. also behaviour enacter, behaviour non-intender</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2158,24 +2158,24 @@
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>behaviour has to be specified
 s. also behaviour enacter, behaviour intender</t>
         </is>
       </c>
-      <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2210,24 +2210,24 @@
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>behaviour has to be specified
 s. also behaviour intender, behaviour non-intender</t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2258,21 +2258,21 @@
           <t>data item</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>The number of times a person performs a behaviour within a specific period.</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>The number of times a person performs a behaviour within a specific period.</t>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="inlineStr">
@@ -2280,13 +2280,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O32" s="2" t="n"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2321,13 +2321,13 @@
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="inlineStr">
@@ -2335,13 +2335,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="n"/>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2376,13 +2376,13 @@
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="inlineStr">
@@ -2390,13 +2390,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O34" s="2" t="n"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2431,13 +2431,13 @@
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="inlineStr">
@@ -2445,13 +2445,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q35" s="2" t="n"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2486,13 +2486,13 @@
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="inlineStr">
@@ -2500,13 +2500,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2541,13 +2541,13 @@
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="inlineStr">
@@ -2555,13 +2555,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="n"/>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q37" s="2" t="n"/>
       <c r="R37" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="inlineStr">
@@ -2614,13 +2614,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O38" s="2" t="n"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2655,13 +2655,13 @@
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="inlineStr">
@@ -2669,13 +2669,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2710,13 +2710,13 @@
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="inlineStr">
@@ -2724,13 +2724,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2765,13 +2765,13 @@
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="inlineStr">
@@ -2779,13 +2779,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O41" s="2" t="n"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2820,13 +2820,13 @@
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
@@ -2834,13 +2834,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="n"/>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2879,13 +2879,13 @@
         </is>
       </c>
       <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="inlineStr">
@@ -2893,13 +2893,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O43" s="2" t="n"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q43" s="2" t="n"/>
       <c r="R43" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -2930,7 +2930,7 @@
           <t>quality</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -2966,13 +2966,13 @@
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="inlineStr">
@@ -2980,13 +2980,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O45" s="2" t="n"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3021,15 +3021,15 @@
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage belonging to a specific caste</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -3039,13 +3039,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O46" s="2" t="n"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="n"/>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3080,15 +3080,15 @@
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The age until which a person is considered a child will vary in different cultures and for different contexts.  For use in research contexts, the maximum age of a "child" needs to be specified.  </t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L47" s="2" t="n"/>
@@ -3098,13 +3098,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O47" s="2" t="n"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="n"/>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q47" s="2" t="n"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3139,13 +3139,13 @@
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="inlineStr">
@@ -3153,13 +3153,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O48" s="2" t="n"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="n"/>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q48" s="2" t="n"/>
       <c r="R48" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3198,13 +3198,13 @@
         </is>
       </c>
       <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="inlineStr">
@@ -3212,13 +3212,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O49" s="2" t="n"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="n"/>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q49" s="2" t="n"/>
       <c r="R49" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
       <c r="N50" s="2" t="inlineStr">
@@ -3271,13 +3271,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O50" s="2" t="n"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="n"/>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q50" s="2" t="n"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3312,13 +3312,13 @@
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
       <c r="N51" s="2" t="inlineStr">
@@ -3326,13 +3326,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O51" s="2" t="n"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="n"/>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q51" s="2" t="n"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3367,13 +3367,13 @@
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="inlineStr">
@@ -3381,13 +3381,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O52" s="2" t="n"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P52" s="2" t="n"/>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q52" s="2" t="n"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3426,15 +3426,15 @@
           <t>psychology, counselling, public health</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>The division of knowledge and practice into different disciplines or fields is complex and depends on historical, social and structural factors</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L53" s="2" t="n"/>
@@ -3444,13 +3444,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O53" s="2" t="n"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q53" s="2" t="n"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3489,13 +3489,13 @@
           <t>Mathematics, English, hairdressing skills, vehicle engineering, nursing, astrophysics, accountancy</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="inlineStr">
@@ -3503,13 +3503,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O54" s="2" t="n"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q54" s="2" t="n"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3544,13 +3544,13 @@
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
       <c r="N55" s="2" t="inlineStr">
@@ -3558,13 +3558,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O55" s="2" t="n"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P55" s="2" t="n"/>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q55" s="2" t="n"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3599,13 +3599,13 @@
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K56" s="3" t="n"/>
       <c r="L56" s="3" t="n"/>
       <c r="M56" s="3" t="n"/>
       <c r="N56" s="3" t="inlineStr">
@@ -3613,13 +3613,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O56" s="3" t="n"/>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P56" s="3" t="n"/>
-      <c r="Q56" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q56" s="3" t="n"/>
       <c r="R56" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -3654,13 +3654,13 @@
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="inlineStr">
@@ -3668,13 +3668,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O57" s="2" t="n"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P57" s="2" t="n"/>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q57" s="2" t="n"/>
       <c r="R57" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3715,13 +3715,13 @@
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>This definition is based on the work of Scholz et al (2025), as published here: https://osf.io/2364r/</t>
         </is>
       </c>
-      <c r="P58" s="2" t="n"/>
-      <c r="Q58" s="2" t="n"/>
       <c r="R58" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3762,15 +3762,15 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
       <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="n"/>
-      <c r="O59" s="2" t="n"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="2" t="inlineStr">
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="inlineStr">
@@ -3825,13 +3825,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O60" s="2" t="n"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="inlineStr">
@@ -3884,13 +3884,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O61" s="2" t="n"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q61" s="2" t="n"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3925,13 +3925,13 @@
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="inlineStr">
@@ -3939,13 +3939,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O62" s="2" t="n"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P62" s="2" t="n"/>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q62" s="2" t="n"/>
       <c r="R62" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -3984,13 +3984,13 @@
         </is>
       </c>
       <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
       <c r="N63" s="2" t="inlineStr">
@@ -3998,13 +3998,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O63" s="2" t="n"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P63" s="2" t="n"/>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q63" s="2" t="n"/>
       <c r="R63" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4043,16 +4043,16 @@
         </is>
       </c>
       <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>An employment process is a  planned process wherein an employee performs actions that are formally or informally specified by an employer in return for remuneration.
 This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -4062,13 +4062,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O64" s="2" t="n"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P64" s="2" t="n"/>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q64" s="2" t="n"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4107,15 +4107,15 @@
         </is>
       </c>
       <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage who identify as belonging to a specific ethnic group</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L65" s="2" t="n"/>
@@ -4125,13 +4125,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O65" s="2" t="n"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P65" s="2" t="n"/>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q65" s="2" t="n"/>
       <c r="R65" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4166,13 +4166,13 @@
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
       <c r="N66" s="2" t="inlineStr">
@@ -4180,13 +4180,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O66" s="2" t="n"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q66" s="2" t="n"/>
       <c r="R66" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4221,13 +4221,13 @@
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n"/>
       <c r="N67" s="2" t="inlineStr">
@@ -4235,13 +4235,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O67" s="2" t="n"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="n"/>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4280,13 +4280,13 @@
         </is>
       </c>
       <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
       <c r="N68" s="2" t="inlineStr">
@@ -4294,13 +4294,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O68" s="2" t="n"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P68" s="2" t="n"/>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q68" s="2" t="n"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4335,13 +4335,13 @@
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="inlineStr">
@@ -4349,13 +4349,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O69" s="2" t="n"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q69" s="2" t="n"/>
       <c r="R69" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4390,13 +4390,13 @@
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="inlineStr">
@@ -4404,13 +4404,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O70" s="2" t="n"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="n"/>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q70" s="2" t="n"/>
       <c r="R70" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4442,24 +4442,24 @@
         </is>
       </c>
       <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:000089</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>woman</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:000089</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
       <c r="N71" s="2" t="inlineStr">
@@ -4467,13 +4467,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O71" s="2" t="n"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P71" s="2" t="n"/>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q71" s="2" t="n"/>
       <c r="R71" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4508,13 +4508,13 @@
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="inlineStr">
@@ -4522,13 +4522,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O72" s="2" t="n"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P72" s="2" t="n"/>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q72" s="2" t="n"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4563,13 +4563,13 @@
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="inlineStr">
@@ -4577,13 +4577,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O73" s="2" t="n"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P73" s="2" t="n"/>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q73" s="2" t="n"/>
       <c r="R73" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4618,13 +4618,13 @@
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="inlineStr">
@@ -4632,13 +4632,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O74" s="2" t="n"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q74" s="2" t="n"/>
       <c r="R74" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4673,13 +4673,13 @@
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
       <c r="N75" s="2" t="inlineStr">
@@ -4687,13 +4687,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q75" s="2" t="n"/>
       <c r="R75" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4728,13 +4728,13 @@
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
       <c r="N76" s="2" t="inlineStr">
@@ -4742,13 +4742,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O76" s="2" t="n"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P76" s="2" t="n"/>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q76" s="2" t="n"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4787,13 +4787,13 @@
         </is>
       </c>
       <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="n"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n"/>
       <c r="N77" s="2" t="inlineStr">
@@ -4801,13 +4801,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O77" s="2" t="n"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P77" s="2" t="n"/>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q77" s="2" t="n"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4842,13 +4842,13 @@
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n"/>
       <c r="N78" s="2" t="inlineStr">
@@ -4856,13 +4856,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O78" s="2" t="n"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P78" s="2" t="n"/>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q78" s="2" t="n"/>
       <c r="R78" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4897,13 +4897,13 @@
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="inlineStr">
@@ -4911,13 +4911,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O79" s="2" t="n"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P79" s="2" t="n"/>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q79" s="2" t="n"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -4952,13 +4952,13 @@
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="inlineStr">
@@ -4966,13 +4966,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O80" s="2" t="n"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P80" s="2" t="n"/>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q80" s="2" t="n"/>
       <c r="R80" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5007,13 +5007,13 @@
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="n"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="n"/>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="inlineStr">
@@ -5021,13 +5021,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O81" s="2" t="n"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P81" s="2" t="n"/>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5062,13 +5062,13 @@
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
       <c r="N82" s="2" t="inlineStr">
@@ -5076,13 +5076,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O82" s="2" t="n"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P82" s="2" t="n"/>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q82" s="2" t="n"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5117,13 +5117,13 @@
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K83" s="3" t="n"/>
       <c r="L83" s="3" t="n"/>
       <c r="M83" s="3" t="n"/>
       <c r="N83" s="3" t="inlineStr">
@@ -5131,13 +5131,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O83" s="3" t="n"/>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P83" s="3" t="n"/>
-      <c r="Q83" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q83" s="3" t="n"/>
       <c r="R83" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -5172,13 +5172,13 @@
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n"/>
       <c r="N84" s="2" t="inlineStr">
@@ -5186,13 +5186,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O84" s="2" t="n"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q84" s="2" t="n"/>
       <c r="R84" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5227,13 +5227,13 @@
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="2" t="n"/>
       <c r="N85" s="2" t="inlineStr">
@@ -5241,13 +5241,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O85" s="2" t="n"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P85" s="2" t="n"/>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q85" s="2" t="n"/>
       <c r="R85" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5282,13 +5282,13 @@
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="inlineStr">
@@ -5296,13 +5296,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O86" s="2" t="n"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q86" s="2" t="n"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5337,13 +5337,13 @@
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="2" t="n"/>
       <c r="N87" s="2" t="inlineStr">
@@ -5351,13 +5351,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O87" s="2" t="n"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P87" s="2" t="n"/>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q87" s="2" t="n"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5392,13 +5392,13 @@
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="n"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="n"/>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="inlineStr">
@@ -5406,13 +5406,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O88" s="2" t="n"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P88" s="2" t="n"/>
-      <c r="Q88" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q88" s="2" t="n"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5451,13 +5451,13 @@
           <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="inlineStr">
@@ -5465,13 +5465,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O89" s="2" t="n"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P89" s="2" t="n"/>
-      <c r="Q89" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q89" s="2" t="n"/>
       <c r="R89" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5514,13 +5514,13 @@
           <t>Having chicken pox, asthma, a heart attack</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J90" s="2" t="n"/>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="n"/>
       <c r="M90" s="2" t="n"/>
       <c r="N90" s="2" t="inlineStr">
@@ -5528,13 +5528,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O90" s="2" t="n"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P90" s="2" t="n"/>
-      <c r="Q90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="n"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="n"/>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="inlineStr">
@@ -5587,13 +5587,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O91" s="2" t="n"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P91" s="2" t="n"/>
-      <c r="Q91" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q91" s="2" t="n"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5628,23 +5628,23 @@
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="n"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P92" s="2" t="n"/>
-      <c r="Q92" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q92" s="2" t="n"/>
       <c r="R92" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5679,13 +5679,13 @@
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K93" s="3" t="n"/>
       <c r="L93" s="3" t="n"/>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="inlineStr">
@@ -5693,13 +5693,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O93" s="3" t="n"/>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P93" s="3" t="n"/>
-      <c r="Q93" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q93" s="3" t="n"/>
       <c r="R93" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -5738,13 +5738,13 @@
           <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="2" t="n"/>
       <c r="N94" s="2" t="inlineStr">
@@ -5752,13 +5752,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O94" s="2" t="n"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P94" s="2" t="n"/>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q94" s="2" t="n"/>
       <c r="R94" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5797,15 +5797,15 @@
         </is>
       </c>
       <c r="H95" s="2" t="n"/>
-      <c r="I95" s="2" t="n"/>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>The highest level of a packaged education process an individual has completed</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L95" s="2" t="n"/>
@@ -5815,13 +5815,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O95" s="2" t="n"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P95" s="2" t="n"/>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q95" s="2" t="n"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5852,7 +5852,7 @@
           <t>process</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -5892,13 +5892,13 @@
           <t>history of exposure to asbestos due to one's job</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="inlineStr">
@@ -5906,13 +5906,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O97" s="2" t="n"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P97" s="2" t="n"/>
-      <c r="Q97" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q97" s="2" t="n"/>
       <c r="R97" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -5951,13 +5951,13 @@
           <t>history of physical abuse by a parent</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="2" t="n"/>
       <c r="N98" s="2" t="inlineStr">
@@ -5965,13 +5965,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O98" s="2" t="n"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P98" s="2" t="n"/>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q98" s="2" t="n"/>
       <c r="R98" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6003,20 +6003,20 @@
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>person experiencing homelessness</t>
-        </is>
-      </c>
+      <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="n"/>
-      <c r="J99" s="2" t="n"/>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>person experiencing homelessness</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="2" t="n"/>
       <c r="N99" s="2" t="inlineStr">
@@ -6024,13 +6024,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O99" s="2" t="n"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P99" s="2" t="n"/>
-      <c r="Q99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q99" s="2" t="n"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6069,13 +6069,13 @@
         </is>
       </c>
       <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="n"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n"/>
       <c r="N100" s="2" t="inlineStr">
@@ -6083,13 +6083,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O100" s="2" t="n"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P100" s="2" t="n"/>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q100" s="2" t="n"/>
       <c r="R100" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6128,13 +6128,13 @@
         </is>
       </c>
       <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="n"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="n"/>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="inlineStr">
@@ -6142,13 +6142,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O101" s="2" t="n"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P101" s="2" t="n"/>
-      <c r="Q101" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q101" s="2" t="n"/>
       <c r="R101" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6179,12 +6179,12 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>A household is a person of group of people that live in the same dwelling. A dwelling is a self-contained unit of accommodation where all of the rooms are behind a single door that only the household can use.</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -6224,13 +6224,13 @@
         </is>
       </c>
       <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
           <t>household</t>
@@ -6242,13 +6242,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O103" s="2" t="n"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P103" s="2" t="n"/>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6287,13 +6287,13 @@
         </is>
       </c>
       <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n"/>
       <c r="N104" s="2" t="inlineStr">
@@ -6301,13 +6301,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O104" s="2" t="n"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+      <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6344,15 +6344,15 @@
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
       <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
       <c r="N105" s="2" t="n"/>
-      <c r="O105" s="2" t="n"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P105" s="2" t="n"/>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
           <t>cognitive representation</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -6421,13 +6421,13 @@
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="inlineStr">
@@ -6435,13 +6435,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O107" s="2" t="n"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6476,13 +6476,13 @@
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="n"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
       <c r="N108" s="2" t="inlineStr">
@@ -6491,13 +6491,13 @@
 </t>
         </is>
       </c>
-      <c r="O108" s="2" t="n"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P108" s="2" t="n"/>
-      <c r="Q108" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6532,15 +6532,15 @@
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="n"/>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"Common law" relationship refers to a person who is living with another person as a couple but who is not in a legally recognised marriage or other civil union. </t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L109" s="2" t="n"/>
@@ -6550,13 +6550,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O109" s="2" t="n"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P109" s="2" t="n"/>
-      <c r="Q109" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q109" s="2" t="n"/>
       <c r="R109" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6591,13 +6591,13 @@
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n"/>
       <c r="N110" s="2" t="inlineStr">
@@ -6605,13 +6605,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O110" s="2" t="n"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P110" s="2" t="n"/>
-      <c r="Q110" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6646,13 +6646,13 @@
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
       <c r="N111" s="2" t="inlineStr">
@@ -6660,13 +6660,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O111" s="2" t="n"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6701,13 +6701,13 @@
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n"/>
       <c r="N112" s="2" t="inlineStr">
@@ -6715,13 +6715,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O112" s="2" t="n"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q112" s="2" t="n"/>
       <c r="R112" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6756,13 +6756,13 @@
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="n"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n"/>
       <c r="N113" s="2" t="inlineStr">
@@ -6770,13 +6770,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O113" s="2" t="n"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P113" s="2" t="n"/>
-      <c r="Q113" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6811,13 +6811,13 @@
       <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="n"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="inlineStr">
@@ -6825,13 +6825,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O114" s="2" t="n"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P114" s="2" t="n"/>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6870,13 +6870,13 @@
           <t>walks for 15 mins/day, never eats meat, attends school daily</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J115" s="2" t="n"/>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="n"/>
       <c r="M115" s="2" t="n"/>
       <c r="N115" s="2" t="inlineStr">
@@ -6884,13 +6884,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O115" s="2" t="n"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P115" s="2" t="n"/>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q115" s="2" t="n"/>
       <c r="R115" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6929,13 +6929,13 @@
         </is>
       </c>
       <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="n"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J116" s="2" t="n"/>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="n"/>
       <c r="M116" s="2" t="n"/>
       <c r="N116" s="2" t="inlineStr">
@@ -6943,13 +6943,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O116" s="2" t="n"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P116" s="2" t="n"/>
-      <c r="Q116" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q116" s="2" t="n"/>
       <c r="R116" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -6984,13 +6984,13 @@
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
-      <c r="I117" s="2" t="n"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J117" s="2" t="n"/>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="n"/>
       <c r="M117" s="2" t="n"/>
       <c r="N117" s="2" t="inlineStr">
@@ -6998,13 +6998,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O117" s="2" t="n"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P117" s="2" t="n"/>
-      <c r="Q117" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7039,13 +7039,13 @@
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
       <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K118" s="3" t="n"/>
       <c r="L118" s="3" t="n"/>
       <c r="M118" s="3" t="n"/>
       <c r="N118" s="3" t="inlineStr">
@@ -7053,13 +7053,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O118" s="3" t="n"/>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P118" s="3" t="n"/>
-      <c r="Q118" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q118" s="3" t="n"/>
       <c r="R118" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7094,13 +7094,13 @@
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J119" s="2" t="n"/>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n"/>
       <c r="N119" s="2" t="inlineStr">
@@ -7108,13 +7108,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O119" s="2" t="n"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P119" s="2" t="n"/>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q119" s="2" t="n"/>
       <c r="R119" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7149,13 +7149,13 @@
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="n"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J120" s="2" t="n"/>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K120" s="2" t="n"/>
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
       <c r="N120" s="2" t="inlineStr">
@@ -7163,13 +7163,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O120" s="2" t="n"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P120" s="2" t="n"/>
-      <c r="Q120" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q120" s="2" t="n"/>
       <c r="R120" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7208,15 +7208,15 @@
         </is>
       </c>
       <c r="H121" s="3" t="n"/>
-      <c r="I121" s="3" t="n"/>
-      <c r="J121" s="3" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="inlineStr">
         <is>
           <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
-        </is>
-      </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -7226,13 +7226,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O121" s="3" t="n"/>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P121" s="3" t="n"/>
-      <c r="Q121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q121" s="3" t="n"/>
       <c r="R121" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7268,24 +7268,24 @@
           <t>OMRSE:00000092</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="I122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="H123" s="2" t="n"/>
-      <c r="I123" s="2" t="n"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J123" s="2" t="n"/>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K123" s="2" t="n"/>
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n"/>
       <c r="N123" s="2" t="inlineStr">
@@ -7337,13 +7337,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O123" s="2" t="n"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P123" s="2" t="n"/>
-      <c r="Q123" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q123" s="2" t="n"/>
       <c r="R123" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7380,15 +7380,15 @@
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
       <c r="J124" s="2" t="n"/>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K124" s="2" t="n"/>
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="2" t="n"/>
       <c r="N124" s="2" t="n"/>
-      <c r="O124" s="2" t="n"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P124" s="2" t="n"/>
       <c r="Q124" s="2" t="n"/>
       <c r="R124" s="2" t="inlineStr">
@@ -7427,15 +7427,15 @@
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
       <c r="J125" s="2" t="n"/>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K125" s="2" t="n"/>
       <c r="L125" s="2" t="n"/>
       <c r="M125" s="2" t="n"/>
       <c r="N125" s="2" t="n"/>
-      <c r="O125" s="2" t="n"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P125" s="2" t="n"/>
       <c r="Q125" s="2" t="n"/>
       <c r="R125" s="2" t="inlineStr">
@@ -7476,13 +7476,13 @@
           <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
         </is>
       </c>
-      <c r="I126" s="2" t="n"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K126" s="2" t="n"/>
       <c r="L126" s="2" t="n"/>
       <c r="M126" s="2" t="n"/>
       <c r="N126" s="2" t="inlineStr">
@@ -7490,13 +7490,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O126" s="2" t="n"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q126" s="2" t="n"/>
       <c r="R126" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7531,27 +7531,31 @@
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="n"/>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n"/>
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>There are many usages of the term ‘leadership'. This class refers to one particular usage.</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
-      <c r="N127" s="2" t="n"/>
-      <c r="O127" s="2" t="n"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P127" s="2" t="n"/>
-      <c r="Q127" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q127" s="2" t="n"/>
       <c r="R127" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7582,9 +7586,9 @@
           <t>mental capability</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>population</t>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -7592,9 +7596,9 @@
           <t>value</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -7628,15 +7632,15 @@
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n"/>
+      <c r="K129" s="2" t="inlineStr">
         <is>
           <t>This is a fuzzy class. The minimum duration for a disability to be deemed long-term is subject to debate.  12 months seems reasonable, but others may wish to specify a different duration if required for their purposes.</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L129" s="2" t="n"/>
@@ -7646,13 +7650,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O129" s="2" t="n"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q129" s="2" t="n"/>
       <c r="R129" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7688,23 +7692,23 @@
       <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K130" s="2" t="n"/>
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
       <c r="N130" s="2" t="n"/>
-      <c r="O130" s="2" t="n"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q130" s="2" t="n"/>
       <c r="R130" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7739,13 +7743,13 @@
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
-      <c r="I131" s="2" t="n"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J131" s="2" t="n"/>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K131" s="2" t="n"/>
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n"/>
       <c r="N131" s="2" t="inlineStr">
@@ -7753,13 +7757,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O131" s="2" t="n"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P131" s="2" t="n"/>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q131" s="2" t="n"/>
       <c r="R131" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7791,24 +7795,24 @@
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:000090</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>man</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:000090</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="n"/>
-      <c r="I132" s="2" t="n"/>
-      <c r="J132" s="2" t="n"/>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K132" s="2" t="n"/>
       <c r="L132" s="2" t="n"/>
       <c r="M132" s="2" t="n"/>
       <c r="N132" s="2" t="inlineStr">
@@ -7816,13 +7820,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O132" s="2" t="n"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P132" s="2" t="n"/>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q132" s="2" t="n"/>
       <c r="R132" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7857,13 +7861,13 @@
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K133" s="3" t="n"/>
       <c r="L133" s="3" t="n"/>
       <c r="M133" s="3" t="n"/>
       <c r="N133" s="3" t="inlineStr">
@@ -7871,13 +7875,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O133" s="3" t="n"/>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P133" s="3" t="n"/>
-      <c r="Q133" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q133" s="3" t="n"/>
       <c r="R133" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -7912,13 +7916,13 @@
       <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
-      <c r="I134" s="2" t="n"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J134" s="2" t="n"/>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K134" s="2" t="n"/>
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n"/>
       <c r="N134" s="2" t="inlineStr">
@@ -7926,13 +7930,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O134" s="2" t="n"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P134" s="2" t="n"/>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q134" s="2" t="n"/>
       <c r="R134" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7971,15 +7975,15 @@
           <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
         </is>
       </c>
-      <c r="I135" s="2" t="n"/>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n"/>
+      <c r="K135" s="2" t="inlineStr">
         <is>
           <t>This entity reflects having been prescribed a medication.  Actual use of the medicine would be captured as a behaviour</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L135" s="2" t="n"/>
@@ -7989,13 +7993,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O135" s="2" t="n"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P135" s="2" t="n"/>
-      <c r="Q135" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q135" s="2" t="n"/>
       <c r="R135" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8030,15 +8034,15 @@
       <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
-      <c r="I136" s="2" t="n"/>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n"/>
+      <c r="K136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A member of a multi-person household lives with at least one other person in the same dwelling. </t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -8048,13 +8052,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O136" s="2" t="n"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q136" s="2" t="n"/>
       <c r="R136" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8097,13 +8101,13 @@
           <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J137" s="2" t="n"/>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K137" s="2" t="n"/>
       <c r="L137" s="2" t="n"/>
       <c r="M137" s="2" t="n"/>
       <c r="N137" s="2" t="inlineStr">
@@ -8111,13 +8115,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O137" s="2" t="n"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q137" s="2" t="n"/>
       <c r="R137" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8156,13 +8160,13 @@
           <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="n"/>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K138" s="2" t="n"/>
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
       <c r="N138" s="2" t="inlineStr">
@@ -8170,13 +8174,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O138" s="2" t="n"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q138" s="2" t="n"/>
       <c r="R138" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8215,13 +8219,13 @@
           <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="n"/>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K139" s="2" t="n"/>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="inlineStr">
@@ -8229,13 +8233,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O139" s="2" t="n"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P139" s="2" t="n"/>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q139" s="2" t="n"/>
       <c r="R139" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8274,15 +8278,15 @@
           <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n"/>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n"/>
+      <c r="K140" s="2" t="inlineStr">
         <is>
           <t>A member of a multi-generational household lives with other people that are from more than one generation. A generation is all the people of about the same age within a society or within a particular family</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -8292,13 +8296,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O140" s="2" t="n"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P140" s="2" t="n"/>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q140" s="2" t="n"/>
       <c r="R140" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8333,13 +8337,13 @@
       <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
-      <c r="I141" s="2" t="n"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J141" s="2" t="n"/>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K141" s="2" t="n"/>
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="2" t="n"/>
       <c r="N141" s="2" t="inlineStr">
@@ -8347,13 +8351,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O141" s="2" t="n"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P141" s="2" t="n"/>
-      <c r="Q141" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q141" s="2" t="n"/>
       <c r="R141" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8384,9 +8388,9 @@
           <t>personal capability</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>population</t>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -8394,9 +8398,9 @@
           <t>value</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -8430,13 +8434,13 @@
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
-      <c r="I143" s="2" t="n"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J143" s="2" t="n"/>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K143" s="2" t="n"/>
       <c r="L143" s="2" t="n"/>
       <c r="M143" s="2" t="n"/>
       <c r="N143" s="2" t="inlineStr">
@@ -8444,13 +8448,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O143" s="2" t="n"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P143" s="2" t="n"/>
-      <c r="Q143" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q143" s="2" t="n"/>
       <c r="R143" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8485,13 +8489,13 @@
       <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="n"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="n"/>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K144" s="2" t="n"/>
       <c r="L144" s="2" t="n"/>
       <c r="M144" s="2" t="n"/>
       <c r="N144" s="2" t="inlineStr">
@@ -8499,13 +8503,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O144" s="2" t="n"/>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P144" s="2" t="n"/>
-      <c r="Q144" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q144" s="2" t="n"/>
       <c r="R144" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8540,13 +8544,13 @@
       <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="n"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J145" s="2" t="n"/>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K145" s="2" t="n"/>
       <c r="L145" s="2" t="n"/>
       <c r="M145" s="2" t="n"/>
       <c r="N145" s="2" t="inlineStr">
@@ -8554,13 +8558,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O145" s="2" t="n"/>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P145" s="2" t="n"/>
-      <c r="Q145" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q145" s="2" t="n"/>
       <c r="R145" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8599,13 +8603,13 @@
         </is>
       </c>
       <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="n"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J146" s="2" t="n"/>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K146" s="2" t="n"/>
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="2" t="n"/>
       <c r="N146" s="2" t="inlineStr">
@@ -8613,13 +8617,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O146" s="2" t="n"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P146" s="2" t="n"/>
-      <c r="Q146" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q146" s="2" t="n"/>
       <c r="R146" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8658,13 +8662,13 @@
         </is>
       </c>
       <c r="H147" s="2" t="n"/>
-      <c r="I147" s="2" t="n"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="n"/>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K147" s="2" t="n"/>
       <c r="L147" s="2" t="n"/>
       <c r="M147" s="2" t="n"/>
       <c r="N147" s="2" t="inlineStr">
@@ -8672,13 +8676,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O147" s="2" t="n"/>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P147" s="2" t="n"/>
-      <c r="Q147" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q147" s="2" t="n"/>
       <c r="R147" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8713,13 +8717,13 @@
       <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="n"/>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K148" s="2" t="n"/>
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="2" t="n"/>
       <c r="N148" s="2" t="inlineStr">
@@ -8727,13 +8731,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O148" s="2" t="n"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P148" s="2" t="n"/>
-      <c r="Q148" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q148" s="2" t="n"/>
       <c r="R148" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8768,13 +8772,13 @@
       <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
-      <c r="I149" s="2" t="n"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J149" s="2" t="n"/>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K149" s="2" t="n"/>
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="2" t="n"/>
       <c r="N149" s="2" t="inlineStr">
@@ -8782,13 +8786,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O149" s="2" t="n"/>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P149" s="2" t="n"/>
-      <c r="Q149" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q149" s="2" t="n"/>
       <c r="R149" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8825,15 +8829,15 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2" t="n"/>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
       <c r="N150" s="2" t="n"/>
-      <c r="O150" s="2" t="n"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P150" s="2" t="n"/>
       <c r="Q150" s="2" t="n"/>
       <c r="R150" s="2" t="inlineStr">
@@ -8870,13 +8874,13 @@
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
-      <c r="I151" s="2" t="n"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
       <c r="J151" s="2" t="n"/>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K151" s="2" t="n"/>
       <c r="L151" s="2" t="n"/>
       <c r="M151" s="2" t="n"/>
       <c r="N151" s="2" t="inlineStr">
@@ -8884,17 +8888,17 @@
           <t>number</t>
         </is>
       </c>
-      <c r="O151" s="2" t="n"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
           <t>education process</t>
         </is>
       </c>
-      <c r="Q151" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+      <c r="Q151" s="2" t="n"/>
       <c r="R151" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8929,13 +8933,13 @@
       <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
-      <c r="I152" s="2" t="n"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="n"/>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K152" s="2" t="n"/>
       <c r="L152" s="2" t="n"/>
       <c r="M152" s="2" t="n"/>
       <c r="N152" s="2" t="inlineStr">
@@ -8943,13 +8947,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O152" s="2" t="n"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P152" s="2" t="n"/>
-      <c r="Q152" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q152" s="2" t="n"/>
       <c r="R152" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -8984,13 +8988,13 @@
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
-      <c r="I153" s="2" t="n"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J153" s="2" t="n"/>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K153" s="2" t="n"/>
       <c r="L153" s="2" t="n"/>
       <c r="M153" s="2" t="n"/>
       <c r="N153" s="2" t="inlineStr">
@@ -8998,13 +9002,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O153" s="2" t="n"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P153" s="2" t="n"/>
-      <c r="Q153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q153" s="2" t="n"/>
       <c r="R153" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9043,13 +9047,13 @@
           <t>Scout leader, club chairperson</t>
         </is>
       </c>
-      <c r="I154" s="2" t="n"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K154" s="2" t="n"/>
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
       <c r="N154" s="2" t="inlineStr">
@@ -9057,13 +9061,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O154" s="2" t="n"/>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="n"/>
-      <c r="Q154" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q154" s="2" t="n"/>
       <c r="R154" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9098,13 +9102,13 @@
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
-      <c r="I155" s="2" t="n"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J155" s="2" t="n"/>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K155" s="2" t="n"/>
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="inlineStr">
@@ -9112,13 +9116,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O155" s="2" t="n"/>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P155" s="2" t="n"/>
-      <c r="Q155" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q155" s="2" t="n"/>
       <c r="R155" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9155,15 +9159,15 @@
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
       <c r="J156" s="2" t="n"/>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K156" s="2" t="n"/>
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
       <c r="N156" s="2" t="n"/>
-      <c r="O156" s="2" t="n"/>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P156" s="2" t="n"/>
       <c r="Q156" s="2" t="n"/>
       <c r="R156" s="2" t="inlineStr">
@@ -9200,13 +9204,13 @@
       <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
-      <c r="I157" s="2" t="n"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J157" s="2" t="n"/>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K157" s="2" t="n"/>
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n"/>
       <c r="N157" s="2" t="inlineStr">
@@ -9214,13 +9218,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O157" s="2" t="n"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P157" s="2" t="n"/>
-      <c r="Q157" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q157" s="2" t="n"/>
       <c r="R157" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9259,15 +9263,15 @@
         </is>
       </c>
       <c r="H158" s="2" t="n"/>
-      <c r="I158" s="2" t="n"/>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n"/>
+      <c r="K158" s="2" t="inlineStr">
         <is>
           <t>This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -9277,13 +9281,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O158" s="2" t="n"/>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P158" s="2" t="n"/>
-      <c r="Q158" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q158" s="2" t="n"/>
       <c r="R158" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9318,13 +9322,13 @@
       <c r="F159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
-      <c r="I159" s="2" t="n"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J159" s="2" t="n"/>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K159" s="2" t="n"/>
       <c r="L159" s="2" t="n"/>
       <c r="M159" s="2" t="n"/>
       <c r="N159" s="2" t="inlineStr">
@@ -9333,13 +9337,13 @@
 </t>
         </is>
       </c>
-      <c r="O159" s="2" t="n"/>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P159" s="2" t="n"/>
-      <c r="Q159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q159" s="2" t="n"/>
       <c r="R159" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9378,13 +9382,13 @@
         </is>
       </c>
       <c r="H160" s="2" t="n"/>
-      <c r="I160" s="2" t="n"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J160" s="2" t="n"/>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K160" s="2" t="n"/>
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="2" t="n"/>
       <c r="N160" s="2" t="inlineStr">
@@ -9392,13 +9396,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O160" s="2" t="n"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P160" s="2" t="n"/>
-      <c r="Q160" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q160" s="2" t="n"/>
       <c r="R160" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9433,15 +9437,15 @@
       <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n"/>
+      <c r="K161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A person can hold a parental role in a child's life without being that child's biological or legal parent. </t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L161" s="2" t="n"/>
@@ -9451,13 +9455,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O161" s="2" t="n"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P161" s="2" t="n"/>
-      <c r="Q161" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q161" s="2" t="n"/>
       <c r="R161" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9492,23 +9496,23 @@
       <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="n"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K162" s="2" t="n"/>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
       <c r="N162" s="2" t="n"/>
-      <c r="O162" s="2" t="n"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P162" s="2" t="n"/>
-      <c r="Q162" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q162" s="2" t="n"/>
       <c r="R162" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9543,23 +9547,23 @@
       <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
-      <c r="I163" s="2" t="n"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J163" s="2" t="n"/>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K163" s="2" t="n"/>
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="2" t="n"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P163" s="2" t="n"/>
-      <c r="Q163" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9590,9 +9594,9 @@
           <t>role</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>population</t>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -9600,9 +9604,9 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -9639,15 +9643,15 @@
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
       <c r="J165" s="2" t="n"/>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K165" s="2" t="n"/>
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n"/>
       <c r="N165" s="2" t="n"/>
-      <c r="O165" s="2" t="n"/>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P165" s="2" t="n"/>
       <c r="Q165" s="2" t="n"/>
       <c r="R165" s="2" t="inlineStr">
@@ -9680,7 +9684,7 @@
           <t>extended organism</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="O166" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -9718,15 +9722,15 @@
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
       <c r="J167" s="2" t="n"/>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="2" t="n"/>
       <c r="N167" s="2" t="n"/>
-      <c r="O167" s="2" t="n"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P167" s="2" t="n"/>
       <c r="Q167" s="2" t="n"/>
       <c r="R167" s="2" t="inlineStr">
@@ -9764,14 +9768,10 @@
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Attributes included under this header are age, immigration, social and economic conditions. </t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -9781,7 +9781,11 @@
       </c>
       <c r="M168" s="2" t="n"/>
       <c r="N168" s="2" t="n"/>
-      <c r="O168" s="2" t="n"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P168" s="2" t="n"/>
       <c r="Q168" s="2" t="n"/>
       <c r="R168" s="2" t="inlineStr">
@@ -9814,18 +9818,18 @@
           <t>bodily disposition</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>The ability of someone to perform some useful and/or beneficial activity.</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>The phrase 'ordinarily brings benefits to an organism or group of organism' is used to explain that capabilities normally provide a benefit. 
 For instance, having a musical ability is ordinarily an ability that is positive for a person (e.g., they receive positive feedback about their ability). However, in certain exceptional cases (e.g., a neighbour becoming annoyed with a person playing the piano and expressing this annoyance), the ability might not bring benefits.</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="O169" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -9863,15 +9867,15 @@
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
       <c r="J170" s="2" t="n"/>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K170" s="2" t="n"/>
       <c r="L170" s="2" t="n"/>
       <c r="M170" s="2" t="n"/>
       <c r="N170" s="2" t="n"/>
-      <c r="O170" s="2" t="n"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P170" s="2" t="n"/>
       <c r="Q170" s="2" t="n"/>
       <c r="R170" s="2" t="inlineStr">
@@ -9908,13 +9912,13 @@
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
-      <c r="I171" s="2" t="n"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J171" s="2" t="n"/>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K171" s="2" t="n"/>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n"/>
       <c r="N171" s="2" t="inlineStr">
@@ -9922,13 +9926,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O171" s="2" t="n"/>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P171" s="2" t="n"/>
-      <c r="Q171" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q171" s="2" t="n"/>
       <c r="R171" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9963,13 +9967,13 @@
       <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="n"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J172" s="2" t="n"/>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K172" s="2" t="n"/>
       <c r="L172" s="2" t="n"/>
       <c r="M172" s="2" t="n"/>
       <c r="N172" s="2" t="inlineStr">
@@ -9977,13 +9981,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O172" s="2" t="n"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P172" s="2" t="n"/>
-      <c r="Q172" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q172" s="2" t="n"/>
       <c r="R172" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10018,13 +10022,13 @@
       <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
-      <c r="I173" s="2" t="n"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J173" s="2" t="n"/>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K173" s="2" t="n"/>
       <c r="L173" s="2" t="n"/>
       <c r="M173" s="2" t="n"/>
       <c r="N173" s="2" t="inlineStr">
@@ -10032,13 +10036,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O173" s="2" t="n"/>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P173" s="2" t="n"/>
-      <c r="Q173" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q173" s="2" t="n"/>
       <c r="R173" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10073,13 +10077,13 @@
       <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
-      <c r="I174" s="2" t="n"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J174" s="2" t="n"/>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K174" s="2" t="n"/>
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="2" t="n"/>
       <c r="N174" s="2" t="inlineStr">
@@ -10087,13 +10091,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O174" s="2" t="n"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P174" s="2" t="n"/>
-      <c r="Q174" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q174" s="2" t="n"/>
       <c r="R174" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10128,15 +10132,15 @@
       <c r="F175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
-      <c r="I175" s="2" t="n"/>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n"/>
+      <c r="K175" s="2" t="inlineStr">
         <is>
           <t>This is a fuzzy class.  Users will need to specify exactly how similar an intervention needs to be to qualify as "the same" as the current intervention in their context.</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L175" s="2" t="n"/>
@@ -10146,13 +10150,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O175" s="2" t="n"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P175" s="2" t="n"/>
-      <c r="Q175" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q175" s="2" t="n"/>
       <c r="R175" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10183,25 +10187,25 @@
           <t>process</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>'process' and 'part of' some 'personal history'</t>
         </is>
       </c>
-      <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
       <c r="J176" s="2" t="n"/>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="2" t="n"/>
       <c r="N176" s="2" t="n"/>
-      <c r="O176" s="2" t="n"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P176" s="2" t="n"/>
       <c r="Q176" s="2" t="n"/>
       <c r="R176" s="2" t="inlineStr">
@@ -10238,13 +10242,13 @@
       <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
-      <c r="I177" s="2" t="n"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J177" s="2" t="n"/>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K177" s="2" t="n"/>
       <c r="L177" s="2" t="n"/>
       <c r="M177" s="2" t="n"/>
       <c r="N177" s="2" t="inlineStr">
@@ -10252,13 +10256,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O177" s="2" t="n"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P177" s="2" t="n"/>
-      <c r="Q177" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q177" s="2" t="n"/>
       <c r="R177" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10297,13 +10301,13 @@
           <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
         </is>
       </c>
-      <c r="I178" s="2" t="n"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="n"/>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K178" s="2" t="n"/>
       <c r="L178" s="2" t="n"/>
       <c r="M178" s="2" t="n"/>
       <c r="N178" s="2" t="inlineStr">
@@ -10311,13 +10315,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O178" s="2" t="n"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P178" s="2" t="n"/>
-      <c r="Q178" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q178" s="2" t="n"/>
       <c r="R178" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10348,29 +10352,29 @@
           <t>role</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n"/>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I179" s="2" t="n"/>
+      <c r="J179" s="2" t="n"/>
+      <c r="K179" s="2" t="inlineStr">
         <is>
           <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
-        </is>
-      </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L179" s="2" t="n"/>
       <c r="M179" s="2" t="n"/>
       <c r="N179" s="2" t="n"/>
-      <c r="O179" s="2" t="n"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P179" s="2" t="n"/>
       <c r="Q179" s="2" t="n"/>
       <c r="R179" s="2" t="inlineStr">
@@ -10411,13 +10415,13 @@
           <t>susceptibility to addiction, vulnerability to depression</t>
         </is>
       </c>
-      <c r="I180" s="2" t="n"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="n"/>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K180" s="2" t="n"/>
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="2" t="n"/>
       <c r="N180" s="2" t="inlineStr">
@@ -10425,13 +10429,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O180" s="2" t="n"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P180" s="2" t="n"/>
-      <c r="Q180" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q180" s="2" t="n"/>
       <c r="R180" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10463,20 +10467,20 @@
         </is>
       </c>
       <c r="E181" s="2" t="n"/>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>risk factor for harmful behaviour</t>
-        </is>
-      </c>
+      <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="n"/>
-      <c r="I181" s="2" t="n"/>
-      <c r="J181" s="2" t="n"/>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>risk factor for harmful behaviour</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="n"/>
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="2" t="n"/>
       <c r="N181" s="2" t="inlineStr">
@@ -10484,13 +10488,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O181" s="2" t="n"/>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P181" s="2" t="n"/>
-      <c r="Q181" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q181" s="2" t="n"/>
       <c r="R181" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10525,13 +10529,13 @@
       <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
-      <c r="I182" s="2" t="n"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J182" s="2" t="n"/>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K182" s="2" t="n"/>
       <c r="L182" s="2" t="n"/>
       <c r="M182" s="2" t="n"/>
       <c r="N182" s="2" t="inlineStr">
@@ -10539,13 +10543,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O182" s="2" t="n"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P182" s="2" t="n"/>
-      <c r="Q182" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q182" s="2" t="n"/>
       <c r="R182" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10576,9 +10580,9 @@
           <t>insured party role</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>population</t>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -10586,9 +10590,9 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -10670,13 +10674,13 @@
       <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
-      <c r="I185" s="2" t="n"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J185" s="2" t="n"/>
-      <c r="K185" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K185" s="2" t="n"/>
       <c r="L185" s="2" t="n"/>
       <c r="M185" s="2" t="n"/>
       <c r="N185" s="2" t="inlineStr">
@@ -10684,13 +10688,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O185" s="2" t="n"/>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P185" s="2" t="n"/>
-      <c r="Q185" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q185" s="2" t="n"/>
       <c r="R185" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10725,13 +10729,13 @@
       <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
-      <c r="I186" s="2" t="n"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J186" s="2" t="n"/>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K186" s="2" t="n"/>
       <c r="L186" s="2" t="n"/>
       <c r="M186" s="2" t="n"/>
       <c r="N186" s="2" t="inlineStr">
@@ -10739,13 +10743,13 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O186" s="2" t="n"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P186" s="2" t="n"/>
-      <c r="Q186" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q186" s="2" t="n"/>
       <c r="R186" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10776,7 +10780,7 @@
           <t>specifically dependent continuant</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="O187" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -10816,13 +10820,13 @@
           <t>12 acres, a flock of 20 goats</t>
         </is>
       </c>
-      <c r="I188" s="2" t="n"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="n"/>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K188" s="2" t="n"/>
       <c r="L188" s="2" t="n"/>
       <c r="M188" s="2" t="n"/>
       <c r="N188" s="2" t="inlineStr">
@@ -10830,17 +10834,17 @@
           <t>number</t>
         </is>
       </c>
-      <c r="O188" s="2" t="n"/>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
           <t>valuable material resource owned</t>
         </is>
       </c>
-      <c r="Q188" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+      <c r="Q188" s="2" t="n"/>
       <c r="R188" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10879,13 +10883,13 @@
         </is>
       </c>
       <c r="H189" s="2" t="n"/>
-      <c r="I189" s="2" t="n"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J189" s="2" t="n"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K189" s="2" t="n"/>
       <c r="L189" s="2" t="n"/>
       <c r="M189" s="2" t="n"/>
       <c r="N189" s="2" t="inlineStr">
@@ -10893,13 +10897,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O189" s="2" t="n"/>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P189" s="2" t="n"/>
-      <c r="Q189" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q189" s="2" t="n"/>
       <c r="R189" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10938,13 +10942,13 @@
         </is>
       </c>
       <c r="H190" s="2" t="n"/>
-      <c r="I190" s="2" t="n"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J190" s="2" t="n"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K190" s="2" t="n"/>
       <c r="L190" s="2" t="n"/>
       <c r="M190" s="2" t="n"/>
       <c r="N190" s="2" t="inlineStr">
@@ -10952,13 +10956,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O190" s="2" t="n"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P190" s="2" t="n"/>
-      <c r="Q190" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q190" s="2" t="n"/>
       <c r="R190" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -10993,13 +10997,13 @@
       <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
-      <c r="I191" s="2" t="n"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J191" s="2" t="n"/>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K191" s="2" t="n"/>
       <c r="L191" s="2" t="n"/>
       <c r="M191" s="2" t="n"/>
       <c r="N191" s="2" t="inlineStr">
@@ -11007,13 +11011,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O191" s="2" t="n"/>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P191" s="2" t="n"/>
-      <c r="Q191" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q191" s="2" t="n"/>
       <c r="R191" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11056,15 +11060,15 @@
           <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
         </is>
       </c>
-      <c r="I192" s="2" t="n"/>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n"/>
+      <c r="K192" s="2" t="inlineStr">
         <is>
           <t>presented in aggregated form as proportion/percentage belonging to a specified religious group</t>
-        </is>
-      </c>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -11074,13 +11078,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O192" s="2" t="n"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P192" s="2" t="n"/>
-      <c r="Q192" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q192" s="2" t="n"/>
       <c r="R192" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11115,13 +11119,13 @@
       <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
-      <c r="I193" s="2" t="n"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J193" s="2" t="n"/>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K193" s="2" t="n"/>
       <c r="L193" s="2" t="n"/>
       <c r="M193" s="2" t="n"/>
       <c r="N193" s="2" t="inlineStr">
@@ -11129,13 +11133,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O193" s="2" t="n"/>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P193" s="2" t="n"/>
-      <c r="Q193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q193" s="2" t="n"/>
       <c r="R193" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11174,13 +11178,13 @@
           <t>squatters</t>
         </is>
       </c>
-      <c r="I194" s="2" t="n"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J194" s="2" t="n"/>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K194" s="2" t="n"/>
       <c r="L194" s="2" t="n"/>
       <c r="M194" s="2" t="n"/>
       <c r="N194" s="2" t="inlineStr">
@@ -11188,13 +11192,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O194" s="2" t="n"/>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P194" s="2" t="n"/>
-      <c r="Q194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q194" s="2" t="n"/>
       <c r="R194" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11229,13 +11233,13 @@
       <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
-      <c r="I195" s="2" t="n"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J195" s="2" t="n"/>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K195" s="2" t="n"/>
       <c r="L195" s="2" t="n"/>
       <c r="M195" s="2" t="n"/>
       <c r="N195" s="2" t="inlineStr">
@@ -11243,13 +11247,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O195" s="2" t="n"/>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P195" s="2" t="n"/>
-      <c r="Q195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q195" s="2" t="n"/>
       <c r="R195" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11288,13 +11292,13 @@
           <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
         </is>
       </c>
-      <c r="I196" s="2" t="n"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
       <c r="J196" s="2" t="n"/>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K196" s="2" t="n"/>
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="2" t="n"/>
       <c r="N196" s="2" t="inlineStr">
@@ -11302,13 +11306,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O196" s="2" t="n"/>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P196" s="2" t="n"/>
-      <c r="Q196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
+      <c r="Q196" s="2" t="n"/>
       <c r="R196" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11343,13 +11347,13 @@
       <c r="F197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
-      <c r="I197" s="2" t="n"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J197" s="2" t="n"/>
-      <c r="K197" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K197" s="2" t="n"/>
       <c r="L197" s="2" t="n"/>
       <c r="M197" s="2" t="n"/>
       <c r="N197" s="2" t="inlineStr">
@@ -11357,13 +11361,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O197" s="2" t="n"/>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P197" s="2" t="n"/>
-      <c r="Q197" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q197" s="2" t="n"/>
       <c r="R197" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11398,13 +11402,13 @@
       <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
-      <c r="I198" s="2" t="n"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="n"/>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K198" s="2" t="n"/>
       <c r="L198" s="2" t="n"/>
       <c r="M198" s="2" t="n"/>
       <c r="N198" s="2" t="inlineStr">
@@ -11412,13 +11416,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O198" s="2" t="n"/>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P198" s="2" t="n"/>
-      <c r="Q198" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q198" s="2" t="n"/>
       <c r="R198" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11449,7 +11453,7 @@
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="O199" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -11485,13 +11489,13 @@
       <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J200" s="3" t="n"/>
-      <c r="K200" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K200" s="3" t="n"/>
       <c r="L200" s="3" t="n"/>
       <c r="M200" s="3" t="n"/>
       <c r="N200" s="3" t="inlineStr">
@@ -11499,13 +11503,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O200" s="3" t="n"/>
+      <c r="O200" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P200" s="3" t="n"/>
-      <c r="Q200" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q200" s="3" t="n"/>
       <c r="R200" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -11540,13 +11544,13 @@
       <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
-      <c r="I201" s="2" t="n"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J201" s="2" t="n"/>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K201" s="2" t="n"/>
       <c r="L201" s="2" t="n"/>
       <c r="M201" s="2" t="n"/>
       <c r="N201" s="2" t="inlineStr">
@@ -11554,13 +11558,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O201" s="2" t="n"/>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P201" s="2" t="n"/>
-      <c r="Q201" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q201" s="2" t="n"/>
       <c r="R201" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11595,13 +11599,13 @@
       <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="n"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J202" s="2" t="n"/>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="2" t="n"/>
       <c r="N202" s="2" t="inlineStr">
@@ -11609,13 +11613,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O202" s="2" t="n"/>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P202" s="2" t="n"/>
-      <c r="Q202" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q202" s="2" t="n"/>
       <c r="R202" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11654,15 +11658,15 @@
         </is>
       </c>
       <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="n"/>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="n"/>
+      <c r="K203" s="2" t="inlineStr">
         <is>
           <t>employment status where the person is their own employer</t>
-        </is>
-      </c>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L203" s="2" t="n"/>
@@ -11672,13 +11676,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O203" s="2" t="n"/>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P203" s="2" t="n"/>
-      <c r="Q203" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q203" s="2" t="n"/>
       <c r="R203" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11709,7 +11713,7 @@
           <t>identity</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="O204" t="inlineStr">
         <is>
           <t>population</t>
         </is>
@@ -11749,13 +11753,13 @@
         </is>
       </c>
       <c r="H205" s="2" t="n"/>
-      <c r="I205" s="2" t="n"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J205" s="2" t="n"/>
-      <c r="K205" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K205" s="2" t="n"/>
       <c r="L205" s="2" t="n"/>
       <c r="M205" s="2" t="n"/>
       <c r="N205" s="2" t="inlineStr">
@@ -11763,13 +11767,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O205" s="2" t="n"/>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P205" s="2" t="n"/>
-      <c r="Q205" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q205" s="2" t="n"/>
       <c r="R205" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11804,13 +11808,13 @@
       <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
-      <c r="I206" s="2" t="n"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J206" s="2" t="n"/>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="n"/>
       <c r="M206" s="2" t="n"/>
       <c r="N206" s="2" t="inlineStr">
@@ -11819,13 +11823,13 @@
 roles</t>
         </is>
       </c>
-      <c r="O206" s="2" t="n"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P206" s="2" t="n"/>
-      <c r="Q206" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q206" s="2" t="n"/>
       <c r="R206" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11860,13 +11864,13 @@
       <c r="F207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
-      <c r="I207" s="2" t="n"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J207" s="2" t="n"/>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K207" s="2" t="n"/>
       <c r="L207" s="2" t="n"/>
       <c r="M207" s="2" t="n"/>
       <c r="N207" s="2" t="inlineStr">
@@ -11874,13 +11878,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O207" s="2" t="n"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P207" s="2" t="n"/>
-      <c r="Q207" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q207" s="2" t="n"/>
       <c r="R207" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -11917,15 +11921,15 @@
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="2" t="n"/>
       <c r="J208" s="2" t="n"/>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K208" s="2" t="n"/>
       <c r="L208" s="2" t="n"/>
       <c r="M208" s="2" t="n"/>
       <c r="N208" s="2" t="n"/>
-      <c r="O208" s="2" t="n"/>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P208" s="2" t="n"/>
       <c r="Q208" s="2" t="n"/>
       <c r="R208" s="2" t="inlineStr">
@@ -11964,15 +11968,15 @@
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="2" t="n"/>
       <c r="J209" s="2" t="n"/>
-      <c r="K209" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K209" s="2" t="n"/>
       <c r="L209" s="2" t="n"/>
       <c r="M209" s="2" t="n"/>
       <c r="N209" s="2" t="n"/>
-      <c r="O209" s="2" t="n"/>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P209" s="2" t="n"/>
       <c r="Q209" s="2" t="n"/>
       <c r="R209" s="2" t="inlineStr">
@@ -12010,20 +12014,20 @@
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="2" t="n"/>
-      <c r="J210" s="2" t="inlineStr">
+      <c r="J210" s="2" t="n"/>
+      <c r="K210" s="2" t="inlineStr">
         <is>
           <t>Population can be two or more people. the interaction may involve how other people treat members of the group.</t>
-        </is>
-      </c>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
       <c r="M210" s="2" t="n"/>
       <c r="N210" s="2" t="n"/>
-      <c r="O210" s="2" t="n"/>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P210" s="2" t="n"/>
       <c r="Q210" s="2" t="n"/>
       <c r="R210" s="2" t="inlineStr">
@@ -12062,15 +12066,15 @@
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="2" t="n"/>
       <c r="J211" s="2" t="n"/>
-      <c r="K211" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K211" s="2" t="n"/>
       <c r="L211" s="2" t="n"/>
       <c r="M211" s="2" t="n"/>
       <c r="N211" s="2" t="n"/>
-      <c r="O211" s="2" t="n"/>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P211" s="2" t="n"/>
       <c r="Q211" s="2" t="n"/>
       <c r="R211" s="2" t="inlineStr">
@@ -12108,20 +12112,20 @@
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="2" t="n"/>
-      <c r="J212" s="2" t="inlineStr">
+      <c r="J212" s="2" t="n"/>
+      <c r="K212" s="2" t="inlineStr">
         <is>
           <t>This can include social history, current circumstances, age, gender identity, occupation, education level, socio-economic position (status or group), ethnicity, sexual orientation, disability</t>
-        </is>
-      </c>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="2" t="n"/>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P212" s="2" t="n"/>
       <c r="Q212" s="2" t="n"/>
       <c r="R212" s="2" t="inlineStr">
@@ -12162,13 +12166,13 @@
         </is>
       </c>
       <c r="H213" s="2" t="n"/>
-      <c r="I213" s="2" t="n"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J213" s="2" t="n"/>
-      <c r="K213" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K213" s="2" t="n"/>
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="2" t="n"/>
       <c r="N213" s="2" t="inlineStr">
@@ -12176,13 +12180,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O213" s="2" t="n"/>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P213" s="2" t="n"/>
-      <c r="Q213" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q213" s="2" t="n"/>
       <c r="R213" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12217,13 +12221,13 @@
       <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="n"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
       <c r="J214" s="2" t="n"/>
-      <c r="K214" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K214" s="2" t="n"/>
       <c r="L214" s="2" t="n"/>
       <c r="M214" s="2" t="n"/>
       <c r="N214" s="2" t="inlineStr">
@@ -12231,17 +12235,17 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O214" s="2" t="n"/>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
           <t>socioeconomic status</t>
         </is>
       </c>
-      <c r="Q214" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+      <c r="Q214" s="2" t="n"/>
       <c r="R214" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12280,13 +12284,13 @@
           <t>Semi-routine and routine occupations, blue collar occupations</t>
         </is>
       </c>
-      <c r="I215" s="3" t="n"/>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J215" s="3" t="n"/>
-      <c r="K215" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K215" s="3" t="n"/>
       <c r="L215" s="3" t="n"/>
       <c r="M215" s="3" t="n"/>
       <c r="N215" s="3" t="inlineStr">
@@ -12294,17 +12298,17 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O215" s="3" t="n"/>
+      <c r="O215" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P215" s="3" t="inlineStr">
         <is>
           <t>socioeconomic status</t>
         </is>
       </c>
-      <c r="Q215" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q215" s="3" t="n"/>
       <c r="R215" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -12343,13 +12347,13 @@
         </is>
       </c>
       <c r="H216" s="2" t="n"/>
-      <c r="I216" s="2" t="n"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J216" s="2" t="n"/>
-      <c r="K216" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K216" s="2" t="n"/>
       <c r="L216" s="2" t="n"/>
       <c r="M216" s="2" t="n"/>
       <c r="N216" s="2" t="inlineStr">
@@ -12357,13 +12361,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O216" s="2" t="n"/>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P216" s="2" t="n"/>
-      <c r="Q216" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q216" s="2" t="n"/>
       <c r="R216" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12402,13 +12406,13 @@
         </is>
       </c>
       <c r="H217" s="2" t="n"/>
-      <c r="I217" s="2" t="n"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="n"/>
-      <c r="K217" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K217" s="2" t="n"/>
       <c r="L217" s="2" t="n"/>
       <c r="M217" s="2" t="n"/>
       <c r="N217" s="2" t="inlineStr">
@@ -12416,13 +12420,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O217" s="2" t="n"/>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P217" s="2" t="n"/>
-      <c r="Q217" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q217" s="2" t="n"/>
       <c r="R217" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12457,13 +12461,13 @@
       <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
-      <c r="I218" s="2" t="n"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J218" s="2" t="n"/>
-      <c r="K218" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K218" s="2" t="n"/>
       <c r="L218" s="2" t="n"/>
       <c r="M218" s="2" t="n"/>
       <c r="N218" s="2" t="inlineStr">
@@ -12471,13 +12475,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O218" s="2" t="n"/>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P218" s="2" t="n"/>
-      <c r="Q218" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q218" s="2" t="n"/>
       <c r="R218" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12512,13 +12516,13 @@
       <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
-      <c r="I219" s="2" t="n"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J219" s="2" t="n"/>
-      <c r="K219" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K219" s="2" t="n"/>
       <c r="L219" s="2" t="n"/>
       <c r="M219" s="2" t="n"/>
       <c r="N219" s="2" t="inlineStr">
@@ -12526,13 +12530,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O219" s="2" t="n"/>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P219" s="2" t="n"/>
-      <c r="Q219" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q219" s="2" t="n"/>
       <c r="R219" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12567,13 +12571,13 @@
       <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
-      <c r="I220" s="2" t="n"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J220" s="2" t="n"/>
-      <c r="K220" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K220" s="2" t="n"/>
       <c r="L220" s="2" t="n"/>
       <c r="M220" s="2" t="n"/>
       <c r="N220" s="2" t="inlineStr">
@@ -12581,13 +12585,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O220" s="2" t="n"/>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P220" s="2" t="n"/>
-      <c r="Q220" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q220" s="2" t="n"/>
       <c r="R220" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12622,13 +12626,13 @@
       <c r="F221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
-      <c r="I221" s="2" t="n"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J221" s="2" t="n"/>
-      <c r="K221" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K221" s="2" t="n"/>
       <c r="L221" s="2" t="n"/>
       <c r="M221" s="2" t="n"/>
       <c r="N221" s="2" t="inlineStr">
@@ -12636,13 +12640,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O221" s="2" t="n"/>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P221" s="2" t="n"/>
-      <c r="Q221" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q221" s="2" t="n"/>
       <c r="R221" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12677,13 +12681,13 @@
       <c r="F222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
-      <c r="I222" s="2" t="n"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J222" s="2" t="n"/>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K222" s="2" t="n"/>
       <c r="L222" s="2" t="n"/>
       <c r="M222" s="2" t="n"/>
       <c r="N222" s="2" t="inlineStr">
@@ -12691,13 +12695,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O222" s="2" t="n"/>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P222" s="2" t="n"/>
-      <c r="Q222" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q222" s="2" t="n"/>
       <c r="R222" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12732,13 +12736,13 @@
       <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
-      <c r="I223" s="2" t="n"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J223" s="2" t="n"/>
-      <c r="K223" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K223" s="2" t="n"/>
       <c r="L223" s="2" t="n"/>
       <c r="M223" s="2" t="n"/>
       <c r="N223" s="2" t="inlineStr">
@@ -12746,13 +12750,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O223" s="2" t="n"/>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P223" s="2" t="n"/>
-      <c r="Q223" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q223" s="2" t="n"/>
       <c r="R223" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12787,13 +12791,13 @@
       <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
-      <c r="I224" s="2" t="n"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J224" s="2" t="n"/>
-      <c r="K224" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K224" s="2" t="n"/>
       <c r="L224" s="2" t="n"/>
       <c r="M224" s="2" t="n"/>
       <c r="N224" s="2" t="inlineStr">
@@ -12801,13 +12805,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O224" s="2" t="n"/>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P224" s="2" t="n"/>
-      <c r="Q224" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q224" s="2" t="n"/>
       <c r="R224" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12842,13 +12846,13 @@
       <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
-      <c r="I225" s="2" t="n"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J225" s="2" t="n"/>
-      <c r="K225" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K225" s="2" t="n"/>
       <c r="L225" s="2" t="n"/>
       <c r="M225" s="2" t="n"/>
       <c r="N225" s="2" t="inlineStr">
@@ -12856,13 +12860,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O225" s="2" t="n"/>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P225" s="2" t="n"/>
-      <c r="Q225" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q225" s="2" t="n"/>
       <c r="R225" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12897,13 +12901,13 @@
       <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
-      <c r="I226" s="2" t="n"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J226" s="2" t="n"/>
-      <c r="K226" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K226" s="2" t="n"/>
       <c r="L226" s="2" t="n"/>
       <c r="M226" s="2" t="n"/>
       <c r="N226" s="2" t="inlineStr">
@@ -12911,13 +12915,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O226" s="2" t="n"/>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P226" s="2" t="n"/>
-      <c r="Q226" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q226" s="2" t="n"/>
       <c r="R226" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -12948,9 +12952,9 @@
           <t>person</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>population</t>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -12958,9 +12962,9 @@
           <t>people</t>
         </is>
       </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -12994,13 +12998,13 @@
       <c r="F228" s="2" t="n"/>
       <c r="G228" s="2" t="n"/>
       <c r="H228" s="2" t="n"/>
-      <c r="I228" s="2" t="n"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J228" s="2" t="n"/>
-      <c r="K228" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K228" s="2" t="n"/>
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="inlineStr">
@@ -13008,13 +13012,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O228" s="2" t="n"/>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P228" s="2" t="n"/>
-      <c r="Q228" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q228" s="2" t="n"/>
       <c r="R228" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13053,13 +13057,13 @@
         </is>
       </c>
       <c r="H229" s="2" t="n"/>
-      <c r="I229" s="2" t="n"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J229" s="2" t="n"/>
-      <c r="K229" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K229" s="2" t="n"/>
       <c r="L229" s="2" t="n"/>
       <c r="M229" s="2" t="n"/>
       <c r="N229" s="2" t="inlineStr">
@@ -13067,13 +13071,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O229" s="2" t="n"/>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P229" s="2" t="n"/>
-      <c r="Q229" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q229" s="2" t="n"/>
       <c r="R229" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13108,13 +13112,13 @@
       <c r="F230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="H230" s="2" t="n"/>
-      <c r="I230" s="2" t="n"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J230" s="2" t="n"/>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K230" s="2" t="n"/>
       <c r="L230" s="2" t="n"/>
       <c r="M230" s="2" t="n"/>
       <c r="N230" s="2" t="inlineStr">
@@ -13122,13 +13126,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O230" s="2" t="n"/>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P230" s="2" t="n"/>
-      <c r="Q230" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q230" s="2" t="n"/>
       <c r="R230" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13163,13 +13167,13 @@
       <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
-      <c r="I231" s="2" t="n"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J231" s="2" t="n"/>
-      <c r="K231" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K231" s="2" t="n"/>
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n"/>
       <c r="N231" s="2" t="inlineStr">
@@ -13177,13 +13181,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O231" s="2" t="n"/>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P231" s="2" t="n"/>
-      <c r="Q231" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q231" s="2" t="n"/>
       <c r="R231" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13218,13 +13222,13 @@
       <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
-      <c r="I232" s="2" t="n"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J232" s="2" t="n"/>
-      <c r="K232" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K232" s="2" t="n"/>
       <c r="L232" s="2" t="n"/>
       <c r="M232" s="2" t="n"/>
       <c r="N232" s="2" t="inlineStr">
@@ -13232,13 +13236,13 @@
           <t>people</t>
         </is>
       </c>
-      <c r="O232" s="2" t="n"/>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P232" s="2" t="n"/>
-      <c r="Q232" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q232" s="2" t="n"/>
       <c r="R232" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13273,13 +13277,13 @@
       <c r="F233" s="2" t="n"/>
       <c r="G233" s="2" t="n"/>
       <c r="H233" s="2" t="n"/>
-      <c r="I233" s="2" t="n"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J233" s="2" t="n"/>
-      <c r="K233" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K233" s="2" t="n"/>
       <c r="L233" s="2" t="n"/>
       <c r="M233" s="2" t="n"/>
       <c r="N233" s="2" t="inlineStr">
@@ -13287,13 +13291,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O233" s="2" t="n"/>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P233" s="2" t="n"/>
-      <c r="Q233" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q233" s="2" t="n"/>
       <c r="R233" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13328,13 +13332,13 @@
       <c r="F234" s="3" t="n"/>
       <c r="G234" s="3" t="n"/>
       <c r="H234" s="3" t="n"/>
-      <c r="I234" s="3" t="n"/>
+      <c r="I234" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J234" s="3" t="n"/>
-      <c r="K234" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K234" s="3" t="n"/>
       <c r="L234" s="3" t="n"/>
       <c r="M234" s="3" t="n"/>
       <c r="N234" s="3" t="inlineStr">
@@ -13342,13 +13346,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O234" s="3" t="n"/>
+      <c r="O234" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P234" s="3" t="n"/>
-      <c r="Q234" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q234" s="3" t="n"/>
       <c r="R234" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -13383,13 +13387,13 @@
       <c r="F235" s="2" t="n"/>
       <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
-      <c r="I235" s="2" t="n"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J235" s="2" t="n"/>
-      <c r="K235" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K235" s="2" t="n"/>
       <c r="L235" s="2" t="n"/>
       <c r="M235" s="2" t="n"/>
       <c r="N235" s="2" t="inlineStr">
@@ -13397,13 +13401,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O235" s="2" t="n"/>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P235" s="2" t="n"/>
-      <c r="Q235" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q235" s="2" t="n"/>
       <c r="R235" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13442,13 +13446,13 @@
         </is>
       </c>
       <c r="H236" s="2" t="n"/>
-      <c r="I236" s="2" t="n"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J236" s="2" t="n"/>
-      <c r="K236" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K236" s="2" t="n"/>
       <c r="L236" s="2" t="n"/>
       <c r="M236" s="2" t="n"/>
       <c r="N236" s="2" t="inlineStr">
@@ -13456,13 +13460,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O236" s="2" t="n"/>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P236" s="2" t="n"/>
-      <c r="Q236" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q236" s="2" t="n"/>
       <c r="R236" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13497,13 +13501,13 @@
       <c r="F237" s="2" t="n"/>
       <c r="G237" s="2" t="n"/>
       <c r="H237" s="2" t="n"/>
-      <c r="I237" s="2" t="n"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J237" s="2" t="n"/>
-      <c r="K237" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K237" s="2" t="n"/>
       <c r="L237" s="2" t="n"/>
       <c r="M237" s="2" t="n"/>
       <c r="N237" s="2" t="inlineStr">
@@ -13511,13 +13515,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O237" s="2" t="n"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P237" s="2" t="n"/>
-      <c r="Q237" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q237" s="2" t="n"/>
       <c r="R237" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13562,15 +13566,15 @@
       </c>
       <c r="I238" s="2" t="n"/>
       <c r="J238" s="2" t="n"/>
-      <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K238" s="2" t="n"/>
       <c r="L238" s="2" t="n"/>
       <c r="M238" s="2" t="n"/>
       <c r="N238" s="2" t="n"/>
-      <c r="O238" s="2" t="n"/>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P238" s="2" t="n"/>
       <c r="Q238" s="2" t="n"/>
       <c r="R238" s="2" t="inlineStr">
@@ -13611,13 +13615,13 @@
           <t>$400, 3000 euros</t>
         </is>
       </c>
-      <c r="I239" s="2" t="n"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
       <c r="J239" s="2" t="n"/>
-      <c r="K239" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K239" s="2" t="n"/>
       <c r="L239" s="2" t="n"/>
       <c r="M239" s="2" t="n"/>
       <c r="N239" s="2" t="inlineStr">
@@ -13625,17 +13629,17 @@
           <t>value</t>
         </is>
       </c>
-      <c r="O239" s="2" t="n"/>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
           <t>valuable material resource owned</t>
         </is>
       </c>
-      <c r="Q239" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+      <c r="Q239" s="2" t="n"/>
       <c r="R239" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13670,13 +13674,13 @@
       <c r="F240" s="3" t="n"/>
       <c r="G240" s="3" t="n"/>
       <c r="H240" s="3" t="n"/>
-      <c r="I240" s="3" t="n"/>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J240" s="3" t="n"/>
-      <c r="K240" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K240" s="3" t="n"/>
       <c r="L240" s="3" t="n"/>
       <c r="M240" s="3" t="n"/>
       <c r="N240" s="3" t="inlineStr">
@@ -13684,13 +13688,13 @@
           <t>roles</t>
         </is>
       </c>
-      <c r="O240" s="3" t="n"/>
+      <c r="O240" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P240" s="3" t="n"/>
-      <c r="Q240" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q240" s="3" t="n"/>
       <c r="R240" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
@@ -13725,15 +13729,15 @@
       <c r="F241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="n"/>
-      <c r="I241" s="2" t="n"/>
-      <c r="J241" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="n"/>
+      <c r="K241" s="2" t="inlineStr">
         <is>
           <t>may include unpaid internships</t>
-        </is>
-      </c>
-      <c r="K241" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
         </is>
       </c>
       <c r="L241" s="2" t="n"/>
@@ -13743,13 +13747,13 @@
           <t>past behaviour</t>
         </is>
       </c>
-      <c r="O241" s="2" t="n"/>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P241" s="2" t="n"/>
-      <c r="Q241" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q241" s="2" t="n"/>
       <c r="R241" s="2" t="inlineStr">
         <is>
           <t>Published</t>
@@ -13784,13 +13788,13 @@
       <c r="F242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>
-      <c r="I242" s="2" t="n"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J242" s="2" t="n"/>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
+      <c r="K242" s="2" t="n"/>
       <c r="L242" s="2" t="n"/>
       <c r="M242" s="2" t="n"/>
       <c r="N242" s="2" t="inlineStr">
@@ -13798,13 +13802,13 @@
           <t>attributes</t>
         </is>
       </c>
-      <c r="O242" s="2" t="n"/>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P242" s="2" t="n"/>
-      <c r="Q242" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="Q242" s="2" t="n"/>
       <c r="R242" s="2" t="inlineStr">
         <is>
           <t>Published</t>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U242"/>
+  <dimension ref="A1:U246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5093,134 +5093,122 @@
       <c r="U82" s="2" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OMRSE:00000504</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>government assistance income data item</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A monetary personal income data item that is about solely the income an individual receives from a governmental organization through a program designed to provide low or no-income individuals with money to offset at least some costs of housing, food, or other necessities.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>monetary human income data item</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>BCIO:015089</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>graduate student role</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="N83" s="3" t="inlineStr">
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+      <c r="M84" s="3" t="n"/>
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="n"/>
-      <c r="Q83" s="3" t="n"/>
-      <c r="R83" s="3" t="inlineStr">
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="n"/>
+      <c r="Q84" s="3" t="n"/>
+      <c r="R84" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="S83" s="3" t="n"/>
-      <c r="T83" s="3" t="n"/>
-      <c r="U83" s="3" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010090</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
-      <c r="L84" s="2" t="n"/>
-      <c r="M84" s="2" t="n"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="n"/>
-      <c r="R84" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S84" s="2" t="n"/>
-      <c r="T84" s="2" t="n"/>
-      <c r="U84" s="2" t="n"/>
+      <c r="S84" s="3" t="n"/>
+      <c r="T84" s="3" t="n"/>
+      <c r="U84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015152</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>grandfather</t>
+          <t>graduate student role</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>A grandparent who is male gender.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>grandparent</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -5238,7 +5226,7 @@
       <c r="M85" s="2" t="n"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -5260,17 +5248,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015151</t>
+          <t>BCIO:015152</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>grandmother</t>
+          <t>grandfather</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>A grandparent who is female gender.</t>
+          <t>A grandparent who is male gender.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5315,22 +5303,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015150</t>
+          <t>BCIO:015151</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
+          <t>grandmother</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>A grandparent who is female gender.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
           <t>grandparent</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>A family member who is the parent of one's parent.</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
         </is>
       </c>
       <c r="E87" s="2" t="n"/>
@@ -5370,22 +5358,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050477</t>
+          <t>BCIO:015150</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>having enacted a behaviour</t>
+          <t>grandparent</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal history part that includes previously performing a behaviour. </t>
+          <t>A family member who is the parent of one's parent.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
@@ -5403,7 +5391,7 @@
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -5425,32 +5413,28 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015038</t>
+          <t>BCIO:050477</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>health insurance policy holder role</t>
+          <t>having enacted a behaviour</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>A policy holder role that inheres in a person who participates in the creation of an insurance contract designed to cover some or all of the cost of treating the insured person's illnesses or injuries as well as possibly providing preventive health care.</t>
+          <t xml:space="preserve">A personal history part that includes previously performing a behaviour. </t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>policy holder role</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
-        </is>
-      </c>
+      <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
@@ -5462,7 +5446,7 @@
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>past behaviour</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -5484,39 +5468,35 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015092</t>
+          <t>BCIO:015038</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>health status attribute</t>
+          <t>health insurance policy holder role</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
+          <t>A policy holder role that inheres in a person who participates in the creation of an insurance contract designed to cover some or all of the cost of treating the insured person's illnesses or injuries as well as possibly providing preventive health care.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>policy holder role</t>
         </is>
       </c>
       <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C16669</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Having chicken pox, asthma, a heart attack</t>
+          <t>having Medicare, Medicaid, Blue Cross, BUPA, being eligible for NHS treatment</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J90" s="2" t="n"/>
@@ -5547,35 +5527,39 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015006</t>
+          <t>BCIO:015092</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>heterosexual</t>
+          <t>health status attribute</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of a different sex.</t>
+          <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>sexual orientation</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>NCIT_C84362</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="n"/>
+          <t>NCIT_C16669</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Having chicken pox, asthma, a heart attack</t>
+        </is>
+      </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
       <c r="J91" s="2" t="n"/>
@@ -5584,7 +5568,7 @@
       <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -5606,27 +5590,31 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050917</t>
+          <t>BCIO:015006</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>high frequency of past behaviour</t>
+          <t>heterosexual</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>A frequency of past behaviour that is above a threshold.</t>
+          <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of a different sex.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>frequency of past behaviour</t>
+          <t>sexual orientation</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
       <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C84362</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -5637,7 +5625,11 @@
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
-      <c r="N92" s="2" t="n"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -5655,159 +5647,147 @@
       <c r="U92" s="2" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050917</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>high frequency of past behaviour</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>A frequency of past behaviour that is above a threshold.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>frequency of past behaviour</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="n"/>
+      <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n"/>
+      <c r="Q93" s="2" t="n"/>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="n"/>
+      <c r="T93" s="2" t="n"/>
+      <c r="U93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>BCIO:015087</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>higher education student role</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. For example, completing a university bachelor's or master's course of study, medical school or other professional school. </t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
-      <c r="N93" s="3" t="inlineStr">
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O93" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n"/>
-      <c r="Q93" s="3" t="n"/>
-      <c r="R93" s="3" t="inlineStr">
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="n"/>
+      <c r="Q94" s="3" t="n"/>
+      <c r="R94" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="S93" s="3" t="n"/>
-      <c r="T93" s="3" t="n"/>
-      <c r="U93" s="3" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010088</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="n"/>
-      <c r="L94" s="2" t="n"/>
-      <c r="M94" s="2" t="n"/>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P94" s="2" t="n"/>
-      <c r="Q94" s="2" t="n"/>
-      <c r="R94" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S94" s="2" t="n"/>
-      <c r="T94" s="2" t="n"/>
-      <c r="U94" s="2" t="n"/>
+      <c r="S94" s="3" t="n"/>
+      <c r="T94" s="3" t="n"/>
+      <c r="U94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015043</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>highest level of formal educational qualification achieved</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute related to the highest level of education achieved.</t>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="n"/>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCIT_C17953 </t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="n"/>
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J95" s="2" t="n"/>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>The highest level of a packaged education process an individual has completed</t>
-        </is>
-      </c>
+      <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n"/>
       <c r="N95" s="2" t="inlineStr">
@@ -5832,110 +5812,114 @@
       <c r="U95" s="2" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015043</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>highest level of formal educational qualification achieved</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>A personal attribute related to the highest level of education achieved.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCIT_C17953 </t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>The highest level of a packaged education process an individual has completed</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n"/>
+      <c r="M96" s="2" t="n"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n"/>
+      <c r="Q96" s="2" t="n"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="n"/>
+      <c r="T96" s="2" t="n"/>
+      <c r="U96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>BFO:0000182</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>history</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>A process that is the sum of the totality of processes taking place in the spatiotemporal region occupied by a material entity or site, including processes on the surface of the entity or within the cavities to which it serves as host.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015163</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>history of exposure to an occupational hazard</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>A personal history part that includes exposure to a potentially harmful agent as a result of one's occupation.</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>history of exposure to asbestos due to one's job</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="n"/>
-      <c r="L97" s="2" t="n"/>
-      <c r="M97" s="2" t="n"/>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="n"/>
-      <c r="Q97" s="2" t="n"/>
-      <c r="R97" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S97" s="2" t="n"/>
-      <c r="T97" s="2" t="n"/>
-      <c r="U97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015162</t>
+          <t>BCIO:015163</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>history of exposure to childhood maltreatment</t>
+          <t>history of exposure to an occupational hazard</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>A personal history part that includes experience of physical, sexual, or psychological maltreatment during the first 18 years of life.</t>
+          <t>A personal history part that includes exposure to a potentially harmful agent as a result of one's occupation.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5948,7 +5932,7 @@
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>history of physical abuse by a parent</t>
+          <t>history of exposure to asbestos due to one's job</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5984,44 +5968,44 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015036</t>
+          <t>BCIO:015162</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>homeless person</t>
+          <t>history of exposure to childhood maltreatment</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>A person who does not own a residential facility and does not have an agreement with a residential facility owner that would enable them to live in a residential facility.</t>
+          <t>A personal history part that includes experience of physical, sexual, or psychological maltreatment during the first 18 years of life.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="n"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>history of physical abuse by a parent</t>
+        </is>
+      </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>person experiencing homelessness</t>
-        </is>
-      </c>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n"/>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="2" t="n"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -6043,44 +6027,44 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015065</t>
+          <t>BCIO:015036</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>homemaker status</t>
+          <t>homeless person</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person who does not bear a role realised in an employment process and who manages their home as their main daily activity.</t>
+          <t>A person who does not own a residential facility and does not have an agreement with a residential facility owner that would enable them to live in a residential facility.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E100" s="2" t="n"/>
       <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C75560</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="n"/>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>person experiencing homelessness</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
@@ -6102,29 +6086,29 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015007</t>
+          <t>BCIO:015065</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>homosexual</t>
+          <t>homemaker status</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of the same sex.</t>
+          <t>A personal attribute inhering in a person who does not bear a role realised in an employment process and who manages their home as their main daily activity.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>sexual orientation</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E101" s="2" t="n"/>
       <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>NCIT_C84363</t>
+          <t>NCIT_C75560</t>
         </is>
       </c>
       <c r="H101" s="2" t="n"/>
@@ -6139,7 +6123,7 @@
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
@@ -6159,282 +6143,297 @@
       <c r="U101" s="2" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015007</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>homosexual</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>A sexual orientation of an individual who experiences sexual attraction exclusively or primarily to members of the same sex.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>sexual orientation</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C84363</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
+      <c r="L102" s="2" t="n"/>
+      <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="n"/>
+      <c r="Q102" s="2" t="n"/>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="n"/>
+      <c r="T102" s="2" t="n"/>
+      <c r="U102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>OMRSE:00000076</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>household</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>A human or collection of humans that occupies a housing unit by storing their possessions there and habitually sleeping there thereby participating in the realization of its residence function.</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>A household is a person of group of people that live in the same dwelling. A dwelling is a self-contained unit of accommodation where all of the rooms are behind a single door that only the household can use.</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>BCIO:015027</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>household income</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>An aggregate of the individual incomes received by all the members of a household.</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EFO_0009695 </t>
         </is>
       </c>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="n"/>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>household</t>
         </is>
       </c>
-      <c r="M103" s="2" t="n"/>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="M104" s="3" t="n"/>
+      <c r="N104" s="3" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P103" s="2" t="n"/>
-      <c r="Q103" s="2" t="n"/>
-      <c r="R103" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S103" s="2" t="n"/>
-      <c r="T103" s="2" t="n"/>
-      <c r="U103" s="2" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="n"/>
+      <c r="Q104" s="3" t="n"/>
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S104" s="3" t="n"/>
+      <c r="T104" s="3" t="n"/>
+      <c r="U104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OMRSE:00000929</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>household income</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>A monetary human income data item that is about the sum of earnings for all the persons in a household.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>monetary human income data item</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>BCIO:015002</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>human age</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>A personal attribute that is a time quality inhering in a person by virtue of how long since the person was born.</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>PATO:0000011</t>
         </is>
       </c>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
-      <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="n"/>
-      <c r="L104" s="2" t="n"/>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="2" t="inlineStr">
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="n"/>
-      <c r="R104" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S104" s="2" t="n"/>
-      <c r="T104" s="2" t="n"/>
-      <c r="U104" s="2" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:041000</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>human population</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>An object aggregate that consists of two or more people.</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="n"/>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="2" t="n"/>
-      <c r="H105" s="2" t="n"/>
-      <c r="I105" s="2" t="n"/>
-      <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="n"/>
-      <c r="L105" s="2" t="n"/>
-      <c r="M105" s="2" t="n"/>
-      <c r="N105" s="2" t="n"/>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P105" s="2" t="n"/>
-      <c r="Q105" s="2" t="n"/>
-      <c r="R105" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S105" s="2" t="n"/>
-      <c r="T105" s="2" t="n"/>
-      <c r="U105" s="2" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ADDICTO:0000381</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>A cognitive representation of themselves by a person or group.</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>cognitive representation</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="n"/>
+      <c r="Q106" s="2" t="n"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="n"/>
+      <c r="T106" s="2" t="n"/>
+      <c r="U106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015012</t>
+          <t>BCIO:041000</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>immigrant</t>
+          <t>human population</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>A person who has previously been a resident of a country and is now resident in another country.</t>
+          <t>An object aggregate that consists of two or more people.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>object aggregate</t>
         </is>
       </c>
       <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I107" s="2" t="n"/>
       <c r="J107" s="2" t="n"/>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>people</t>
-        </is>
-      </c>
+      <c r="N107" s="2" t="n"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -6452,80 +6451,56 @@
       <c r="U107" s="2" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015074</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>in a legal marriage or union</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A relationship status where the individual is in a legally formalised marriage or civil partnership. </t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="n"/>
-      <c r="G108" s="2" t="n"/>
-      <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="n"/>
-      <c r="L108" s="2" t="n"/>
-      <c r="M108" s="2" t="n"/>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attributes
-</t>
-        </is>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P108" s="2" t="n"/>
-      <c r="Q108" s="2" t="n"/>
-      <c r="R108" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S108" s="2" t="n"/>
-      <c r="T108" s="2" t="n"/>
-      <c r="U108" s="2" t="n"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ADDICTO:0000381</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>A cognitive representation of themselves by a person or group.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015073</t>
+          <t>BCIO:015012</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>in a stable or common law relationship</t>
+          <t>immigrant</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>A relationship status where the individual has had the same partner for a significant length of time but is not in a legal union.</t>
+          <t>A person who has previously been a resident of a country and is now resident in another country.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>relationship status</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
@@ -6538,16 +6513,12 @@
         </is>
       </c>
       <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Common law" relationship refers to a person who is living with another person as a couple but who is not in a legally recognised marriage or other civil union. </t>
-        </is>
-      </c>
+      <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -6569,22 +6540,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015055</t>
+          <t>BCIO:015074</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>in permanent employment</t>
+          <t>in a legal marriage or union</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>An employment status realised by an individual working for a company or other organisation without a pre-determined end date, with security of employment and known working conditions.</t>
+          <t xml:space="preserve">A relationship status where the individual is in a legally formalised marriage or civil partnership. </t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>employment status</t>
+          <t>relationship status</t>
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
@@ -6602,7 +6573,8 @@
       <c r="M110" s="2" t="n"/>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t xml:space="preserve">attributes
+</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
@@ -6624,22 +6596,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015056</t>
+          <t>BCIO:015073</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>in short term or temporary employment with known conditions</t>
+          <t>in a stable or common law relationship</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>An employment status realised by an individual working for a company or other organisation in a position that is of a known, fixed duration with security of employment for that duration and certain working conditions.</t>
+          <t>A relationship status where the individual has had the same partner for a significant length of time but is not in a legal union.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>employment status</t>
+          <t>relationship status</t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
@@ -6652,7 +6624,11 @@
         </is>
       </c>
       <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Common law" relationship refers to a person who is living with another person as a couple but who is not in a legally recognised marriage or other civil union. </t>
+        </is>
+      </c>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
       <c r="N111" s="2" t="inlineStr">
@@ -6679,17 +6655,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015057</t>
+          <t>BCIO:015055</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>in uncertain employment</t>
+          <t>in permanent employment</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>An employment status realised by an individual working for a company or other organisation in a position with uncertain duration or hours with unknown or low security of working conditions or pay.</t>
+          <t>An employment status realised by an individual working for a company or other organisation without a pre-determined end date, with security of employment and known working conditions.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6734,22 +6710,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015037</t>
+          <t>BCIO:015056</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>income-related welfare benefit</t>
+          <t>in short term or temporary employment with known conditions</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
+          <t>An employment status realised by an individual working for a company or other organisation in a position that is of a known, fixed duration with security of employment for that duration and certain working conditions.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>individual income</t>
+          <t>employment status</t>
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
@@ -6767,7 +6743,7 @@
       <c r="M113" s="2" t="n"/>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
@@ -6789,22 +6765,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015066</t>
+          <t>BCIO:015057</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>independently wealthy status</t>
+          <t>in uncertain employment</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person who does not bear a role realised in an employment process due to possessing enough wealth to not need financial support from another person or require income from employment.</t>
+          <t>An employment status realised by an individual working for a company or other organisation in a position with uncertain duration or hours with unknown or low security of working conditions or pay.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>employment status</t>
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
@@ -6822,7 +6798,7 @@
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
@@ -6842,78 +6818,74 @@
       <c r="U114" s="2" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:036000</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>individual human behaviour</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="n"/>
-      <c r="K115" s="2" t="n"/>
-      <c r="L115" s="2" t="n"/>
-      <c r="M115" s="2" t="n"/>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P115" s="2" t="n"/>
-      <c r="Q115" s="2" t="n"/>
-      <c r="R115" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S115" s="2" t="n"/>
-      <c r="T115" s="2" t="n"/>
-      <c r="U115" s="2" t="n"/>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015037</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>income-related welfare benefit</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Individual income that an individual otherwise of low-income receives as a payment made by the state or an insurance scheme in the form of housing vouchers,  credit or benefits.</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>individual income</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
+      <c r="L115" s="3" t="n"/>
+      <c r="M115" s="3" t="n"/>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>past behaviour</t>
+        </is>
+      </c>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P115" s="3" t="n"/>
+      <c r="Q115" s="3" t="n"/>
+      <c r="R115" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S115" s="3" t="n"/>
+      <c r="T115" s="3" t="n"/>
+      <c r="U115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015026</t>
+          <t>BCIO:015066</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>individual income</t>
+          <t>independently wealthy status</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute reflecting a benefit the person receives  derived from their capital or labour, usually measured in money.</t>
+          <t>A personal attribute inhering in a person who does not bear a role realised in an employment process due to possessing enough wealth to not need financial support from another person or require income from employment.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6923,15 +6895,11 @@
       </c>
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>OMRSE_00002061</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J116" s="2" t="n"/>
@@ -6940,7 +6908,7 @@
       <c r="M116" s="2" t="n"/>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>past behaviour</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
@@ -6962,31 +6930,35 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050478</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>influencer role</t>
+          <t>individual human behaviour</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>A social role that involves influencing other people to adopt new ideas or behaviours.</t>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>social role</t>
+          <t>bodily process</t>
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
-      <c r="H117" s="2" t="n"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>walks for 15 mins/day, never eats meat, attends school daily</t>
+        </is>
+      </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="J117" s="2" t="n"/>
@@ -6995,7 +6967,7 @@
       <c r="M117" s="2" t="n"/>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
@@ -7017,31 +6989,35 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BCIO:015083</t>
+          <t>BCIO:015026</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t>individual income</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by  currently learning in a non-institutional setting.</t>
+          <t>A personal attribute reflecting a benefit the person receives  derived from their capital or labour, usually measured in money.</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>OMRSE_00002061</t>
+        </is>
+      </c>
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="J118" s="3" t="n"/>
@@ -7050,7 +7026,7 @@
       <c r="M118" s="3" t="n"/>
       <c r="N118" s="3" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O118" s="3" t="inlineStr">
@@ -7070,79 +7046,67 @@
       <c r="U118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010085</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>informal education student role</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="n"/>
-      <c r="K119" s="2" t="n"/>
-      <c r="L119" s="2" t="n"/>
-      <c r="M119" s="2" t="n"/>
-      <c r="N119" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P119" s="2" t="n"/>
-      <c r="Q119" s="2" t="n"/>
-      <c r="R119" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S119" s="2" t="n"/>
-      <c r="T119" s="2" t="n"/>
-      <c r="U119" s="2" t="n"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>OMRSE:00000311</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>individual person income data item</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>A monetary human income data item that is the sum of earnings of one, individual human being.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>monetary human income data item</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015079</t>
+          <t>BCIO:050478</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>inpatient role</t>
+          <t>influencer role</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
+          <t>A social role that involves influencing other people to adopt new ideas or behaviours.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>patient role</t>
+          <t>social role</t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
@@ -7182,43 +7146,35 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>BCIO:015158</t>
+          <t>BCIO:015083</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>insured party role</t>
+          <t>informal education student role</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
+          <t>A student or trainee role realised by  currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>OMRSE:00000092</t>
-        </is>
-      </c>
+      <c r="G121" s="3" t="n"/>
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J121" s="3" t="n"/>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
-        </is>
-      </c>
+      <c r="K121" s="3" t="n"/>
       <c r="L121" s="3" t="n"/>
       <c r="M121" s="3" t="n"/>
       <c r="N121" s="3" t="inlineStr">
@@ -7243,85 +7199,84 @@
       <c r="U121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>OMRSE:00000092</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>insured party role</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>OMRSE:00000092</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">percentage; proportion </t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010085</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>roles</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="n"/>
+      <c r="Q122" s="2" t="n"/>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="n"/>
+      <c r="T122" s="2" t="n"/>
+      <c r="U122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015070</t>
+          <t>BCIO:015079</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>interpersonal role</t>
+          <t>inpatient role</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
+          <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>patient role</t>
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
       <c r="F123" s="2" t="n"/>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C92454</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="inlineStr">
         <is>
@@ -7354,131 +7309,152 @@
       <c r="U123" s="2" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015094</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>intervention participant</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>A person who is exposed to an intervention.</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="n"/>
-      <c r="G124" s="2" t="n"/>
-      <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n"/>
-      <c r="J124" s="2" t="n"/>
-      <c r="K124" s="2" t="n"/>
-      <c r="L124" s="2" t="n"/>
-      <c r="M124" s="2" t="n"/>
-      <c r="N124" s="2" t="n"/>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P124" s="2" t="n"/>
-      <c r="Q124" s="2" t="n"/>
-      <c r="R124" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S124" s="2" t="n"/>
-      <c r="T124" s="2" t="n"/>
-      <c r="U124" s="2" t="n"/>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015158</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>insured party role</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>OMRSE:00000092</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="n"/>
+      <c r="M124" s="3" t="n"/>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="n"/>
+      <c r="Q124" s="3" t="n"/>
+      <c r="R124" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S124" s="3" t="n"/>
+      <c r="T124" s="3" t="n"/>
+      <c r="U124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015095</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>intervention population</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>A human population who are exposed to an intervention.</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>human population</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="n"/>
-      <c r="F125" s="2" t="n"/>
-      <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2" t="n"/>
-      <c r="I125" s="2" t="n"/>
-      <c r="J125" s="2" t="n"/>
-      <c r="K125" s="2" t="n"/>
-      <c r="L125" s="2" t="n"/>
-      <c r="M125" s="2" t="n"/>
-      <c r="N125" s="2" t="n"/>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P125" s="2" t="n"/>
-      <c r="Q125" s="2" t="n"/>
-      <c r="R125" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S125" s="2" t="n"/>
-      <c r="T125" s="2" t="n"/>
-      <c r="U125" s="2" t="n"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OMRSE:00000092</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>insured party role</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A role that inheres in an organism that is able to receive benefits from an insurance policy. </t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>OMRSE:00000092</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>The role, if realized, is realized by receiving benefits that are covered by the insurance policy.</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015015</t>
+          <t>BCIO:015070</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>language proficiency</t>
+          <t>interpersonal role</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>A linguistic capability that is realised by using a language accurately and appropriately in more than one setting.</t>
+          <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linguistic capability </t>
+          <t>role</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C92454</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J126" s="2" t="n"/>
@@ -7487,7 +7463,7 @@
       <c r="M126" s="2" t="n"/>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
@@ -7509,46 +7485,34 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050887</t>
+          <t>BCIO:015094</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>leadership role</t>
+          <t>intervention participant</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>A social role in which the holder is given or creates authority to exert influence on other members of a social group.</t>
+          <t>A person who is exposed to an intervention.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>social role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I127" s="2" t="n"/>
       <c r="J127" s="2" t="n"/>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>There are many usages of the term ‘leadership'. This class refers to one particular usage.</t>
-        </is>
-      </c>
+      <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
+      <c r="N127" s="2" t="n"/>
       <c r="O127" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -7566,88 +7530,93 @@
       <c r="U127" s="2" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>MF:0000050</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>linguistic capability</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>A mental capability that is realised in processes of communication involving language or in expressions of language.</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>mental capability</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015095</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>intervention population</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>A human population who are exposed to an intervention.</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>human population</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
+      <c r="J128" s="2" t="n"/>
+      <c r="K128" s="2" t="n"/>
+      <c r="L128" s="2" t="n"/>
+      <c r="M128" s="2" t="n"/>
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="n"/>
+      <c r="Q128" s="2" t="n"/>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="n"/>
+      <c r="T128" s="2" t="n"/>
+      <c r="U128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050479</t>
+          <t>BCIO:015015</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>long-term disabled</t>
+          <t>language proficiency</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Disabled for at least 12 months.</t>
+          <t>A linguistic capability that is realised by using a language accurately and appropriately in more than one setting.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t xml:space="preserve">linguistic capability </t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Callers eligible for the study were adult cigarette smokers able to communicate in English </t>
+        </is>
+      </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="J129" s="2" t="n"/>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>This is a fuzzy class. The minimum duration for a disability to be deemed long-term is subject to debate.  12 months seems reasonable, but others may wish to specify a different duration if required for their purposes.</t>
-        </is>
-      </c>
+      <c r="K129" s="2" t="n"/>
       <c r="L129" s="2" t="n"/>
       <c r="M129" s="2" t="n"/>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -7669,23 +7638,22 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050918</t>
+          <t>BCIO:050887</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">low frequency of past behaviour
-</t>
+          <t>leadership role</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>A frequency of past behaviour that is below a threshold.</t>
+          <t>A social role in which the holder is given or creates authority to exert influence on other members of a social group.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>frequency of past behaviour</t>
+          <t>social role</t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
@@ -7698,10 +7666,18 @@
         </is>
       </c>
       <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="n"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>There are many usages of the term ‘leadership'. This class refers to one particular usage.</t>
+        </is>
+      </c>
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
-      <c r="N130" s="2" t="n"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -7719,105 +7695,88 @@
       <c r="U130" s="2" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015107</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>male biological sex</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>A biological sex associated with the ability to produce male gametes.</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>biological sex</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="n"/>
-      <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2" t="n"/>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="n"/>
-      <c r="K131" s="2" t="n"/>
-      <c r="L131" s="2" t="n"/>
-      <c r="M131" s="2" t="n"/>
-      <c r="N131" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O131" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P131" s="2" t="n"/>
-      <c r="Q131" s="2" t="n"/>
-      <c r="R131" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S131" s="2" t="n"/>
-      <c r="T131" s="2" t="n"/>
-      <c r="U131" s="2" t="n"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MF:0000050</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>linguistic capability</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>A mental capability that is realised in processes of communication involving language or in expressions of language.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>mental capability</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:050479</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>male gender</t>
+          <t>long-term disabled</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
+          <t>Disabled for at least 12 months.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
       <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:000090</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="n"/>
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>man</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>This is a fuzzy class. The minimum duration for a disability to be deemed long-term is subject to debate.  12 months seems reasonable, but others may wish to specify a different duration if required for their purposes.</t>
+        </is>
+      </c>
       <c r="L132" s="2" t="n"/>
       <c r="M132" s="2" t="n"/>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -7837,79 +7796,76 @@
       <c r="U132" s="2" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:015090</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>masters student role</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="n"/>
-      <c r="L133" s="3" t="n"/>
-      <c r="M133" s="3" t="n"/>
-      <c r="N133" s="3" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P133" s="3" t="n"/>
-      <c r="Q133" s="3" t="n"/>
-      <c r="R133" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S133" s="3" t="n"/>
-      <c r="T133" s="3" t="n"/>
-      <c r="U133" s="3" t="n"/>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050918</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low frequency of past behaviour
+</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>A frequency of past behaviour that is below a threshold.</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>frequency of past behaviour</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n"/>
+      <c r="K133" s="2" t="n"/>
+      <c r="L133" s="2" t="n"/>
+      <c r="M133" s="2" t="n"/>
+      <c r="N133" s="2" t="n"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="n"/>
+      <c r="Q133" s="2" t="n"/>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="n"/>
+      <c r="T133" s="2" t="n"/>
+      <c r="U133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:015107</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>male biological sex</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>A biological sex associated with the ability to produce male gametes.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>biological sex</t>
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
@@ -7949,48 +7905,48 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015093</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>medication use status</t>
+          <t>male gender</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>A health status attribute that is having been prescribed the use of one or more drugs to improve, maintain or protect one's health.</t>
+          <t>A gender identity as being male.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>health status attribute</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
       <c r="F135" s="2" t="n"/>
-      <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:000090</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
       </c>
-      <c r="J135" s="2" t="n"/>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>This entity reflects having been prescribed a medication.  Actual use of the medicine would be captured as a behaviour</t>
-        </is>
-      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="n"/>
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n"/>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -8010,97 +7966,85 @@
       <c r="U135" s="2" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015021</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>member of a multi-person household</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>A person living in  a household with at least one other person.</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="n"/>
-      <c r="F136" s="2" t="n"/>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2" t="n"/>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="n"/>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A member of a multi-person household lives with at least one other person in the same dwelling. </t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n"/>
-      <c r="M136" s="2" t="n"/>
-      <c r="N136" s="2" t="inlineStr">
-        <is>
-          <t>people</t>
-        </is>
-      </c>
-      <c r="O136" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="n"/>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S136" s="2" t="n"/>
-      <c r="T136" s="2" t="n"/>
-      <c r="U136" s="2" t="n"/>
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015090</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>masters student role</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
+      <c r="L136" s="3" t="n"/>
+      <c r="M136" s="3" t="n"/>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="n"/>
+      <c r="Q136" s="3" t="n"/>
+      <c r="R136" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S136" s="3" t="n"/>
+      <c r="T136" s="3" t="n"/>
+      <c r="U136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015023</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household all related</t>
+          <t>masters student role</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>A member of a multi-person household where all of the household members are related.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
       <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
@@ -8112,7 +8056,7 @@
       <c r="M137" s="2" t="n"/>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
@@ -8134,22 +8078,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015025</t>
+          <t>BCIO:015093</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household not related</t>
+          <t>medication use status</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>A member of a multi-person household where none of the household members are related.</t>
+          <t>A health status attribute that is having been prescribed the use of one or more drugs to improve, maintain or protect one's health.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>health status attribute</t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -8157,7 +8101,7 @@
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
+          <t>prescribed at least one antihypertensive medication, taking asthma preventer inhalers</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -8166,12 +8110,16 @@
         </is>
       </c>
       <c r="J138" s="2" t="n"/>
-      <c r="K138" s="2" t="n"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>This entity reflects having been prescribed a medication.  Actual use of the medicine would be captured as a behaviour</t>
+        </is>
+      </c>
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>past behaviour</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
@@ -8193,39 +8141,39 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015024</t>
+          <t>BCIO:015021</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household some related</t>
+          <t>member of a multi-person household</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>A member of a multi-person household where some household members are related.</t>
+          <t>A person living in  a household with at least one other person.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person household</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
       <c r="F139" s="2" t="n"/>
       <c r="G139" s="2" t="n"/>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
-        </is>
-      </c>
+      <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J139" s="2" t="n"/>
-      <c r="K139" s="2" t="n"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A member of a multi-person household lives with at least one other person in the same dwelling. </t>
+        </is>
+      </c>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="inlineStr">
@@ -8252,17 +8200,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015022</t>
+          <t>BCIO:015023</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>member of a multi-person multi-generational household</t>
+          <t>member of a multi-person household all related</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>A member of a multi-person household where some household members belong to different generations.</t>
+          <t>A member of a multi-person household where all of the household members are related.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -8272,10 +8220,14 @@
       </c>
       <c r="E140" s="2" t="n"/>
       <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCIT:C25173;PCO:0000020;STATO:0000257 </t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
+          <t>1) Co-habitating couple and their socially recognised children and elderly parents. 2) Co habitating couple with child and grandchild.</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -8284,11 +8236,7 @@
         </is>
       </c>
       <c r="J140" s="2" t="n"/>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>A member of a multi-generational household lives with other people that are from more than one generation. A generation is all the people of about the same age within a society or within a particular family</t>
-        </is>
-      </c>
+      <c r="K140" s="2" t="n"/>
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="2" t="n"/>
       <c r="N140" s="2" t="inlineStr">
@@ -8315,28 +8263,32 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015020</t>
+          <t>BCIO:015025</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>member of a one person household</t>
+          <t>member of a multi-person household not related</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>A person living alone in a household.</t>
+          <t>A member of a multi-person household where none of the household members are related.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>member of a multi-person household</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
       <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
-      <c r="H141" s="2" t="n"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>1) Two unrelated couples (unmarried couples). 2) Students sharing living accommodation. 3) Single professionals renting a room in a shared house.</t>
+        </is>
+      </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
@@ -8368,79 +8320,104 @@
       <c r="U141" s="2" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>MF:0000048</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>mental capability</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>A personal capability that includes mental processes in its realisation.</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>personal capability</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015024</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>member of a multi-person household some related</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>A member of a multi-person household where some household members are related.</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>member of a multi-person household</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>1) Cohabiting couple plus son and girlfriend. 2) Two brothers and their partners</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
+      <c r="L142" s="2" t="n"/>
+      <c r="M142" s="2" t="n"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="n"/>
+      <c r="Q142" s="2" t="n"/>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="n"/>
+      <c r="T142" s="2" t="n"/>
+      <c r="U142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050480</t>
+          <t>BCIO:015022</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>member of a multi-person multi-generational household</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>A parent who is female gender.</t>
+          <t>A member of a multi-person household where some household members belong to different generations.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>member of a multi-person household</t>
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
-      <c r="H143" s="2" t="n"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>1) A family unit of a pair of adults and their socially recognized children. 2) Co-habitating couples plus socially recognised children and elderly parents or grandchildren.</t>
+        </is>
+      </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J143" s="2" t="n"/>
-      <c r="K143" s="2" t="n"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>A member of a multi-generational household lives with other people that are from more than one generation. A generation is all the people of about the same age within a society or within a particular family</t>
+        </is>
+      </c>
       <c r="L143" s="2" t="n"/>
       <c r="M143" s="2" t="n"/>
       <c r="N143" s="2" t="inlineStr">
@@ -8467,22 +8444,22 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015157</t>
+          <t>BCIO:015020</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>nephew</t>
+          <t>member of a one person household</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A family member who is a child relation of one's sibling and is male gender. </t>
+          <t>A person living alone in a household.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
@@ -8520,147 +8497,114 @@
       <c r="U144" s="2" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015156</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>niece</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>A family member who is a child relation of one's sibling and is female gender.</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n"/>
-      <c r="G145" s="2" t="n"/>
-      <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n"/>
-      <c r="K145" s="2" t="n"/>
-      <c r="L145" s="2" t="n"/>
-      <c r="M145" s="2" t="n"/>
-      <c r="N145" s="2" t="inlineStr">
-        <is>
-          <t>people</t>
-        </is>
-      </c>
-      <c r="O145" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P145" s="2" t="n"/>
-      <c r="Q145" s="2" t="n"/>
-      <c r="R145" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S145" s="2" t="n"/>
-      <c r="T145" s="2" t="n"/>
-      <c r="U145" s="2" t="n"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MF:0000048</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>mental capability</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>A personal capability that includes mental processes in its realisation.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>personal capability</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015102</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>non-gendered identity</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>A self-identity as not having a particular gender.</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:002331</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n"/>
-      <c r="K146" s="2" t="n"/>
-      <c r="L146" s="2" t="n"/>
-      <c r="M146" s="2" t="n"/>
-      <c r="N146" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O146" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P146" s="2" t="n"/>
-      <c r="Q146" s="2" t="n"/>
-      <c r="R146" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S146" s="2" t="n"/>
-      <c r="T146" s="2" t="n"/>
-      <c r="U146" s="2" t="n"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>OMRSE:00002061</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>monetary human income data item</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>A data item that is about the sum of earnings for some person(s) from various forms of payment or profits.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015101</t>
+          <t>BCIO:050480</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>nonbinary gender</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>A gender identity as having a gender that is not well-described by the binary categories of male or female.</t>
+          <t>A parent who is female gender.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="E147" s="2" t="n"/>
       <c r="F147" s="2" t="n"/>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:002328</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
@@ -8673,7 +8617,7 @@
       <c r="M147" s="2" t="n"/>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
@@ -8695,22 +8639,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015061</t>
+          <t>BCIO:015157</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>not seeking employment</t>
+          <t>nephew</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person by virtue of that person not having a paid job and not currently seeking to begin participating in an employment process.</t>
+          <t xml:space="preserve">A family member who is a child relation of one's sibling and is male gender. </t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E148" s="2" t="n"/>
@@ -8728,7 +8672,7 @@
       <c r="M148" s="2" t="n"/>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -8750,22 +8694,22 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015062</t>
+          <t>BCIO:015156</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>not working for health reasons</t>
+          <t>niece</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being unable to work due to illness or disability.</t>
+          <t>A family member who is a child relation of one's sibling and is female gender.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E149" s="2" t="n"/>
@@ -8783,7 +8727,7 @@
       <c r="M149" s="2" t="n"/>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
@@ -8805,34 +8749,46 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050976</t>
+          <t>BCIO:015102</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>number of people in a population</t>
+          <t>non-gendered identity</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>A data item about the number of people in a population.</t>
+          <t>A self-identity as not having a particular gender.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>self-identity</t>
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
       <c r="F150" s="2" t="n"/>
-      <c r="G150" s="2" t="n"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:002331</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="n"/>
-      <c r="I150" s="2" t="n"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="n"/>
       <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
-      <c r="N150" s="2" t="n"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -8852,31 +8808,35 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015042</t>
+          <t>BCIO:015101</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>number of years in education completed</t>
+          <t>nonbinary gender</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>The number of years a person spent engaged in an education process.</t>
+          <t>A gender identity as having a gender that is not well-described by the binary categories of male or female.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
       <c r="F151" s="2" t="n"/>
-      <c r="G151" s="2" t="n"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:002328</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Mean;Minimum;Maximum;Median</t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J151" s="2" t="n"/>
@@ -8885,7 +8845,7 @@
       <c r="M151" s="2" t="n"/>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -8893,11 +8853,7 @@
           <t>population</t>
         </is>
       </c>
-      <c r="P151" s="2" t="inlineStr">
-        <is>
-          <t>education process</t>
-        </is>
-      </c>
+      <c r="P151" s="2" t="n"/>
       <c r="Q151" s="2" t="n"/>
       <c r="R151" s="2" t="inlineStr">
         <is>
@@ -8911,22 +8867,22 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015430</t>
+          <t>BCIO:015061</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>occupational role</t>
+          <t>not seeking employment</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
+          <t>A personal attribute inhering in a person by virtue of that person not having a paid job and not currently seeking to begin participating in an employment process.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>personal role</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E152" s="2" t="n"/>
@@ -8944,7 +8900,7 @@
       <c r="M152" s="2" t="n"/>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
@@ -8966,22 +8922,22 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015035</t>
+          <t>BCIO:015062</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>occupier of employer-provided housing</t>
+          <t>not working for health reasons</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>A person who lives in a residential facility they do not own  with the agreement of the residential facility owner, by virtue of the occupier bearing a role realised in an employment process.</t>
+          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being unable to work due to illness or disability.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E153" s="2" t="n"/>
@@ -8990,7 +8946,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J153" s="2" t="n"/>
@@ -8999,7 +8955,7 @@
       <c r="M153" s="2" t="n"/>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -9021,46 +8977,34 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015078</t>
+          <t>BCIO:050976</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>organisational role</t>
+          <t>number of people in a population</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
+          <t>A data item about the number of people in a population.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E154" s="2" t="n"/>
       <c r="F154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>Scout leader, club chairperson</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="H154" s="2" t="n"/>
+      <c r="I154" s="2" t="n"/>
       <c r="J154" s="2" t="n"/>
       <c r="K154" s="2" t="n"/>
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
-      <c r="N154" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
+      <c r="N154" s="2" t="n"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9080,22 +9024,22 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015010</t>
+          <t>BCIO:015042</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>other sexual orientation</t>
+          <t>number of years in education completed</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>A sexual orientation of an individual who is sure of their sexual orientation and reports it as other than asexual, bisexual, heterosexual, homosexual, queer or questioning.</t>
+          <t>The number of years a person spent engaged in an education process.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>sexual orientation</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E155" s="2" t="n"/>
@@ -9104,7 +9048,7 @@
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
       <c r="J155" s="2" t="n"/>
@@ -9113,7 +9057,7 @@
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>number</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -9121,7 +9065,11 @@
           <t>population</t>
         </is>
       </c>
-      <c r="P155" s="2" t="n"/>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>education process</t>
+        </is>
+      </c>
       <c r="Q155" s="2" t="n"/>
       <c r="R155" s="2" t="inlineStr">
         <is>
@@ -9135,34 +9083,42 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050888</t>
+          <t>BCIO:015430</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>out-group</t>
+          <t>occupational role</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>A social group that is part of a person’s social environmental system and with which the person does not identify.</t>
+          <t>A personal role that is realised in a person by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>social group</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="E156" s="2" t="n"/>
       <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
-      <c r="I156" s="2" t="n"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J156" s="2" t="n"/>
       <c r="K156" s="2" t="n"/>
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
-      <c r="N156" s="2" t="n"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9182,22 +9138,22 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015080</t>
+          <t>BCIO:015035</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>outpatient role</t>
+          <t>occupier of employer-provided housing</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
+          <t>A person who lives in a residential facility they do not own  with the agreement of the residential facility owner, by virtue of the occupier bearing a role realised in an employment process.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>patient role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E157" s="2" t="n"/>
@@ -9206,7 +9162,7 @@
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
       <c r="J157" s="2" t="n"/>
@@ -9215,7 +9171,7 @@
       <c r="M157" s="2" t="n"/>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -9237,48 +9193,44 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>BCIO:051000</t>
+          <t>BCIO:015078</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>organisational role</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
+          <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>role</t>
         </is>
       </c>
       <c r="E158" s="2" t="n"/>
       <c r="F158" s="2" t="n"/>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Scout leader, club chairperson</t>
+        </is>
+      </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J158" s="2" t="n"/>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
-        </is>
-      </c>
+      <c r="K158" s="2" t="n"/>
       <c r="L158" s="2" t="n"/>
       <c r="M158" s="2" t="n"/>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -9300,22 +9252,22 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015029</t>
+          <t>BCIO:015010</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>owner-occupier</t>
+          <t>other sexual orientation</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>A person who lives in a residential facility of which they are the residential facility owner</t>
+          <t>A sexual orientation of an individual who is sure of their sexual orientation and reports it as other than asexual, bisexual, heterosexual, homosexual, queer or questioning.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>sexual orientation</t>
         </is>
       </c>
       <c r="E159" s="2" t="n"/>
@@ -9324,7 +9276,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J159" s="2" t="n"/>
@@ -9333,8 +9285,7 @@
       <c r="M159" s="2" t="n"/>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">people
-</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -9356,46 +9307,34 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015110</t>
+          <t>BCIO:050888</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>out-group</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A family member who is a key caretaker or immediate progenitor of a child. </t>
+          <t>A social group that is part of a person’s social environmental system and with which the person does not identify.</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>social group</t>
         </is>
       </c>
       <c r="E160" s="2" t="n"/>
       <c r="F160" s="2" t="n"/>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:001953</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="n"/>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I160" s="2" t="n"/>
       <c r="J160" s="2" t="n"/>
       <c r="K160" s="2" t="n"/>
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="2" t="n"/>
-      <c r="N160" s="2" t="inlineStr">
-        <is>
-          <t>people</t>
-        </is>
-      </c>
+      <c r="N160" s="2" t="n"/>
       <c r="O160" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9415,22 +9354,22 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015108</t>
+          <t>BCIO:015080</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>parental role</t>
+          <t>outpatient role</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
+          <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>interpersonal role</t>
+          <t>patient role</t>
         </is>
       </c>
       <c r="E161" s="2" t="n"/>
@@ -9443,11 +9382,7 @@
         </is>
       </c>
       <c r="J161" s="2" t="n"/>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A person can hold a parental role in a child's life without being that child's biological or legal parent. </t>
-        </is>
-      </c>
+      <c r="K161" s="2" t="n"/>
       <c r="L161" s="2" t="n"/>
       <c r="M161" s="2" t="n"/>
       <c r="N161" s="2" t="inlineStr">
@@ -9474,27 +9409,31 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050481</t>
+          <t>BCIO:051000</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">past behaviour </t>
+          <t>owner</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>A personal history part that includes a behaviour.</t>
+          <t>A person or organization that participates in an ownership process wherein they realize their role as owner by exercising their right to use, sell, rent, or gift an object.</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="E162" s="2" t="n"/>
       <c r="F162" s="2" t="n"/>
-      <c r="G162" s="2" t="n"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>owner in the Sustainable Development Goals Interface Ontology (SDGIO:00010028)</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
@@ -9502,10 +9441,18 @@
         </is>
       </c>
       <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="n"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>This class's definition is reused from SDGIO. As the ontology is no longer maintained a separate ID for this class was generated. However, the ID of the original class is included as a crossreference.</t>
+        </is>
+      </c>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
-      <c r="N162" s="2" t="n"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9525,22 +9472,22 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050827</t>
+          <t>BCIO:015029</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>past occurrence of a target behaviour</t>
+          <t>owner-occupier</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>A past behaviour that is the target of an intervention.</t>
+          <t>A person who lives in a residential facility of which they are the residential facility owner</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">past behaviour </t>
+          <t>person</t>
         </is>
       </c>
       <c r="E163" s="2" t="n"/>
@@ -9549,14 +9496,19 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
       <c r="J163" s="2" t="n"/>
       <c r="K163" s="2" t="n"/>
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
-      <c r="N163" s="2" t="n"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">people
+</t>
+        </is>
+      </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9574,79 +9526,107 @@
       <c r="U163" s="2" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>OBI:0000093</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>patient role</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015110</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A family member who is a key caretaker or immediate progenitor of a child. </t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:001953</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n"/>
+      <c r="K164" s="2" t="n"/>
+      <c r="L164" s="2" t="n"/>
+      <c r="M164" s="2" t="n"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="n"/>
+      <c r="Q164" s="2" t="n"/>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="n"/>
+      <c r="T164" s="2" t="n"/>
+      <c r="U164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BCIO:050975
-</t>
+          <t>BCIO:015108</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>people with intervention source role</t>
+          <t>parental role</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
+          <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>human population</t>
+          <t>interpersonal role</t>
         </is>
       </c>
       <c r="E165" s="2" t="n"/>
       <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
-      <c r="I165" s="2" t="n"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J165" s="2" t="n"/>
-      <c r="K165" s="2" t="n"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A person can hold a parental role in a child's life without being that child's biological or legal parent. </t>
+        </is>
+      </c>
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n"/>
-      <c r="N165" s="2" t="n"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9664,63 +9644,86 @@
       <c r="U165" s="2" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>MF:0000016</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>extended organism</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050481</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">past behaviour </t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>A personal history part that includes a behaviour.</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>personal history part</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="n"/>
+      <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n"/>
+      <c r="K166" s="2" t="n"/>
+      <c r="L166" s="2" t="n"/>
+      <c r="M166" s="2" t="n"/>
+      <c r="N166" s="2" t="n"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="n"/>
+      <c r="Q166" s="2" t="n"/>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="n"/>
+      <c r="T166" s="2" t="n"/>
+      <c r="U166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050889</t>
+          <t>BCIO:050827</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>person in a social environmental system</t>
+          <t>past occurrence of a target behaviour</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; who is part of a social environmental system.</t>
+          <t>A past behaviour that is the target of an intervention.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t xml:space="preserve">past behaviour </t>
         </is>
       </c>
       <c r="E167" s="2" t="n"/>
       <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
-      <c r="I167" s="2" t="n"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J167" s="2" t="n"/>
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="n"/>
@@ -9743,189 +9746,158 @@
       <c r="U167" s="2" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:050300</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>A specifically dependent continuant that inheres in a person.</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="n"/>
-      <c r="F168" s="2" t="n"/>
-      <c r="G168" s="2" t="n"/>
-      <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
-      <c r="J168" s="2" t="n"/>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attributes included under this header are age, immigration, social and economic conditions. </t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OBI:0000093</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>patient role</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCIO:050975
+</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>people with intervention source role</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>A &lt;human population&gt; whose members are people with an intervention source role for a specified intervention.</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>human population</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="n"/>
+      <c r="K169" s="2" t="n"/>
+      <c r="L169" s="2" t="n"/>
+      <c r="M169" s="2" t="n"/>
+      <c r="N169" s="2" t="n"/>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="n"/>
+      <c r="Q169" s="2" t="n"/>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="n"/>
+      <c r="T169" s="2" t="n"/>
+      <c r="U169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MF:0000016</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="M168" s="2" t="n"/>
-      <c r="N168" s="2" t="n"/>
-      <c r="O168" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P168" s="2" t="n"/>
-      <c r="Q168" s="2" t="n"/>
-      <c r="R168" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S168" s="2" t="n"/>
-      <c r="T168" s="2" t="n"/>
-      <c r="U168" s="2" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>MF:0000043</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>personal capability</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>A bodily disposition whose realization ordinarily brings benefits to an organism or group of organisms, where "ordinarily" means within a typical range or context.</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>bodily disposition</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>The ability of someone to perform some useful and/or beneficial activity.</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>The phrase 'ordinarily brings benefits to an organism or group of organism' is used to explain that capabilities normally provide a benefit. 
-For instance, having a musical ability is ordinarily an ability that is positive for a person (e.g., they receive positive feedback about their ability). However, in certain exceptional cases (e.g., a neighbour becoming annoyed with a person playing the piano and expressing this annoyance), the ability might not bring benefits.</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015161</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>personal history</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>A history that is of a person.</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>history</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="n"/>
-      <c r="F170" s="2" t="n"/>
-      <c r="G170" s="2" t="n"/>
-      <c r="H170" s="2" t="n"/>
-      <c r="I170" s="2" t="n"/>
-      <c r="J170" s="2" t="n"/>
-      <c r="K170" s="2" t="n"/>
-      <c r="L170" s="2" t="n"/>
-      <c r="M170" s="2" t="n"/>
-      <c r="N170" s="2" t="n"/>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P170" s="2" t="n"/>
-      <c r="Q170" s="2" t="n"/>
-      <c r="R170" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S170" s="2" t="n"/>
-      <c r="T170" s="2" t="n"/>
-      <c r="U170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050482</t>
+          <t>BCIO:050889</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>personal history of behavioural lapse</t>
+          <t>person in a social environmental system</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal history part that includes a change from a less desired behaviour pattern to a more desired behaviour pattern followed by a temporary reversion to the previous behaviour pattern. </t>
+          <t>A &lt;person&gt; who is part of a social environmental system.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E171" s="2" t="n"/>
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I171" s="2" t="n"/>
       <c r="J171" s="2" t="n"/>
       <c r="K171" s="2" t="n"/>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n"/>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
+      <c r="N171" s="2" t="n"/>
       <c r="O171" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9945,42 +9917,42 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050483</t>
+          <t>BCIO:050300</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal history of events that influence behaviour </t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal history part that includes experience of events that influence behaviour. </t>
+          <t>A specifically dependent continuant that inheres in a person.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E172" s="2" t="n"/>
       <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I172" s="2" t="n"/>
       <c r="J172" s="2" t="n"/>
-      <c r="K172" s="2" t="n"/>
-      <c r="L172" s="2" t="n"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attributes included under this header are age, immigration, social and economic conditions. </t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="M172" s="2" t="n"/>
-      <c r="N172" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
+      <c r="N172" s="2" t="n"/>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -9998,99 +9970,79 @@
       <c r="U172" s="2" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:050484</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>personal history of intervention exposure for the same outcome</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>A personal history part of exposure to an intervention targeting the same outcome as the current intervention.</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>personal history part</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="n"/>
-      <c r="F173" s="2" t="n"/>
-      <c r="G173" s="2" t="n"/>
-      <c r="H173" s="2" t="n"/>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n"/>
-      <c r="K173" s="2" t="n"/>
-      <c r="L173" s="2" t="n"/>
-      <c r="M173" s="2" t="n"/>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P173" s="2" t="n"/>
-      <c r="Q173" s="2" t="n"/>
-      <c r="R173" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S173" s="2" t="n"/>
-      <c r="T173" s="2" t="n"/>
-      <c r="U173" s="2" t="n"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MF:0000043</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>personal capability</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>A bodily disposition whose realization ordinarily brings benefits to an organism or group of organisms, where "ordinarily" means within a typical range or context.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>bodily disposition</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>The ability of someone to perform some useful and/or beneficial activity.</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>The phrase 'ordinarily brings benefits to an organism or group of organism' is used to explain that capabilities normally provide a benefit. 
+For instance, having a musical ability is ordinarily an ability that is positive for a person (e.g., they receive positive feedback about their ability). However, in certain exceptional cases (e.g., a neighbour becoming annoyed with a person playing the piano and expressing this annoyance), the ability might not bring benefits.</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050485</t>
+          <t>BCIO:015161</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>personal history of intervention exposure for the same outcome behaviour</t>
+          <t>personal history</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>A personal history part  that includes exposure to a prior intervention targeting the same outcome behaviour as the current intervention.</t>
+          <t>A history that is of a person.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>personal history part</t>
+          <t>history</t>
         </is>
       </c>
       <c r="E174" s="2" t="n"/>
       <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I174" s="2" t="n"/>
       <c r="J174" s="2" t="n"/>
       <c r="K174" s="2" t="n"/>
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="2" t="n"/>
-      <c r="N174" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
+      <c r="N174" s="2" t="n"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -10110,17 +10062,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050486</t>
+          <t>BCIO:050482</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>personal history of same intervention exposure</t>
+          <t>personal history of behavioural lapse</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>A personal history part that includes exposure to the same intervention as the current intervention.</t>
+          <t xml:space="preserve">A personal history part that includes a change from a less desired behaviour pattern to a more desired behaviour pattern followed by a temporary reversion to the previous behaviour pattern. </t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -10138,11 +10090,7 @@
         </is>
       </c>
       <c r="J175" s="2" t="n"/>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>This is a fuzzy class.  Users will need to specify exactly how similar an intervention needs to be to qualify as "the same" as the current intervention in their context.</t>
-        </is>
-      </c>
+      <c r="K175" s="2" t="n"/>
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="2" t="n"/>
       <c r="N175" s="2" t="inlineStr">
@@ -10169,38 +10117,42 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050487</t>
+          <t>BCIO:050483</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">personal history of events that influence behaviour </t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A personal history part that includes experience of events that influence behaviour. </t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
           <t>personal history part</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>A process that is part of a personal history.</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
       <c r="E176" s="2" t="n"/>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>'process' and 'part of' some 'personal history'</t>
-        </is>
-      </c>
+      <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
-      <c r="I176" s="2" t="n"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="n"/>
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="2" t="n"/>
-      <c r="N176" s="2" t="n"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -10220,17 +10172,17 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050488</t>
+          <t>BCIO:050484</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>personal history part of intervention exposure</t>
+          <t>personal history of intervention exposure for the same outcome</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal history part  that includes exposure to one or more interventions. </t>
+          <t>A personal history part of exposure to an intervention targeting the same outcome as the current intervention.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -10275,32 +10227,28 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015159</t>
+          <t>BCIO:050485</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>personal psychological attribute</t>
+          <t>personal history of intervention exposure for the same outcome behaviour</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
+          <t>A personal history part  that includes exposure to a prior intervention targeting the same outcome behaviour as the current intervention.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="E178" s="2" t="n"/>
       <c r="F178" s="2" t="n"/>
       <c r="G178" s="2" t="n"/>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
-        </is>
-      </c>
+      <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
@@ -10334,42 +10282,46 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>BCIO:006081</t>
+          <t>BCIO:050486</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>personal role</t>
+          <t>personal history of same intervention exposure</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+          <t>A personal history part that includes exposure to the same intervention as the current intervention.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
-        </is>
-      </c>
+          <t>personal history part</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n"/>
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="n"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="n"/>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+          <t>This is a fuzzy class.  Users will need to specify exactly how similar an intervention needs to be to qualify as "the same" as the current intervention in their context.</t>
         </is>
       </c>
       <c r="L179" s="2" t="n"/>
       <c r="M179" s="2" t="n"/>
-      <c r="N179" s="2" t="n"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -10389,46 +10341,38 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015160</t>
+          <t>BCIO:050487</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>personal vulnerability</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>A disposition to undergo undesirable change in response to exposure to another entity.</t>
+          <t>A process that is part of a personal history.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E180" s="2" t="n"/>
-      <c r="F180" s="2" t="n"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>'process' and 'part of' some 'personal history'</t>
+        </is>
+      </c>
       <c r="G180" s="2" t="n"/>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>susceptibility to addiction, vulnerability to depression</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
-        </is>
-      </c>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
       <c r="J180" s="2" t="n"/>
       <c r="K180" s="2" t="n"/>
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="2" t="n"/>
-      <c r="N180" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
+      <c r="N180" s="2" t="n"/>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -10448,22 +10392,22 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050489</t>
+          <t>BCIO:050488</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>personal vulnerability to harmful behaviour</t>
+          <t>personal history part of intervention exposure</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>A personal vulnerability towards performing a behaviour that causes net harm.</t>
+          <t xml:space="preserve">A personal history part  that includes exposure to one or more interventions. </t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>personal vulnerability</t>
+          <t>personal history part</t>
         </is>
       </c>
       <c r="E181" s="2" t="n"/>
@@ -10475,11 +10419,7 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
-        <is>
-          <t>risk factor for harmful behaviour</t>
-        </is>
-      </c>
+      <c r="J181" s="2" t="n"/>
       <c r="K181" s="2" t="n"/>
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="2" t="n"/>
@@ -10507,31 +10447,35 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050490</t>
+          <t>BCIO:015159</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>place of residence</t>
+          <t>personal psychological attribute</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>A geographic location in which a person resides.</t>
+          <t>A personal attribute reflecting a person's mental dispositions, mental processes or capabilities.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>geographic location</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E182" s="2" t="n"/>
       <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
-      <c r="H182" s="2" t="n"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>low motivation to quit,  low self efficacy for physical activity, negative attitudes to healthy eating, contemplation stage of change, low numeracy</t>
+        </is>
+      </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="J182" s="2" t="n"/>
@@ -10540,7 +10484,7 @@
       <c r="M182" s="2" t="n"/>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O182" s="2" t="inlineStr">
@@ -10560,66 +10504,79 @@
       <c r="U182" s="2" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>OMRSE:00000094</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>policy holder role</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>An insured party role that inheres in a person who participates in the creation of the insurance contract and is eligible to receive benefits as specified by the insurance contract.</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>insured party role</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:006081</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
+      <c r="J183" s="2" t="n"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n"/>
+      <c r="M183" s="2" t="n"/>
+      <c r="N183" s="2" t="n"/>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="n"/>
+      <c r="Q183" s="2" t="n"/>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="n"/>
+      <c r="T183" s="2" t="n"/>
+      <c r="U183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050978</t>
+          <t>BCIO:015160</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>population statistic</t>
+          <t>personal vulnerability</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
+          <t>A disposition to undergo undesirable change in response to exposure to another entity.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="E184" s="2" t="n"/>
@@ -10627,17 +10584,28 @@
       <c r="G184" s="2" t="n"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Percentage of highly educated individuals in a population. 
-Mean age in a population.</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="n"/>
+          <t>susceptibility to addiction, vulnerability to depression</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
       <c r="J184" s="2" t="n"/>
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="n"/>
       <c r="M184" s="2" t="n"/>
-      <c r="N184" s="2" t="n"/>
-      <c r="O184" s="2" t="n"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
       <c r="P184" s="2" t="n"/>
       <c r="Q184" s="2" t="n"/>
       <c r="R184" s="2" t="inlineStr">
@@ -10652,22 +10620,22 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015084</t>
+          <t>BCIO:050489</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>preschool student role</t>
+          <t>personal vulnerability to harmful behaviour</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
+          <t>A personal vulnerability towards performing a behaviour that causes net harm.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>personal vulnerability</t>
         </is>
       </c>
       <c r="E185" s="2" t="n"/>
@@ -10676,16 +10644,20 @@
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n"/>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>risk factor for harmful behaviour</t>
+        </is>
+      </c>
       <c r="K185" s="2" t="n"/>
       <c r="L185" s="2" t="n"/>
       <c r="M185" s="2" t="n"/>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O185" s="2" t="inlineStr">
@@ -10707,22 +10679,22 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050890</t>
+          <t>BCIO:050490</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>protective factor for harmful behaviour</t>
+          <t>place of residence</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>A &lt;disposition&gt; that decreases the likelihood of engaging with harmful behaviour.</t>
+          <t>A geographic location in which a person resides.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>geographic location</t>
         </is>
       </c>
       <c r="E186" s="2" t="n"/>
@@ -10731,7 +10703,7 @@
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J186" s="2" t="n"/>
@@ -10740,7 +10712,7 @@
       <c r="M186" s="2" t="n"/>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O186" s="2" t="inlineStr">
@@ -10762,22 +10734,32 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BFO:0000019</t>
+          <t>OMRSE:00000094</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>policy holder role</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant that, in contrast to roles and dispositions, does not require any further process in order to be realized.</t>
+          <t>An insured party role that inheres in a person who participates in the creation of the insurance contract and is eligible to receive benefits as specified by the insurance contract.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>insured party role</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>roles</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -10794,17 +10776,17 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015040</t>
+          <t>BCIO:050978</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>quantity of valuable material resource owned</t>
+          <t>population statistic</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>A data item about the number of units of a valuable material resource possessed by a person.</t>
+          <t xml:space="preserve">A data item that is about the number or extent of something in a population. </t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -10817,33 +10799,18 @@
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>12 acres, a flock of 20 goats</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+          <t>Percentage of highly educated individuals in a population. 
+Mean age in a population.</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="n"/>
       <c r="J188" s="2" t="n"/>
       <c r="K188" s="2" t="n"/>
       <c r="L188" s="2" t="n"/>
       <c r="M188" s="2" t="n"/>
-      <c r="N188" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P188" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
+      <c r="N188" s="2" t="n"/>
+      <c r="O188" s="2" t="n"/>
+      <c r="P188" s="2" t="n"/>
       <c r="Q188" s="2" t="n"/>
       <c r="R188" s="2" t="inlineStr">
         <is>
@@ -10857,31 +10824,27 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015009</t>
+          <t>BCIO:015084</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>queer</t>
+          <t>preschool student role</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>A sexual orientation that is not exclusively homosexual or heterosexual, or of a person who does not identify with heterosexual, homosexual or bisexual labels.</t>
+          <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>sexual orientation</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E189" s="2" t="n"/>
       <c r="F189" s="2" t="n"/>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C155691</t>
-        </is>
-      </c>
+      <c r="G189" s="2" t="n"/>
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="inlineStr">
         <is>
@@ -10894,7 +10857,7 @@
       <c r="M189" s="2" t="n"/>
       <c r="N189" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O189" s="2" t="inlineStr">
@@ -10916,35 +10879,31 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015008</t>
+          <t>BCIO:050890</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>questioning sexual orientation</t>
+          <t>protective factor for harmful behaviour</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A self-identity as being in the process of exploring one's sexual orientation. </t>
+          <t>A &lt;disposition&gt; that decreases the likelihood of engaging with harmful behaviour.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>self-identity</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="E190" s="2" t="n"/>
       <c r="F190" s="2" t="n"/>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C155692</t>
-        </is>
-      </c>
+      <c r="G190" s="2" t="n"/>
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
       <c r="J190" s="2" t="n"/>
@@ -10953,7 +10912,7 @@
       <c r="M190" s="2" t="n"/>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O190" s="2" t="inlineStr">
@@ -10973,109 +10932,78 @@
       <c r="U190" s="2" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015071</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>relationship status</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>A personal attribute that is whether an individual is connected or associated with another through romantic attraction or marriage.</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="n"/>
-      <c r="F191" s="2" t="n"/>
-      <c r="G191" s="2" t="n"/>
-      <c r="H191" s="2" t="n"/>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="n"/>
-      <c r="K191" s="2" t="n"/>
-      <c r="L191" s="2" t="n"/>
-      <c r="M191" s="2" t="n"/>
-      <c r="N191" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O191" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P191" s="2" t="n"/>
-      <c r="Q191" s="2" t="n"/>
-      <c r="R191" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S191" s="2" t="n"/>
-      <c r="T191" s="2" t="n"/>
-      <c r="U191" s="2" t="n"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BFO:0000019</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>A specifically dependent continuant that, in contrast to roles and dispositions, does not require any further process in order to be realized.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015014</t>
+          <t>BCIO:015040</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>religious group membership</t>
+          <t>quantity of valuable material resource owned</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal attribute that is belonging to a group that is characterised by the practice of a common religion by the group members. </t>
+          <t>A data item about the number of units of a valuable material resource possessed by a person.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E192" s="2" t="n"/>
       <c r="F192" s="2" t="n"/>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C103282</t>
-        </is>
-      </c>
+      <c r="G192" s="2" t="n"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
+          <t>12 acres, a flock of 20 goats</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
       <c r="J192" s="2" t="n"/>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>presented in aggregated form as proportion/percentage belonging to a specified religious group</t>
-        </is>
-      </c>
+      <c r="K192" s="2" t="n"/>
       <c r="L192" s="2" t="n"/>
       <c r="M192" s="2" t="n"/>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>number</t>
         </is>
       </c>
       <c r="O192" s="2" t="inlineStr">
@@ -11083,7 +11011,11 @@
           <t>population</t>
         </is>
       </c>
-      <c r="P192" s="2" t="n"/>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>valuable material resource owned</t>
+        </is>
+      </c>
       <c r="Q192" s="2" t="n"/>
       <c r="R192" s="2" t="inlineStr">
         <is>
@@ -11097,31 +11029,35 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015032</t>
+          <t>BCIO:015009</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>rent-free occupier</t>
+          <t>queer</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>A person who lives in a residential facility they do not own without paying an agreed sum of money to the residential facility owner.</t>
+          <t>A sexual orientation that is not exclusively homosexual or heterosexual, or of a person who does not identify with heterosexual, homosexual or bisexual labels.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>sexual orientation</t>
         </is>
       </c>
       <c r="E193" s="2" t="n"/>
       <c r="F193" s="2" t="n"/>
-      <c r="G193" s="2" t="n"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C155691</t>
+        </is>
+      </c>
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J193" s="2" t="n"/>
@@ -11130,7 +11066,7 @@
       <c r="M193" s="2" t="n"/>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O193" s="2" t="inlineStr">
@@ -11152,35 +11088,35 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015034</t>
+          <t>BCIO:015008</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>rent-free occupier without owner's permission</t>
+          <t>questioning sexual orientation</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>A rent-free occupier who lives in the residential facility without the agreement of the residential facility owner.</t>
+          <t xml:space="preserve">A self-identity as being in the process of exploring one's sexual orientation. </t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>rent-free occupier</t>
+          <t>self-identity</t>
         </is>
       </c>
       <c r="E194" s="2" t="n"/>
       <c r="F194" s="2" t="n"/>
-      <c r="G194" s="2" t="n"/>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>squatters</t>
-        </is>
-      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C155692</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J194" s="2" t="n"/>
@@ -11189,7 +11125,7 @@
       <c r="M194" s="2" t="n"/>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O194" s="2" t="inlineStr">
@@ -11211,22 +11147,22 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015030</t>
+          <t>BCIO:015071</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>renter</t>
+          <t>relationship status</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>A person who lives in a residential facility they do not own in return for paying an agreed sum of money to the residential facility owner</t>
+          <t>A personal attribute that is whether an individual is connected or associated with another through romantic attraction or marriage.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E195" s="2" t="n"/>
@@ -11235,7 +11171,7 @@
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J195" s="2" t="n"/>
@@ -11244,7 +11180,7 @@
       <c r="M195" s="2" t="n"/>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O195" s="2" t="inlineStr">
@@ -11266,44 +11202,52 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015031</t>
+          <t>BCIO:015014</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>renter of housing from a social provider</t>
+          <t>religious group membership</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>A renter who lives in a residential facility where the residential facility owner decides who can live in the residential facility based on their perceived social or economic needs.</t>
+          <t xml:space="preserve">A personal attribute that is belonging to a group that is characterised by the practice of a common religion by the group members. </t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>renter</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E196" s="2" t="n"/>
       <c r="F196" s="2" t="n"/>
-      <c r="G196" s="2" t="n"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C103282</t>
+        </is>
+      </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
+          <t xml:space="preserve"> Religion Baptist 157 (37.0%) 163 (40.3%) Catholic 54 (12.7%) 60 (14.9%) Muslim 39 (9.2%) </t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">percentage; proportion </t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J196" s="2" t="n"/>
-      <c r="K196" s="2" t="n"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>presented in aggregated form as proportion/percentage belonging to a specified religious group</t>
+        </is>
+      </c>
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="2" t="n"/>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O196" s="2" t="inlineStr">
@@ -11325,22 +11269,22 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015028</t>
+          <t>BCIO:015032</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>residential facility owner</t>
+          <t>rent-free occupier</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>An owner of a residential facility.</t>
+          <t>A person who lives in a residential facility they do not own without paying an agreed sum of money to the residential facility owner.</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E197" s="2" t="n"/>
@@ -11349,7 +11293,7 @@
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
       <c r="J197" s="2" t="n"/>
@@ -11380,31 +11324,35 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015067</t>
+          <t>BCIO:015034</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>retired status</t>
+          <t>rent-free occupier without owner's permission</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person who previously bore a role realised in an employment process but has withdrawn from that employment process, having concluded their working or professional career.</t>
+          <t>A rent-free occupier who lives in the residential facility without the agreement of the residential facility owner.</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>rent-free occupier</t>
         </is>
       </c>
       <c r="E198" s="2" t="n"/>
       <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
-      <c r="H198" s="2" t="n"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>squatters</t>
+        </is>
+      </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t xml:space="preserve">percentage; proportion </t>
         </is>
       </c>
       <c r="J198" s="2" t="n"/>
@@ -11413,7 +11361,7 @@
       <c r="M198" s="2" t="n"/>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
@@ -11433,111 +11381,138 @@
       <c r="U198" s="2" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>BFO:0000023</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015030</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>renter</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>A person who lives in a residential facility they do not own in return for paying an agreed sum of money to the residential facility owner</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="2" t="n"/>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="n"/>
+      <c r="K199" s="2" t="n"/>
+      <c r="L199" s="2" t="n"/>
+      <c r="M199" s="2" t="n"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="n"/>
+      <c r="Q199" s="2" t="n"/>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="n"/>
+      <c r="T199" s="2" t="n"/>
+      <c r="U199" s="2" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:015085</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>school student role</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J200" s="3" t="n"/>
-      <c r="K200" s="3" t="n"/>
-      <c r="L200" s="3" t="n"/>
-      <c r="M200" s="3" t="n"/>
-      <c r="N200" s="3" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O200" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P200" s="3" t="n"/>
-      <c r="Q200" s="3" t="n"/>
-      <c r="R200" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S200" s="3" t="n"/>
-      <c r="T200" s="3" t="n"/>
-      <c r="U200" s="3" t="n"/>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015031</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>renter of housing from a social provider</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>A renter who lives in a residential facility where the residential facility owner decides who can live in the residential facility based on their perceived social or economic needs.</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>renter</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="n"/>
+      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>renters living in "public housing"[US], council housing [UK], housing association properties, non-profit organisation, alms house occupier</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percentage; proportion </t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="n"/>
+      <c r="K200" s="2" t="n"/>
+      <c r="L200" s="2" t="n"/>
+      <c r="M200" s="2" t="n"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="n"/>
+      <c r="Q200" s="2" t="n"/>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="n"/>
+      <c r="T200" s="2" t="n"/>
+      <c r="U200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:015028</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>school student role</t>
+          <t>residential facility owner</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
+          <t>An owner of a residential facility.</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="E201" s="2" t="n"/>
@@ -11555,7 +11530,7 @@
       <c r="M201" s="2" t="n"/>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O201" s="2" t="inlineStr">
@@ -11577,22 +11552,22 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015013</t>
+          <t>BCIO:015067</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>second generation immigrant</t>
+          <t>retired status</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>A person who has at least one parent who is an immigrant.</t>
+          <t>A personal attribute inhering in a person who previously bore a role realised in an employment process but has withdrawn from that employment process, having concluded their working or professional career.</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E202" s="2" t="n"/>
@@ -11610,7 +11585,7 @@
       <c r="M202" s="2" t="n"/>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>past behaviour</t>
         </is>
       </c>
       <c r="O202" s="2" t="inlineStr">
@@ -11630,128 +11605,116 @@
       <c r="U202" s="2" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015058</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>self employed status</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>An employment status realised by a person earning income directly from customers, clients, or other organisations rather than as a specified salary or wages from an employer.</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>employment status</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="n"/>
-      <c r="F203" s="2" t="n"/>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCIT_C116000 </t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J203" s="2" t="n"/>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>employment status where the person is their own employer</t>
-        </is>
-      </c>
-      <c r="L203" s="2" t="n"/>
-      <c r="M203" s="2" t="n"/>
-      <c r="N203" s="2" t="inlineStr">
-        <is>
-          <t>past behaviour</t>
-        </is>
-      </c>
-      <c r="O203" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P203" s="2" t="n"/>
-      <c r="Q203" s="2" t="n"/>
-      <c r="R203" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S203" s="2" t="n"/>
-      <c r="T203" s="2" t="n"/>
-      <c r="U203" s="2" t="n"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BFO:0000023</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>realizable entity</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>ADDICTO:0000399</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>An identity that a person has about themselves.</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015085</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>school student role</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n"/>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
+      <c r="L204" s="3" t="n"/>
+      <c r="M204" s="3" t="n"/>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O204" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P204" s="3" t="n"/>
+      <c r="Q204" s="3" t="n"/>
+      <c r="R204" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S204" s="3" t="n"/>
+      <c r="T204" s="3" t="n"/>
+      <c r="U204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015003</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>sexual orientation</t>
+          <t>school student role</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A personal attribute that is the pattern of a person's emotional, romantic and/or sexual attractions. </t>
+          <t xml:space="preserve">A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E205" s="2" t="n"/>
       <c r="F205" s="2" t="n"/>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C84361</t>
-        </is>
-      </c>
+      <c r="G205" s="2" t="n"/>
       <c r="H205" s="2" t="n"/>
       <c r="I205" s="2" t="inlineStr">
         <is>
@@ -11764,7 +11727,7 @@
       <c r="M205" s="2" t="n"/>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -11786,22 +11749,22 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015136</t>
+          <t>BCIO:015013</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>second generation immigrant</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>A family member with whom the subject shares a parent.</t>
+          <t>A person who has at least one parent who is an immigrant.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E206" s="2" t="n"/>
@@ -11819,8 +11782,7 @@
       <c r="M206" s="2" t="n"/>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O206" s="2" t="inlineStr">
@@ -11842,27 +11804,31 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015072</t>
+          <t>BCIO:015058</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>self employed status</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>A relationship status where the individual is not in a relationship with another person.</t>
+          <t>An employment status realised by a person earning income directly from customers, clients, or other organisations rather than as a specified salary or wages from an employer.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>relationship status</t>
+          <t>employment status</t>
         </is>
       </c>
       <c r="E207" s="2" t="n"/>
       <c r="F207" s="2" t="n"/>
-      <c r="G207" s="2" t="n"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCIT_C116000 </t>
+        </is>
+      </c>
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="inlineStr">
         <is>
@@ -11870,12 +11836,16 @@
         </is>
       </c>
       <c r="J207" s="2" t="n"/>
-      <c r="K207" s="2" t="n"/>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>employment status where the person is their own employer</t>
+        </is>
+      </c>
       <c r="L207" s="2" t="n"/>
       <c r="M207" s="2" t="n"/>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>past behaviour</t>
         </is>
       </c>
       <c r="O207" s="2" t="inlineStr">
@@ -11895,83 +11865,80 @@
       <c r="U207" s="2" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:050491</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>situational personal attribute</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>A personal attribute that holds within a given situation.</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="n"/>
-      <c r="F208" s="2" t="n"/>
-      <c r="G208" s="2" t="n"/>
-      <c r="H208" s="2" t="n"/>
-      <c r="I208" s="2" t="n"/>
-      <c r="J208" s="2" t="n"/>
-      <c r="K208" s="2" t="n"/>
-      <c r="L208" s="2" t="n"/>
-      <c r="M208" s="2" t="n"/>
-      <c r="N208" s="2" t="n"/>
-      <c r="O208" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P208" s="2" t="n"/>
-      <c r="Q208" s="2" t="n"/>
-      <c r="R208" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S208" s="2" t="n"/>
-      <c r="T208" s="2" t="n"/>
-      <c r="U208" s="2" t="n"/>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ADDICTO:0000399</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>An identity that a person has about themselves.</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050891</t>
+          <t>BCIO:015003</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>social group</t>
+          <t>sexual orientation</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>A social grouping that identifies as such and sometimes acts collectively.</t>
+          <t xml:space="preserve">A personal attribute that is the pattern of a person's emotional, romantic and/or sexual attractions. </t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>social grouping</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E209" s="2" t="n"/>
       <c r="F209" s="2" t="n"/>
-      <c r="G209" s="2" t="n"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C84361</t>
+        </is>
+      </c>
       <c r="H209" s="2" t="n"/>
-      <c r="I209" s="2" t="n"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J209" s="2" t="n"/>
       <c r="K209" s="2" t="n"/>
       <c r="L209" s="2" t="n"/>
       <c r="M209" s="2" t="n"/>
-      <c r="N209" s="2" t="n"/>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -11991,38 +11958,43 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050892</t>
+          <t>BCIO:015136</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>social grouping</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>A human population who share some common attribute that involves some form of social interaction.</t>
+          <t>A family member with whom the subject shares a parent.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>human population</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E210" s="2" t="n"/>
       <c r="F210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
-      <c r="I210" s="2" t="n"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="n"/>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>Population can be two or more people. the interaction may involve how other people treat members of the group.</t>
-        </is>
-      </c>
+      <c r="K210" s="2" t="n"/>
       <c r="L210" s="2" t="n"/>
       <c r="M210" s="2" t="n"/>
-      <c r="N210" s="2" t="n"/>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+roles</t>
+        </is>
+      </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -12042,34 +12014,42 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>BCIO:006082</t>
+          <t>BCIO:015072</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>social role</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>A personal role that is realised in human social processes.</t>
+          <t>A relationship status where the individual is not in a relationship with another person.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>personal role</t>
+          <t>relationship status</t>
         </is>
       </c>
       <c r="E211" s="2" t="n"/>
       <c r="F211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
-      <c r="I211" s="2" t="n"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
       <c r="J211" s="2" t="n"/>
       <c r="K211" s="2" t="n"/>
       <c r="L211" s="2" t="n"/>
       <c r="M211" s="2" t="n"/>
-      <c r="N211" s="2" t="n"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -12089,17 +12069,17 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050893</t>
+          <t>BCIO:050491</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>socio-demographic characteristic</t>
+          <t>situational personal attribute</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>A &lt;personal attribute&gt; that, together with other attributes, characterises a person’s position in society.</t>
+          <t>A personal attribute that holds within a given situation.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -12113,11 +12093,7 @@
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="2" t="n"/>
       <c r="J212" s="2" t="n"/>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>This can include social history, current circumstances, age, gender identity, occupation, education level, socio-economic position (status or group), ethnicity, sexual orientation, disability</t>
-        </is>
-      </c>
+      <c r="K212" s="2" t="n"/>
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
       <c r="N212" s="2" t="n"/>
@@ -12140,46 +12116,34 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>BCIO:051022</t>
+          <t>BCIO:050891</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>socioeconomic position</t>
+          <t>social group</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute reflecting a person's economic and social position in relation to others</t>
+          <t>A social grouping that identifies as such and sometimes acts collectively.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>social grouping</t>
         </is>
       </c>
       <c r="E213" s="2" t="n"/>
       <c r="F213" s="2" t="n"/>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>OPMI:0000121</t>
-        </is>
-      </c>
+      <c r="G213" s="2" t="n"/>
       <c r="H213" s="2" t="n"/>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I213" s="2" t="n"/>
       <c r="J213" s="2" t="n"/>
       <c r="K213" s="2" t="n"/>
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="2" t="n"/>
-      <c r="N213" s="2" t="inlineStr">
-        <is>
-          <t>attributes</t>
-        </is>
-      </c>
+      <c r="N213" s="2" t="n"/>
       <c r="O213" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -12199,52 +12163,44 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015069</t>
+          <t>BCIO:050892</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>socioeconomic position score</t>
+          <t>social grouping</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic position, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
+          <t>A human population who share some common attribute that involves some form of social interaction.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>human population</t>
         </is>
       </c>
       <c r="E214" s="2" t="n"/>
       <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="inlineStr">
-        <is>
-          <t>Mean;Minimum;Maximum;Median</t>
-        </is>
-      </c>
+      <c r="I214" s="2" t="n"/>
       <c r="J214" s="2" t="n"/>
-      <c r="K214" s="2" t="n"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Population can be two or more people. the interaction may involve how other people treat members of the group.</t>
+        </is>
+      </c>
       <c r="L214" s="2" t="n"/>
       <c r="M214" s="2" t="n"/>
-      <c r="N214" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
+      <c r="N214" s="2" t="n"/>
       <c r="O214" s="2" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="P214" s="2" t="inlineStr">
-        <is>
-          <t>socioeconomic status</t>
-        </is>
-      </c>
+      <c r="P214" s="2" t="n"/>
       <c r="Q214" s="2" t="n"/>
       <c r="R214" s="2" t="inlineStr">
         <is>
@@ -12256,82 +12212,66 @@
       <c r="U214" s="2" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:015068</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>socioeconomic status category</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A  data item about a category assigned to a person based on an assessment of a score calculated from various measures of their income, education, occupation, family size or household. </t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="n"/>
-      <c r="F215" s="3" t="n"/>
-      <c r="G215" s="3" t="n"/>
-      <c r="H215" s="3" t="inlineStr">
-        <is>
-          <t>Semi-routine and routine occupations, blue collar occupations</t>
-        </is>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J215" s="3" t="n"/>
-      <c r="K215" s="3" t="n"/>
-      <c r="L215" s="3" t="n"/>
-      <c r="M215" s="3" t="n"/>
-      <c r="N215" s="3" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O215" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P215" s="3" t="inlineStr">
-        <is>
-          <t>socioeconomic status</t>
-        </is>
-      </c>
-      <c r="Q215" s="3" t="n"/>
-      <c r="R215" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S215" s="3" t="n"/>
-      <c r="T215" s="3" t="n"/>
-      <c r="U215" s="3" t="n"/>
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:006082</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>social role</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>A personal role that is realised in human social processes.</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n"/>
+      <c r="F215" s="2" t="n"/>
+      <c r="G215" s="2" t="n"/>
+      <c r="H215" s="2" t="n"/>
+      <c r="I215" s="2" t="n"/>
+      <c r="J215" s="2" t="n"/>
+      <c r="K215" s="2" t="n"/>
+      <c r="L215" s="2" t="n"/>
+      <c r="M215" s="2" t="n"/>
+      <c r="N215" s="2" t="n"/>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="n"/>
+      <c r="Q215" s="2" t="n"/>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="n"/>
+      <c r="T215" s="2" t="n"/>
+      <c r="U215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015063</t>
+          <t>BCIO:050893</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>stay at home parent or guardian status</t>
+          <t>socio-demographic characteristic</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being a homemaker whose work includes caring for children.</t>
+          <t>A &lt;personal attribute&gt; that, together with other attributes, characterises a person’s position in society.</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -12341,26 +12281,18 @@
       </c>
       <c r="E216" s="2" t="n"/>
       <c r="F216" s="2" t="n"/>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>NCIT_C148253</t>
-        </is>
-      </c>
+      <c r="G216" s="2" t="n"/>
       <c r="H216" s="2" t="n"/>
-      <c r="I216" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="I216" s="2" t="n"/>
       <c r="J216" s="2" t="n"/>
-      <c r="K216" s="2" t="n"/>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>This can include social history, current circumstances, age, gender identity, occupation, education level, socio-economic position (status or group), ethnicity, sexual orientation, disability</t>
+        </is>
+      </c>
       <c r="L216" s="2" t="n"/>
       <c r="M216" s="2" t="n"/>
-      <c r="N216" s="2" t="inlineStr">
-        <is>
-          <t>past behaviour</t>
-        </is>
-      </c>
+      <c r="N216" s="2" t="n"/>
       <c r="O216" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -12380,29 +12312,29 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015117</t>
+          <t>BCIO:051022</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>step-parent</t>
+          <t>socioeconomic position</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>A parent in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
+          <t>A personal attribute reflecting a person's economic and social position in relation to others</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E217" s="2" t="n"/>
       <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>NCIT:C166116</t>
+          <t>OPMI:0000121</t>
         </is>
       </c>
       <c r="H217" s="2" t="n"/>
@@ -12417,7 +12349,7 @@
       <c r="M217" s="2" t="n"/>
       <c r="N217" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O217" s="2" t="inlineStr">
@@ -12439,22 +12371,22 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015143</t>
+          <t>BCIO:015069</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>step-sibling</t>
+          <t>socioeconomic position score</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>A sibling who is the child of one's step-parent.</t>
+          <t xml:space="preserve">A data item about a score on a measure of a person's socioeconomic position, calculated by combining information about the number of years of education completed, their individual or household income, their current occupation or the industry in which they work or family size or household. </t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E218" s="2" t="n"/>
@@ -12463,7 +12395,7 @@
       <c r="H218" s="2" t="n"/>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>percentage; proportion</t>
+          <t>Mean;Minimum;Maximum;Median</t>
         </is>
       </c>
       <c r="J218" s="2" t="n"/>
@@ -12472,7 +12404,7 @@
       <c r="M218" s="2" t="n"/>
       <c r="N218" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>value</t>
         </is>
       </c>
       <c r="O218" s="2" t="inlineStr">
@@ -12480,7 +12412,11 @@
           <t>population</t>
         </is>
       </c>
-      <c r="P218" s="2" t="n"/>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>socioeconomic status</t>
+        </is>
+      </c>
       <c r="Q218" s="2" t="n"/>
       <c r="R218" s="2" t="inlineStr">
         <is>
@@ -12492,84 +12428,96 @@
       <c r="U218" s="2" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015145</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>stepbrother</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>A step-sibling who is male gender.</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>step-sibling</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="n"/>
-      <c r="F219" s="2" t="n"/>
-      <c r="G219" s="2" t="n"/>
-      <c r="H219" s="2" t="n"/>
-      <c r="I219" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J219" s="2" t="n"/>
-      <c r="K219" s="2" t="n"/>
-      <c r="L219" s="2" t="n"/>
-      <c r="M219" s="2" t="n"/>
-      <c r="N219" s="2" t="inlineStr">
-        <is>
-          <t>people</t>
-        </is>
-      </c>
-      <c r="O219" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P219" s="2" t="n"/>
-      <c r="Q219" s="2" t="n"/>
-      <c r="R219" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S219" s="2" t="n"/>
-      <c r="T219" s="2" t="n"/>
-      <c r="U219" s="2" t="n"/>
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015068</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>socioeconomic status category</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A  data item about a category assigned to a person based on an assessment of a score calculated from various measures of their income, education, occupation, family size or household. </t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="n"/>
+      <c r="F219" s="3" t="n"/>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>Semi-routine and routine occupations, blue collar occupations</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="n"/>
+      <c r="L219" s="3" t="n"/>
+      <c r="M219" s="3" t="n"/>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O219" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P219" s="3" t="inlineStr">
+        <is>
+          <t>socioeconomic status</t>
+        </is>
+      </c>
+      <c r="Q219" s="3" t="n"/>
+      <c r="R219" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S219" s="3" t="n"/>
+      <c r="T219" s="3" t="n"/>
+      <c r="U219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015130</t>
+          <t>BCIO:015063</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>stepchild</t>
+          <t>stay at home parent or guardian status</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>A child relation in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
+          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to being a homemaker whose work includes caring for children.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>child relation</t>
+          <t>personal attribute</t>
         </is>
       </c>
       <c r="E220" s="2" t="n"/>
       <c r="F220" s="2" t="n"/>
-      <c r="G220" s="2" t="n"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>NCIT_C148253</t>
+        </is>
+      </c>
       <c r="H220" s="2" t="n"/>
       <c r="I220" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12530,7 @@
       <c r="M220" s="2" t="n"/>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>past behaviour</t>
         </is>
       </c>
       <c r="O220" s="2" t="inlineStr">
@@ -12604,27 +12552,31 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015131</t>
+          <t>BCIO:015117</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>stepdaughter</t>
+          <t>step-parent</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>A stepchild who is female gender.</t>
+          <t>A parent in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>stepchild</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="E221" s="2" t="n"/>
       <c r="F221" s="2" t="n"/>
-      <c r="G221" s="2" t="n"/>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>NCIT:C166116</t>
+        </is>
+      </c>
       <c r="H221" s="2" t="n"/>
       <c r="I221" s="2" t="inlineStr">
         <is>
@@ -12659,22 +12611,22 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015119</t>
+          <t>BCIO:015143</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>stepfather</t>
+          <t>step-sibling</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>A step-parent who is male gender.</t>
+          <t>A sibling who is the child of one's step-parent.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>step-parent</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="E222" s="2" t="n"/>
@@ -12714,22 +12666,22 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015118</t>
+          <t>BCIO:015145</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>stepmother</t>
+          <t>stepbrother</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>A step-parent who is female gender.</t>
+          <t>A step-sibling who is male gender.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>step-parent</t>
+          <t>step-sibling</t>
         </is>
       </c>
       <c r="E223" s="2" t="n"/>
@@ -12769,22 +12721,22 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015144</t>
+          <t>BCIO:015130</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>stepsister</t>
+          <t>stepchild</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>A step-sibling who is female gender.</t>
+          <t>A child relation in a parent-child relationship established by the parent's subsequent marriage to one of the child's original biological or legal parents.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>step-sibling</t>
+          <t>child relation</t>
         </is>
       </c>
       <c r="E224" s="2" t="n"/>
@@ -12824,17 +12776,17 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015132</t>
+          <t>BCIO:015131</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>stepson</t>
+          <t>stepdaughter</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>A stepchild who is male gender.</t>
+          <t>A stepchild who is female gender.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -12879,22 +12831,22 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:015119</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>stepfather</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A step-parent who is male gender.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>step-parent</t>
         </is>
       </c>
       <c r="E226" s="2" t="n"/>
@@ -12912,7 +12864,7 @@
       <c r="M226" s="2" t="n"/>
       <c r="N226" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O226" s="2" t="inlineStr">
@@ -12932,66 +12884,79 @@
       <c r="U226" s="2" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>ADDICTO:0001050</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>teenager</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>A person between 13 and 19 years of age.</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015118</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>stepmother</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>A step-parent who is female gender.</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>step-parent</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n"/>
+      <c r="F227" s="2" t="n"/>
+      <c r="G227" s="2" t="n"/>
+      <c r="H227" s="2" t="n"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="n"/>
+      <c r="K227" s="2" t="n"/>
+      <c r="L227" s="2" t="n"/>
+      <c r="M227" s="2" t="n"/>
+      <c r="N227" s="2" t="inlineStr">
         <is>
           <t>people</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="n"/>
+      <c r="Q227" s="2" t="n"/>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="n"/>
+      <c r="T227" s="2" t="n"/>
+      <c r="U227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:015144</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>trainee role</t>
+          <t>stepsister</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A step-sibling who is female gender.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>step-sibling</t>
         </is>
       </c>
       <c r="E228" s="2" t="n"/>
@@ -13009,7 +12974,7 @@
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O228" s="2" t="inlineStr">
@@ -13031,31 +12996,27 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015103</t>
+          <t>BCIO:015132</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>transgender</t>
+          <t>stepson</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>A gender identity that differs from the person's assigned sex at birth.</t>
+          <t>A stepchild who is male gender.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>stepchild</t>
         </is>
       </c>
       <c r="E229" s="2" t="n"/>
       <c r="F229" s="2" t="n"/>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>GSSO:000096</t>
-        </is>
-      </c>
+      <c r="G229" s="2" t="n"/>
       <c r="H229" s="2" t="n"/>
       <c r="I229" s="2" t="inlineStr">
         <is>
@@ -13068,7 +13029,7 @@
       <c r="M229" s="2" t="n"/>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O229" s="2" t="inlineStr">
@@ -13090,22 +13051,22 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015149</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>twin</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>role</t>
         </is>
       </c>
       <c r="E230" s="2" t="n"/>
@@ -13123,7 +13084,7 @@
       <c r="M230" s="2" t="n"/>
       <c r="N230" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O230" s="2" t="inlineStr">
@@ -13143,79 +13104,66 @@
       <c r="U230" s="2" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:050492</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>unawareness of a behaviour</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>situational personal attribute</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="n"/>
-      <c r="F231" s="2" t="n"/>
-      <c r="G231" s="2" t="n"/>
-      <c r="H231" s="2" t="n"/>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J231" s="2" t="n"/>
-      <c r="K231" s="2" t="n"/>
-      <c r="L231" s="2" t="n"/>
-      <c r="M231" s="2" t="n"/>
-      <c r="N231" s="2" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O231" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P231" s="2" t="n"/>
-      <c r="Q231" s="2" t="n"/>
-      <c r="R231" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S231" s="2" t="n"/>
-      <c r="T231" s="2" t="n"/>
-      <c r="U231" s="2" t="n"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ADDICTO:0001050</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>teenager</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>A person between 13 and 19 years of age.</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015154</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>uncle</t>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>A family member who is the brother of one's parent.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E232" s="2" t="n"/>
@@ -13233,7 +13181,7 @@
       <c r="M232" s="2" t="n"/>
       <c r="N232" s="2" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O232" s="2" t="inlineStr">
@@ -13255,27 +13203,31 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050493</t>
+          <t>BCIO:015103</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>undecidedness about enacting a behaviour</t>
+          <t>transgender</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
+          <t>A gender identity that differs from the person's assigned sex at birth.</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>situational personal attribute</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E233" s="2" t="n"/>
       <c r="F233" s="2" t="n"/>
-      <c r="G233" s="2" t="n"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>GSSO:000096</t>
+        </is>
+      </c>
       <c r="H233" s="2" t="n"/>
       <c r="I233" s="2" t="inlineStr">
         <is>
@@ -13288,7 +13240,7 @@
       <c r="M233" s="2" t="n"/>
       <c r="N233" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>attributes</t>
         </is>
       </c>
       <c r="O233" s="2" t="inlineStr">
@@ -13308,79 +13260,79 @@
       <c r="U233" s="2" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:015088</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="C234" s="3" t="inlineStr">
-        <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="n"/>
-      <c r="F234" s="3" t="n"/>
-      <c r="G234" s="3" t="n"/>
-      <c r="H234" s="3" t="n"/>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J234" s="3" t="n"/>
-      <c r="K234" s="3" t="n"/>
-      <c r="L234" s="3" t="n"/>
-      <c r="M234" s="3" t="n"/>
-      <c r="N234" s="3" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O234" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P234" s="3" t="n"/>
-      <c r="Q234" s="3" t="n"/>
-      <c r="R234" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S234" s="3" t="n"/>
-      <c r="T234" s="3" t="n"/>
-      <c r="U234" s="3" t="n"/>
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015149</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>twin</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One of two siblings who resulted from the same pregnancy. </t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n"/>
+      <c r="F234" s="2" t="n"/>
+      <c r="G234" s="2" t="n"/>
+      <c r="H234" s="2" t="n"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="n"/>
+      <c r="K234" s="2" t="n"/>
+      <c r="L234" s="2" t="n"/>
+      <c r="M234" s="2" t="n"/>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="n"/>
+      <c r="Q234" s="2" t="n"/>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="n"/>
+      <c r="T234" s="2" t="n"/>
+      <c r="U234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:050492</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>undergraduate student role</t>
+          <t>unawareness of a behaviour</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A situational personal attribute in which a person has not thought about enacting a behaviour.</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>situational personal attribute</t>
         </is>
       </c>
       <c r="E235" s="2" t="n"/>
@@ -13420,31 +13372,27 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050977</t>
+          <t>BCIO:015154</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>uncle</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
+          <t>A family member who is the brother of one's parent.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>employment status</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E236" s="2" t="n"/>
       <c r="F236" s="2" t="n"/>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SDGIO_00010026 </t>
-        </is>
-      </c>
+      <c r="G236" s="2" t="n"/>
       <c r="H236" s="2" t="n"/>
       <c r="I236" s="2" t="inlineStr">
         <is>
@@ -13457,7 +13405,7 @@
       <c r="M236" s="2" t="n"/>
       <c r="N236" s="2" t="inlineStr">
         <is>
-          <t>attributes</t>
+          <t>people</t>
         </is>
       </c>
       <c r="O236" s="2" t="inlineStr">
@@ -13479,22 +13427,22 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015064</t>
+          <t>BCIO:050493</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>unpaid carer for an adult status</t>
+          <t>undecidedness about enacting a behaviour</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+          <t>A situational personal attribute in which the person has thought about a behaviour but not formed an intention regarding whether to enact it.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>situational personal attribute</t>
         </is>
       </c>
       <c r="E237" s="2" t="n"/>
@@ -13512,7 +13460,7 @@
       <c r="M237" s="2" t="n"/>
       <c r="N237" s="2" t="inlineStr">
         <is>
-          <t>past behaviour</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O237" s="2" t="inlineStr">
@@ -13532,92 +13480,88 @@
       <c r="U237" s="2" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:015039</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>An object aggregate under the control of some person or organisation which confers an economic benefit to that person or organisation in an economic system.</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="n"/>
-      <c r="F238" s="2" t="n"/>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>SDGIO:00010048</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="inlineStr">
-        <is>
-          <t>farmland, jewellery, livestock</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="n"/>
-      <c r="J238" s="2" t="n"/>
-      <c r="K238" s="2" t="n"/>
-      <c r="L238" s="2" t="n"/>
-      <c r="M238" s="2" t="n"/>
-      <c r="N238" s="2" t="n"/>
-      <c r="O238" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P238" s="2" t="n"/>
-      <c r="Q238" s="2" t="n"/>
-      <c r="R238" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="S238" s="2" t="n"/>
-      <c r="T238" s="2" t="n"/>
-      <c r="U238" s="2" t="n"/>
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015088</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="n"/>
+      <c r="F238" s="3" t="n"/>
+      <c r="G238" s="3" t="n"/>
+      <c r="H238" s="3" t="n"/>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="n"/>
+      <c r="K238" s="3" t="n"/>
+      <c r="L238" s="3" t="n"/>
+      <c r="M238" s="3" t="n"/>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O238" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P238" s="3" t="n"/>
+      <c r="Q238" s="3" t="n"/>
+      <c r="R238" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S238" s="3" t="n"/>
+      <c r="T238" s="3" t="n"/>
+      <c r="U238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015041</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>value of valuable material resource owned</t>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>A data item about the monetary value of a valuable material resource possessed by a person.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E239" s="2" t="n"/>
       <c r="F239" s="2" t="n"/>
       <c r="G239" s="2" t="n"/>
-      <c r="H239" s="2" t="inlineStr">
-        <is>
-          <t>$400, 3000 euros</t>
-        </is>
-      </c>
+      <c r="H239" s="2" t="n"/>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Mean;Minimum;Maximum;Median</t>
+          <t>percentage; proportion</t>
         </is>
       </c>
       <c r="J239" s="2" t="n"/>
@@ -13626,7 +13570,7 @@
       <c r="M239" s="2" t="n"/>
       <c r="N239" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>roles</t>
         </is>
       </c>
       <c r="O239" s="2" t="inlineStr">
@@ -13634,11 +13578,7 @@
           <t>population</t>
         </is>
       </c>
-      <c r="P239" s="2" t="inlineStr">
-        <is>
-          <t>valuable material resource owned</t>
-        </is>
-      </c>
+      <c r="P239" s="2" t="n"/>
       <c r="Q239" s="2" t="n"/>
       <c r="R239" s="2" t="inlineStr">
         <is>
@@ -13650,74 +13590,78 @@
       <c r="U239" s="2" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:015086</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee role</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>A student or trainee role realised by currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="n"/>
-      <c r="F240" s="3" t="n"/>
-      <c r="G240" s="3" t="n"/>
-      <c r="H240" s="3" t="n"/>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
-      <c r="J240" s="3" t="n"/>
-      <c r="K240" s="3" t="n"/>
-      <c r="L240" s="3" t="n"/>
-      <c r="M240" s="3" t="n"/>
-      <c r="N240" s="3" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="O240" s="3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="P240" s="3" t="n"/>
-      <c r="Q240" s="3" t="n"/>
-      <c r="R240" s="3" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="S240" s="3" t="n"/>
-      <c r="T240" s="3" t="n"/>
-      <c r="U240" s="3" t="n"/>
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050977</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>unemployed</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>An employment status in which the person is not employed or self-employed, is looking for work and able to start in paid employment.</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>employment status</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n"/>
+      <c r="F240" s="2" t="n"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDGIO_00010026 </t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="n"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="n"/>
+      <c r="K240" s="2" t="n"/>
+      <c r="L240" s="2" t="n"/>
+      <c r="M240" s="2" t="n"/>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="n"/>
+      <c r="Q240" s="2" t="n"/>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="n"/>
+      <c r="T240" s="2" t="n"/>
+      <c r="U240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015060</t>
+          <t>BCIO:015064</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>voluntary worker status</t>
+          <t>unpaid carer for an adult status</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>A personal attribute inhering in a person by virtue of that person working or assisting at a workplace without receiving remuneration.</t>
+          <t>A personal attribute inhering in a person by virtue of that person not bearing a role realised in an employment process, due to their primary occupation being caring, without receiving a wage for it, for an adult friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -13735,11 +13679,7 @@
         </is>
       </c>
       <c r="J241" s="2" t="n"/>
-      <c r="K241" s="2" t="inlineStr">
-        <is>
-          <t>may include unpaid internships</t>
-        </is>
-      </c>
+      <c r="K241" s="2" t="n"/>
       <c r="L241" s="2" t="n"/>
       <c r="M241" s="2" t="n"/>
       <c r="N241" s="2" t="inlineStr">
@@ -13766,42 +13706,42 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015076</t>
+          <t>BCIO:015039</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>valuable material resource owned</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A relationship status where the individual is no longer in a legally formalised marriage or civil partnership due to the death of their spouse or partner. </t>
+          <t>An object aggregate under the control of some person or organisation which confers an economic benefit to that person or organisation in an economic system.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>relationship status</t>
+          <t>object aggregate</t>
         </is>
       </c>
       <c r="E242" s="2" t="n"/>
       <c r="F242" s="2" t="n"/>
-      <c r="G242" s="2" t="n"/>
-      <c r="H242" s="2" t="n"/>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>percentage; proportion</t>
-        </is>
-      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>SDGIO:00010048</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>farmland, jewellery, livestock</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="n"/>
       <c r="J242" s="2" t="n"/>
       <c r="K242" s="2" t="n"/>
       <c r="L242" s="2" t="n"/>
       <c r="M242" s="2" t="n"/>
-      <c r="N242" s="2" t="inlineStr">
-        <is>
-          <t>attributes</t>
-        </is>
-      </c>
+      <c r="N242" s="2" t="n"/>
       <c r="O242" s="2" t="inlineStr">
         <is>
           <t>population</t>
@@ -13817,6 +13757,238 @@
       <c r="S242" s="2" t="n"/>
       <c r="T242" s="2" t="n"/>
       <c r="U242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015041</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>value of valuable material resource owned</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>A data item about the monetary value of a valuable material resource possessed by a person.</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n"/>
+      <c r="F243" s="2" t="n"/>
+      <c r="G243" s="2" t="n"/>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>$400, 3000 euros</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Mean;Minimum;Maximum;Median</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="n"/>
+      <c r="K243" s="2" t="n"/>
+      <c r="L243" s="2" t="n"/>
+      <c r="M243" s="2" t="n"/>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>valuable material resource owned</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="n"/>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S243" s="2" t="n"/>
+      <c r="T243" s="2" t="n"/>
+      <c r="U243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:015086</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>vocational training student or trainee role</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>A student or trainee role realised by currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="n"/>
+      <c r="F244" s="3" t="n"/>
+      <c r="G244" s="3" t="n"/>
+      <c r="H244" s="3" t="n"/>
+      <c r="I244" s="3" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="n"/>
+      <c r="K244" s="3" t="n"/>
+      <c r="L244" s="3" t="n"/>
+      <c r="M244" s="3" t="n"/>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="O244" s="3" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P244" s="3" t="n"/>
+      <c r="Q244" s="3" t="n"/>
+      <c r="R244" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="S244" s="3" t="n"/>
+      <c r="T244" s="3" t="n"/>
+      <c r="U244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015060</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>voluntary worker status</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>A personal attribute inhering in a person by virtue of that person working or assisting at a workplace without receiving remuneration.</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n"/>
+      <c r="F245" s="2" t="n"/>
+      <c r="G245" s="2" t="n"/>
+      <c r="H245" s="2" t="n"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="n"/>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>may include unpaid internships</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="n"/>
+      <c r="M245" s="2" t="n"/>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>past behaviour</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="n"/>
+      <c r="Q245" s="2" t="n"/>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="n"/>
+      <c r="T245" s="2" t="n"/>
+      <c r="U245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:015076</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>widowed</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A relationship status where the individual is no longer in a legally formalised marriage or civil partnership due to the death of their spouse or partner. </t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>relationship status</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n"/>
+      <c r="F246" s="2" t="n"/>
+      <c r="G246" s="2" t="n"/>
+      <c r="H246" s="2" t="n"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>percentage; proportion</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="n"/>
+      <c r="K246" s="2" t="n"/>
+      <c r="L246" s="2" t="n"/>
+      <c r="M246" s="2" t="n"/>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="n"/>
+      <c r="Q246" s="2" t="n"/>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="n"/>
+      <c r="T246" s="2" t="n"/>
+      <c r="U246" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Population/BCIO_Population.xlsx
+++ b/Population/BCIO_Population.xlsx
@@ -2954,12 +2954,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
+          <t>A personal role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="E45" s="2" t="n"/>
@@ -3803,35 +3803,21 @@
           <t>planned process</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>education process in the Sustainable Development Goals Interface Ontology (SDGIO:00010001)</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5164,7 +5150,6 @@
           <t>monetary human income data item</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
@@ -6896,7 +6881,7 @@
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="inlineStr"/>
+      <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
@@ -7075,7 +7060,7 @@
           <t>Mean;Minimum;Maximum;Median; percentage; proportion</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="n"/>
       <c r="K119" s="3" t="n"/>
       <c r="L119" s="3" t="n"/>
       <c r="M119" s="3" t="n"/>
@@ -13114,12 +13099,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="E231" s="2" t="n"/>
